--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C509B55E-F6EF-4D7F-9464-C9CFB55126F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFBED51-A7C9-4ED5-A06E-97C6073FBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -631,46 +631,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>①：概要
-本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録することで、AIが被害状況を分析し、今後必要となる対応を案内するWebシステムである。分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報をまとめて確認できる。また、登録した写真や分析結果を履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
-②：実現可能な機能
-・被害状況写真の撮影・登録
-・AIによる被害状況分析
-・修理費用の目安提示
-・修理業者の情報提示
-・罹災証明書の申請案内
-・被災後の対応案内
-・被害状況分析履歴
-③：システム規模
-・個人(事業者・建物管理者を含む)での利用を想定している
-・災害発生直後にはアクセスが集中すると想定される
-④：システムとの関係
-提案先：建物調査を実施している企業、修理業者
-利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
-    <rPh sb="2" eb="4">
-      <t>ガイヨウ</t>
-    </rPh>
-    <rPh sb="194" eb="196">
-      <t>ジツゲン</t>
-    </rPh>
-    <rPh sb="196" eb="198">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="199" eb="201">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="290" eb="292">
-      <t>キボ</t>
-    </rPh>
-    <rPh sb="307" eb="308">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="356" eb="358">
-      <t>カンケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Amazon Linux 2023</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1460,62 +1420,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>LINE Loginを利用し、本人確認を行った利用者のみシステムを利用できるようにする</t>
-    <rPh sb="11" eb="13">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>認可</t>
     <rPh sb="0" eb="2">
       <t>ニンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>利用者自身の被害情報・写真・分析結果のみ参照・編集できるようにする</t>
-    <rPh sb="0" eb="3">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シャシン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1925,6 +1832,133 @@
   </si>
   <si>
     <t>ウチミテ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①：概要
+本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録すると、AIが被害状況を分析し、その目安を提示することで、被害状況の把握や専門家への相談を支援するWebシステムである。
+また、分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報を提示する。登録した写真や分析結果は履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
+②：実現可能な機能
+必須機能
+・被害情報の登録(建物情報・質問回答)
+・被害写真の撮影・登録
+・AIによる被害状況分析
+・LINEログイン
+・被害状況分析履歴
+追加機能
+・修理費用の目安提示
+・修理業者の情報提示
+・罹災証明書の申請案内
+③：システム規模
+・個人(事業者・建物管理者を含む)での利用を想定している
+・災害発生直後にはアクセスが集中すると想定される
+④：システムとの関係
+提案先：建物調査を実施している企業、修理業者
+利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
+    <rPh sb="2" eb="4">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="212" eb="214">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="215" eb="217">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="217" eb="219">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="221" eb="223">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="223" eb="225">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="226" eb="228">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="229" eb="231">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="234" eb="236">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="236" eb="238">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="285" eb="287">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="287" eb="289">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="331" eb="333">
+      <t>キボ</t>
+    </rPh>
+    <rPh sb="348" eb="349">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="397" eb="399">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINE Loginを利用し、ログインを希望する利用者の認証を行う</t>
+    <rPh sb="11" eb="13">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キボウ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン利用者は自身の被害情報・写真・分析結果のみ参照・編集できるようにする</t>
+    <rPh sb="4" eb="7">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンシュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2999,6 +3033,510 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3009,511 +3547,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -4403,1592 +4437,1601 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="126">
+      <c r="A2" s="34">
         <v>1</v>
       </c>
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="176" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
-      <c r="I2" s="176"/>
-      <c r="J2" s="177"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="127"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="179"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="126">
+      <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="141" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="142"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="128"/>
-      <c r="B5" s="144" t="s">
+      <c r="A5" s="35"/>
+      <c r="B5" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="145"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="128"/>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="144"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="145"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="128"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="147"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="128"/>
-      <c r="B8" s="150" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="152"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="128"/>
-      <c r="B9" s="153"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="155"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="73"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="128"/>
-      <c r="B10" s="153"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="155"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="73"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="128"/>
-      <c r="B11" s="153"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="155"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="73"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="128"/>
-      <c r="B12" s="153"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="154"/>
-      <c r="E12" s="154"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="154"/>
-      <c r="H12" s="154"/>
-      <c r="I12" s="154"/>
-      <c r="J12" s="155"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="73"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="128"/>
-      <c r="B13" s="153"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="154"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="154"/>
-      <c r="H13" s="154"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="155"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="128"/>
-      <c r="B14" s="153"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="154"/>
-      <c r="I14" s="154"/>
-      <c r="J14" s="155"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="128"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="155"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="73"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="128"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="155"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="127"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="154"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="155"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="127"/>
-      <c r="B18" s="153"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="154"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="154"/>
-      <c r="J18" s="155"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="127"/>
-      <c r="B19" s="153"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="154"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="154"/>
-      <c r="H19" s="154"/>
-      <c r="I19" s="154"/>
-      <c r="J19" s="155"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="73"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="127"/>
-      <c r="B20" s="153"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
-      <c r="H20" s="154"/>
-      <c r="I20" s="154"/>
-      <c r="J20" s="155"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="73"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="126">
+      <c r="A21" s="34">
         <v>3</v>
       </c>
-      <c r="B21" s="141" t="s">
+      <c r="B21" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="141"/>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="128"/>
-      <c r="B22" s="163" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="164"/>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="164"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="165"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="59"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="128"/>
-      <c r="B23" s="163"/>
-      <c r="C23" s="164"/>
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="165"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="128"/>
-      <c r="B24" s="163"/>
-      <c r="C24" s="164"/>
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="164"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="164"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="165"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="59"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="128"/>
-      <c r="B25" s="166"/>
-      <c r="C25" s="167"/>
-      <c r="D25" s="167"/>
-      <c r="E25" s="167"/>
-      <c r="F25" s="167"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
-      <c r="J25" s="168"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="62"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="128"/>
-      <c r="B26" s="169" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="64"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="35"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="64"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="35"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="64"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="35"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="64"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="35"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="64"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="35"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="64"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="35"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="64"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="35"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="64"/>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="35"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="64"/>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="35"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="64"/>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="35"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="64"/>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="35"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="64"/>
+    </row>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="35"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="64"/>
+    </row>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="64"/>
+    </row>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="35"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="64"/>
+    </row>
+    <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="35"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="64"/>
+    </row>
+    <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="35"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="64"/>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="35"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="64"/>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="35"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="64"/>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="64"/>
+    </row>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="35"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="64"/>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="35"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="64"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="35"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="64"/>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="64"/>
+    </row>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="35"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="64"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="35"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="64"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="35"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="64"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="35"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="64"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="35"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="64"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="35"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="64"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="35"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="64"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="64"/>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="35"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="63"/>
+      <c r="J60" s="64"/>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="35"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="64"/>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="36"/>
+      <c r="B62" s="65"/>
+      <c r="C62" s="65"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="65"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="65"/>
+      <c r="J62" s="66"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="34">
+        <v>4</v>
+      </c>
+      <c r="B63" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="74"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="35"/>
+      <c r="B64" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="37"/>
+      <c r="D64" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="169"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="169"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="169"/>
-      <c r="J26" s="170"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="128"/>
-      <c r="B27" s="169"/>
-      <c r="C27" s="169"/>
-      <c r="D27" s="169"/>
-      <c r="E27" s="169"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="170"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="128"/>
-      <c r="B28" s="169"/>
-      <c r="C28" s="169"/>
-      <c r="D28" s="169"/>
-      <c r="E28" s="169"/>
-      <c r="F28" s="169"/>
-      <c r="G28" s="169"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="169"/>
-      <c r="J28" s="170"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="128"/>
-      <c r="B29" s="169"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="169"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="169"/>
-      <c r="G29" s="169"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="169"/>
-      <c r="J29" s="170"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="128"/>
-      <c r="B30" s="169"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="169"/>
-      <c r="J30" s="170"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="128"/>
-      <c r="B31" s="169"/>
-      <c r="C31" s="169"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="169"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="169"/>
-      <c r="J31" s="170"/>
-    </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="128"/>
-      <c r="B32" s="169"/>
-      <c r="C32" s="169"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="169"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="169"/>
-      <c r="J32" s="170"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="128"/>
-      <c r="B33" s="169"/>
-      <c r="C33" s="169"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="169"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="169"/>
-      <c r="J33" s="170"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="128"/>
-      <c r="B34" s="169"/>
-      <c r="C34" s="169"/>
-      <c r="D34" s="169"/>
-      <c r="E34" s="169"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="170"/>
-    </row>
-    <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="128"/>
-      <c r="B35" s="169"/>
-      <c r="C35" s="169"/>
-      <c r="D35" s="169"/>
-      <c r="E35" s="169"/>
-      <c r="F35" s="169"/>
-      <c r="G35" s="169"/>
-      <c r="H35" s="169"/>
-      <c r="I35" s="169"/>
-      <c r="J35" s="170"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="128"/>
-      <c r="B36" s="169"/>
-      <c r="C36" s="169"/>
-      <c r="D36" s="169"/>
-      <c r="E36" s="169"/>
-      <c r="F36" s="169"/>
-      <c r="G36" s="169"/>
-      <c r="H36" s="169"/>
-      <c r="I36" s="169"/>
-      <c r="J36" s="170"/>
-    </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="128"/>
-      <c r="B37" s="169"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="169"/>
-      <c r="F37" s="169"/>
-      <c r="G37" s="169"/>
-      <c r="H37" s="169"/>
-      <c r="I37" s="169"/>
-      <c r="J37" s="170"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="128"/>
-      <c r="B38" s="169"/>
-      <c r="C38" s="169"/>
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="169"/>
-      <c r="J38" s="170"/>
-    </row>
-    <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="128"/>
-      <c r="B39" s="169"/>
-      <c r="C39" s="169"/>
-      <c r="D39" s="169"/>
-      <c r="E39" s="169"/>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="169"/>
-      <c r="I39" s="169"/>
-      <c r="J39" s="170"/>
-    </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="128"/>
-      <c r="B40" s="169"/>
-      <c r="C40" s="169"/>
-      <c r="D40" s="169"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="169"/>
-      <c r="G40" s="169"/>
-      <c r="H40" s="169"/>
-      <c r="I40" s="169"/>
-      <c r="J40" s="170"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="128"/>
-      <c r="B41" s="169"/>
-      <c r="C41" s="169"/>
-      <c r="D41" s="169"/>
-      <c r="E41" s="169"/>
-      <c r="F41" s="169"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="169"/>
-      <c r="I41" s="169"/>
-      <c r="J41" s="170"/>
-    </row>
-    <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="128"/>
-      <c r="B42" s="169"/>
-      <c r="C42" s="169"/>
-      <c r="D42" s="169"/>
-      <c r="E42" s="169"/>
-      <c r="F42" s="169"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="169"/>
-      <c r="I42" s="169"/>
-      <c r="J42" s="170"/>
-    </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="128"/>
-      <c r="B43" s="169"/>
-      <c r="C43" s="169"/>
-      <c r="D43" s="169"/>
-      <c r="E43" s="169"/>
-      <c r="F43" s="169"/>
-      <c r="G43" s="169"/>
-      <c r="H43" s="169"/>
-      <c r="I43" s="169"/>
-      <c r="J43" s="170"/>
-    </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="128"/>
-      <c r="B44" s="169"/>
-      <c r="C44" s="169"/>
-      <c r="D44" s="169"/>
-      <c r="E44" s="169"/>
-      <c r="F44" s="169"/>
-      <c r="G44" s="169"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="169"/>
-      <c r="J44" s="170"/>
-    </row>
-    <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="128"/>
-      <c r="B45" s="169"/>
-      <c r="C45" s="169"/>
-      <c r="D45" s="169"/>
-      <c r="E45" s="169"/>
-      <c r="F45" s="169"/>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169"/>
-      <c r="I45" s="169"/>
-      <c r="J45" s="170"/>
-    </row>
-    <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="128"/>
-      <c r="B46" s="169"/>
-      <c r="C46" s="169"/>
-      <c r="D46" s="169"/>
-      <c r="E46" s="169"/>
-      <c r="F46" s="169"/>
-      <c r="G46" s="169"/>
-      <c r="H46" s="169"/>
-      <c r="I46" s="169"/>
-      <c r="J46" s="170"/>
-    </row>
-    <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="128"/>
-      <c r="B47" s="169"/>
-      <c r="C47" s="169"/>
-      <c r="D47" s="169"/>
-      <c r="E47" s="169"/>
-      <c r="F47" s="169"/>
-      <c r="G47" s="169"/>
-      <c r="H47" s="169"/>
-      <c r="I47" s="169"/>
-      <c r="J47" s="170"/>
-    </row>
-    <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="128"/>
-      <c r="B48" s="169"/>
-      <c r="C48" s="169"/>
-      <c r="D48" s="169"/>
-      <c r="E48" s="169"/>
-      <c r="F48" s="169"/>
-      <c r="G48" s="169"/>
-      <c r="H48" s="169"/>
-      <c r="I48" s="169"/>
-      <c r="J48" s="170"/>
-    </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="128"/>
-      <c r="B49" s="169"/>
-      <c r="C49" s="169"/>
-      <c r="D49" s="169"/>
-      <c r="E49" s="169"/>
-      <c r="F49" s="169"/>
-      <c r="G49" s="169"/>
-      <c r="H49" s="169"/>
-      <c r="I49" s="169"/>
-      <c r="J49" s="170"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="128"/>
-      <c r="B50" s="169"/>
-      <c r="C50" s="169"/>
-      <c r="D50" s="169"/>
-      <c r="E50" s="169"/>
-      <c r="F50" s="169"/>
-      <c r="G50" s="169"/>
-      <c r="H50" s="169"/>
-      <c r="I50" s="169"/>
-      <c r="J50" s="170"/>
-    </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="128"/>
-      <c r="B51" s="169"/>
-      <c r="C51" s="169"/>
-      <c r="D51" s="169"/>
-      <c r="E51" s="169"/>
-      <c r="F51" s="169"/>
-      <c r="G51" s="169"/>
-      <c r="H51" s="169"/>
-      <c r="I51" s="169"/>
-      <c r="J51" s="170"/>
-    </row>
-    <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="128"/>
-      <c r="B52" s="169"/>
-      <c r="C52" s="169"/>
-      <c r="D52" s="169"/>
-      <c r="E52" s="169"/>
-      <c r="F52" s="169"/>
-      <c r="G52" s="169"/>
-      <c r="H52" s="169"/>
-      <c r="I52" s="169"/>
-      <c r="J52" s="170"/>
-    </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="128"/>
-      <c r="B53" s="169"/>
-      <c r="C53" s="169"/>
-      <c r="D53" s="169"/>
-      <c r="E53" s="169"/>
-      <c r="F53" s="169"/>
-      <c r="G53" s="169"/>
-      <c r="H53" s="169"/>
-      <c r="I53" s="169"/>
-      <c r="J53" s="170"/>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="128"/>
-      <c r="B54" s="169"/>
-      <c r="C54" s="169"/>
-      <c r="D54" s="169"/>
-      <c r="E54" s="169"/>
-      <c r="F54" s="169"/>
-      <c r="G54" s="169"/>
-      <c r="H54" s="169"/>
-      <c r="I54" s="169"/>
-      <c r="J54" s="170"/>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="128"/>
-      <c r="B55" s="169"/>
-      <c r="C55" s="169"/>
-      <c r="D55" s="169"/>
-      <c r="E55" s="169"/>
-      <c r="F55" s="169"/>
-      <c r="G55" s="169"/>
-      <c r="H55" s="169"/>
-      <c r="I55" s="169"/>
-      <c r="J55" s="170"/>
-    </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="128"/>
-      <c r="B56" s="169"/>
-      <c r="C56" s="169"/>
-      <c r="D56" s="169"/>
-      <c r="E56" s="169"/>
-      <c r="F56" s="169"/>
-      <c r="G56" s="169"/>
-      <c r="H56" s="169"/>
-      <c r="I56" s="169"/>
-      <c r="J56" s="170"/>
-    </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="128"/>
-      <c r="B57" s="169"/>
-      <c r="C57" s="169"/>
-      <c r="D57" s="169"/>
-      <c r="E57" s="169"/>
-      <c r="F57" s="169"/>
-      <c r="G57" s="169"/>
-      <c r="H57" s="169"/>
-      <c r="I57" s="169"/>
-      <c r="J57" s="170"/>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="128"/>
-      <c r="B58" s="169"/>
-      <c r="C58" s="169"/>
-      <c r="D58" s="169"/>
-      <c r="E58" s="169"/>
-      <c r="F58" s="169"/>
-      <c r="G58" s="169"/>
-      <c r="H58" s="169"/>
-      <c r="I58" s="169"/>
-      <c r="J58" s="170"/>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="128"/>
-      <c r="B59" s="169"/>
-      <c r="C59" s="169"/>
-      <c r="D59" s="169"/>
-      <c r="E59" s="169"/>
-      <c r="F59" s="169"/>
-      <c r="G59" s="169"/>
-      <c r="H59" s="169"/>
-      <c r="I59" s="169"/>
-      <c r="J59" s="170"/>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="128"/>
-      <c r="B60" s="169"/>
-      <c r="C60" s="169"/>
-      <c r="D60" s="169"/>
-      <c r="E60" s="169"/>
-      <c r="F60" s="169"/>
-      <c r="G60" s="169"/>
-      <c r="H60" s="169"/>
-      <c r="I60" s="169"/>
-      <c r="J60" s="170"/>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="128"/>
-      <c r="B61" s="169"/>
-      <c r="C61" s="169"/>
-      <c r="D61" s="169"/>
-      <c r="E61" s="169"/>
-      <c r="F61" s="169"/>
-      <c r="G61" s="169"/>
-      <c r="H61" s="169"/>
-      <c r="I61" s="169"/>
-      <c r="J61" s="170"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="129"/>
-      <c r="B62" s="171"/>
-      <c r="C62" s="171"/>
-      <c r="D62" s="171"/>
-      <c r="E62" s="171"/>
-      <c r="F62" s="171"/>
-      <c r="G62" s="171"/>
-      <c r="H62" s="171"/>
-      <c r="I62" s="171"/>
-      <c r="J62" s="172"/>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="126">
-        <v>4</v>
-      </c>
-      <c r="B63" s="130" t="s">
+      <c r="E64" s="51"/>
+      <c r="F64" s="51"/>
+      <c r="G64" s="51"/>
+      <c r="H64" s="51"/>
+      <c r="I64" s="51"/>
+      <c r="J64" s="52"/>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="35"/>
+      <c r="B65" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="37"/>
+      <c r="D65" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
+      <c r="H65" s="51"/>
+      <c r="I65" s="51"/>
+      <c r="J65" s="52"/>
+    </row>
+    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="35"/>
+      <c r="B66" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="37"/>
+      <c r="D66" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="51"/>
+      <c r="J66" s="52"/>
+    </row>
+    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="35"/>
+      <c r="B67" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="37"/>
+      <c r="D67" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="51"/>
+      <c r="J67" s="52"/>
+    </row>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="35"/>
+      <c r="B68" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="67"/>
+    </row>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="35"/>
+      <c r="B69" s="47" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
+      <c r="J69" s="48"/>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="35"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="48"/>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="35"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="48"/>
+    </row>
+    <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="35"/>
+      <c r="B72" s="47"/>
+      <c r="C72" s="47"/>
+      <c r="D72" s="47"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="47"/>
+      <c r="G72" s="47"/>
+      <c r="H72" s="47"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="48"/>
+    </row>
+    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="35"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="47"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="47"/>
+      <c r="G73" s="47"/>
+      <c r="H73" s="47"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="48"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="35"/>
+      <c r="B74" s="47"/>
+      <c r="C74" s="47"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="47"/>
+      <c r="G74" s="47"/>
+      <c r="H74" s="47"/>
+      <c r="I74" s="47"/>
+      <c r="J74" s="48"/>
+    </row>
+    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="35"/>
+      <c r="B75" s="47"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="47"/>
+      <c r="G75" s="47"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="48"/>
+    </row>
+    <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="35"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="47"/>
+      <c r="G76" s="47"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="47"/>
+      <c r="J76" s="48"/>
+    </row>
+    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="35"/>
+      <c r="B77" s="47"/>
+      <c r="C77" s="47"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="47"/>
+      <c r="F77" s="47"/>
+      <c r="G77" s="47"/>
+      <c r="H77" s="47"/>
+      <c r="I77" s="47"/>
+      <c r="J77" s="48"/>
+    </row>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="35"/>
+      <c r="B78" s="47"/>
+      <c r="C78" s="47"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="47"/>
+      <c r="F78" s="47"/>
+      <c r="G78" s="47"/>
+      <c r="H78" s="47"/>
+      <c r="I78" s="47"/>
+      <c r="J78" s="48"/>
+    </row>
+    <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="35"/>
+      <c r="B79" s="47"/>
+      <c r="C79" s="47"/>
+      <c r="D79" s="47"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="47"/>
+      <c r="G79" s="47"/>
+      <c r="H79" s="47"/>
+      <c r="I79" s="47"/>
+      <c r="J79" s="48"/>
+    </row>
+    <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="35"/>
+      <c r="B80" s="47"/>
+      <c r="C80" s="47"/>
+      <c r="D80" s="47"/>
+      <c r="E80" s="47"/>
+      <c r="F80" s="47"/>
+      <c r="G80" s="47"/>
+      <c r="H80" s="47"/>
+      <c r="I80" s="47"/>
+      <c r="J80" s="48"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="35"/>
+      <c r="B81" s="47"/>
+      <c r="C81" s="47"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="47"/>
+      <c r="F81" s="47"/>
+      <c r="G81" s="47"/>
+      <c r="H81" s="47"/>
+      <c r="I81" s="47"/>
+      <c r="J81" s="48"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="35"/>
+      <c r="B82" s="47"/>
+      <c r="C82" s="47"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="47"/>
+      <c r="G82" s="47"/>
+      <c r="H82" s="47"/>
+      <c r="I82" s="47"/>
+      <c r="J82" s="48"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="35"/>
+      <c r="B83" s="47"/>
+      <c r="C83" s="47"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="47"/>
+      <c r="F83" s="47"/>
+      <c r="G83" s="47"/>
+      <c r="H83" s="47"/>
+      <c r="I83" s="47"/>
+      <c r="J83" s="48"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="35"/>
+      <c r="B84" s="47"/>
+      <c r="C84" s="47"/>
+      <c r="D84" s="47"/>
+      <c r="E84" s="47"/>
+      <c r="F84" s="47"/>
+      <c r="G84" s="47"/>
+      <c r="H84" s="47"/>
+      <c r="I84" s="47"/>
+      <c r="J84" s="48"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="35"/>
+      <c r="B85" s="47"/>
+      <c r="C85" s="47"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="47"/>
+      <c r="F85" s="47"/>
+      <c r="G85" s="47"/>
+      <c r="H85" s="47"/>
+      <c r="I85" s="47"/>
+      <c r="J85" s="48"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="38"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="49"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="49"/>
+      <c r="H86" s="49"/>
+      <c r="I86" s="49"/>
+      <c r="J86" s="50"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="34">
+        <v>5</v>
+      </c>
+      <c r="B87" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
+      <c r="J87" s="74"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="35"/>
+      <c r="B88" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="84"/>
+      <c r="D88" s="84"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
+      <c r="I88" s="84"/>
+      <c r="J88" s="85"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="34">
         <v>6</v>
       </c>
-      <c r="C63" s="130"/>
-      <c r="D63" s="130"/>
-      <c r="E63" s="130"/>
-      <c r="F63" s="130"/>
-      <c r="G63" s="130"/>
-      <c r="H63" s="130"/>
-      <c r="I63" s="130"/>
-      <c r="J63" s="131"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="128"/>
-      <c r="B64" s="173" t="s">
+      <c r="B89" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="40"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="83"/>
+      <c r="B90" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="53"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="54"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="83"/>
+      <c r="B91" s="53"/>
+      <c r="C91" s="53"/>
+      <c r="D91" s="53"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="53"/>
+      <c r="J91" s="54"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="83"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="56"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="35"/>
+      <c r="B93" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C93" s="69"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="69"/>
+      <c r="F93" s="69"/>
+      <c r="G93" s="69"/>
+      <c r="H93" s="69"/>
+      <c r="I93" s="69"/>
+      <c r="J93" s="70"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="35"/>
+      <c r="B94" s="71"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="73"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="35"/>
+      <c r="B95" s="71"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
+      <c r="H95" s="72"/>
+      <c r="I95" s="72"/>
+      <c r="J95" s="73"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="35"/>
+      <c r="B96" s="71"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="72"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="72"/>
+      <c r="G96" s="72"/>
+      <c r="H96" s="72"/>
+      <c r="I96" s="72"/>
+      <c r="J96" s="73"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="35"/>
+      <c r="B97" s="71"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="72"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="72"/>
+      <c r="G97" s="72"/>
+      <c r="H97" s="72"/>
+      <c r="I97" s="72"/>
+      <c r="J97" s="73"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="35"/>
+      <c r="B98" s="71"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="72"/>
+      <c r="E98" s="72"/>
+      <c r="F98" s="72"/>
+      <c r="G98" s="72"/>
+      <c r="H98" s="72"/>
+      <c r="I98" s="72"/>
+      <c r="J98" s="73"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="35"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="72"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="72"/>
+      <c r="G99" s="72"/>
+      <c r="H99" s="72"/>
+      <c r="I99" s="72"/>
+      <c r="J99" s="73"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="35"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="72"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="72"/>
+      <c r="G100" s="72"/>
+      <c r="H100" s="72"/>
+      <c r="I100" s="72"/>
+      <c r="J100" s="73"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="35"/>
+      <c r="B101" s="71"/>
+      <c r="C101" s="72"/>
+      <c r="D101" s="72"/>
+      <c r="E101" s="72"/>
+      <c r="F101" s="72"/>
+      <c r="G101" s="72"/>
+      <c r="H101" s="72"/>
+      <c r="I101" s="72"/>
+      <c r="J101" s="73"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="35"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
+      <c r="G102" s="72"/>
+      <c r="H102" s="72"/>
+      <c r="I102" s="72"/>
+      <c r="J102" s="73"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="35"/>
+      <c r="B103" s="71"/>
+      <c r="C103" s="72"/>
+      <c r="D103" s="72"/>
+      <c r="E103" s="72"/>
+      <c r="F103" s="72"/>
+      <c r="G103" s="72"/>
+      <c r="H103" s="72"/>
+      <c r="I103" s="72"/>
+      <c r="J103" s="73"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="35"/>
+      <c r="B104" s="71"/>
+      <c r="C104" s="72"/>
+      <c r="D104" s="72"/>
+      <c r="E104" s="72"/>
+      <c r="F104" s="72"/>
+      <c r="G104" s="72"/>
+      <c r="H104" s="72"/>
+      <c r="I104" s="72"/>
+      <c r="J104" s="73"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="35"/>
+      <c r="B105" s="71"/>
+      <c r="C105" s="72"/>
+      <c r="D105" s="72"/>
+      <c r="E105" s="72"/>
+      <c r="F105" s="72"/>
+      <c r="G105" s="72"/>
+      <c r="H105" s="72"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="73"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="35"/>
+      <c r="B106" s="71"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="72"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="72"/>
+      <c r="G106" s="72"/>
+      <c r="H106" s="72"/>
+      <c r="I106" s="72"/>
+      <c r="J106" s="73"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="36"/>
+      <c r="B107" s="86"/>
+      <c r="C107" s="87"/>
+      <c r="D107" s="87"/>
+      <c r="E107" s="87"/>
+      <c r="F107" s="87"/>
+      <c r="G107" s="87"/>
+      <c r="H107" s="87"/>
+      <c r="I107" s="87"/>
+      <c r="J107" s="88"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="34">
         <v>7</v>
       </c>
-      <c r="C64" s="173"/>
-      <c r="D64" s="133" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="133"/>
-      <c r="F64" s="133"/>
-      <c r="G64" s="133"/>
-      <c r="H64" s="133"/>
-      <c r="I64" s="133"/>
-      <c r="J64" s="134"/>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="128"/>
-      <c r="B65" s="173" t="s">
+      <c r="B108" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="41"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="41"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="41"/>
+      <c r="H108" s="41"/>
+      <c r="I108" s="41"/>
+      <c r="J108" s="74"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="38"/>
+      <c r="B109" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" s="81"/>
+      <c r="D109" s="81"/>
+      <c r="E109" s="81"/>
+      <c r="F109" s="81"/>
+      <c r="G109" s="81"/>
+      <c r="H109" s="81"/>
+      <c r="I109" s="81"/>
+      <c r="J109" s="82"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="34">
         <v>8</v>
       </c>
-      <c r="C65" s="173"/>
-      <c r="D65" s="133" t="s">
-        <v>160</v>
-      </c>
-      <c r="E65" s="133"/>
-      <c r="F65" s="133"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="133"/>
-      <c r="I65" s="133"/>
-      <c r="J65" s="134"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="128"/>
-      <c r="B66" s="173" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="173"/>
-      <c r="D66" s="133" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" s="133"/>
-      <c r="F66" s="133"/>
-      <c r="G66" s="133"/>
-      <c r="H66" s="133"/>
-      <c r="I66" s="133"/>
-      <c r="J66" s="134"/>
-    </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="128"/>
-      <c r="B67" s="173" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="173"/>
-      <c r="D67" s="133" t="s">
-        <v>158</v>
-      </c>
-      <c r="E67" s="133"/>
-      <c r="F67" s="133"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="133"/>
-      <c r="I67" s="133"/>
-      <c r="J67" s="134"/>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="128"/>
-      <c r="B68" s="173" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="173"/>
-      <c r="D68" s="173"/>
-      <c r="E68" s="173"/>
-      <c r="F68" s="173"/>
-      <c r="G68" s="173"/>
-      <c r="H68" s="173"/>
-      <c r="I68" s="173"/>
-      <c r="J68" s="174"/>
-    </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="128"/>
-      <c r="B69" s="159" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C69" s="159"/>
-      <c r="D69" s="159"/>
-      <c r="E69" s="159"/>
-      <c r="F69" s="159"/>
-      <c r="G69" s="159"/>
-      <c r="H69" s="159"/>
-      <c r="I69" s="159"/>
-      <c r="J69" s="160"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="128"/>
-      <c r="B70" s="159"/>
-      <c r="C70" s="159"/>
-      <c r="D70" s="159"/>
-      <c r="E70" s="159"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="159"/>
-      <c r="H70" s="159"/>
-      <c r="I70" s="159"/>
-      <c r="J70" s="160"/>
-    </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="128"/>
-      <c r="B71" s="159"/>
-      <c r="C71" s="159"/>
-      <c r="D71" s="159"/>
-      <c r="E71" s="159"/>
-      <c r="F71" s="159"/>
-      <c r="G71" s="159"/>
-      <c r="H71" s="159"/>
-      <c r="I71" s="159"/>
-      <c r="J71" s="160"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="128"/>
-      <c r="B72" s="159"/>
-      <c r="C72" s="159"/>
-      <c r="D72" s="159"/>
-      <c r="E72" s="159"/>
-      <c r="F72" s="159"/>
-      <c r="G72" s="159"/>
-      <c r="H72" s="159"/>
-      <c r="I72" s="159"/>
-      <c r="J72" s="160"/>
-    </row>
-    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="128"/>
-      <c r="B73" s="159"/>
-      <c r="C73" s="159"/>
-      <c r="D73" s="159"/>
-      <c r="E73" s="159"/>
-      <c r="F73" s="159"/>
-      <c r="G73" s="159"/>
-      <c r="H73" s="159"/>
-      <c r="I73" s="159"/>
-      <c r="J73" s="160"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="128"/>
-      <c r="B74" s="159"/>
-      <c r="C74" s="159"/>
-      <c r="D74" s="159"/>
-      <c r="E74" s="159"/>
-      <c r="F74" s="159"/>
-      <c r="G74" s="159"/>
-      <c r="H74" s="159"/>
-      <c r="I74" s="159"/>
-      <c r="J74" s="160"/>
-    </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="128"/>
-      <c r="B75" s="159"/>
-      <c r="C75" s="159"/>
-      <c r="D75" s="159"/>
-      <c r="E75" s="159"/>
-      <c r="F75" s="159"/>
-      <c r="G75" s="159"/>
-      <c r="H75" s="159"/>
-      <c r="I75" s="159"/>
-      <c r="J75" s="160"/>
-    </row>
-    <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="128"/>
-      <c r="B76" s="159"/>
-      <c r="C76" s="159"/>
-      <c r="D76" s="159"/>
-      <c r="E76" s="159"/>
-      <c r="F76" s="159"/>
-      <c r="G76" s="159"/>
-      <c r="H76" s="159"/>
-      <c r="I76" s="159"/>
-      <c r="J76" s="160"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="128"/>
-      <c r="B77" s="159"/>
-      <c r="C77" s="159"/>
-      <c r="D77" s="159"/>
-      <c r="E77" s="159"/>
-      <c r="F77" s="159"/>
-      <c r="G77" s="159"/>
-      <c r="H77" s="159"/>
-      <c r="I77" s="159"/>
-      <c r="J77" s="160"/>
-    </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="128"/>
-      <c r="B78" s="159"/>
-      <c r="C78" s="159"/>
-      <c r="D78" s="159"/>
-      <c r="E78" s="159"/>
-      <c r="F78" s="159"/>
-      <c r="G78" s="159"/>
-      <c r="H78" s="159"/>
-      <c r="I78" s="159"/>
-      <c r="J78" s="160"/>
-    </row>
-    <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="128"/>
-      <c r="B79" s="159"/>
-      <c r="C79" s="159"/>
-      <c r="D79" s="159"/>
-      <c r="E79" s="159"/>
-      <c r="F79" s="159"/>
-      <c r="G79" s="159"/>
-      <c r="H79" s="159"/>
-      <c r="I79" s="159"/>
-      <c r="J79" s="160"/>
-    </row>
-    <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="128"/>
-      <c r="B80" s="159"/>
-      <c r="C80" s="159"/>
-      <c r="D80" s="159"/>
-      <c r="E80" s="159"/>
-      <c r="F80" s="159"/>
-      <c r="G80" s="159"/>
-      <c r="H80" s="159"/>
-      <c r="I80" s="159"/>
-      <c r="J80" s="160"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="128"/>
-      <c r="B81" s="159"/>
-      <c r="C81" s="159"/>
-      <c r="D81" s="159"/>
-      <c r="E81" s="159"/>
-      <c r="F81" s="159"/>
-      <c r="G81" s="159"/>
-      <c r="H81" s="159"/>
-      <c r="I81" s="159"/>
-      <c r="J81" s="160"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="128"/>
-      <c r="B82" s="159"/>
-      <c r="C82" s="159"/>
-      <c r="D82" s="159"/>
-      <c r="E82" s="159"/>
-      <c r="F82" s="159"/>
-      <c r="G82" s="159"/>
-      <c r="H82" s="159"/>
-      <c r="I82" s="159"/>
-      <c r="J82" s="160"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="128"/>
-      <c r="B83" s="159"/>
-      <c r="C83" s="159"/>
-      <c r="D83" s="159"/>
-      <c r="E83" s="159"/>
-      <c r="F83" s="159"/>
-      <c r="G83" s="159"/>
-      <c r="H83" s="159"/>
-      <c r="I83" s="159"/>
-      <c r="J83" s="160"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="128"/>
-      <c r="B84" s="159"/>
-      <c r="C84" s="159"/>
-      <c r="D84" s="159"/>
-      <c r="E84" s="159"/>
-      <c r="F84" s="159"/>
-      <c r="G84" s="159"/>
-      <c r="H84" s="159"/>
-      <c r="I84" s="159"/>
-      <c r="J84" s="160"/>
-    </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="128"/>
-      <c r="B85" s="159"/>
-      <c r="C85" s="159"/>
-      <c r="D85" s="159"/>
-      <c r="E85" s="159"/>
-      <c r="F85" s="159"/>
-      <c r="G85" s="159"/>
-      <c r="H85" s="159"/>
-      <c r="I85" s="159"/>
-      <c r="J85" s="160"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="127"/>
-      <c r="B86" s="161"/>
-      <c r="C86" s="161"/>
-      <c r="D86" s="161"/>
-      <c r="E86" s="161"/>
-      <c r="F86" s="161"/>
-      <c r="G86" s="161"/>
-      <c r="H86" s="161"/>
-      <c r="I86" s="161"/>
-      <c r="J86" s="162"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="126">
-        <v>5</v>
-      </c>
-      <c r="B87" s="130" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="130"/>
-      <c r="D87" s="130"/>
-      <c r="E87" s="130"/>
-      <c r="F87" s="130"/>
-      <c r="G87" s="130"/>
-      <c r="H87" s="130"/>
-      <c r="I87" s="130"/>
-      <c r="J87" s="131"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="128"/>
-      <c r="B88" s="148" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="148"/>
-      <c r="D88" s="148"/>
-      <c r="E88" s="148"/>
-      <c r="F88" s="148"/>
-      <c r="G88" s="148"/>
-      <c r="H88" s="148"/>
-      <c r="I88" s="148"/>
-      <c r="J88" s="149"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="126">
-        <v>6</v>
-      </c>
-      <c r="B89" s="141" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" s="141"/>
-      <c r="D89" s="141"/>
-      <c r="E89" s="141"/>
-      <c r="F89" s="141"/>
-      <c r="G89" s="141"/>
-      <c r="H89" s="141"/>
-      <c r="I89" s="141"/>
-      <c r="J89" s="142"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="143"/>
-      <c r="B90" s="144" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="144"/>
-      <c r="D90" s="144"/>
-      <c r="E90" s="144"/>
-      <c r="F90" s="144"/>
-      <c r="G90" s="144"/>
-      <c r="H90" s="144"/>
-      <c r="I90" s="144"/>
-      <c r="J90" s="145"/>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="143"/>
-      <c r="B91" s="144"/>
-      <c r="C91" s="144"/>
-      <c r="D91" s="144"/>
-      <c r="E91" s="144"/>
-      <c r="F91" s="144"/>
-      <c r="G91" s="144"/>
-      <c r="H91" s="144"/>
-      <c r="I91" s="144"/>
-      <c r="J91" s="145"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="143"/>
-      <c r="B92" s="146"/>
-      <c r="C92" s="146"/>
-      <c r="D92" s="146"/>
-      <c r="E92" s="146"/>
-      <c r="F92" s="146"/>
-      <c r="G92" s="146"/>
-      <c r="H92" s="146"/>
-      <c r="I92" s="146"/>
-      <c r="J92" s="147"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="128"/>
-      <c r="B93" s="150" t="s">
-        <v>155</v>
-      </c>
-      <c r="C93" s="151"/>
-      <c r="D93" s="151"/>
-      <c r="E93" s="151"/>
-      <c r="F93" s="151"/>
-      <c r="G93" s="151"/>
-      <c r="H93" s="151"/>
-      <c r="I93" s="151"/>
-      <c r="J93" s="152"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="128"/>
-      <c r="B94" s="153"/>
-      <c r="C94" s="154"/>
-      <c r="D94" s="154"/>
-      <c r="E94" s="154"/>
-      <c r="F94" s="154"/>
-      <c r="G94" s="154"/>
-      <c r="H94" s="154"/>
-      <c r="I94" s="154"/>
-      <c r="J94" s="155"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="128"/>
-      <c r="B95" s="153"/>
-      <c r="C95" s="154"/>
-      <c r="D95" s="154"/>
-      <c r="E95" s="154"/>
-      <c r="F95" s="154"/>
-      <c r="G95" s="154"/>
-      <c r="H95" s="154"/>
-      <c r="I95" s="154"/>
-      <c r="J95" s="155"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="128"/>
-      <c r="B96" s="153"/>
-      <c r="C96" s="154"/>
-      <c r="D96" s="154"/>
-      <c r="E96" s="154"/>
-      <c r="F96" s="154"/>
-      <c r="G96" s="154"/>
-      <c r="H96" s="154"/>
-      <c r="I96" s="154"/>
-      <c r="J96" s="155"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="128"/>
-      <c r="B97" s="153"/>
-      <c r="C97" s="154"/>
-      <c r="D97" s="154"/>
-      <c r="E97" s="154"/>
-      <c r="F97" s="154"/>
-      <c r="G97" s="154"/>
-      <c r="H97" s="154"/>
-      <c r="I97" s="154"/>
-      <c r="J97" s="155"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="128"/>
-      <c r="B98" s="153"/>
-      <c r="C98" s="154"/>
-      <c r="D98" s="154"/>
-      <c r="E98" s="154"/>
-      <c r="F98" s="154"/>
-      <c r="G98" s="154"/>
-      <c r="H98" s="154"/>
-      <c r="I98" s="154"/>
-      <c r="J98" s="155"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="128"/>
-      <c r="B99" s="153"/>
-      <c r="C99" s="154"/>
-      <c r="D99" s="154"/>
-      <c r="E99" s="154"/>
-      <c r="F99" s="154"/>
-      <c r="G99" s="154"/>
-      <c r="H99" s="154"/>
-      <c r="I99" s="154"/>
-      <c r="J99" s="155"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="128"/>
-      <c r="B100" s="153"/>
-      <c r="C100" s="154"/>
-      <c r="D100" s="154"/>
-      <c r="E100" s="154"/>
-      <c r="F100" s="154"/>
-      <c r="G100" s="154"/>
-      <c r="H100" s="154"/>
-      <c r="I100" s="154"/>
-      <c r="J100" s="155"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="128"/>
-      <c r="B101" s="153"/>
-      <c r="C101" s="154"/>
-      <c r="D101" s="154"/>
-      <c r="E101" s="154"/>
-      <c r="F101" s="154"/>
-      <c r="G101" s="154"/>
-      <c r="H101" s="154"/>
-      <c r="I101" s="154"/>
-      <c r="J101" s="155"/>
-    </row>
-    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="128"/>
-      <c r="B102" s="153"/>
-      <c r="C102" s="154"/>
-      <c r="D102" s="154"/>
-      <c r="E102" s="154"/>
-      <c r="F102" s="154"/>
-      <c r="G102" s="154"/>
-      <c r="H102" s="154"/>
-      <c r="I102" s="154"/>
-      <c r="J102" s="155"/>
-    </row>
-    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="128"/>
-      <c r="B103" s="153"/>
-      <c r="C103" s="154"/>
-      <c r="D103" s="154"/>
-      <c r="E103" s="154"/>
-      <c r="F103" s="154"/>
-      <c r="G103" s="154"/>
-      <c r="H103" s="154"/>
-      <c r="I103" s="154"/>
-      <c r="J103" s="155"/>
-    </row>
-    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="128"/>
-      <c r="B104" s="153"/>
-      <c r="C104" s="154"/>
-      <c r="D104" s="154"/>
-      <c r="E104" s="154"/>
-      <c r="F104" s="154"/>
-      <c r="G104" s="154"/>
-      <c r="H104" s="154"/>
-      <c r="I104" s="154"/>
-      <c r="J104" s="155"/>
-    </row>
-    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="128"/>
-      <c r="B105" s="153"/>
-      <c r="C105" s="154"/>
-      <c r="D105" s="154"/>
-      <c r="E105" s="154"/>
-      <c r="F105" s="154"/>
-      <c r="G105" s="154"/>
-      <c r="H105" s="154"/>
-      <c r="I105" s="154"/>
-      <c r="J105" s="155"/>
-    </row>
-    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="128"/>
-      <c r="B106" s="153"/>
-      <c r="C106" s="154"/>
-      <c r="D106" s="154"/>
-      <c r="E106" s="154"/>
-      <c r="F106" s="154"/>
-      <c r="G106" s="154"/>
-      <c r="H106" s="154"/>
-      <c r="I106" s="154"/>
-      <c r="J106" s="155"/>
-    </row>
-    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="129"/>
-      <c r="B107" s="156"/>
-      <c r="C107" s="157"/>
-      <c r="D107" s="157"/>
-      <c r="E107" s="157"/>
-      <c r="F107" s="157"/>
-      <c r="G107" s="157"/>
-      <c r="H107" s="157"/>
-      <c r="I107" s="157"/>
-      <c r="J107" s="158"/>
-    </row>
-    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="126">
-        <v>7</v>
-      </c>
-      <c r="B108" s="130" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="130"/>
-      <c r="D108" s="130"/>
-      <c r="E108" s="130"/>
-      <c r="F108" s="130"/>
-      <c r="G108" s="130"/>
-      <c r="H108" s="130"/>
-      <c r="I108" s="130"/>
-      <c r="J108" s="131"/>
-    </row>
-    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="127"/>
-      <c r="B109" s="139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" s="139"/>
-      <c r="D109" s="139"/>
-      <c r="E109" s="139"/>
-      <c r="F109" s="139"/>
-      <c r="G109" s="139"/>
-      <c r="H109" s="139"/>
-      <c r="I109" s="139"/>
-      <c r="J109" s="140"/>
-    </row>
-    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="126">
-        <v>8</v>
-      </c>
-      <c r="B110" s="130" t="s">
+      <c r="B110" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="130"/>
-      <c r="D110" s="130"/>
-      <c r="E110" s="130"/>
-      <c r="F110" s="130"/>
-      <c r="G110" s="130"/>
-      <c r="H110" s="130"/>
-      <c r="I110" s="130"/>
-      <c r="J110" s="131"/>
+      <c r="C110" s="41"/>
+      <c r="D110" s="41"/>
+      <c r="E110" s="41"/>
+      <c r="F110" s="41"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="41"/>
+      <c r="I110" s="41"/>
+      <c r="J110" s="74"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="128"/>
-      <c r="B111" s="132" t="s">
-        <v>156</v>
-      </c>
-      <c r="C111" s="133"/>
-      <c r="D111" s="133"/>
-      <c r="E111" s="133"/>
-      <c r="F111" s="133"/>
-      <c r="G111" s="133"/>
-      <c r="H111" s="133"/>
-      <c r="I111" s="133"/>
-      <c r="J111" s="134"/>
+      <c r="A111" s="35"/>
+      <c r="B111" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C111" s="51"/>
+      <c r="D111" s="51"/>
+      <c r="E111" s="51"/>
+      <c r="F111" s="51"/>
+      <c r="G111" s="51"/>
+      <c r="H111" s="51"/>
+      <c r="I111" s="51"/>
+      <c r="J111" s="52"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="128"/>
-      <c r="B112" s="133"/>
-      <c r="C112" s="133"/>
-      <c r="D112" s="133"/>
-      <c r="E112" s="133"/>
-      <c r="F112" s="133"/>
-      <c r="G112" s="133"/>
-      <c r="H112" s="133"/>
-      <c r="I112" s="133"/>
-      <c r="J112" s="134"/>
+      <c r="A112" s="35"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="51"/>
+      <c r="G112" s="51"/>
+      <c r="H112" s="51"/>
+      <c r="I112" s="51"/>
+      <c r="J112" s="52"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="128"/>
-      <c r="B113" s="133"/>
-      <c r="C113" s="133"/>
-      <c r="D113" s="133"/>
-      <c r="E113" s="133"/>
-      <c r="F113" s="133"/>
-      <c r="G113" s="133"/>
-      <c r="H113" s="133"/>
-      <c r="I113" s="133"/>
-      <c r="J113" s="134"/>
+      <c r="A113" s="35"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="51"/>
+      <c r="G113" s="51"/>
+      <c r="H113" s="51"/>
+      <c r="I113" s="51"/>
+      <c r="J113" s="52"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="128"/>
-      <c r="B114" s="133"/>
-      <c r="C114" s="133"/>
-      <c r="D114" s="133"/>
-      <c r="E114" s="133"/>
-      <c r="F114" s="133"/>
-      <c r="G114" s="133"/>
-      <c r="H114" s="133"/>
-      <c r="I114" s="133"/>
-      <c r="J114" s="134"/>
+      <c r="A114" s="35"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="51"/>
+      <c r="D114" s="51"/>
+      <c r="E114" s="51"/>
+      <c r="F114" s="51"/>
+      <c r="G114" s="51"/>
+      <c r="H114" s="51"/>
+      <c r="I114" s="51"/>
+      <c r="J114" s="52"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="128"/>
-      <c r="B115" s="133"/>
-      <c r="C115" s="133"/>
-      <c r="D115" s="133"/>
-      <c r="E115" s="133"/>
-      <c r="F115" s="133"/>
-      <c r="G115" s="133"/>
-      <c r="H115" s="133"/>
-      <c r="I115" s="133"/>
-      <c r="J115" s="134"/>
+      <c r="A115" s="35"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="51"/>
+      <c r="D115" s="51"/>
+      <c r="E115" s="51"/>
+      <c r="F115" s="51"/>
+      <c r="G115" s="51"/>
+      <c r="H115" s="51"/>
+      <c r="I115" s="51"/>
+      <c r="J115" s="52"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="128"/>
-      <c r="B116" s="133"/>
-      <c r="C116" s="133"/>
-      <c r="D116" s="133"/>
-      <c r="E116" s="133"/>
-      <c r="F116" s="133"/>
-      <c r="G116" s="133"/>
-      <c r="H116" s="133"/>
-      <c r="I116" s="133"/>
-      <c r="J116" s="134"/>
+      <c r="A116" s="35"/>
+      <c r="B116" s="51"/>
+      <c r="C116" s="51"/>
+      <c r="D116" s="51"/>
+      <c r="E116" s="51"/>
+      <c r="F116" s="51"/>
+      <c r="G116" s="51"/>
+      <c r="H116" s="51"/>
+      <c r="I116" s="51"/>
+      <c r="J116" s="52"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="128"/>
-      <c r="B117" s="135" t="s">
+      <c r="A117" s="35"/>
+      <c r="B117" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="135"/>
-      <c r="D117" s="135"/>
-      <c r="E117" s="135"/>
-      <c r="F117" s="135"/>
-      <c r="G117" s="135"/>
-      <c r="H117" s="135"/>
-      <c r="I117" s="135"/>
-      <c r="J117" s="136"/>
+      <c r="C117" s="77"/>
+      <c r="D117" s="77"/>
+      <c r="E117" s="77"/>
+      <c r="F117" s="77"/>
+      <c r="G117" s="77"/>
+      <c r="H117" s="77"/>
+      <c r="I117" s="77"/>
+      <c r="J117" s="78"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="128"/>
-      <c r="B118" s="132" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="133"/>
-      <c r="D118" s="133"/>
-      <c r="E118" s="133"/>
-      <c r="F118" s="133"/>
-      <c r="G118" s="133"/>
-      <c r="H118" s="133"/>
-      <c r="I118" s="133"/>
-      <c r="J118" s="134"/>
+      <c r="A118" s="35"/>
+      <c r="B118" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" s="51"/>
+      <c r="D118" s="51"/>
+      <c r="E118" s="51"/>
+      <c r="F118" s="51"/>
+      <c r="G118" s="51"/>
+      <c r="H118" s="51"/>
+      <c r="I118" s="51"/>
+      <c r="J118" s="52"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="128"/>
-      <c r="B119" s="133"/>
-      <c r="C119" s="133"/>
-      <c r="D119" s="133"/>
-      <c r="E119" s="133"/>
-      <c r="F119" s="133"/>
-      <c r="G119" s="133"/>
-      <c r="H119" s="133"/>
-      <c r="I119" s="133"/>
-      <c r="J119" s="134"/>
+      <c r="A119" s="35"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="51"/>
+      <c r="D119" s="51"/>
+      <c r="E119" s="51"/>
+      <c r="F119" s="51"/>
+      <c r="G119" s="51"/>
+      <c r="H119" s="51"/>
+      <c r="I119" s="51"/>
+      <c r="J119" s="52"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="128"/>
-      <c r="B120" s="133"/>
-      <c r="C120" s="133"/>
-      <c r="D120" s="133"/>
-      <c r="E120" s="133"/>
-      <c r="F120" s="133"/>
-      <c r="G120" s="133"/>
-      <c r="H120" s="133"/>
-      <c r="I120" s="133"/>
-      <c r="J120" s="134"/>
+      <c r="A120" s="35"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="51"/>
+      <c r="D120" s="51"/>
+      <c r="E120" s="51"/>
+      <c r="F120" s="51"/>
+      <c r="G120" s="51"/>
+      <c r="H120" s="51"/>
+      <c r="I120" s="51"/>
+      <c r="J120" s="52"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="128"/>
-      <c r="B121" s="133"/>
-      <c r="C121" s="133"/>
-      <c r="D121" s="133"/>
-      <c r="E121" s="133"/>
-      <c r="F121" s="133"/>
-      <c r="G121" s="133"/>
-      <c r="H121" s="133"/>
-      <c r="I121" s="133"/>
-      <c r="J121" s="134"/>
+      <c r="A121" s="35"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="51"/>
+      <c r="D121" s="51"/>
+      <c r="E121" s="51"/>
+      <c r="F121" s="51"/>
+      <c r="G121" s="51"/>
+      <c r="H121" s="51"/>
+      <c r="I121" s="51"/>
+      <c r="J121" s="52"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="128"/>
-      <c r="B122" s="133"/>
-      <c r="C122" s="133"/>
-      <c r="D122" s="133"/>
-      <c r="E122" s="133"/>
-      <c r="F122" s="133"/>
-      <c r="G122" s="133"/>
-      <c r="H122" s="133"/>
-      <c r="I122" s="133"/>
-      <c r="J122" s="134"/>
+      <c r="A122" s="35"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="51"/>
+      <c r="D122" s="51"/>
+      <c r="E122" s="51"/>
+      <c r="F122" s="51"/>
+      <c r="G122" s="51"/>
+      <c r="H122" s="51"/>
+      <c r="I122" s="51"/>
+      <c r="J122" s="52"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="128"/>
-      <c r="B123" s="133"/>
-      <c r="C123" s="133"/>
-      <c r="D123" s="133"/>
-      <c r="E123" s="133"/>
-      <c r="F123" s="133"/>
-      <c r="G123" s="133"/>
-      <c r="H123" s="133"/>
-      <c r="I123" s="133"/>
-      <c r="J123" s="134"/>
+      <c r="A123" s="35"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="51"/>
+      <c r="D123" s="51"/>
+      <c r="E123" s="51"/>
+      <c r="F123" s="51"/>
+      <c r="G123" s="51"/>
+      <c r="H123" s="51"/>
+      <c r="I123" s="51"/>
+      <c r="J123" s="52"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="128"/>
-      <c r="B124" s="133"/>
-      <c r="C124" s="133"/>
-      <c r="D124" s="133"/>
-      <c r="E124" s="133"/>
-      <c r="F124" s="133"/>
-      <c r="G124" s="133"/>
-      <c r="H124" s="133"/>
-      <c r="I124" s="133"/>
-      <c r="J124" s="134"/>
+      <c r="A124" s="35"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="51"/>
+      <c r="D124" s="51"/>
+      <c r="E124" s="51"/>
+      <c r="F124" s="51"/>
+      <c r="G124" s="51"/>
+      <c r="H124" s="51"/>
+      <c r="I124" s="51"/>
+      <c r="J124" s="52"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="129"/>
-      <c r="B125" s="137"/>
-      <c r="C125" s="137"/>
-      <c r="D125" s="137"/>
-      <c r="E125" s="137"/>
-      <c r="F125" s="137"/>
-      <c r="G125" s="137"/>
-      <c r="H125" s="137"/>
-      <c r="I125" s="137"/>
-      <c r="J125" s="138"/>
+      <c r="A125" s="36"/>
+      <c r="B125" s="79"/>
+      <c r="C125" s="79"/>
+      <c r="D125" s="79"/>
+      <c r="E125" s="79"/>
+      <c r="F125" s="79"/>
+      <c r="G125" s="79"/>
+      <c r="H125" s="79"/>
+      <c r="I125" s="79"/>
+      <c r="J125" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
     <mergeCell ref="B69:J86"/>
     <mergeCell ref="A63:A86"/>
     <mergeCell ref="D64:J64"/>
@@ -6005,22 +6048,13 @@
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A125"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="B111:J116"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B118:J125"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="A89:A107"/>
-    <mergeCell ref="B90:J92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="B93:J107"/>
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6049,71 +6083,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="187"/>
-      <c r="B3" s="187"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="187"/>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="148"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="186" t="s">
+      <c r="A6" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="188" t="s">
+      <c r="F6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="189"/>
-      <c r="H6" s="192" t="s">
+      <c r="G6" s="92"/>
+      <c r="H6" s="95" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="186"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6123,287 +6157,287 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="186"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="193"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="96"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="161" t="s">
+      <c r="B8" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="161" t="s">
+      <c r="D8" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>73</v>
-      </c>
       <c r="E8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="184" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="185"/>
+        <v>97</v>
+      </c>
+      <c r="F8" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="98"/>
       <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="181"/>
-      <c r="C9" s="181"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="184" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" s="185"/>
+        <v>97</v>
+      </c>
+      <c r="F9" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="98"/>
       <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="181"/>
-      <c r="C10" s="182"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="184" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="185"/>
+        <v>97</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="98"/>
       <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="181"/>
-      <c r="C11" s="161" t="s">
+      <c r="B11" s="100"/>
+      <c r="C11" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>77</v>
-      </c>
       <c r="E11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="184" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="185"/>
+        <v>97</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="98"/>
       <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="182"/>
-      <c r="C12" s="182"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
       <c r="D12" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F12" s="184" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="185"/>
+        <v>97</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="98"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="161" t="s">
+      <c r="B13" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="D13" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>81</v>
-      </c>
       <c r="E13" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="184" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="185"/>
+        <v>98</v>
+      </c>
+      <c r="F13" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="98"/>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="183"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>83</v>
-      </c>
       <c r="E14" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="184" t="s">
-        <v>107</v>
-      </c>
-      <c r="G14" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F14" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="98"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="183"/>
-      <c r="C15" s="161" t="s">
+      <c r="B15" s="102"/>
+      <c r="C15" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>85</v>
-      </c>
       <c r="E15" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="184" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F15" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="98"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="180"/>
-      <c r="C16" s="180"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" s="184" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F16" s="97" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="98"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="161" t="s">
+      <c r="B17" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="D17" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>89</v>
-      </c>
       <c r="E17" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="184" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F17" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="98"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="183"/>
+      <c r="B18" s="102"/>
       <c r="C18" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>91</v>
-      </c>
       <c r="E18" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="184" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F18" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="98"/>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="180"/>
+      <c r="B19" s="99"/>
       <c r="C19" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>93</v>
-      </c>
       <c r="E19" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="184" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="185"/>
+        <v>99</v>
+      </c>
+      <c r="F19" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="98"/>
       <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="161" t="s">
+      <c r="B20" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="D20" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>96</v>
-      </c>
       <c r="E20" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="184" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="185"/>
+        <v>100</v>
+      </c>
+      <c r="F20" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="98"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="180"/>
-      <c r="C21" s="180"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="184" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="185"/>
+        <v>100</v>
+      </c>
+      <c r="F21" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="98"/>
       <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6414,8 +6448,8 @@
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
       <c r="E22" s="27"/>
-      <c r="F22" s="184"/>
-      <c r="G22" s="185"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="98"/>
       <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6426,8 +6460,8 @@
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
       <c r="E23" s="27"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="185"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="98"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6438,8 +6472,8 @@
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
       <c r="E24" s="27"/>
-      <c r="F24" s="184"/>
-      <c r="G24" s="185"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="98"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6450,8 +6484,8 @@
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="185"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="98"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6462,8 +6496,8 @@
       <c r="C26" s="27"/>
       <c r="D26" s="27"/>
       <c r="E26" s="27"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="185"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="98"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6474,8 +6508,8 @@
       <c r="C27" s="27"/>
       <c r="D27" s="27"/>
       <c r="E27" s="27"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="185"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="98"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6486,8 +6520,8 @@
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="184"/>
-      <c r="G28" s="185"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="98"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6498,8 +6532,8 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="185"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="98"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6510,8 +6544,8 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="184"/>
-      <c r="G30" s="185"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="98"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6522,8 +6556,8 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="184"/>
-      <c r="G31" s="185"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="98"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6534,8 +6568,8 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="185"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="98"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6546,8 +6580,8 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="184"/>
-      <c r="G33" s="185"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="98"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6558,8 +6592,8 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="185"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="98"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6570,8 +6604,8 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="185"/>
+      <c r="F35" s="97"/>
+      <c r="G35" s="98"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6582,8 +6616,8 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="185"/>
+      <c r="F36" s="97"/>
+      <c r="G36" s="98"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6594,12 +6628,50 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="185"/>
+      <c r="F37" s="97"/>
+      <c r="G37" s="98"/>
       <c r="H37" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:A7"/>
@@ -6608,44 +6680,6 @@
     <mergeCell ref="A2:H4"/>
     <mergeCell ref="F6:G7"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C15:C16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6672,458 +6706,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="205"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="187"/>
-      <c r="B3" s="187"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="148"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="186" t="s">
+      <c r="A5" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="192" t="s">
+      <c r="B5" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="188" t="s">
+      <c r="D5" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="186" t="s">
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="89" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="186"/>
-      <c r="B6" s="193"/>
-      <c r="C6" s="193"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="191"/>
-      <c r="I6" s="186"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="89"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="194" t="s">
+      <c r="B7" s="103" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="133" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="195"/>
+      <c r="B8" s="106"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="195"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="196"/>
+      <c r="B10" s="104"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="197" t="s">
+      <c r="B11" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="103" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="133" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="195"/>
-      <c r="C12" s="196"/>
-      <c r="D12" s="133" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="195"/>
+      <c r="B13" s="106"/>
       <c r="C13" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="196"/>
+      <c r="B14" s="104"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="197" t="s">
+      <c r="B15" s="105" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="133" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="195"/>
+      <c r="B16" s="106"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="195"/>
+      <c r="B17" s="106"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="196"/>
+      <c r="B18" s="104"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="197" t="s">
+      <c r="B19" s="105" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="133" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="195"/>
+      <c r="B20" s="106"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="195"/>
+      <c r="B21" s="106"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="196"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="197" t="s">
+      <c r="B23" s="105" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="133" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="198"/>
+      <c r="B24" s="110"/>
       <c r="C24" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="133" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
+        <v>128</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="198"/>
+      <c r="B25" s="110"/>
       <c r="C25" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="133" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
+        <v>129</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="198"/>
+      <c r="B26" s="110"/>
       <c r="C26" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="132" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
+        <v>130</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="199"/>
+      <c r="B27" s="111"/>
       <c r="C27" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="200" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="201"/>
-      <c r="F27" s="201"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="202"/>
+        <v>132</v>
+      </c>
+      <c r="D27" s="112" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="114"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="197" t="s">
+      <c r="B28" s="105" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="133" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
+        <v>133</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="195"/>
+      <c r="B29" s="106"/>
       <c r="C29" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="133" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="133"/>
+        <v>135</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="195"/>
+      <c r="B30" s="106"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="133"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="133"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="196"/>
+      <c r="B31" s="104"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="133"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7132,11 +7166,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="133"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7145,11 +7179,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7158,11 +7192,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="133"/>
-      <c r="H34" s="133"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7171,11 +7205,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="133"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="133"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7184,11 +7218,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="133"/>
-      <c r="F36" s="133"/>
-      <c r="G36" s="133"/>
-      <c r="H36" s="133"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7197,29 +7231,31 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="133"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="133"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="133"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D25:H25"/>
@@ -7236,22 +7272,20 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -7275,23 +7309,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="203"/>
+      <c r="O1" s="203"/>
+      <c r="P1" s="203"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7308,141 +7342,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="155" t="s">
+        <v>158</v>
+      </c>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155"/>
+      <c r="AD2" s="155"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113" t="s">
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="117" t="s">
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="121"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="117" t="s">
+      <c r="R4" s="160"/>
+      <c r="S4" s="157"/>
+      <c r="T4" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="121"/>
-      <c r="V4" s="121"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="117" t="s">
+      <c r="U4" s="160"/>
+      <c r="V4" s="160"/>
+      <c r="W4" s="157"/>
+      <c r="X4" s="156" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="113" t="s">
+      <c r="Y4" s="157"/>
+      <c r="Z4" s="149" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA4" s="149"/>
+      <c r="AB4" s="149"/>
+      <c r="AC4" s="149" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD4" s="149"/>
+      <c r="AE4" s="149"/>
+      <c r="AF4" s="149" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG4" s="149"/>
+      <c r="AH4" s="149"/>
+      <c r="AI4" s="149" t="s">
         <v>146</v>
       </c>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113" t="s">
+      <c r="AJ4" s="149"/>
+      <c r="AK4" s="149"/>
+      <c r="AL4" s="149" t="s">
         <v>147</v>
       </c>
-      <c r="AD4" s="113"/>
-      <c r="AE4" s="113"/>
-      <c r="AF4" s="113" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG4" s="113"/>
-      <c r="AH4" s="113"/>
-      <c r="AI4" s="113" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ4" s="113"/>
-      <c r="AK4" s="113"/>
-      <c r="AL4" s="113" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM4" s="113"/>
-      <c r="AN4" s="113"/>
-      <c r="AO4" s="113" t="s">
+      <c r="AM4" s="149"/>
+      <c r="AN4" s="149"/>
+      <c r="AO4" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="113"/>
-      <c r="AQ4" s="113"/>
-      <c r="AR4" s="113"/>
-      <c r="AS4" s="113"/>
-      <c r="AT4" s="113"/>
-      <c r="AU4" s="113"/>
-      <c r="AV4" s="113"/>
-      <c r="AW4" s="113"/>
-      <c r="AX4" s="113"/>
-      <c r="AY4" s="113"/>
-      <c r="AZ4" s="114"/>
+      <c r="AP4" s="149"/>
+      <c r="AQ4" s="149"/>
+      <c r="AR4" s="149"/>
+      <c r="AS4" s="149"/>
+      <c r="AT4" s="149"/>
+      <c r="AU4" s="149"/>
+      <c r="AV4" s="149"/>
+      <c r="AW4" s="149"/>
+      <c r="AX4" s="149"/>
+      <c r="AY4" s="149"/>
+      <c r="AZ4" s="150"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="124"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="122"/>
-      <c r="W5" s="120"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="120"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
+      <c r="L5" s="151"/>
+      <c r="M5" s="151"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="151"/>
+      <c r="Q5" s="158"/>
+      <c r="R5" s="161"/>
+      <c r="S5" s="159"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="161"/>
+      <c r="W5" s="159"/>
+      <c r="X5" s="158"/>
+      <c r="Y5" s="159"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7488,58 +7522,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="115"/>
-      <c r="AP5" s="115"/>
-      <c r="AQ5" s="115"/>
-      <c r="AR5" s="115"/>
-      <c r="AS5" s="115"/>
-      <c r="AT5" s="115"/>
-      <c r="AU5" s="115"/>
-      <c r="AV5" s="115"/>
-      <c r="AW5" s="115"/>
-      <c r="AX5" s="115"/>
-      <c r="AY5" s="115"/>
-      <c r="AZ5" s="116"/>
+      <c r="AO5" s="151"/>
+      <c r="AP5" s="151"/>
+      <c r="AQ5" s="151"/>
+      <c r="AR5" s="151"/>
+      <c r="AS5" s="151"/>
+      <c r="AT5" s="151"/>
+      <c r="AU5" s="151"/>
+      <c r="AV5" s="151"/>
+      <c r="AW5" s="151"/>
+      <c r="AX5" s="151"/>
+      <c r="AY5" s="151"/>
+      <c r="AZ5" s="152"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="40">
+      <c r="B6" s="178">
         <v>1</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="164" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="41" t="s">
+      <c r="D6" s="164"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="164"/>
+      <c r="J6" s="164" t="s">
+        <v>138</v>
+      </c>
+      <c r="K6" s="164"/>
+      <c r="L6" s="164"/>
+      <c r="M6" s="164"/>
+      <c r="N6" s="164"/>
+      <c r="O6" s="164"/>
+      <c r="P6" s="164"/>
+      <c r="Q6" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="R6" s="155"/>
+      <c r="S6" s="155"/>
+      <c r="T6" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="41"/>
-      <c r="V6" s="38">
+      <c r="U6" s="169"/>
+      <c r="V6" s="167">
         <v>0</v>
       </c>
-      <c r="W6" s="38"/>
-      <c r="X6" s="60">
+      <c r="W6" s="167"/>
+      <c r="X6" s="153">
         <v>0</v>
       </c>
-      <c r="Y6" s="60"/>
+      <c r="Y6" s="153"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7555,50 +7589,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="37"/>
-      <c r="AP6" s="37"/>
-      <c r="AQ6" s="37"/>
-      <c r="AR6" s="37"/>
-      <c r="AS6" s="37"/>
-      <c r="AT6" s="37"/>
-      <c r="AU6" s="37"/>
-      <c r="AV6" s="37"/>
-      <c r="AW6" s="37"/>
-      <c r="AX6" s="37"/>
-      <c r="AY6" s="37"/>
-      <c r="AZ6" s="59"/>
+      <c r="AO6" s="164"/>
+      <c r="AP6" s="164"/>
+      <c r="AQ6" s="164"/>
+      <c r="AR6" s="164"/>
+      <c r="AS6" s="164"/>
+      <c r="AT6" s="164"/>
+      <c r="AU6" s="164"/>
+      <c r="AV6" s="164"/>
+      <c r="AW6" s="164"/>
+      <c r="AX6" s="164"/>
+      <c r="AY6" s="164"/>
+      <c r="AZ6" s="165"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="40"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="42" t="s">
+      <c r="B7" s="178"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="164"/>
+      <c r="M7" s="164"/>
+      <c r="N7" s="164"/>
+      <c r="O7" s="164"/>
+      <c r="P7" s="164"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="155"/>
+      <c r="S7" s="155"/>
+      <c r="T7" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="42"/>
-      <c r="V7" s="39">
+      <c r="U7" s="166"/>
+      <c r="V7" s="168">
         <v>0</v>
       </c>
-      <c r="W7" s="39"/>
-      <c r="X7" s="61">
+      <c r="W7" s="168"/>
+      <c r="X7" s="154">
         <v>1</v>
       </c>
-      <c r="Y7" s="61"/>
+      <c r="Y7" s="154"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7614,58 +7648,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="37"/>
-      <c r="AP7" s="37"/>
-      <c r="AQ7" s="37"/>
-      <c r="AR7" s="37"/>
-      <c r="AS7" s="37"/>
-      <c r="AT7" s="37"/>
-      <c r="AU7" s="37"/>
-      <c r="AV7" s="37"/>
-      <c r="AW7" s="37"/>
-      <c r="AX7" s="37"/>
-      <c r="AY7" s="37"/>
-      <c r="AZ7" s="59"/>
+      <c r="AO7" s="164"/>
+      <c r="AP7" s="164"/>
+      <c r="AQ7" s="164"/>
+      <c r="AR7" s="164"/>
+      <c r="AS7" s="164"/>
+      <c r="AT7" s="164"/>
+      <c r="AU7" s="164"/>
+      <c r="AV7" s="164"/>
+      <c r="AW7" s="164"/>
+      <c r="AX7" s="164"/>
+      <c r="AY7" s="164"/>
+      <c r="AZ7" s="165"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="40">
+      <c r="B8" s="178">
         <v>2</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="164" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="41" t="s">
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="140" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="123"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="124"/>
+      <c r="Q8" s="205" t="s">
+        <v>141</v>
+      </c>
+      <c r="R8" s="205"/>
+      <c r="S8" s="205"/>
+      <c r="T8" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="41"/>
-      <c r="V8" s="38">
+      <c r="U8" s="169"/>
+      <c r="V8" s="167">
         <v>0</v>
       </c>
-      <c r="W8" s="38"/>
-      <c r="X8" s="60">
+      <c r="W8" s="167"/>
+      <c r="X8" s="153">
         <v>0</v>
       </c>
-      <c r="Y8" s="60"/>
+      <c r="Y8" s="153"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7681,50 +7715,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="37"/>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="59"/>
+      <c r="AO8" s="164"/>
+      <c r="AP8" s="164"/>
+      <c r="AQ8" s="164"/>
+      <c r="AR8" s="164"/>
+      <c r="AS8" s="164"/>
+      <c r="AT8" s="164"/>
+      <c r="AU8" s="164"/>
+      <c r="AV8" s="164"/>
+      <c r="AW8" s="164"/>
+      <c r="AX8" s="164"/>
+      <c r="AY8" s="164"/>
+      <c r="AZ8" s="165"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="40"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="42" t="s">
+      <c r="B9" s="178"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="164"/>
+      <c r="H9" s="164"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="205"/>
+      <c r="R9" s="205"/>
+      <c r="S9" s="205"/>
+      <c r="T9" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="42"/>
-      <c r="V9" s="39">
+      <c r="U9" s="166"/>
+      <c r="V9" s="168">
         <v>0</v>
       </c>
-      <c r="W9" s="39"/>
-      <c r="X9" s="61">
+      <c r="W9" s="168"/>
+      <c r="X9" s="154">
         <v>1</v>
       </c>
-      <c r="Y9" s="61"/>
+      <c r="Y9" s="154"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -7740,58 +7774,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="37"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="37"/>
-      <c r="AS9" s="37"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="37"/>
-      <c r="AV9" s="37"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="37"/>
-      <c r="AY9" s="37"/>
-      <c r="AZ9" s="59"/>
+      <c r="AO9" s="164"/>
+      <c r="AP9" s="164"/>
+      <c r="AQ9" s="164"/>
+      <c r="AR9" s="164"/>
+      <c r="AS9" s="164"/>
+      <c r="AT9" s="164"/>
+      <c r="AU9" s="164"/>
+      <c r="AV9" s="164"/>
+      <c r="AW9" s="164"/>
+      <c r="AX9" s="164"/>
+      <c r="AY9" s="164"/>
+      <c r="AZ9" s="165"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="40">
+      <c r="B10" s="178">
         <v>3</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="164" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="41" t="s">
+      <c r="D10" s="164"/>
+      <c r="E10" s="164"/>
+      <c r="F10" s="164"/>
+      <c r="G10" s="164"/>
+      <c r="H10" s="164"/>
+      <c r="I10" s="164"/>
+      <c r="J10" s="204" t="s">
+        <v>148</v>
+      </c>
+      <c r="K10" s="164"/>
+      <c r="L10" s="164"/>
+      <c r="M10" s="164"/>
+      <c r="N10" s="164"/>
+      <c r="O10" s="164"/>
+      <c r="P10" s="164"/>
+      <c r="Q10" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="R10" s="155"/>
+      <c r="S10" s="155"/>
+      <c r="T10" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="41"/>
-      <c r="V10" s="38">
+      <c r="U10" s="169"/>
+      <c r="V10" s="167">
         <v>0</v>
       </c>
-      <c r="W10" s="38"/>
-      <c r="X10" s="60">
+      <c r="W10" s="167"/>
+      <c r="X10" s="153">
         <v>0</v>
       </c>
-      <c r="Y10" s="60"/>
+      <c r="Y10" s="153"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -7807,50 +7841,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="37"/>
-      <c r="AR10" s="37"/>
-      <c r="AS10" s="37"/>
-      <c r="AT10" s="37"/>
-      <c r="AU10" s="37"/>
-      <c r="AV10" s="37"/>
-      <c r="AW10" s="37"/>
-      <c r="AX10" s="37"/>
-      <c r="AY10" s="37"/>
-      <c r="AZ10" s="59"/>
+      <c r="AO10" s="164"/>
+      <c r="AP10" s="164"/>
+      <c r="AQ10" s="164"/>
+      <c r="AR10" s="164"/>
+      <c r="AS10" s="164"/>
+      <c r="AT10" s="164"/>
+      <c r="AU10" s="164"/>
+      <c r="AV10" s="164"/>
+      <c r="AW10" s="164"/>
+      <c r="AX10" s="164"/>
+      <c r="AY10" s="164"/>
+      <c r="AZ10" s="165"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="40"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="42" t="s">
+      <c r="B11" s="178"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="164"/>
+      <c r="F11" s="164"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="164"/>
+      <c r="I11" s="164"/>
+      <c r="J11" s="164"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="164"/>
+      <c r="M11" s="164"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="164"/>
+      <c r="Q11" s="155"/>
+      <c r="R11" s="155"/>
+      <c r="S11" s="155"/>
+      <c r="T11" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="42"/>
-      <c r="V11" s="39">
+      <c r="U11" s="166"/>
+      <c r="V11" s="168">
         <v>0</v>
       </c>
-      <c r="W11" s="39"/>
-      <c r="X11" s="61">
+      <c r="W11" s="168"/>
+      <c r="X11" s="154">
         <v>0</v>
       </c>
-      <c r="Y11" s="61"/>
+      <c r="Y11" s="154"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -7866,58 +7900,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="37"/>
-      <c r="AS11" s="37"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="37"/>
-      <c r="AV11" s="37"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="37"/>
-      <c r="AY11" s="37"/>
-      <c r="AZ11" s="59"/>
+      <c r="AO11" s="164"/>
+      <c r="AP11" s="164"/>
+      <c r="AQ11" s="164"/>
+      <c r="AR11" s="164"/>
+      <c r="AS11" s="164"/>
+      <c r="AT11" s="164"/>
+      <c r="AU11" s="164"/>
+      <c r="AV11" s="164"/>
+      <c r="AW11" s="164"/>
+      <c r="AX11" s="164"/>
+      <c r="AY11" s="164"/>
+      <c r="AZ11" s="165"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="40">
+      <c r="B12" s="178">
         <v>4</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="164" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="103" t="s">
+      <c r="D12" s="164"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="164"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="164" t="s">
         <v>142</v>
       </c>
-      <c r="R12" s="104"/>
-      <c r="S12" s="105"/>
-      <c r="T12" s="41" t="s">
+      <c r="K12" s="164"/>
+      <c r="L12" s="164"/>
+      <c r="M12" s="164"/>
+      <c r="N12" s="164"/>
+      <c r="O12" s="164"/>
+      <c r="P12" s="164"/>
+      <c r="Q12" s="128" t="s">
+        <v>139</v>
+      </c>
+      <c r="R12" s="129"/>
+      <c r="S12" s="130"/>
+      <c r="T12" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="41"/>
-      <c r="V12" s="38">
+      <c r="U12" s="169"/>
+      <c r="V12" s="167">
         <v>0</v>
       </c>
-      <c r="W12" s="38"/>
-      <c r="X12" s="60">
+      <c r="W12" s="167"/>
+      <c r="X12" s="153">
         <v>0</v>
       </c>
-      <c r="Y12" s="60"/>
+      <c r="Y12" s="153"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -7933,50 +7967,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="37"/>
-      <c r="AR12" s="37"/>
-      <c r="AS12" s="37"/>
-      <c r="AT12" s="37"/>
-      <c r="AU12" s="37"/>
-      <c r="AV12" s="37"/>
-      <c r="AW12" s="37"/>
-      <c r="AX12" s="37"/>
-      <c r="AY12" s="37"/>
-      <c r="AZ12" s="59"/>
+      <c r="AO12" s="164"/>
+      <c r="AP12" s="164"/>
+      <c r="AQ12" s="164"/>
+      <c r="AR12" s="164"/>
+      <c r="AS12" s="164"/>
+      <c r="AT12" s="164"/>
+      <c r="AU12" s="164"/>
+      <c r="AV12" s="164"/>
+      <c r="AW12" s="164"/>
+      <c r="AX12" s="164"/>
+      <c r="AY12" s="164"/>
+      <c r="AZ12" s="165"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="40"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="107"/>
-      <c r="S13" s="108"/>
-      <c r="T13" s="42" t="s">
+      <c r="B13" s="178"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="164"/>
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="164"/>
+      <c r="H13" s="164"/>
+      <c r="I13" s="164"/>
+      <c r="J13" s="164"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="164"/>
+      <c r="M13" s="164"/>
+      <c r="N13" s="164"/>
+      <c r="O13" s="164"/>
+      <c r="P13" s="164"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="133"/>
+      <c r="T13" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="42"/>
-      <c r="V13" s="39">
+      <c r="U13" s="166"/>
+      <c r="V13" s="168">
         <v>0</v>
       </c>
-      <c r="W13" s="39"/>
-      <c r="X13" s="61">
+      <c r="W13" s="168"/>
+      <c r="X13" s="154">
         <v>0</v>
       </c>
-      <c r="Y13" s="61"/>
+      <c r="Y13" s="154"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -7992,54 +8026,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="37"/>
-      <c r="AY13" s="37"/>
-      <c r="AZ13" s="59"/>
+      <c r="AO13" s="164"/>
+      <c r="AP13" s="164"/>
+      <c r="AQ13" s="164"/>
+      <c r="AR13" s="164"/>
+      <c r="AS13" s="164"/>
+      <c r="AT13" s="164"/>
+      <c r="AU13" s="164"/>
+      <c r="AV13" s="164"/>
+      <c r="AW13" s="164"/>
+      <c r="AX13" s="164"/>
+      <c r="AY13" s="164"/>
+      <c r="AZ13" s="165"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="40">
+      <c r="B14" s="178">
         <v>5</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="104"/>
-      <c r="S14" s="105"/>
-      <c r="T14" s="41" t="s">
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="124"/>
+      <c r="J14" s="204"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="164"/>
+      <c r="M14" s="164"/>
+      <c r="N14" s="164"/>
+      <c r="O14" s="164"/>
+      <c r="P14" s="164"/>
+      <c r="Q14" s="128"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="130"/>
+      <c r="T14" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="41"/>
-      <c r="V14" s="38">
+      <c r="U14" s="169"/>
+      <c r="V14" s="167">
         <v>0</v>
       </c>
-      <c r="W14" s="38"/>
-      <c r="X14" s="60">
+      <c r="W14" s="167"/>
+      <c r="X14" s="153">
         <v>0</v>
       </c>
-      <c r="Y14" s="60"/>
+      <c r="Y14" s="153"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8055,50 +8089,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="37"/>
-      <c r="AP14" s="37"/>
-      <c r="AQ14" s="37"/>
-      <c r="AR14" s="37"/>
-      <c r="AS14" s="37"/>
-      <c r="AT14" s="37"/>
-      <c r="AU14" s="37"/>
-      <c r="AV14" s="37"/>
-      <c r="AW14" s="37"/>
-      <c r="AX14" s="37"/>
-      <c r="AY14" s="37"/>
-      <c r="AZ14" s="59"/>
+      <c r="AO14" s="164"/>
+      <c r="AP14" s="164"/>
+      <c r="AQ14" s="164"/>
+      <c r="AR14" s="164"/>
+      <c r="AS14" s="164"/>
+      <c r="AT14" s="164"/>
+      <c r="AU14" s="164"/>
+      <c r="AV14" s="164"/>
+      <c r="AW14" s="164"/>
+      <c r="AX14" s="164"/>
+      <c r="AY14" s="164"/>
+      <c r="AZ14" s="165"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="40"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="108"/>
-      <c r="T15" s="42" t="s">
+      <c r="B15" s="178"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="164"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="164"/>
+      <c r="M15" s="164"/>
+      <c r="N15" s="164"/>
+      <c r="O15" s="164"/>
+      <c r="P15" s="164"/>
+      <c r="Q15" s="131"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="133"/>
+      <c r="T15" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="42"/>
-      <c r="V15" s="39">
+      <c r="U15" s="166"/>
+      <c r="V15" s="168">
         <v>0</v>
       </c>
-      <c r="W15" s="39"/>
-      <c r="X15" s="61">
+      <c r="W15" s="168"/>
+      <c r="X15" s="154">
         <v>0</v>
       </c>
-      <c r="Y15" s="61"/>
+      <c r="Y15" s="154"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8114,56 +8148,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="37"/>
-      <c r="AP15" s="37"/>
-      <c r="AQ15" s="37"/>
-      <c r="AR15" s="37"/>
-      <c r="AS15" s="37"/>
-      <c r="AT15" s="37"/>
-      <c r="AU15" s="37"/>
-      <c r="AV15" s="37"/>
-      <c r="AW15" s="37"/>
-      <c r="AX15" s="37"/>
-      <c r="AY15" s="37"/>
-      <c r="AZ15" s="59"/>
+      <c r="AO15" s="164"/>
+      <c r="AP15" s="164"/>
+      <c r="AQ15" s="164"/>
+      <c r="AR15" s="164"/>
+      <c r="AS15" s="164"/>
+      <c r="AT15" s="164"/>
+      <c r="AU15" s="164"/>
+      <c r="AV15" s="164"/>
+      <c r="AW15" s="164"/>
+      <c r="AX15" s="164"/>
+      <c r="AY15" s="164"/>
+      <c r="AZ15" s="165"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="40">
+      <c r="B16" s="178">
         <v>6</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="41" t="s">
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="204" t="s">
+        <v>149</v>
+      </c>
+      <c r="K16" s="164"/>
+      <c r="L16" s="164"/>
+      <c r="M16" s="164"/>
+      <c r="N16" s="164"/>
+      <c r="O16" s="164"/>
+      <c r="P16" s="164"/>
+      <c r="Q16" s="155"/>
+      <c r="R16" s="155"/>
+      <c r="S16" s="155"/>
+      <c r="T16" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="41"/>
-      <c r="V16" s="38">
+      <c r="U16" s="169"/>
+      <c r="V16" s="167">
         <v>0</v>
       </c>
-      <c r="W16" s="38"/>
-      <c r="X16" s="60">
+      <c r="W16" s="167"/>
+      <c r="X16" s="153">
         <v>0</v>
       </c>
-      <c r="Y16" s="60"/>
+      <c r="Y16" s="153"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8179,50 +8213,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="37"/>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="37"/>
-      <c r="AT16" s="37"/>
-      <c r="AU16" s="37"/>
-      <c r="AV16" s="37"/>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="37"/>
-      <c r="AY16" s="37"/>
-      <c r="AZ16" s="59"/>
+      <c r="AO16" s="164"/>
+      <c r="AP16" s="164"/>
+      <c r="AQ16" s="164"/>
+      <c r="AR16" s="164"/>
+      <c r="AS16" s="164"/>
+      <c r="AT16" s="164"/>
+      <c r="AU16" s="164"/>
+      <c r="AV16" s="164"/>
+      <c r="AW16" s="164"/>
+      <c r="AX16" s="164"/>
+      <c r="AY16" s="164"/>
+      <c r="AZ16" s="165"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="40"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="44"/>
-      <c r="R17" s="44"/>
-      <c r="S17" s="44"/>
-      <c r="T17" s="42" t="s">
+      <c r="B17" s="178"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="164"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="164"/>
+      <c r="M17" s="164"/>
+      <c r="N17" s="164"/>
+      <c r="O17" s="164"/>
+      <c r="P17" s="164"/>
+      <c r="Q17" s="155"/>
+      <c r="R17" s="155"/>
+      <c r="S17" s="155"/>
+      <c r="T17" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="42"/>
-      <c r="V17" s="39">
+      <c r="U17" s="166"/>
+      <c r="V17" s="168">
         <v>0</v>
       </c>
-      <c r="W17" s="39"/>
-      <c r="X17" s="61">
+      <c r="W17" s="168"/>
+      <c r="X17" s="154">
         <v>0</v>
       </c>
-      <c r="Y17" s="61"/>
+      <c r="Y17" s="154"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8238,56 +8272,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="37"/>
-      <c r="AP17" s="37"/>
-      <c r="AQ17" s="37"/>
-      <c r="AR17" s="37"/>
-      <c r="AS17" s="37"/>
-      <c r="AT17" s="37"/>
-      <c r="AU17" s="37"/>
-      <c r="AV17" s="37"/>
-      <c r="AW17" s="37"/>
-      <c r="AX17" s="37"/>
-      <c r="AY17" s="37"/>
-      <c r="AZ17" s="59"/>
+      <c r="AO17" s="164"/>
+      <c r="AP17" s="164"/>
+      <c r="AQ17" s="164"/>
+      <c r="AR17" s="164"/>
+      <c r="AS17" s="164"/>
+      <c r="AT17" s="164"/>
+      <c r="AU17" s="164"/>
+      <c r="AV17" s="164"/>
+      <c r="AW17" s="164"/>
+      <c r="AX17" s="164"/>
+      <c r="AY17" s="164"/>
+      <c r="AZ17" s="165"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="57">
+      <c r="B18" s="115">
         <v>7</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="104"/>
-      <c r="S18" s="105"/>
-      <c r="T18" s="93" t="s">
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="140" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="128"/>
+      <c r="R18" s="129"/>
+      <c r="S18" s="130"/>
+      <c r="T18" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="94"/>
-      <c r="V18" s="53">
+      <c r="U18" s="135"/>
+      <c r="V18" s="136">
         <v>0</v>
       </c>
-      <c r="W18" s="54"/>
-      <c r="X18" s="99">
+      <c r="W18" s="137"/>
+      <c r="X18" s="138">
         <v>0</v>
       </c>
-      <c r="Y18" s="100"/>
+      <c r="Y18" s="139"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8303,50 +8337,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="45"/>
-      <c r="AP18" s="46"/>
-      <c r="AQ18" s="46"/>
-      <c r="AR18" s="46"/>
-      <c r="AS18" s="46"/>
-      <c r="AT18" s="46"/>
-      <c r="AU18" s="46"/>
-      <c r="AV18" s="46"/>
-      <c r="AW18" s="46"/>
-      <c r="AX18" s="46"/>
-      <c r="AY18" s="46"/>
-      <c r="AZ18" s="95"/>
+      <c r="AO18" s="140"/>
+      <c r="AP18" s="123"/>
+      <c r="AQ18" s="123"/>
+      <c r="AR18" s="123"/>
+      <c r="AS18" s="123"/>
+      <c r="AT18" s="123"/>
+      <c r="AU18" s="123"/>
+      <c r="AV18" s="123"/>
+      <c r="AW18" s="123"/>
+      <c r="AX18" s="123"/>
+      <c r="AY18" s="123"/>
+      <c r="AZ18" s="141"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="58"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="108"/>
-      <c r="T19" s="97" t="s">
+      <c r="B19" s="116"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="127"/>
+      <c r="Q19" s="131"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="133"/>
+      <c r="T19" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="98"/>
-      <c r="V19" s="55">
+      <c r="U19" s="144"/>
+      <c r="V19" s="145">
         <v>0</v>
       </c>
-      <c r="W19" s="56"/>
-      <c r="X19" s="101">
+      <c r="W19" s="146"/>
+      <c r="X19" s="147">
         <v>0</v>
       </c>
-      <c r="Y19" s="102"/>
+      <c r="Y19" s="148"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8362,56 +8396,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="48"/>
-      <c r="AP19" s="49"/>
-      <c r="AQ19" s="49"/>
-      <c r="AR19" s="49"/>
-      <c r="AS19" s="49"/>
-      <c r="AT19" s="49"/>
-      <c r="AU19" s="49"/>
-      <c r="AV19" s="49"/>
-      <c r="AW19" s="49"/>
-      <c r="AX19" s="49"/>
-      <c r="AY19" s="49"/>
-      <c r="AZ19" s="96"/>
+      <c r="AO19" s="125"/>
+      <c r="AP19" s="126"/>
+      <c r="AQ19" s="126"/>
+      <c r="AR19" s="126"/>
+      <c r="AS19" s="126"/>
+      <c r="AT19" s="126"/>
+      <c r="AU19" s="126"/>
+      <c r="AV19" s="126"/>
+      <c r="AW19" s="126"/>
+      <c r="AX19" s="126"/>
+      <c r="AY19" s="126"/>
+      <c r="AZ19" s="142"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="57">
+      <c r="B20" s="115">
         <v>8</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="90" t="s">
-        <v>154</v>
-      </c>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="104"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="93" t="s">
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="117" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="130"/>
+      <c r="T20" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="94"/>
-      <c r="V20" s="53">
+      <c r="U20" s="135"/>
+      <c r="V20" s="136">
         <v>0</v>
       </c>
-      <c r="W20" s="54"/>
-      <c r="X20" s="99">
+      <c r="W20" s="137"/>
+      <c r="X20" s="138">
         <v>0</v>
       </c>
-      <c r="Y20" s="100"/>
+      <c r="Y20" s="139"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8427,50 +8461,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="45"/>
-      <c r="AP20" s="46"/>
-      <c r="AQ20" s="46"/>
-      <c r="AR20" s="46"/>
-      <c r="AS20" s="46"/>
-      <c r="AT20" s="46"/>
-      <c r="AU20" s="46"/>
-      <c r="AV20" s="46"/>
-      <c r="AW20" s="46"/>
-      <c r="AX20" s="46"/>
-      <c r="AY20" s="46"/>
-      <c r="AZ20" s="95"/>
+      <c r="AO20" s="140"/>
+      <c r="AP20" s="123"/>
+      <c r="AQ20" s="123"/>
+      <c r="AR20" s="123"/>
+      <c r="AS20" s="123"/>
+      <c r="AT20" s="123"/>
+      <c r="AU20" s="123"/>
+      <c r="AV20" s="123"/>
+      <c r="AW20" s="123"/>
+      <c r="AX20" s="123"/>
+      <c r="AY20" s="123"/>
+      <c r="AZ20" s="141"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="58"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="106"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="108"/>
-      <c r="T21" s="97" t="s">
+      <c r="B21" s="116"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="126"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="127"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="133"/>
+      <c r="T21" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="98"/>
-      <c r="V21" s="55">
+      <c r="U21" s="144"/>
+      <c r="V21" s="145">
         <v>0</v>
       </c>
-      <c r="W21" s="56"/>
-      <c r="X21" s="101">
+      <c r="W21" s="146"/>
+      <c r="X21" s="147">
         <v>0</v>
       </c>
-      <c r="Y21" s="102"/>
+      <c r="Y21" s="148"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8486,54 +8520,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="48"/>
-      <c r="AP21" s="49"/>
-      <c r="AQ21" s="49"/>
-      <c r="AR21" s="49"/>
-      <c r="AS21" s="49"/>
-      <c r="AT21" s="49"/>
-      <c r="AU21" s="49"/>
-      <c r="AV21" s="49"/>
-      <c r="AW21" s="49"/>
-      <c r="AX21" s="49"/>
-      <c r="AY21" s="49"/>
-      <c r="AZ21" s="96"/>
+      <c r="AO21" s="125"/>
+      <c r="AP21" s="126"/>
+      <c r="AQ21" s="126"/>
+      <c r="AR21" s="126"/>
+      <c r="AS21" s="126"/>
+      <c r="AT21" s="126"/>
+      <c r="AU21" s="126"/>
+      <c r="AV21" s="126"/>
+      <c r="AW21" s="126"/>
+      <c r="AX21" s="126"/>
+      <c r="AY21" s="126"/>
+      <c r="AZ21" s="142"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="70">
+      <c r="B22" s="185">
         <v>9</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="187" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="78" t="s">
+      <c r="D22" s="188"/>
+      <c r="E22" s="188"/>
+      <c r="F22" s="188"/>
+      <c r="G22" s="188"/>
+      <c r="H22" s="188"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="172"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="173"/>
+      <c r="M22" s="173"/>
+      <c r="N22" s="173"/>
+      <c r="O22" s="173"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="194"/>
+      <c r="R22" s="195"/>
+      <c r="S22" s="196"/>
+      <c r="T22" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="79"/>
-      <c r="V22" s="109">
+      <c r="U22" s="191"/>
+      <c r="V22" s="170">
         <v>0</v>
       </c>
-      <c r="W22" s="110"/>
-      <c r="X22" s="68">
+      <c r="W22" s="171"/>
+      <c r="X22" s="183">
         <v>0</v>
       </c>
-      <c r="Y22" s="69"/>
+      <c r="Y22" s="184"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8549,50 +8583,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="62"/>
-      <c r="AP22" s="63"/>
-      <c r="AQ22" s="63"/>
-      <c r="AR22" s="63"/>
-      <c r="AS22" s="63"/>
-      <c r="AT22" s="63"/>
-      <c r="AU22" s="63"/>
-      <c r="AV22" s="63"/>
-      <c r="AW22" s="63"/>
-      <c r="AX22" s="63"/>
-      <c r="AY22" s="63"/>
-      <c r="AZ22" s="64"/>
+      <c r="AO22" s="172"/>
+      <c r="AP22" s="173"/>
+      <c r="AQ22" s="173"/>
+      <c r="AR22" s="173"/>
+      <c r="AS22" s="173"/>
+      <c r="AT22" s="173"/>
+      <c r="AU22" s="173"/>
+      <c r="AV22" s="173"/>
+      <c r="AW22" s="173"/>
+      <c r="AX22" s="173"/>
+      <c r="AY22" s="173"/>
+      <c r="AZ22" s="181"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="71"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="85"/>
-      <c r="R23" s="86"/>
-      <c r="S23" s="87"/>
-      <c r="T23" s="80" t="s">
+      <c r="B23" s="186"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="122"/>
+      <c r="J23" s="175"/>
+      <c r="K23" s="176"/>
+      <c r="L23" s="176"/>
+      <c r="M23" s="176"/>
+      <c r="N23" s="176"/>
+      <c r="O23" s="176"/>
+      <c r="P23" s="177"/>
+      <c r="Q23" s="197"/>
+      <c r="R23" s="198"/>
+      <c r="S23" s="199"/>
+      <c r="T23" s="192" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="81"/>
-      <c r="V23" s="51">
+      <c r="U23" s="193"/>
+      <c r="V23" s="179">
         <v>0</v>
       </c>
-      <c r="W23" s="52"/>
-      <c r="X23" s="88">
+      <c r="W23" s="180"/>
+      <c r="X23" s="200">
         <v>0</v>
       </c>
-      <c r="Y23" s="89"/>
+      <c r="Y23" s="201"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8608,18 +8642,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="65"/>
-      <c r="AP23" s="66"/>
-      <c r="AQ23" s="66"/>
-      <c r="AR23" s="66"/>
-      <c r="AS23" s="66"/>
-      <c r="AT23" s="66"/>
-      <c r="AU23" s="66"/>
-      <c r="AV23" s="66"/>
-      <c r="AW23" s="66"/>
-      <c r="AX23" s="66"/>
-      <c r="AY23" s="66"/>
-      <c r="AZ23" s="67"/>
+      <c r="AO23" s="175"/>
+      <c r="AP23" s="176"/>
+      <c r="AQ23" s="176"/>
+      <c r="AR23" s="176"/>
+      <c r="AS23" s="176"/>
+      <c r="AT23" s="176"/>
+      <c r="AU23" s="176"/>
+      <c r="AV23" s="176"/>
+      <c r="AW23" s="176"/>
+      <c r="AX23" s="176"/>
+      <c r="AY23" s="176"/>
+      <c r="AZ23" s="182"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8678,50 +8712,51 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AO16:AZ17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AO22:AZ23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:I23"/>
+    <mergeCell ref="J18:P19"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q16:S17"/>
+    <mergeCell ref="Q22:S23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C18:I19"/>
+    <mergeCell ref="T18:U18"/>
     <mergeCell ref="AO18:AZ19"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="X18:Y18"/>
@@ -8746,51 +8781,50 @@
     <mergeCell ref="X15:Y15"/>
     <mergeCell ref="Q12:S13"/>
     <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AO16:AZ17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AO22:AZ23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:I23"/>
-    <mergeCell ref="J18:P19"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q16:S17"/>
-    <mergeCell ref="Q22:S23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C18:I19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8814,53 +8848,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="126">
+      <c r="A1" s="34">
         <v>1</v>
       </c>
-      <c r="B1" s="130" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="176" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="177"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="127"/>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
-      <c r="J2" s="179"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="126">
+      <c r="A3" s="34">
         <v>2</v>
       </c>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="131"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="128"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="206" t="s">
         <v>60</v>
       </c>
@@ -8874,551 +8908,552 @@
       <c r="J4" s="207"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="126">
+      <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="74"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="127"/>
-      <c r="B6" s="139" t="s">
+      <c r="A6" s="38"/>
+      <c r="B6" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="139"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="139"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="139"/>
-      <c r="I6" s="139"/>
-      <c r="J6" s="140"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="126">
+      <c r="A7" s="34">
         <v>4</v>
       </c>
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="128"/>
-      <c r="B8" s="135" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="136"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="78"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="128"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="52"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="128"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="134"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="128"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="52"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="128"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="128"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="134"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="128"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="134"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="128"/>
-      <c r="B15" s="135" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="136"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="78"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="128"/>
-      <c r="B16" s="133"/>
-      <c r="C16" s="133"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="128"/>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
-      <c r="J17" s="134"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="52"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="128"/>
-      <c r="B18" s="133"/>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="128"/>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="134"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="128"/>
-      <c r="B20" s="133"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="134"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="52"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="127"/>
-      <c r="B21" s="178"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="178"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="178"/>
-      <c r="G21" s="178"/>
-      <c r="H21" s="178"/>
-      <c r="I21" s="178"/>
-      <c r="J21" s="179"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="126">
+      <c r="A22" s="34">
         <v>5</v>
       </c>
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
-      <c r="J22" s="131"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="74"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="128"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="134"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="128"/>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="134"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="128"/>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
-      <c r="I25" s="133"/>
-      <c r="J25" s="134"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="128"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="134"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="128"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="133"/>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="134"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="128"/>
-      <c r="B28" s="133"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="133"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
-      <c r="J28" s="134"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="128"/>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
-      <c r="J29" s="134"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="52"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="127"/>
-      <c r="B30" s="178"/>
-      <c r="C30" s="178"/>
-      <c r="D30" s="178"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="178"/>
-      <c r="G30" s="178"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="179"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="46"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="126">
+      <c r="A31" s="34">
         <v>6</v>
       </c>
-      <c r="B31" s="130" t="s">
+      <c r="B31" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="130"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="131"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="74"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="128"/>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
-      <c r="J32" s="134"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="52"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="128"/>
-      <c r="B33" s="133"/>
-      <c r="C33" s="133"/>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="134"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="52"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="128"/>
-      <c r="B34" s="133"/>
-      <c r="C34" s="133"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="133"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="133"/>
-      <c r="J34" s="134"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="128"/>
-      <c r="B35" s="133"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="133"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
-      <c r="J35" s="134"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="52"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="128"/>
-      <c r="B36" s="133"/>
-      <c r="C36" s="133"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="133"/>
-      <c r="F36" s="133"/>
-      <c r="G36" s="133"/>
-      <c r="H36" s="133"/>
-      <c r="I36" s="133"/>
-      <c r="J36" s="134"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="52"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="128"/>
-      <c r="B37" s="133"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="133"/>
-      <c r="E37" s="133"/>
-      <c r="F37" s="133"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="133"/>
-      <c r="I37" s="133"/>
-      <c r="J37" s="134"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="52"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="128"/>
-      <c r="B38" s="133"/>
-      <c r="C38" s="133"/>
-      <c r="D38" s="133"/>
-      <c r="E38" s="133"/>
-      <c r="F38" s="133"/>
-      <c r="G38" s="133"/>
-      <c r="H38" s="133"/>
-      <c r="I38" s="133"/>
-      <c r="J38" s="134"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="52"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="128"/>
-      <c r="B39" s="133"/>
-      <c r="C39" s="133"/>
-      <c r="D39" s="133"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="133"/>
-      <c r="I39" s="133"/>
-      <c r="J39" s="134"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="52"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="128"/>
-      <c r="B40" s="133"/>
-      <c r="C40" s="133"/>
-      <c r="D40" s="133"/>
-      <c r="E40" s="133"/>
-      <c r="F40" s="133"/>
-      <c r="G40" s="133"/>
-      <c r="H40" s="133"/>
-      <c r="I40" s="133"/>
-      <c r="J40" s="134"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="52"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="128"/>
-      <c r="B41" s="133"/>
-      <c r="C41" s="133"/>
-      <c r="D41" s="133"/>
-      <c r="E41" s="133"/>
-      <c r="F41" s="133"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="133"/>
-      <c r="I41" s="133"/>
-      <c r="J41" s="134"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="52"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="128"/>
-      <c r="B42" s="133"/>
-      <c r="C42" s="133"/>
-      <c r="D42" s="133"/>
-      <c r="E42" s="133"/>
-      <c r="F42" s="133"/>
-      <c r="G42" s="133"/>
-      <c r="H42" s="133"/>
-      <c r="I42" s="133"/>
-      <c r="J42" s="134"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="52"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="128"/>
-      <c r="B43" s="133"/>
-      <c r="C43" s="133"/>
-      <c r="D43" s="133"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="133"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="133"/>
-      <c r="I43" s="133"/>
-      <c r="J43" s="134"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="52"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="128"/>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
-      <c r="D44" s="133"/>
-      <c r="E44" s="133"/>
-      <c r="F44" s="133"/>
-      <c r="G44" s="133"/>
-      <c r="H44" s="133"/>
-      <c r="I44" s="133"/>
-      <c r="J44" s="134"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="52"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="128"/>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
-      <c r="D45" s="133"/>
-      <c r="E45" s="133"/>
-      <c r="F45" s="133"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="133"/>
-      <c r="I45" s="133"/>
-      <c r="J45" s="134"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="52"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="128"/>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
-      <c r="D46" s="133"/>
-      <c r="E46" s="133"/>
-      <c r="F46" s="133"/>
-      <c r="G46" s="133"/>
-      <c r="H46" s="133"/>
-      <c r="I46" s="133"/>
-      <c r="J46" s="134"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="52"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="129"/>
-      <c r="B47" s="137"/>
-      <c r="C47" s="137"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="137"/>
-      <c r="I47" s="137"/>
-      <c r="J47" s="138"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -9427,13 +9462,12 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9446,17 +9480,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -9663,6 +9686,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9673,6 +9707,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -9691,25 +9744,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
   <ds:schemaRefs>

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFBED51-A7C9-4ED5-A06E-97C6073FBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CE61B7-6581-44A5-BB21-0652E35E4B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="実績＆評価" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'別紙１）非機能要件'!$A$1:$I$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'別紙２）開発スケジュール予定＆実績'!$A$1:$AZ$23</definedName>
   </definedNames>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="178">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -661,19 +661,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>建物情報登録</t>
-    <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>被害写真登録</t>
     <rPh sb="0" eb="2">
       <t>ヒガイ</t>
@@ -700,45 +687,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>被害情報更新</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害情報編集</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害情報削除</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>被害状況分析</t>
     <rPh sb="0" eb="2">
       <t>ヒガイ</t>
@@ -1046,38 +994,6 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した被害情報を編集できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した被害情報を削除できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1835,6 +1751,56 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>LINE Loginを利用し、ログインを希望する利用者の認証を行う</t>
+    <rPh sb="11" eb="13">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キボウ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン利用者は自身の被害情報・写真・分析結果のみ参照・編集できるようにする</t>
+    <rPh sb="4" eb="7">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>①：概要
 本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録すると、AIが被害状況を分析し、その目安を提示することで、被害状況の把握や専門家への相談を支援するWebシステムである。
 また、分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報を提示する。登録した写真や分析結果は履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
@@ -1843,11 +1809,11 @@
 ・被害情報の登録(建物情報・質問回答)
 ・被害写真の撮影・登録
 ・AIによる被害状況分析
+・修理費用の目安提示
+・修理業者の情報提示
 ・LINEログイン
 ・被害状況分析履歴
 追加機能
-・修理費用の目安提示
-・修理業者の情報提示
 ・罹災証明書の申請案内
 ③：システム規模
 ・個人(事業者・建物管理者を含む)での利用を想定している
@@ -1894,70 +1860,262 @@
     <rPh sb="236" eb="238">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="285" eb="287">
+    <rPh sb="326" eb="328">
+      <t>キボ</t>
+    </rPh>
+    <rPh sb="343" eb="344">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="392" eb="394">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャットボット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不足情報追加質問</t>
+    <rPh sb="0" eb="2">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
       <t>ツイカ</t>
     </rPh>
-    <rPh sb="287" eb="289">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="331" eb="333">
-      <t>キボ</t>
-    </rPh>
-    <rPh sb="348" eb="349">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="397" eb="399">
-      <t>カンケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LINE Loginを利用し、ログインを希望する利用者の認証を行う</t>
+    <rPh sb="6" eb="8">
+      <t>シツモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI・分析系</t>
+  </si>
+  <si>
+    <t>追加回答登録</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加質問に対する回答を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイトウ</t>
+    </rPh>
     <rPh sb="11" eb="13">
-      <t>リヨウ</t>
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果に関する質問受付</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ウケツケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質問に対する回答表示</t>
+    <rPh sb="0" eb="2">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果に関する質問を入力できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIが質問内容と分析結果を基に回答を生成し表示できる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析に必要な情報が不足している場合、不足情報について追加質問できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フソク</t>
     </rPh>
     <rPh sb="20" eb="22">
-      <t>キボウ</t>
-    </rPh>
-    <rPh sb="24" eb="27">
-      <t>リヨウシャ</t>
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツイカ</t>
     </rPh>
     <rPh sb="28" eb="30">
-      <t>ニンショウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ログイン利用者は自身の被害情報・写真・分析結果のみ参照・編集できるようにする</t>
-    <rPh sb="4" eb="7">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
+      <t>シツモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報管理</t>
+  </si>
+  <si>
+    <t>建物情報管理</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="16" eb="18">
-      <t>シャシン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報一覧表示</t>
+  </si>
+  <si>
+    <t>建物情報詳細表示</t>
+  </si>
+  <si>
+    <t>建物情報編集</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報削除</t>
+  </si>
+  <si>
+    <t>登録した建物の一覧を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の詳細を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の情報を編集できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の情報を削除できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1969,7 +2127,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2042,8 +2200,15 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2068,6 +2233,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="67">
     <border>
@@ -2930,7 +3101,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3033,6 +3204,66 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3057,9 +3288,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3078,9 +3306,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3183,9 +3408,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3198,48 +3420,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3554,6 +3734,33 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3585,7 +3792,7 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>298825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>74706</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4437,1582 +4644,1582 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34">
+      <c r="A2" s="54">
         <v>1</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34">
+      <c r="A4" s="54">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
-      <c r="B5" s="53" t="s">
+      <c r="A5" s="55"/>
+      <c r="B5" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="74"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="88"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="73"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="91"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="73"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="91"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="73"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="91"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="73"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="91"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="35"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="73"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="91"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="73"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="73"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="91"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="73"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="91"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="73"/>
+      <c r="A17" s="58"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="91"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="38"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="73"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="91"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="38"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="73"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="91"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="73"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="91"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34">
+      <c r="A21" s="54">
         <v>3</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="60"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35"/>
-      <c r="B22" s="57" t="s">
+      <c r="A22" s="55"/>
+      <c r="B22" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="59"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="77"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="77"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="59"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="77"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="62"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="80"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
-      <c r="B26" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="64"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="82"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="64"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="82"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="35"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="64"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="82"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="64"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="82"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="64"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="82"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="64"/>
+      <c r="A31" s="55"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="82"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="64"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="82"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="64"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="82"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="63"/>
-      <c r="J34" s="64"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="82"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="64"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="82"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="35"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="64"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="82"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
-      <c r="B37" s="63"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="64"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="82"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="35"/>
-      <c r="B38" s="63"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="64"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="82"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35"/>
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="64"/>
+      <c r="A39" s="55"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="82"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35"/>
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="64"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="82"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
-      <c r="B41" s="63"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="64"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="82"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="35"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="64"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="82"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35"/>
-      <c r="B43" s="63"/>
-      <c r="C43" s="63"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
-      <c r="F43" s="63"/>
-      <c r="G43" s="63"/>
-      <c r="H43" s="63"/>
-      <c r="I43" s="63"/>
-      <c r="J43" s="64"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="82"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="63"/>
-      <c r="I44" s="63"/>
-      <c r="J44" s="64"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="82"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="35"/>
-      <c r="B45" s="63"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="63"/>
-      <c r="H45" s="63"/>
-      <c r="I45" s="63"/>
-      <c r="J45" s="64"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="82"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="63"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="63"/>
-      <c r="G46" s="63"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="63"/>
-      <c r="J46" s="64"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="82"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35"/>
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="63"/>
-      <c r="J47" s="64"/>
+      <c r="A47" s="55"/>
+      <c r="B47" s="81"/>
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="82"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="35"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="63"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="63"/>
-      <c r="I48" s="63"/>
-      <c r="J48" s="64"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="82"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="35"/>
-      <c r="B49" s="63"/>
-      <c r="C49" s="63"/>
-      <c r="D49" s="63"/>
-      <c r="E49" s="63"/>
-      <c r="F49" s="63"/>
-      <c r="G49" s="63"/>
-      <c r="H49" s="63"/>
-      <c r="I49" s="63"/>
-      <c r="J49" s="64"/>
+      <c r="A49" s="55"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="82"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="35"/>
-      <c r="B50" s="63"/>
-      <c r="C50" s="63"/>
-      <c r="D50" s="63"/>
-      <c r="E50" s="63"/>
-      <c r="F50" s="63"/>
-      <c r="G50" s="63"/>
-      <c r="H50" s="63"/>
-      <c r="I50" s="63"/>
-      <c r="J50" s="64"/>
+      <c r="A50" s="55"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="82"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="35"/>
-      <c r="B51" s="63"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="64"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="82"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="64"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="82"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="35"/>
-      <c r="B53" s="63"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="63"/>
-      <c r="G53" s="63"/>
-      <c r="H53" s="63"/>
-      <c r="I53" s="63"/>
-      <c r="J53" s="64"/>
+      <c r="A53" s="55"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="82"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35"/>
-      <c r="B54" s="63"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="63"/>
-      <c r="H54" s="63"/>
-      <c r="I54" s="63"/>
-      <c r="J54" s="64"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="82"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="35"/>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
-      <c r="I55" s="63"/>
-      <c r="J55" s="64"/>
+      <c r="A55" s="55"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="82"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="35"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="63"/>
-      <c r="I56" s="63"/>
-      <c r="J56" s="64"/>
+      <c r="A56" s="55"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="82"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="35"/>
-      <c r="B57" s="63"/>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="63"/>
-      <c r="I57" s="63"/>
-      <c r="J57" s="64"/>
+      <c r="A57" s="55"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="82"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="35"/>
-      <c r="B58" s="63"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="63"/>
-      <c r="F58" s="63"/>
-      <c r="G58" s="63"/>
-      <c r="H58" s="63"/>
-      <c r="I58" s="63"/>
-      <c r="J58" s="64"/>
+      <c r="A58" s="55"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="82"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="35"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="63"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="63"/>
-      <c r="I59" s="63"/>
-      <c r="J59" s="64"/>
+      <c r="A59" s="55"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="81"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="81"/>
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="82"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="35"/>
-      <c r="B60" s="63"/>
-      <c r="C60" s="63"/>
-      <c r="D60" s="63"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="63"/>
-      <c r="I60" s="63"/>
-      <c r="J60" s="64"/>
+      <c r="A60" s="55"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="81"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="81"/>
+      <c r="G60" s="81"/>
+      <c r="H60" s="81"/>
+      <c r="I60" s="81"/>
+      <c r="J60" s="82"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="35"/>
-      <c r="B61" s="63"/>
-      <c r="C61" s="63"/>
-      <c r="D61" s="63"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="64"/>
+      <c r="A61" s="55"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
+      <c r="I61" s="81"/>
+      <c r="J61" s="82"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
-      <c r="B62" s="65"/>
-      <c r="C62" s="65"/>
-      <c r="D62" s="65"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="65"/>
-      <c r="H62" s="65"/>
-      <c r="I62" s="65"/>
-      <c r="J62" s="66"/>
+      <c r="A62" s="56"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="83"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="83"/>
+      <c r="I62" s="83"/>
+      <c r="J62" s="84"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="34">
+      <c r="A63" s="54">
         <v>4</v>
       </c>
-      <c r="B63" s="41" t="s">
+      <c r="B63" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="74"/>
+      <c r="C63" s="61"/>
+      <c r="D63" s="61"/>
+      <c r="E63" s="61"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="92"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="35"/>
-      <c r="B64" s="37" t="s">
+      <c r="A64" s="55"/>
+      <c r="B64" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="51" t="s">
+      <c r="C64" s="57"/>
+      <c r="D64" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="51"/>
-      <c r="F64" s="51"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="52"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="70"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="35"/>
-      <c r="B65" s="37" t="s">
+      <c r="A65" s="55"/>
+      <c r="B65" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="52"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" s="69"/>
+      <c r="F65" s="69"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="69"/>
+      <c r="J65" s="70"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="35"/>
-      <c r="B66" s="37" t="s">
+      <c r="A66" s="55"/>
+      <c r="B66" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="E66" s="51"/>
-      <c r="F66" s="51"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="52"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="69"/>
+      <c r="I66" s="69"/>
+      <c r="J66" s="70"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="35"/>
-      <c r="B67" s="37" t="s">
+      <c r="A67" s="55"/>
+      <c r="B67" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="37"/>
-      <c r="D67" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="52"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="69"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="69"/>
+      <c r="I67" s="69"/>
+      <c r="J67" s="70"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="35"/>
-      <c r="B68" s="37" t="s">
+      <c r="A68" s="55"/>
+      <c r="B68" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="67"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="85"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="35"/>
-      <c r="B69" s="47" t="e" vm="1">
+      <c r="A69" s="55"/>
+      <c r="B69" s="66" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
-      <c r="J69" s="48"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="66"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="67"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="35"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
-      <c r="J70" s="48"/>
+      <c r="A70" s="55"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="66"/>
+      <c r="I70" s="66"/>
+      <c r="J70" s="67"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="35"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
-      <c r="J71" s="48"/>
+      <c r="A71" s="55"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="66"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="67"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="35"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="47"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="47"/>
-      <c r="G72" s="47"/>
-      <c r="H72" s="47"/>
-      <c r="I72" s="47"/>
-      <c r="J72" s="48"/>
+      <c r="A72" s="55"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="66"/>
+      <c r="E72" s="66"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="66"/>
+      <c r="H72" s="66"/>
+      <c r="I72" s="66"/>
+      <c r="J72" s="67"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="35"/>
-      <c r="B73" s="47"/>
-      <c r="C73" s="47"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="47"/>
-      <c r="G73" s="47"/>
-      <c r="H73" s="47"/>
-      <c r="I73" s="47"/>
-      <c r="J73" s="48"/>
+      <c r="A73" s="55"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="66"/>
+      <c r="D73" s="66"/>
+      <c r="E73" s="66"/>
+      <c r="F73" s="66"/>
+      <c r="G73" s="66"/>
+      <c r="H73" s="66"/>
+      <c r="I73" s="66"/>
+      <c r="J73" s="67"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="35"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="47"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="47"/>
-      <c r="I74" s="47"/>
-      <c r="J74" s="48"/>
+      <c r="A74" s="55"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="66"/>
+      <c r="F74" s="66"/>
+      <c r="G74" s="66"/>
+      <c r="H74" s="66"/>
+      <c r="I74" s="66"/>
+      <c r="J74" s="67"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="48"/>
+      <c r="A75" s="55"/>
+      <c r="B75" s="66"/>
+      <c r="C75" s="66"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="66"/>
+      <c r="F75" s="66"/>
+      <c r="G75" s="66"/>
+      <c r="H75" s="66"/>
+      <c r="I75" s="66"/>
+      <c r="J75" s="67"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
-      <c r="J76" s="48"/>
+      <c r="A76" s="55"/>
+      <c r="B76" s="66"/>
+      <c r="C76" s="66"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="66"/>
+      <c r="F76" s="66"/>
+      <c r="G76" s="66"/>
+      <c r="H76" s="66"/>
+      <c r="I76" s="66"/>
+      <c r="J76" s="67"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="35"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
-      <c r="D77" s="47"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="47"/>
-      <c r="G77" s="47"/>
-      <c r="H77" s="47"/>
-      <c r="I77" s="47"/>
-      <c r="J77" s="48"/>
+      <c r="A77" s="55"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="66"/>
+      <c r="F77" s="66"/>
+      <c r="G77" s="66"/>
+      <c r="H77" s="66"/>
+      <c r="I77" s="66"/>
+      <c r="J77" s="67"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="35"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="47"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="47"/>
-      <c r="I78" s="47"/>
-      <c r="J78" s="48"/>
+      <c r="A78" s="55"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="66"/>
+      <c r="D78" s="66"/>
+      <c r="E78" s="66"/>
+      <c r="F78" s="66"/>
+      <c r="G78" s="66"/>
+      <c r="H78" s="66"/>
+      <c r="I78" s="66"/>
+      <c r="J78" s="67"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="35"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="48"/>
+      <c r="A79" s="55"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="66"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="66"/>
+      <c r="I79" s="66"/>
+      <c r="J79" s="67"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="35"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
-      <c r="J80" s="48"/>
+      <c r="A80" s="55"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="66"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="66"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="66"/>
+      <c r="H80" s="66"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="67"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="35"/>
-      <c r="B81" s="47"/>
-      <c r="C81" s="47"/>
-      <c r="D81" s="47"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="47"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="47"/>
-      <c r="I81" s="47"/>
-      <c r="J81" s="48"/>
+      <c r="A81" s="55"/>
+      <c r="B81" s="66"/>
+      <c r="C81" s="66"/>
+      <c r="D81" s="66"/>
+      <c r="E81" s="66"/>
+      <c r="F81" s="66"/>
+      <c r="G81" s="66"/>
+      <c r="H81" s="66"/>
+      <c r="I81" s="66"/>
+      <c r="J81" s="67"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="35"/>
-      <c r="B82" s="47"/>
-      <c r="C82" s="47"/>
-      <c r="D82" s="47"/>
-      <c r="E82" s="47"/>
-      <c r="F82" s="47"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="47"/>
-      <c r="I82" s="47"/>
-      <c r="J82" s="48"/>
+      <c r="A82" s="55"/>
+      <c r="B82" s="66"/>
+      <c r="C82" s="66"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="66"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="66"/>
+      <c r="H82" s="66"/>
+      <c r="I82" s="66"/>
+      <c r="J82" s="67"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="35"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="47"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47"/>
-      <c r="J83" s="48"/>
+      <c r="A83" s="55"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="66"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="66"/>
+      <c r="H83" s="66"/>
+      <c r="I83" s="66"/>
+      <c r="J83" s="67"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="35"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="47"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="48"/>
+      <c r="A84" s="55"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="66"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="66"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="66"/>
+      <c r="H84" s="66"/>
+      <c r="I84" s="66"/>
+      <c r="J84" s="67"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="35"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="48"/>
+      <c r="A85" s="55"/>
+      <c r="B85" s="66"/>
+      <c r="C85" s="66"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="66"/>
+      <c r="I85" s="66"/>
+      <c r="J85" s="67"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="38"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="49"/>
-      <c r="J86" s="50"/>
+      <c r="A86" s="58"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="68"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="34">
+      <c r="A87" s="54">
         <v>5</v>
       </c>
-      <c r="B87" s="41" t="s">
+      <c r="B87" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="41"/>
-      <c r="J87" s="74"/>
+      <c r="C87" s="61"/>
+      <c r="D87" s="61"/>
+      <c r="E87" s="61"/>
+      <c r="F87" s="61"/>
+      <c r="G87" s="61"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="61"/>
+      <c r="J87" s="92"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="35"/>
-      <c r="B88" s="84" t="s">
+      <c r="A88" s="55"/>
+      <c r="B88" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="84"/>
-      <c r="D88" s="84"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
-      <c r="I88" s="84"/>
-      <c r="J88" s="85"/>
+      <c r="C88" s="35"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="35"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="102"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="34">
+      <c r="A89" s="54">
         <v>6</v>
       </c>
-      <c r="B89" s="39" t="s">
+      <c r="B89" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="39"/>
-      <c r="D89" s="39"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39"/>
-      <c r="G89" s="39"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="40"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="59"/>
+      <c r="E89" s="59"/>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="59"/>
+      <c r="J89" s="60"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="83"/>
-      <c r="B90" s="53" t="s">
+      <c r="A90" s="101"/>
+      <c r="B90" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="53"/>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="53"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="54"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
+      <c r="F90" s="71"/>
+      <c r="G90" s="71"/>
+      <c r="H90" s="71"/>
+      <c r="I90" s="71"/>
+      <c r="J90" s="72"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="83"/>
-      <c r="B91" s="53"/>
-      <c r="C91" s="53"/>
-      <c r="D91" s="53"/>
-      <c r="E91" s="53"/>
-      <c r="F91" s="53"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="53"/>
-      <c r="I91" s="53"/>
-      <c r="J91" s="54"/>
+      <c r="A91" s="101"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="71"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="71"/>
+      <c r="G91" s="71"/>
+      <c r="H91" s="71"/>
+      <c r="I91" s="71"/>
+      <c r="J91" s="72"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="83"/>
-      <c r="B92" s="55"/>
-      <c r="C92" s="55"/>
-      <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="55"/>
-      <c r="I92" s="55"/>
-      <c r="J92" s="56"/>
+      <c r="A92" s="101"/>
+      <c r="B92" s="73"/>
+      <c r="C92" s="73"/>
+      <c r="D92" s="73"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="73"/>
+      <c r="G92" s="73"/>
+      <c r="H92" s="73"/>
+      <c r="I92" s="73"/>
+      <c r="J92" s="74"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="35"/>
-      <c r="B93" s="68" t="s">
-        <v>152</v>
-      </c>
-      <c r="C93" s="69"/>
-      <c r="D93" s="69"/>
-      <c r="E93" s="69"/>
-      <c r="F93" s="69"/>
-      <c r="G93" s="69"/>
-      <c r="H93" s="69"/>
-      <c r="I93" s="69"/>
-      <c r="J93" s="70"/>
+      <c r="A93" s="55"/>
+      <c r="B93" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
+      <c r="J93" s="88"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="35"/>
-      <c r="B94" s="71"/>
-      <c r="C94" s="72"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
-      <c r="H94" s="72"/>
-      <c r="I94" s="72"/>
-      <c r="J94" s="73"/>
+      <c r="A94" s="55"/>
+      <c r="B94" s="89"/>
+      <c r="C94" s="90"/>
+      <c r="D94" s="90"/>
+      <c r="E94" s="90"/>
+      <c r="F94" s="90"/>
+      <c r="G94" s="90"/>
+      <c r="H94" s="90"/>
+      <c r="I94" s="90"/>
+      <c r="J94" s="91"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="35"/>
-      <c r="B95" s="71"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
-      <c r="F95" s="72"/>
-      <c r="G95" s="72"/>
-      <c r="H95" s="72"/>
-      <c r="I95" s="72"/>
-      <c r="J95" s="73"/>
+      <c r="A95" s="55"/>
+      <c r="B95" s="89"/>
+      <c r="C95" s="90"/>
+      <c r="D95" s="90"/>
+      <c r="E95" s="90"/>
+      <c r="F95" s="90"/>
+      <c r="G95" s="90"/>
+      <c r="H95" s="90"/>
+      <c r="I95" s="90"/>
+      <c r="J95" s="91"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="35"/>
-      <c r="B96" s="71"/>
-      <c r="C96" s="72"/>
-      <c r="D96" s="72"/>
-      <c r="E96" s="72"/>
-      <c r="F96" s="72"/>
-      <c r="G96" s="72"/>
-      <c r="H96" s="72"/>
-      <c r="I96" s="72"/>
-      <c r="J96" s="73"/>
+      <c r="A96" s="55"/>
+      <c r="B96" s="89"/>
+      <c r="C96" s="90"/>
+      <c r="D96" s="90"/>
+      <c r="E96" s="90"/>
+      <c r="F96" s="90"/>
+      <c r="G96" s="90"/>
+      <c r="H96" s="90"/>
+      <c r="I96" s="90"/>
+      <c r="J96" s="91"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="35"/>
-      <c r="B97" s="71"/>
-      <c r="C97" s="72"/>
-      <c r="D97" s="72"/>
-      <c r="E97" s="72"/>
-      <c r="F97" s="72"/>
-      <c r="G97" s="72"/>
-      <c r="H97" s="72"/>
-      <c r="I97" s="72"/>
-      <c r="J97" s="73"/>
+      <c r="A97" s="55"/>
+      <c r="B97" s="89"/>
+      <c r="C97" s="90"/>
+      <c r="D97" s="90"/>
+      <c r="E97" s="90"/>
+      <c r="F97" s="90"/>
+      <c r="G97" s="90"/>
+      <c r="H97" s="90"/>
+      <c r="I97" s="90"/>
+      <c r="J97" s="91"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="35"/>
-      <c r="B98" s="71"/>
-      <c r="C98" s="72"/>
-      <c r="D98" s="72"/>
-      <c r="E98" s="72"/>
-      <c r="F98" s="72"/>
-      <c r="G98" s="72"/>
-      <c r="H98" s="72"/>
-      <c r="I98" s="72"/>
-      <c r="J98" s="73"/>
+      <c r="A98" s="55"/>
+      <c r="B98" s="89"/>
+      <c r="C98" s="90"/>
+      <c r="D98" s="90"/>
+      <c r="E98" s="90"/>
+      <c r="F98" s="90"/>
+      <c r="G98" s="90"/>
+      <c r="H98" s="90"/>
+      <c r="I98" s="90"/>
+      <c r="J98" s="91"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="35"/>
-      <c r="B99" s="71"/>
-      <c r="C99" s="72"/>
-      <c r="D99" s="72"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="72"/>
-      <c r="G99" s="72"/>
-      <c r="H99" s="72"/>
-      <c r="I99" s="72"/>
-      <c r="J99" s="73"/>
+      <c r="A99" s="55"/>
+      <c r="B99" s="89"/>
+      <c r="C99" s="90"/>
+      <c r="D99" s="90"/>
+      <c r="E99" s="90"/>
+      <c r="F99" s="90"/>
+      <c r="G99" s="90"/>
+      <c r="H99" s="90"/>
+      <c r="I99" s="90"/>
+      <c r="J99" s="91"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="35"/>
-      <c r="B100" s="71"/>
-      <c r="C100" s="72"/>
-      <c r="D100" s="72"/>
-      <c r="E100" s="72"/>
-      <c r="F100" s="72"/>
-      <c r="G100" s="72"/>
-      <c r="H100" s="72"/>
-      <c r="I100" s="72"/>
-      <c r="J100" s="73"/>
+      <c r="A100" s="55"/>
+      <c r="B100" s="89"/>
+      <c r="C100" s="90"/>
+      <c r="D100" s="90"/>
+      <c r="E100" s="90"/>
+      <c r="F100" s="90"/>
+      <c r="G100" s="90"/>
+      <c r="H100" s="90"/>
+      <c r="I100" s="90"/>
+      <c r="J100" s="91"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="35"/>
-      <c r="B101" s="71"/>
-      <c r="C101" s="72"/>
-      <c r="D101" s="72"/>
-      <c r="E101" s="72"/>
-      <c r="F101" s="72"/>
-      <c r="G101" s="72"/>
-      <c r="H101" s="72"/>
-      <c r="I101" s="72"/>
-      <c r="J101" s="73"/>
+      <c r="A101" s="55"/>
+      <c r="B101" s="89"/>
+      <c r="C101" s="90"/>
+      <c r="D101" s="90"/>
+      <c r="E101" s="90"/>
+      <c r="F101" s="90"/>
+      <c r="G101" s="90"/>
+      <c r="H101" s="90"/>
+      <c r="I101" s="90"/>
+      <c r="J101" s="91"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="35"/>
-      <c r="B102" s="71"/>
-      <c r="C102" s="72"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
-      <c r="G102" s="72"/>
-      <c r="H102" s="72"/>
-      <c r="I102" s="72"/>
-      <c r="J102" s="73"/>
+      <c r="A102" s="55"/>
+      <c r="B102" s="89"/>
+      <c r="C102" s="90"/>
+      <c r="D102" s="90"/>
+      <c r="E102" s="90"/>
+      <c r="F102" s="90"/>
+      <c r="G102" s="90"/>
+      <c r="H102" s="90"/>
+      <c r="I102" s="90"/>
+      <c r="J102" s="91"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="35"/>
-      <c r="B103" s="71"/>
-      <c r="C103" s="72"/>
-      <c r="D103" s="72"/>
-      <c r="E103" s="72"/>
-      <c r="F103" s="72"/>
-      <c r="G103" s="72"/>
-      <c r="H103" s="72"/>
-      <c r="I103" s="72"/>
-      <c r="J103" s="73"/>
+      <c r="A103" s="55"/>
+      <c r="B103" s="89"/>
+      <c r="C103" s="90"/>
+      <c r="D103" s="90"/>
+      <c r="E103" s="90"/>
+      <c r="F103" s="90"/>
+      <c r="G103" s="90"/>
+      <c r="H103" s="90"/>
+      <c r="I103" s="90"/>
+      <c r="J103" s="91"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="35"/>
-      <c r="B104" s="71"/>
-      <c r="C104" s="72"/>
-      <c r="D104" s="72"/>
-      <c r="E104" s="72"/>
-      <c r="F104" s="72"/>
-      <c r="G104" s="72"/>
-      <c r="H104" s="72"/>
-      <c r="I104" s="72"/>
-      <c r="J104" s="73"/>
+      <c r="A104" s="55"/>
+      <c r="B104" s="89"/>
+      <c r="C104" s="90"/>
+      <c r="D104" s="90"/>
+      <c r="E104" s="90"/>
+      <c r="F104" s="90"/>
+      <c r="G104" s="90"/>
+      <c r="H104" s="90"/>
+      <c r="I104" s="90"/>
+      <c r="J104" s="91"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="35"/>
-      <c r="B105" s="71"/>
-      <c r="C105" s="72"/>
-      <c r="D105" s="72"/>
-      <c r="E105" s="72"/>
-      <c r="F105" s="72"/>
-      <c r="G105" s="72"/>
-      <c r="H105" s="72"/>
-      <c r="I105" s="72"/>
-      <c r="J105" s="73"/>
+      <c r="A105" s="55"/>
+      <c r="B105" s="89"/>
+      <c r="C105" s="90"/>
+      <c r="D105" s="90"/>
+      <c r="E105" s="90"/>
+      <c r="F105" s="90"/>
+      <c r="G105" s="90"/>
+      <c r="H105" s="90"/>
+      <c r="I105" s="90"/>
+      <c r="J105" s="91"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="35"/>
-      <c r="B106" s="71"/>
-      <c r="C106" s="72"/>
-      <c r="D106" s="72"/>
-      <c r="E106" s="72"/>
-      <c r="F106" s="72"/>
-      <c r="G106" s="72"/>
-      <c r="H106" s="72"/>
-      <c r="I106" s="72"/>
-      <c r="J106" s="73"/>
+      <c r="A106" s="55"/>
+      <c r="B106" s="89"/>
+      <c r="C106" s="90"/>
+      <c r="D106" s="90"/>
+      <c r="E106" s="90"/>
+      <c r="F106" s="90"/>
+      <c r="G106" s="90"/>
+      <c r="H106" s="90"/>
+      <c r="I106" s="90"/>
+      <c r="J106" s="91"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="36"/>
-      <c r="B107" s="86"/>
-      <c r="C107" s="87"/>
-      <c r="D107" s="87"/>
-      <c r="E107" s="87"/>
-      <c r="F107" s="87"/>
-      <c r="G107" s="87"/>
-      <c r="H107" s="87"/>
-      <c r="I107" s="87"/>
-      <c r="J107" s="88"/>
+      <c r="A107" s="56"/>
+      <c r="B107" s="103"/>
+      <c r="C107" s="104"/>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="104"/>
+      <c r="G107" s="104"/>
+      <c r="H107" s="104"/>
+      <c r="I107" s="104"/>
+      <c r="J107" s="105"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="34">
+      <c r="A108" s="54">
         <v>7</v>
       </c>
-      <c r="B108" s="41" t="s">
+      <c r="B108" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="41"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="41"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="41"/>
-      <c r="H108" s="41"/>
-      <c r="I108" s="41"/>
-      <c r="J108" s="74"/>
+      <c r="C108" s="61"/>
+      <c r="D108" s="61"/>
+      <c r="E108" s="61"/>
+      <c r="F108" s="61"/>
+      <c r="G108" s="61"/>
+      <c r="H108" s="61"/>
+      <c r="I108" s="61"/>
+      <c r="J108" s="92"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="38"/>
-      <c r="B109" s="81" t="s">
+      <c r="A109" s="58"/>
+      <c r="B109" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="81"/>
-      <c r="D109" s="81"/>
-      <c r="E109" s="81"/>
-      <c r="F109" s="81"/>
-      <c r="G109" s="81"/>
-      <c r="H109" s="81"/>
-      <c r="I109" s="81"/>
-      <c r="J109" s="82"/>
+      <c r="C109" s="99"/>
+      <c r="D109" s="99"/>
+      <c r="E109" s="99"/>
+      <c r="F109" s="99"/>
+      <c r="G109" s="99"/>
+      <c r="H109" s="99"/>
+      <c r="I109" s="99"/>
+      <c r="J109" s="100"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="34">
+      <c r="A110" s="54">
         <v>8</v>
       </c>
-      <c r="B110" s="41" t="s">
+      <c r="B110" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="41"/>
-      <c r="E110" s="41"/>
-      <c r="F110" s="41"/>
-      <c r="G110" s="41"/>
-      <c r="H110" s="41"/>
-      <c r="I110" s="41"/>
-      <c r="J110" s="74"/>
+      <c r="C110" s="61"/>
+      <c r="D110" s="61"/>
+      <c r="E110" s="61"/>
+      <c r="F110" s="61"/>
+      <c r="G110" s="61"/>
+      <c r="H110" s="61"/>
+      <c r="I110" s="61"/>
+      <c r="J110" s="92"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="35"/>
-      <c r="B111" s="76" t="s">
-        <v>153</v>
-      </c>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="51"/>
-      <c r="G111" s="51"/>
-      <c r="H111" s="51"/>
-      <c r="I111" s="51"/>
-      <c r="J111" s="52"/>
+      <c r="A111" s="55"/>
+      <c r="B111" s="94" t="s">
+        <v>147</v>
+      </c>
+      <c r="C111" s="69"/>
+      <c r="D111" s="69"/>
+      <c r="E111" s="69"/>
+      <c r="F111" s="69"/>
+      <c r="G111" s="69"/>
+      <c r="H111" s="69"/>
+      <c r="I111" s="69"/>
+      <c r="J111" s="70"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="35"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="51"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
-      <c r="J112" s="52"/>
+      <c r="A112" s="55"/>
+      <c r="B112" s="69"/>
+      <c r="C112" s="69"/>
+      <c r="D112" s="69"/>
+      <c r="E112" s="69"/>
+      <c r="F112" s="69"/>
+      <c r="G112" s="69"/>
+      <c r="H112" s="69"/>
+      <c r="I112" s="69"/>
+      <c r="J112" s="70"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="35"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="51"/>
-      <c r="G113" s="51"/>
-      <c r="H113" s="51"/>
-      <c r="I113" s="51"/>
-      <c r="J113" s="52"/>
+      <c r="A113" s="55"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="69"/>
+      <c r="D113" s="69"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="69"/>
+      <c r="H113" s="69"/>
+      <c r="I113" s="69"/>
+      <c r="J113" s="70"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="35"/>
-      <c r="B114" s="51"/>
-      <c r="C114" s="51"/>
-      <c r="D114" s="51"/>
-      <c r="E114" s="51"/>
-      <c r="F114" s="51"/>
-      <c r="G114" s="51"/>
-      <c r="H114" s="51"/>
-      <c r="I114" s="51"/>
-      <c r="J114" s="52"/>
+      <c r="A114" s="55"/>
+      <c r="B114" s="69"/>
+      <c r="C114" s="69"/>
+      <c r="D114" s="69"/>
+      <c r="E114" s="69"/>
+      <c r="F114" s="69"/>
+      <c r="G114" s="69"/>
+      <c r="H114" s="69"/>
+      <c r="I114" s="69"/>
+      <c r="J114" s="70"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="35"/>
-      <c r="B115" s="51"/>
-      <c r="C115" s="51"/>
-      <c r="D115" s="51"/>
-      <c r="E115" s="51"/>
-      <c r="F115" s="51"/>
-      <c r="G115" s="51"/>
-      <c r="H115" s="51"/>
-      <c r="I115" s="51"/>
-      <c r="J115" s="52"/>
+      <c r="A115" s="55"/>
+      <c r="B115" s="69"/>
+      <c r="C115" s="69"/>
+      <c r="D115" s="69"/>
+      <c r="E115" s="69"/>
+      <c r="F115" s="69"/>
+      <c r="G115" s="69"/>
+      <c r="H115" s="69"/>
+      <c r="I115" s="69"/>
+      <c r="J115" s="70"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="35"/>
-      <c r="B116" s="51"/>
-      <c r="C116" s="51"/>
-      <c r="D116" s="51"/>
-      <c r="E116" s="51"/>
-      <c r="F116" s="51"/>
-      <c r="G116" s="51"/>
-      <c r="H116" s="51"/>
-      <c r="I116" s="51"/>
-      <c r="J116" s="52"/>
+      <c r="A116" s="55"/>
+      <c r="B116" s="69"/>
+      <c r="C116" s="69"/>
+      <c r="D116" s="69"/>
+      <c r="E116" s="69"/>
+      <c r="F116" s="69"/>
+      <c r="G116" s="69"/>
+      <c r="H116" s="69"/>
+      <c r="I116" s="69"/>
+      <c r="J116" s="70"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="35"/>
-      <c r="B117" s="77" t="s">
+      <c r="A117" s="55"/>
+      <c r="B117" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="77"/>
-      <c r="D117" s="77"/>
-      <c r="E117" s="77"/>
-      <c r="F117" s="77"/>
-      <c r="G117" s="77"/>
-      <c r="H117" s="77"/>
-      <c r="I117" s="77"/>
-      <c r="J117" s="78"/>
+      <c r="C117" s="95"/>
+      <c r="D117" s="95"/>
+      <c r="E117" s="95"/>
+      <c r="F117" s="95"/>
+      <c r="G117" s="95"/>
+      <c r="H117" s="95"/>
+      <c r="I117" s="95"/>
+      <c r="J117" s="96"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="35"/>
-      <c r="B118" s="76" t="s">
-        <v>154</v>
-      </c>
-      <c r="C118" s="51"/>
-      <c r="D118" s="51"/>
-      <c r="E118" s="51"/>
-      <c r="F118" s="51"/>
-      <c r="G118" s="51"/>
-      <c r="H118" s="51"/>
-      <c r="I118" s="51"/>
-      <c r="J118" s="52"/>
+      <c r="A118" s="55"/>
+      <c r="B118" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="C118" s="69"/>
+      <c r="D118" s="69"/>
+      <c r="E118" s="69"/>
+      <c r="F118" s="69"/>
+      <c r="G118" s="69"/>
+      <c r="H118" s="69"/>
+      <c r="I118" s="69"/>
+      <c r="J118" s="70"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="35"/>
-      <c r="B119" s="51"/>
-      <c r="C119" s="51"/>
-      <c r="D119" s="51"/>
-      <c r="E119" s="51"/>
-      <c r="F119" s="51"/>
-      <c r="G119" s="51"/>
-      <c r="H119" s="51"/>
-      <c r="I119" s="51"/>
-      <c r="J119" s="52"/>
+      <c r="A119" s="55"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="69"/>
+      <c r="D119" s="69"/>
+      <c r="E119" s="69"/>
+      <c r="F119" s="69"/>
+      <c r="G119" s="69"/>
+      <c r="H119" s="69"/>
+      <c r="I119" s="69"/>
+      <c r="J119" s="70"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="35"/>
-      <c r="B120" s="51"/>
-      <c r="C120" s="51"/>
-      <c r="D120" s="51"/>
-      <c r="E120" s="51"/>
-      <c r="F120" s="51"/>
-      <c r="G120" s="51"/>
-      <c r="H120" s="51"/>
-      <c r="I120" s="51"/>
-      <c r="J120" s="52"/>
+      <c r="A120" s="55"/>
+      <c r="B120" s="69"/>
+      <c r="C120" s="69"/>
+      <c r="D120" s="69"/>
+      <c r="E120" s="69"/>
+      <c r="F120" s="69"/>
+      <c r="G120" s="69"/>
+      <c r="H120" s="69"/>
+      <c r="I120" s="69"/>
+      <c r="J120" s="70"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="35"/>
-      <c r="B121" s="51"/>
-      <c r="C121" s="51"/>
-      <c r="D121" s="51"/>
-      <c r="E121" s="51"/>
-      <c r="F121" s="51"/>
-      <c r="G121" s="51"/>
-      <c r="H121" s="51"/>
-      <c r="I121" s="51"/>
-      <c r="J121" s="52"/>
+      <c r="A121" s="55"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="69"/>
+      <c r="D121" s="69"/>
+      <c r="E121" s="69"/>
+      <c r="F121" s="69"/>
+      <c r="G121" s="69"/>
+      <c r="H121" s="69"/>
+      <c r="I121" s="69"/>
+      <c r="J121" s="70"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="35"/>
-      <c r="B122" s="51"/>
-      <c r="C122" s="51"/>
-      <c r="D122" s="51"/>
-      <c r="E122" s="51"/>
-      <c r="F122" s="51"/>
-      <c r="G122" s="51"/>
-      <c r="H122" s="51"/>
-      <c r="I122" s="51"/>
-      <c r="J122" s="52"/>
+      <c r="A122" s="55"/>
+      <c r="B122" s="69"/>
+      <c r="C122" s="69"/>
+      <c r="D122" s="69"/>
+      <c r="E122" s="69"/>
+      <c r="F122" s="69"/>
+      <c r="G122" s="69"/>
+      <c r="H122" s="69"/>
+      <c r="I122" s="69"/>
+      <c r="J122" s="70"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="35"/>
-      <c r="B123" s="51"/>
-      <c r="C123" s="51"/>
-      <c r="D123" s="51"/>
-      <c r="E123" s="51"/>
-      <c r="F123" s="51"/>
-      <c r="G123" s="51"/>
-      <c r="H123" s="51"/>
-      <c r="I123" s="51"/>
-      <c r="J123" s="52"/>
+      <c r="A123" s="55"/>
+      <c r="B123" s="69"/>
+      <c r="C123" s="69"/>
+      <c r="D123" s="69"/>
+      <c r="E123" s="69"/>
+      <c r="F123" s="69"/>
+      <c r="G123" s="69"/>
+      <c r="H123" s="69"/>
+      <c r="I123" s="69"/>
+      <c r="J123" s="70"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="35"/>
-      <c r="B124" s="51"/>
-      <c r="C124" s="51"/>
-      <c r="D124" s="51"/>
-      <c r="E124" s="51"/>
-      <c r="F124" s="51"/>
-      <c r="G124" s="51"/>
-      <c r="H124" s="51"/>
-      <c r="I124" s="51"/>
-      <c r="J124" s="52"/>
+      <c r="A124" s="55"/>
+      <c r="B124" s="69"/>
+      <c r="C124" s="69"/>
+      <c r="D124" s="69"/>
+      <c r="E124" s="69"/>
+      <c r="F124" s="69"/>
+      <c r="G124" s="69"/>
+      <c r="H124" s="69"/>
+      <c r="I124" s="69"/>
+      <c r="J124" s="70"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="36"/>
-      <c r="B125" s="79"/>
-      <c r="C125" s="79"/>
-      <c r="D125" s="79"/>
-      <c r="E125" s="79"/>
-      <c r="F125" s="79"/>
-      <c r="G125" s="79"/>
-      <c r="H125" s="79"/>
-      <c r="I125" s="79"/>
-      <c r="J125" s="80"/>
+      <c r="A125" s="56"/>
+      <c r="B125" s="97"/>
+      <c r="C125" s="97"/>
+      <c r="D125" s="97"/>
+      <c r="E125" s="97"/>
+      <c r="F125" s="97"/>
+      <c r="G125" s="97"/>
+      <c r="H125" s="97"/>
+      <c r="I125" s="97"/>
+      <c r="J125" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -6071,83 +6278,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
     <col min="2" max="3" width="20.69921875" style="3" customWidth="1"/>
     <col min="4" max="4" width="25.69921875" style="3" customWidth="1"/>
-    <col min="5" max="8" width="16.69921875" style="3" customWidth="1"/>
+    <col min="5" max="6" width="16.69921875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.8984375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.296875" style="3" customWidth="1"/>
     <col min="10" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="84"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="F6" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="95" t="s">
+      <c r="G6" s="39"/>
+      <c r="H6" s="42" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="89"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6157,521 +6366,581 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="89"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="96"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>1</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="27" t="s">
+      <c r="A8" s="211"/>
+      <c r="B8" s="217" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="212" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="213" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="213" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="215" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="98"/>
-      <c r="H8" s="27"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="214"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>2</v>
-      </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="97" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="98"/>
-      <c r="H9" s="27"/>
+      <c r="A9" s="211"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="217" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="213" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="213" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="215" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="216"/>
+      <c r="H9" s="214"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>3</v>
-      </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="98"/>
-      <c r="H10" s="27"/>
+      <c r="A10" s="211"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
+      <c r="D10" s="213" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="213" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="215" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="216"/>
+      <c r="H10" s="214"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>4</v>
-      </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="27"/>
+      <c r="A11" s="211"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="218"/>
+      <c r="D11" s="213" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="213" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="215" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="216"/>
+      <c r="H11" s="214"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>5</v>
-      </c>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="98"/>
-      <c r="H12" s="27"/>
+      <c r="A12" s="211"/>
+      <c r="B12" s="219"/>
+      <c r="C12" s="219"/>
+      <c r="D12" s="213" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="213" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="215" t="s">
+        <v>177</v>
+      </c>
+      <c r="G12" s="216"/>
+      <c r="H12" s="214"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>6</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>79</v>
+        <v>2</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>71</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E13" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="F13" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="98"/>
+      <c r="G13" s="45"/>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>7</v>
-      </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="27" t="s">
-        <v>81</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="27" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E14" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="98"/>
+      <c r="G14" s="45"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>8</v>
-      </c>
-      <c r="B15" s="102"/>
-      <c r="C15" s="49" t="s">
-        <v>83</v>
+        <v>6</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>75</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="98"/>
+        <v>94</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="45"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>9</v>
-      </c>
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
+        <v>7</v>
+      </c>
+      <c r="B16" s="50"/>
+      <c r="C16" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="D16" s="27" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="97" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="98"/>
+        <v>95</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="45"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>10</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>87</v>
+        <v>8</v>
+      </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="48" t="s">
+        <v>79</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="98"/>
+        <v>95</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="45"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>11</v>
-      </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="27" t="s">
-        <v>89</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B18" s="50"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="27" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="97" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="98"/>
+        <v>95</v>
+      </c>
+      <c r="F18" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="45"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>12</v>
-      </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="27" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="B19" s="50"/>
+      <c r="C19" s="53" t="s">
+        <v>156</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="97" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="98"/>
+        <v>158</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="47"/>
       <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>13</v>
-      </c>
-      <c r="B20" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="97" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="98"/>
+      <c r="F20" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="45"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>14</v>
-      </c>
-      <c r="B21" s="99"/>
-      <c r="C21" s="99"/>
+        <v>12</v>
+      </c>
+      <c r="B21" s="50"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="27" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="97" t="s">
-        <v>112</v>
-      </c>
-      <c r="G21" s="98"/>
+        <v>93</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="47"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <v>15</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="98"/>
+        <v>13</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="47"/>
       <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>16</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="98"/>
+        <v>14</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="45"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>17</v>
-      </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="97"/>
-      <c r="G24" s="98"/>
+        <v>15</v>
+      </c>
+      <c r="B24" s="52"/>
+      <c r="C24" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="45"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>18</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="98"/>
+        <v>16</v>
+      </c>
+      <c r="B25" s="49"/>
+      <c r="C25" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="45"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>19</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="98"/>
+        <v>17</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26" s="45"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
-        <v>20</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="98"/>
+        <v>18</v>
+      </c>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="45"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="98"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="45"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="98"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="45"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="98"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="45"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="98"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="45"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="98"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="45"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="98"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="45"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="98"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="45"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="98"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="45"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="97"/>
-      <c r="G36" s="98"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="45"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="98"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="45"/>
       <c r="H37" s="27"/>
     </row>
+    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>29</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="27"/>
+    </row>
+    <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>30</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
+  <mergeCells count="50">
     <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B15:B22"/>
+    <mergeCell ref="C19:C22"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F38:G38"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:A7"/>
@@ -6706,458 +6975,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="109"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="112"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="95" t="s">
+      <c r="C5" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="89" t="s">
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="36" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89"/>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="89"/>
+      <c r="A6" s="36"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="36"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="106" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
+        <v>109</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="106"/>
+      <c r="B8" s="109"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="106"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="104"/>
+      <c r="B10" s="107"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="103" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
+      <c r="C11" s="106" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="106"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="106"/>
+      <c r="B13" s="109"/>
       <c r="C13" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="76" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
+        <v>114</v>
+      </c>
+      <c r="D13" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="107"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="108" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
+        <v>116</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="106"/>
+      <c r="B16" s="109"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="106"/>
+      <c r="B17" s="109"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="104"/>
+      <c r="B18" s="107"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="108" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
+        <v>118</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="106"/>
+      <c r="B20" s="109"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="106"/>
+      <c r="B21" s="109"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="104"/>
+      <c r="B22" s="107"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="105" t="s">
+      <c r="B23" s="108" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
+        <v>120</v>
+      </c>
+      <c r="D23" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="110"/>
+      <c r="B24" s="113"/>
       <c r="C24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
+        <v>122</v>
+      </c>
+      <c r="D24" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="110"/>
+      <c r="B25" s="113"/>
       <c r="C25" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
+        <v>123</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="110"/>
+      <c r="B26" s="113"/>
       <c r="C26" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+        <v>124</v>
+      </c>
+      <c r="D26" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="94"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="111"/>
+      <c r="B27" s="114"/>
       <c r="C27" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="112" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="113"/>
-      <c r="F27" s="113"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="114"/>
+        <v>126</v>
+      </c>
+      <c r="D27" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="117"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="105" t="s">
+      <c r="B28" s="108" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
+        <v>127</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="106"/>
+      <c r="B29" s="109"/>
       <c r="C29" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
+        <v>129</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="106"/>
+      <c r="B30" s="109"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="104"/>
+      <c r="B31" s="107"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7166,11 +7435,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7179,11 +7448,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7192,11 +7461,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7205,11 +7474,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7218,11 +7487,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7231,11 +7500,11 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
@@ -7309,23 +7578,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="203"/>
-      <c r="P1" s="203"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
+      <c r="O1" s="206"/>
+      <c r="P1" s="206"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7342,141 +7611,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="155" t="s">
-        <v>158</v>
-      </c>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155"/>
-      <c r="X2" s="155"/>
-      <c r="Y2" s="155"/>
-      <c r="Z2" s="155"/>
-      <c r="AA2" s="155"/>
-      <c r="AB2" s="155"/>
-      <c r="AC2" s="155"/>
-      <c r="AD2" s="155"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="158" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="158"/>
+      <c r="S2" s="158"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="158"/>
+      <c r="V2" s="158"/>
+      <c r="W2" s="158"/>
+      <c r="X2" s="158"/>
+      <c r="Y2" s="158"/>
+      <c r="Z2" s="158"/>
+      <c r="AA2" s="158"/>
+      <c r="AB2" s="158"/>
+      <c r="AC2" s="158"/>
+      <c r="AD2" s="158"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="162" t="s">
+      <c r="B4" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="149"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149" t="s">
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
+      <c r="H4" s="152"/>
+      <c r="I4" s="152"/>
+      <c r="J4" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="149"/>
-      <c r="O4" s="149"/>
-      <c r="P4" s="149"/>
-      <c r="Q4" s="156" t="s">
+      <c r="K4" s="152"/>
+      <c r="L4" s="152"/>
+      <c r="M4" s="152"/>
+      <c r="N4" s="152"/>
+      <c r="O4" s="152"/>
+      <c r="P4" s="152"/>
+      <c r="Q4" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="160"/>
-      <c r="S4" s="157"/>
-      <c r="T4" s="156" t="s">
+      <c r="R4" s="163"/>
+      <c r="S4" s="160"/>
+      <c r="T4" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="160"/>
-      <c r="V4" s="160"/>
-      <c r="W4" s="157"/>
-      <c r="X4" s="156" t="s">
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="160"/>
+      <c r="X4" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="157"/>
-      <c r="Z4" s="149" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA4" s="149"/>
-      <c r="AB4" s="149"/>
-      <c r="AC4" s="149" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD4" s="149"/>
-      <c r="AE4" s="149"/>
-      <c r="AF4" s="149" t="s">
-        <v>145</v>
-      </c>
-      <c r="AG4" s="149"/>
-      <c r="AH4" s="149"/>
-      <c r="AI4" s="149" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ4" s="149"/>
-      <c r="AK4" s="149"/>
-      <c r="AL4" s="149" t="s">
-        <v>147</v>
-      </c>
-      <c r="AM4" s="149"/>
-      <c r="AN4" s="149"/>
-      <c r="AO4" s="149" t="s">
+      <c r="Y4" s="160"/>
+      <c r="Z4" s="152" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA4" s="152"/>
+      <c r="AB4" s="152"/>
+      <c r="AC4" s="152" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD4" s="152"/>
+      <c r="AE4" s="152"/>
+      <c r="AF4" s="152" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG4" s="152"/>
+      <c r="AH4" s="152"/>
+      <c r="AI4" s="152" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ4" s="152"/>
+      <c r="AK4" s="152"/>
+      <c r="AL4" s="152" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM4" s="152"/>
+      <c r="AN4" s="152"/>
+      <c r="AO4" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="149"/>
-      <c r="AQ4" s="149"/>
-      <c r="AR4" s="149"/>
-      <c r="AS4" s="149"/>
-      <c r="AT4" s="149"/>
-      <c r="AU4" s="149"/>
-      <c r="AV4" s="149"/>
-      <c r="AW4" s="149"/>
-      <c r="AX4" s="149"/>
-      <c r="AY4" s="149"/>
-      <c r="AZ4" s="150"/>
+      <c r="AP4" s="152"/>
+      <c r="AQ4" s="152"/>
+      <c r="AR4" s="152"/>
+      <c r="AS4" s="152"/>
+      <c r="AT4" s="152"/>
+      <c r="AU4" s="152"/>
+      <c r="AV4" s="152"/>
+      <c r="AW4" s="152"/>
+      <c r="AX4" s="152"/>
+      <c r="AY4" s="152"/>
+      <c r="AZ4" s="153"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="163"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="151"/>
-      <c r="M5" s="151"/>
-      <c r="N5" s="151"/>
-      <c r="O5" s="151"/>
-      <c r="P5" s="151"/>
-      <c r="Q5" s="158"/>
-      <c r="R5" s="161"/>
-      <c r="S5" s="159"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="161"/>
-      <c r="W5" s="159"/>
-      <c r="X5" s="158"/>
-      <c r="Y5" s="159"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="161"/>
+      <c r="R5" s="164"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="161"/>
+      <c r="U5" s="164"/>
+      <c r="V5" s="164"/>
+      <c r="W5" s="162"/>
+      <c r="X5" s="161"/>
+      <c r="Y5" s="162"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7522,58 +7791,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="151"/>
-      <c r="AP5" s="151"/>
-      <c r="AQ5" s="151"/>
-      <c r="AR5" s="151"/>
-      <c r="AS5" s="151"/>
-      <c r="AT5" s="151"/>
-      <c r="AU5" s="151"/>
-      <c r="AV5" s="151"/>
-      <c r="AW5" s="151"/>
-      <c r="AX5" s="151"/>
-      <c r="AY5" s="151"/>
-      <c r="AZ5" s="152"/>
+      <c r="AO5" s="154"/>
+      <c r="AP5" s="154"/>
+      <c r="AQ5" s="154"/>
+      <c r="AR5" s="154"/>
+      <c r="AS5" s="154"/>
+      <c r="AT5" s="154"/>
+      <c r="AU5" s="154"/>
+      <c r="AV5" s="154"/>
+      <c r="AW5" s="154"/>
+      <c r="AX5" s="154"/>
+      <c r="AY5" s="154"/>
+      <c r="AZ5" s="155"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="178">
+      <c r="B6" s="181">
         <v>1</v>
       </c>
-      <c r="C6" s="164" t="s">
+      <c r="C6" s="167" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
-      <c r="F6" s="164"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="164"/>
-      <c r="I6" s="164"/>
-      <c r="J6" s="164" t="s">
-        <v>138</v>
-      </c>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
-      <c r="O6" s="164"/>
-      <c r="P6" s="164"/>
-      <c r="Q6" s="155" t="s">
-        <v>139</v>
-      </c>
-      <c r="R6" s="155"/>
-      <c r="S6" s="155"/>
-      <c r="T6" s="169" t="s">
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
+      <c r="J6" s="167" t="s">
+        <v>132</v>
+      </c>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
+      <c r="O6" s="167"/>
+      <c r="P6" s="167"/>
+      <c r="Q6" s="158" t="s">
+        <v>133</v>
+      </c>
+      <c r="R6" s="158"/>
+      <c r="S6" s="158"/>
+      <c r="T6" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="169"/>
-      <c r="V6" s="167">
+      <c r="U6" s="172"/>
+      <c r="V6" s="170">
         <v>0</v>
       </c>
-      <c r="W6" s="167"/>
-      <c r="X6" s="153">
+      <c r="W6" s="170"/>
+      <c r="X6" s="156">
         <v>0</v>
       </c>
-      <c r="Y6" s="153"/>
+      <c r="Y6" s="156"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7589,50 +7858,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="164"/>
-      <c r="AP6" s="164"/>
-      <c r="AQ6" s="164"/>
-      <c r="AR6" s="164"/>
-      <c r="AS6" s="164"/>
-      <c r="AT6" s="164"/>
-      <c r="AU6" s="164"/>
-      <c r="AV6" s="164"/>
-      <c r="AW6" s="164"/>
-      <c r="AX6" s="164"/>
-      <c r="AY6" s="164"/>
-      <c r="AZ6" s="165"/>
+      <c r="AO6" s="167"/>
+      <c r="AP6" s="167"/>
+      <c r="AQ6" s="167"/>
+      <c r="AR6" s="167"/>
+      <c r="AS6" s="167"/>
+      <c r="AT6" s="167"/>
+      <c r="AU6" s="167"/>
+      <c r="AV6" s="167"/>
+      <c r="AW6" s="167"/>
+      <c r="AX6" s="167"/>
+      <c r="AY6" s="167"/>
+      <c r="AZ6" s="168"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="178"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="164"/>
-      <c r="N7" s="164"/>
-      <c r="O7" s="164"/>
-      <c r="P7" s="164"/>
-      <c r="Q7" s="155"/>
-      <c r="R7" s="155"/>
-      <c r="S7" s="155"/>
-      <c r="T7" s="166" t="s">
+      <c r="B7" s="181"/>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="167"/>
+      <c r="L7" s="167"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="167"/>
+      <c r="O7" s="167"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="158"/>
+      <c r="R7" s="158"/>
+      <c r="S7" s="158"/>
+      <c r="T7" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="166"/>
-      <c r="V7" s="168">
+      <c r="U7" s="169"/>
+      <c r="V7" s="171">
         <v>0</v>
       </c>
-      <c r="W7" s="168"/>
-      <c r="X7" s="154">
+      <c r="W7" s="171"/>
+      <c r="X7" s="157">
         <v>1</v>
       </c>
-      <c r="Y7" s="154"/>
+      <c r="Y7" s="157"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7648,58 +7917,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="164"/>
-      <c r="AP7" s="164"/>
-      <c r="AQ7" s="164"/>
-      <c r="AR7" s="164"/>
-      <c r="AS7" s="164"/>
-      <c r="AT7" s="164"/>
-      <c r="AU7" s="164"/>
-      <c r="AV7" s="164"/>
-      <c r="AW7" s="164"/>
-      <c r="AX7" s="164"/>
-      <c r="AY7" s="164"/>
-      <c r="AZ7" s="165"/>
+      <c r="AO7" s="167"/>
+      <c r="AP7" s="167"/>
+      <c r="AQ7" s="167"/>
+      <c r="AR7" s="167"/>
+      <c r="AS7" s="167"/>
+      <c r="AT7" s="167"/>
+      <c r="AU7" s="167"/>
+      <c r="AV7" s="167"/>
+      <c r="AW7" s="167"/>
+      <c r="AX7" s="167"/>
+      <c r="AY7" s="167"/>
+      <c r="AZ7" s="168"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="178">
+      <c r="B8" s="181">
         <v>2</v>
       </c>
-      <c r="C8" s="164" t="s">
+      <c r="C8" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="140" t="s">
-        <v>140</v>
-      </c>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="205" t="s">
-        <v>141</v>
-      </c>
-      <c r="R8" s="205"/>
-      <c r="S8" s="205"/>
-      <c r="T8" s="169" t="s">
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="143" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="126"/>
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="208" t="s">
+        <v>135</v>
+      </c>
+      <c r="R8" s="208"/>
+      <c r="S8" s="208"/>
+      <c r="T8" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="169"/>
-      <c r="V8" s="167">
+      <c r="U8" s="172"/>
+      <c r="V8" s="170">
         <v>0</v>
       </c>
-      <c r="W8" s="167"/>
-      <c r="X8" s="153">
+      <c r="W8" s="170"/>
+      <c r="X8" s="156">
         <v>0</v>
       </c>
-      <c r="Y8" s="153"/>
+      <c r="Y8" s="156"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7715,50 +7984,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="164"/>
-      <c r="AP8" s="164"/>
-      <c r="AQ8" s="164"/>
-      <c r="AR8" s="164"/>
-      <c r="AS8" s="164"/>
-      <c r="AT8" s="164"/>
-      <c r="AU8" s="164"/>
-      <c r="AV8" s="164"/>
-      <c r="AW8" s="164"/>
-      <c r="AX8" s="164"/>
-      <c r="AY8" s="164"/>
-      <c r="AZ8" s="165"/>
+      <c r="AO8" s="167"/>
+      <c r="AP8" s="167"/>
+      <c r="AQ8" s="167"/>
+      <c r="AR8" s="167"/>
+      <c r="AS8" s="167"/>
+      <c r="AT8" s="167"/>
+      <c r="AU8" s="167"/>
+      <c r="AV8" s="167"/>
+      <c r="AW8" s="167"/>
+      <c r="AX8" s="167"/>
+      <c r="AY8" s="167"/>
+      <c r="AZ8" s="168"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="178"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="164"/>
-      <c r="H9" s="164"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="127"/>
-      <c r="Q9" s="205"/>
-      <c r="R9" s="205"/>
-      <c r="S9" s="205"/>
-      <c r="T9" s="166" t="s">
+      <c r="B9" s="181"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="129"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="129"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="208"/>
+      <c r="S9" s="208"/>
+      <c r="T9" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="166"/>
-      <c r="V9" s="168">
+      <c r="U9" s="169"/>
+      <c r="V9" s="171">
         <v>0</v>
       </c>
-      <c r="W9" s="168"/>
-      <c r="X9" s="154">
+      <c r="W9" s="171"/>
+      <c r="X9" s="157">
         <v>1</v>
       </c>
-      <c r="Y9" s="154"/>
+      <c r="Y9" s="157"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -7774,58 +8043,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="164"/>
-      <c r="AP9" s="164"/>
-      <c r="AQ9" s="164"/>
-      <c r="AR9" s="164"/>
-      <c r="AS9" s="164"/>
-      <c r="AT9" s="164"/>
-      <c r="AU9" s="164"/>
-      <c r="AV9" s="164"/>
-      <c r="AW9" s="164"/>
-      <c r="AX9" s="164"/>
-      <c r="AY9" s="164"/>
-      <c r="AZ9" s="165"/>
+      <c r="AO9" s="167"/>
+      <c r="AP9" s="167"/>
+      <c r="AQ9" s="167"/>
+      <c r="AR9" s="167"/>
+      <c r="AS9" s="167"/>
+      <c r="AT9" s="167"/>
+      <c r="AU9" s="167"/>
+      <c r="AV9" s="167"/>
+      <c r="AW9" s="167"/>
+      <c r="AX9" s="167"/>
+      <c r="AY9" s="167"/>
+      <c r="AZ9" s="168"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="178">
+      <c r="B10" s="181">
         <v>3</v>
       </c>
-      <c r="C10" s="164" t="s">
+      <c r="C10" s="167" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="204" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="164"/>
-      <c r="L10" s="164"/>
-      <c r="M10" s="164"/>
-      <c r="N10" s="164"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="155" t="s">
-        <v>139</v>
-      </c>
-      <c r="R10" s="155"/>
-      <c r="S10" s="155"/>
-      <c r="T10" s="169" t="s">
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="207" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="167"/>
+      <c r="L10" s="167"/>
+      <c r="M10" s="167"/>
+      <c r="N10" s="167"/>
+      <c r="O10" s="167"/>
+      <c r="P10" s="167"/>
+      <c r="Q10" s="158" t="s">
+        <v>133</v>
+      </c>
+      <c r="R10" s="158"/>
+      <c r="S10" s="158"/>
+      <c r="T10" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="169"/>
-      <c r="V10" s="167">
+      <c r="U10" s="172"/>
+      <c r="V10" s="170">
         <v>0</v>
       </c>
-      <c r="W10" s="167"/>
-      <c r="X10" s="153">
+      <c r="W10" s="170"/>
+      <c r="X10" s="156">
         <v>0</v>
       </c>
-      <c r="Y10" s="153"/>
+      <c r="Y10" s="156"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -7841,50 +8110,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="164"/>
-      <c r="AP10" s="164"/>
-      <c r="AQ10" s="164"/>
-      <c r="AR10" s="164"/>
-      <c r="AS10" s="164"/>
-      <c r="AT10" s="164"/>
-      <c r="AU10" s="164"/>
-      <c r="AV10" s="164"/>
-      <c r="AW10" s="164"/>
-      <c r="AX10" s="164"/>
-      <c r="AY10" s="164"/>
-      <c r="AZ10" s="165"/>
+      <c r="AO10" s="167"/>
+      <c r="AP10" s="167"/>
+      <c r="AQ10" s="167"/>
+      <c r="AR10" s="167"/>
+      <c r="AS10" s="167"/>
+      <c r="AT10" s="167"/>
+      <c r="AU10" s="167"/>
+      <c r="AV10" s="167"/>
+      <c r="AW10" s="167"/>
+      <c r="AX10" s="167"/>
+      <c r="AY10" s="167"/>
+      <c r="AZ10" s="168"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="178"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164"/>
-      <c r="L11" s="164"/>
-      <c r="M11" s="164"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164"/>
-      <c r="P11" s="164"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="166" t="s">
+      <c r="B11" s="181"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="167"/>
+      <c r="K11" s="167"/>
+      <c r="L11" s="167"/>
+      <c r="M11" s="167"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="167"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="158"/>
+      <c r="R11" s="158"/>
+      <c r="S11" s="158"/>
+      <c r="T11" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="166"/>
-      <c r="V11" s="168">
+      <c r="U11" s="169"/>
+      <c r="V11" s="171">
         <v>0</v>
       </c>
-      <c r="W11" s="168"/>
-      <c r="X11" s="154">
+      <c r="W11" s="171"/>
+      <c r="X11" s="157">
         <v>0</v>
       </c>
-      <c r="Y11" s="154"/>
+      <c r="Y11" s="157"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -7900,58 +8169,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="164"/>
-      <c r="AP11" s="164"/>
-      <c r="AQ11" s="164"/>
-      <c r="AR11" s="164"/>
-      <c r="AS11" s="164"/>
-      <c r="AT11" s="164"/>
-      <c r="AU11" s="164"/>
-      <c r="AV11" s="164"/>
-      <c r="AW11" s="164"/>
-      <c r="AX11" s="164"/>
-      <c r="AY11" s="164"/>
-      <c r="AZ11" s="165"/>
+      <c r="AO11" s="167"/>
+      <c r="AP11" s="167"/>
+      <c r="AQ11" s="167"/>
+      <c r="AR11" s="167"/>
+      <c r="AS11" s="167"/>
+      <c r="AT11" s="167"/>
+      <c r="AU11" s="167"/>
+      <c r="AV11" s="167"/>
+      <c r="AW11" s="167"/>
+      <c r="AX11" s="167"/>
+      <c r="AY11" s="167"/>
+      <c r="AZ11" s="168"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="178">
+      <c r="B12" s="181">
         <v>4</v>
       </c>
-      <c r="C12" s="164" t="s">
+      <c r="C12" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="164" t="s">
-        <v>142</v>
-      </c>
-      <c r="K12" s="164"/>
-      <c r="L12" s="164"/>
-      <c r="M12" s="164"/>
-      <c r="N12" s="164"/>
-      <c r="O12" s="164"/>
-      <c r="P12" s="164"/>
-      <c r="Q12" s="128" t="s">
-        <v>139</v>
-      </c>
-      <c r="R12" s="129"/>
-      <c r="S12" s="130"/>
-      <c r="T12" s="169" t="s">
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="167" t="s">
+        <v>136</v>
+      </c>
+      <c r="K12" s="167"/>
+      <c r="L12" s="167"/>
+      <c r="M12" s="167"/>
+      <c r="N12" s="167"/>
+      <c r="O12" s="167"/>
+      <c r="P12" s="167"/>
+      <c r="Q12" s="131" t="s">
+        <v>133</v>
+      </c>
+      <c r="R12" s="132"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="169"/>
-      <c r="V12" s="167">
+      <c r="U12" s="172"/>
+      <c r="V12" s="170">
         <v>0</v>
       </c>
-      <c r="W12" s="167"/>
-      <c r="X12" s="153">
+      <c r="W12" s="170"/>
+      <c r="X12" s="156">
         <v>0</v>
       </c>
-      <c r="Y12" s="153"/>
+      <c r="Y12" s="156"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -7967,50 +8236,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="164"/>
-      <c r="AP12" s="164"/>
-      <c r="AQ12" s="164"/>
-      <c r="AR12" s="164"/>
-      <c r="AS12" s="164"/>
-      <c r="AT12" s="164"/>
-      <c r="AU12" s="164"/>
-      <c r="AV12" s="164"/>
-      <c r="AW12" s="164"/>
-      <c r="AX12" s="164"/>
-      <c r="AY12" s="164"/>
-      <c r="AZ12" s="165"/>
+      <c r="AO12" s="167"/>
+      <c r="AP12" s="167"/>
+      <c r="AQ12" s="167"/>
+      <c r="AR12" s="167"/>
+      <c r="AS12" s="167"/>
+      <c r="AT12" s="167"/>
+      <c r="AU12" s="167"/>
+      <c r="AV12" s="167"/>
+      <c r="AW12" s="167"/>
+      <c r="AX12" s="167"/>
+      <c r="AY12" s="167"/>
+      <c r="AZ12" s="168"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="178"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="164"/>
-      <c r="K13" s="164"/>
-      <c r="L13" s="164"/>
-      <c r="M13" s="164"/>
-      <c r="N13" s="164"/>
-      <c r="O13" s="164"/>
-      <c r="P13" s="164"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="133"/>
-      <c r="T13" s="166" t="s">
+      <c r="B13" s="181"/>
+      <c r="C13" s="167"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="167"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="167"/>
+      <c r="K13" s="167"/>
+      <c r="L13" s="167"/>
+      <c r="M13" s="167"/>
+      <c r="N13" s="167"/>
+      <c r="O13" s="167"/>
+      <c r="P13" s="167"/>
+      <c r="Q13" s="134"/>
+      <c r="R13" s="135"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="166"/>
-      <c r="V13" s="168">
+      <c r="U13" s="169"/>
+      <c r="V13" s="171">
         <v>0</v>
       </c>
-      <c r="W13" s="168"/>
-      <c r="X13" s="154">
+      <c r="W13" s="171"/>
+      <c r="X13" s="157">
         <v>0</v>
       </c>
-      <c r="Y13" s="154"/>
+      <c r="Y13" s="157"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8026,54 +8295,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="164"/>
-      <c r="AP13" s="164"/>
-      <c r="AQ13" s="164"/>
-      <c r="AR13" s="164"/>
-      <c r="AS13" s="164"/>
-      <c r="AT13" s="164"/>
-      <c r="AU13" s="164"/>
-      <c r="AV13" s="164"/>
-      <c r="AW13" s="164"/>
-      <c r="AX13" s="164"/>
-      <c r="AY13" s="164"/>
-      <c r="AZ13" s="165"/>
+      <c r="AO13" s="167"/>
+      <c r="AP13" s="167"/>
+      <c r="AQ13" s="167"/>
+      <c r="AR13" s="167"/>
+      <c r="AS13" s="167"/>
+      <c r="AT13" s="167"/>
+      <c r="AU13" s="167"/>
+      <c r="AV13" s="167"/>
+      <c r="AW13" s="167"/>
+      <c r="AX13" s="167"/>
+      <c r="AY13" s="167"/>
+      <c r="AZ13" s="168"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="178">
+      <c r="B14" s="181">
         <v>5</v>
       </c>
-      <c r="C14" s="140" t="s">
+      <c r="C14" s="143" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="204"/>
-      <c r="K14" s="164"/>
-      <c r="L14" s="164"/>
-      <c r="M14" s="164"/>
-      <c r="N14" s="164"/>
-      <c r="O14" s="164"/>
-      <c r="P14" s="164"/>
-      <c r="Q14" s="128"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="130"/>
-      <c r="T14" s="169" t="s">
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="207"/>
+      <c r="K14" s="167"/>
+      <c r="L14" s="167"/>
+      <c r="M14" s="167"/>
+      <c r="N14" s="167"/>
+      <c r="O14" s="167"/>
+      <c r="P14" s="167"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="132"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="169"/>
-      <c r="V14" s="167">
+      <c r="U14" s="172"/>
+      <c r="V14" s="170">
         <v>0</v>
       </c>
-      <c r="W14" s="167"/>
-      <c r="X14" s="153">
+      <c r="W14" s="170"/>
+      <c r="X14" s="156">
         <v>0</v>
       </c>
-      <c r="Y14" s="153"/>
+      <c r="Y14" s="156"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8089,50 +8358,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="164"/>
-      <c r="AP14" s="164"/>
-      <c r="AQ14" s="164"/>
-      <c r="AR14" s="164"/>
-      <c r="AS14" s="164"/>
-      <c r="AT14" s="164"/>
-      <c r="AU14" s="164"/>
-      <c r="AV14" s="164"/>
-      <c r="AW14" s="164"/>
-      <c r="AX14" s="164"/>
-      <c r="AY14" s="164"/>
-      <c r="AZ14" s="165"/>
+      <c r="AO14" s="167"/>
+      <c r="AP14" s="167"/>
+      <c r="AQ14" s="167"/>
+      <c r="AR14" s="167"/>
+      <c r="AS14" s="167"/>
+      <c r="AT14" s="167"/>
+      <c r="AU14" s="167"/>
+      <c r="AV14" s="167"/>
+      <c r="AW14" s="167"/>
+      <c r="AX14" s="167"/>
+      <c r="AY14" s="167"/>
+      <c r="AZ14" s="168"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="178"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="164"/>
-      <c r="P15" s="164"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="132"/>
-      <c r="S15" s="133"/>
-      <c r="T15" s="166" t="s">
+      <c r="B15" s="181"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="167"/>
+      <c r="K15" s="167"/>
+      <c r="L15" s="167"/>
+      <c r="M15" s="167"/>
+      <c r="N15" s="167"/>
+      <c r="O15" s="167"/>
+      <c r="P15" s="167"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="135"/>
+      <c r="S15" s="136"/>
+      <c r="T15" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="166"/>
-      <c r="V15" s="168">
+      <c r="U15" s="169"/>
+      <c r="V15" s="171">
         <v>0</v>
       </c>
-      <c r="W15" s="168"/>
-      <c r="X15" s="154">
+      <c r="W15" s="171"/>
+      <c r="X15" s="157">
         <v>0</v>
       </c>
-      <c r="Y15" s="154"/>
+      <c r="Y15" s="157"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8148,56 +8417,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="164"/>
-      <c r="AP15" s="164"/>
-      <c r="AQ15" s="164"/>
-      <c r="AR15" s="164"/>
-      <c r="AS15" s="164"/>
-      <c r="AT15" s="164"/>
-      <c r="AU15" s="164"/>
-      <c r="AV15" s="164"/>
-      <c r="AW15" s="164"/>
-      <c r="AX15" s="164"/>
-      <c r="AY15" s="164"/>
-      <c r="AZ15" s="165"/>
+      <c r="AO15" s="167"/>
+      <c r="AP15" s="167"/>
+      <c r="AQ15" s="167"/>
+      <c r="AR15" s="167"/>
+      <c r="AS15" s="167"/>
+      <c r="AT15" s="167"/>
+      <c r="AU15" s="167"/>
+      <c r="AV15" s="167"/>
+      <c r="AW15" s="167"/>
+      <c r="AX15" s="167"/>
+      <c r="AY15" s="167"/>
+      <c r="AZ15" s="168"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="178">
+      <c r="B16" s="181">
         <v>6</v>
       </c>
-      <c r="C16" s="140" t="s">
+      <c r="C16" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="204" t="s">
-        <v>149</v>
-      </c>
-      <c r="K16" s="164"/>
-      <c r="L16" s="164"/>
-      <c r="M16" s="164"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="164"/>
-      <c r="P16" s="164"/>
-      <c r="Q16" s="155"/>
-      <c r="R16" s="155"/>
-      <c r="S16" s="155"/>
-      <c r="T16" s="169" t="s">
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="207" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="167"/>
+      <c r="L16" s="167"/>
+      <c r="M16" s="167"/>
+      <c r="N16" s="167"/>
+      <c r="O16" s="167"/>
+      <c r="P16" s="167"/>
+      <c r="Q16" s="158"/>
+      <c r="R16" s="158"/>
+      <c r="S16" s="158"/>
+      <c r="T16" s="172" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="169"/>
-      <c r="V16" s="167">
+      <c r="U16" s="172"/>
+      <c r="V16" s="170">
         <v>0</v>
       </c>
-      <c r="W16" s="167"/>
-      <c r="X16" s="153">
+      <c r="W16" s="170"/>
+      <c r="X16" s="156">
         <v>0</v>
       </c>
-      <c r="Y16" s="153"/>
+      <c r="Y16" s="156"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8213,50 +8482,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="164"/>
-      <c r="AP16" s="164"/>
-      <c r="AQ16" s="164"/>
-      <c r="AR16" s="164"/>
-      <c r="AS16" s="164"/>
-      <c r="AT16" s="164"/>
-      <c r="AU16" s="164"/>
-      <c r="AV16" s="164"/>
-      <c r="AW16" s="164"/>
-      <c r="AX16" s="164"/>
-      <c r="AY16" s="164"/>
-      <c r="AZ16" s="165"/>
+      <c r="AO16" s="167"/>
+      <c r="AP16" s="167"/>
+      <c r="AQ16" s="167"/>
+      <c r="AR16" s="167"/>
+      <c r="AS16" s="167"/>
+      <c r="AT16" s="167"/>
+      <c r="AU16" s="167"/>
+      <c r="AV16" s="167"/>
+      <c r="AW16" s="167"/>
+      <c r="AX16" s="167"/>
+      <c r="AY16" s="167"/>
+      <c r="AZ16" s="168"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="178"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="164"/>
-      <c r="K17" s="164"/>
-      <c r="L17" s="164"/>
-      <c r="M17" s="164"/>
-      <c r="N17" s="164"/>
-      <c r="O17" s="164"/>
-      <c r="P17" s="164"/>
-      <c r="Q17" s="155"/>
-      <c r="R17" s="155"/>
-      <c r="S17" s="155"/>
-      <c r="T17" s="166" t="s">
+      <c r="B17" s="181"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="167"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="167"/>
+      <c r="Q17" s="158"/>
+      <c r="R17" s="158"/>
+      <c r="S17" s="158"/>
+      <c r="T17" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="166"/>
-      <c r="V17" s="168">
+      <c r="U17" s="169"/>
+      <c r="V17" s="171">
         <v>0</v>
       </c>
-      <c r="W17" s="168"/>
-      <c r="X17" s="154">
+      <c r="W17" s="171"/>
+      <c r="X17" s="157">
         <v>0</v>
       </c>
-      <c r="Y17" s="154"/>
+      <c r="Y17" s="157"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8272,56 +8541,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="164"/>
-      <c r="AP17" s="164"/>
-      <c r="AQ17" s="164"/>
-      <c r="AR17" s="164"/>
-      <c r="AS17" s="164"/>
-      <c r="AT17" s="164"/>
-      <c r="AU17" s="164"/>
-      <c r="AV17" s="164"/>
-      <c r="AW17" s="164"/>
-      <c r="AX17" s="164"/>
-      <c r="AY17" s="164"/>
-      <c r="AZ17" s="165"/>
+      <c r="AO17" s="167"/>
+      <c r="AP17" s="167"/>
+      <c r="AQ17" s="167"/>
+      <c r="AR17" s="167"/>
+      <c r="AS17" s="167"/>
+      <c r="AT17" s="167"/>
+      <c r="AU17" s="167"/>
+      <c r="AV17" s="167"/>
+      <c r="AW17" s="167"/>
+      <c r="AX17" s="167"/>
+      <c r="AY17" s="167"/>
+      <c r="AZ17" s="168"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="115">
+      <c r="B18" s="118">
         <v>7</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="140" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="123"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="128"/>
-      <c r="R18" s="129"/>
-      <c r="S18" s="130"/>
-      <c r="T18" s="134" t="s">
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="143" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="126"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="131"/>
+      <c r="R18" s="132"/>
+      <c r="S18" s="133"/>
+      <c r="T18" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="135"/>
-      <c r="V18" s="136">
+      <c r="U18" s="138"/>
+      <c r="V18" s="139">
         <v>0</v>
       </c>
-      <c r="W18" s="137"/>
-      <c r="X18" s="138">
+      <c r="W18" s="140"/>
+      <c r="X18" s="141">
         <v>0</v>
       </c>
-      <c r="Y18" s="139"/>
+      <c r="Y18" s="142"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8337,50 +8606,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="140"/>
-      <c r="AP18" s="123"/>
-      <c r="AQ18" s="123"/>
-      <c r="AR18" s="123"/>
-      <c r="AS18" s="123"/>
-      <c r="AT18" s="123"/>
-      <c r="AU18" s="123"/>
-      <c r="AV18" s="123"/>
-      <c r="AW18" s="123"/>
-      <c r="AX18" s="123"/>
-      <c r="AY18" s="123"/>
-      <c r="AZ18" s="141"/>
+      <c r="AO18" s="143"/>
+      <c r="AP18" s="126"/>
+      <c r="AQ18" s="126"/>
+      <c r="AR18" s="126"/>
+      <c r="AS18" s="126"/>
+      <c r="AT18" s="126"/>
+      <c r="AU18" s="126"/>
+      <c r="AV18" s="126"/>
+      <c r="AW18" s="126"/>
+      <c r="AX18" s="126"/>
+      <c r="AY18" s="126"/>
+      <c r="AZ18" s="144"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="116"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="131"/>
-      <c r="R19" s="132"/>
-      <c r="S19" s="133"/>
-      <c r="T19" s="143" t="s">
+      <c r="B19" s="119"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="129"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="129"/>
+      <c r="O19" s="129"/>
+      <c r="P19" s="130"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="135"/>
+      <c r="S19" s="136"/>
+      <c r="T19" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="144"/>
-      <c r="V19" s="145">
+      <c r="U19" s="147"/>
+      <c r="V19" s="148">
         <v>0</v>
       </c>
-      <c r="W19" s="146"/>
-      <c r="X19" s="147">
+      <c r="W19" s="149"/>
+      <c r="X19" s="150">
         <v>0</v>
       </c>
-      <c r="Y19" s="148"/>
+      <c r="Y19" s="151"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8396,56 +8665,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="125"/>
-      <c r="AP19" s="126"/>
-      <c r="AQ19" s="126"/>
-      <c r="AR19" s="126"/>
-      <c r="AS19" s="126"/>
-      <c r="AT19" s="126"/>
-      <c r="AU19" s="126"/>
-      <c r="AV19" s="126"/>
-      <c r="AW19" s="126"/>
-      <c r="AX19" s="126"/>
-      <c r="AY19" s="126"/>
-      <c r="AZ19" s="142"/>
+      <c r="AO19" s="128"/>
+      <c r="AP19" s="129"/>
+      <c r="AQ19" s="129"/>
+      <c r="AR19" s="129"/>
+      <c r="AS19" s="129"/>
+      <c r="AT19" s="129"/>
+      <c r="AU19" s="129"/>
+      <c r="AV19" s="129"/>
+      <c r="AW19" s="129"/>
+      <c r="AX19" s="129"/>
+      <c r="AY19" s="129"/>
+      <c r="AZ19" s="145"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="115">
+      <c r="B20" s="118">
         <v>8</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="119"/>
-      <c r="J20" s="117" t="s">
-        <v>151</v>
-      </c>
-      <c r="K20" s="123"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="128"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="130"/>
-      <c r="T20" s="134" t="s">
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="120" t="s">
+        <v>145</v>
+      </c>
+      <c r="K20" s="126"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="126"/>
+      <c r="N20" s="126"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="127"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="132"/>
+      <c r="S20" s="133"/>
+      <c r="T20" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="135"/>
-      <c r="V20" s="136">
+      <c r="U20" s="138"/>
+      <c r="V20" s="139">
         <v>0</v>
       </c>
-      <c r="W20" s="137"/>
-      <c r="X20" s="138">
+      <c r="W20" s="140"/>
+      <c r="X20" s="141">
         <v>0</v>
       </c>
-      <c r="Y20" s="139"/>
+      <c r="Y20" s="142"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8461,50 +8730,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="140"/>
-      <c r="AP20" s="123"/>
-      <c r="AQ20" s="123"/>
-      <c r="AR20" s="123"/>
-      <c r="AS20" s="123"/>
-      <c r="AT20" s="123"/>
-      <c r="AU20" s="123"/>
-      <c r="AV20" s="123"/>
-      <c r="AW20" s="123"/>
-      <c r="AX20" s="123"/>
-      <c r="AY20" s="123"/>
-      <c r="AZ20" s="141"/>
+      <c r="AO20" s="143"/>
+      <c r="AP20" s="126"/>
+      <c r="AQ20" s="126"/>
+      <c r="AR20" s="126"/>
+      <c r="AS20" s="126"/>
+      <c r="AT20" s="126"/>
+      <c r="AU20" s="126"/>
+      <c r="AV20" s="126"/>
+      <c r="AW20" s="126"/>
+      <c r="AX20" s="126"/>
+      <c r="AY20" s="126"/>
+      <c r="AZ20" s="144"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="116"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="127"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="133"/>
-      <c r="T21" s="143" t="s">
+      <c r="B21" s="119"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="129"/>
+      <c r="L21" s="129"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="129"/>
+      <c r="O21" s="129"/>
+      <c r="P21" s="130"/>
+      <c r="Q21" s="134"/>
+      <c r="R21" s="135"/>
+      <c r="S21" s="136"/>
+      <c r="T21" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="144"/>
-      <c r="V21" s="145">
+      <c r="U21" s="147"/>
+      <c r="V21" s="148">
         <v>0</v>
       </c>
-      <c r="W21" s="146"/>
-      <c r="X21" s="147">
+      <c r="W21" s="149"/>
+      <c r="X21" s="150">
         <v>0</v>
       </c>
-      <c r="Y21" s="148"/>
+      <c r="Y21" s="151"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8520,54 +8789,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="125"/>
-      <c r="AP21" s="126"/>
-      <c r="AQ21" s="126"/>
-      <c r="AR21" s="126"/>
-      <c r="AS21" s="126"/>
-      <c r="AT21" s="126"/>
-      <c r="AU21" s="126"/>
-      <c r="AV21" s="126"/>
-      <c r="AW21" s="126"/>
-      <c r="AX21" s="126"/>
-      <c r="AY21" s="126"/>
-      <c r="AZ21" s="142"/>
+      <c r="AO21" s="128"/>
+      <c r="AP21" s="129"/>
+      <c r="AQ21" s="129"/>
+      <c r="AR21" s="129"/>
+      <c r="AS21" s="129"/>
+      <c r="AT21" s="129"/>
+      <c r="AU21" s="129"/>
+      <c r="AV21" s="129"/>
+      <c r="AW21" s="129"/>
+      <c r="AX21" s="129"/>
+      <c r="AY21" s="129"/>
+      <c r="AZ21" s="145"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="185">
+      <c r="B22" s="188">
         <v>9</v>
       </c>
-      <c r="C22" s="187" t="s">
+      <c r="C22" s="190" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="188"/>
-      <c r="E22" s="188"/>
-      <c r="F22" s="188"/>
-      <c r="G22" s="188"/>
-      <c r="H22" s="188"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="172"/>
-      <c r="K22" s="173"/>
-      <c r="L22" s="173"/>
-      <c r="M22" s="173"/>
-      <c r="N22" s="173"/>
-      <c r="O22" s="173"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="194"/>
-      <c r="R22" s="195"/>
-      <c r="S22" s="196"/>
-      <c r="T22" s="190" t="s">
+      <c r="D22" s="191"/>
+      <c r="E22" s="191"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="191"/>
+      <c r="H22" s="191"/>
+      <c r="I22" s="192"/>
+      <c r="J22" s="175"/>
+      <c r="K22" s="176"/>
+      <c r="L22" s="176"/>
+      <c r="M22" s="176"/>
+      <c r="N22" s="176"/>
+      <c r="O22" s="176"/>
+      <c r="P22" s="177"/>
+      <c r="Q22" s="197"/>
+      <c r="R22" s="198"/>
+      <c r="S22" s="199"/>
+      <c r="T22" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="191"/>
-      <c r="V22" s="170">
+      <c r="U22" s="194"/>
+      <c r="V22" s="173">
         <v>0</v>
       </c>
-      <c r="W22" s="171"/>
-      <c r="X22" s="183">
+      <c r="W22" s="174"/>
+      <c r="X22" s="186">
         <v>0</v>
       </c>
-      <c r="Y22" s="184"/>
+      <c r="Y22" s="187"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8583,50 +8852,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="172"/>
-      <c r="AP22" s="173"/>
-      <c r="AQ22" s="173"/>
-      <c r="AR22" s="173"/>
-      <c r="AS22" s="173"/>
-      <c r="AT22" s="173"/>
-      <c r="AU22" s="173"/>
-      <c r="AV22" s="173"/>
-      <c r="AW22" s="173"/>
-      <c r="AX22" s="173"/>
-      <c r="AY22" s="173"/>
-      <c r="AZ22" s="181"/>
+      <c r="AO22" s="175"/>
+      <c r="AP22" s="176"/>
+      <c r="AQ22" s="176"/>
+      <c r="AR22" s="176"/>
+      <c r="AS22" s="176"/>
+      <c r="AT22" s="176"/>
+      <c r="AU22" s="176"/>
+      <c r="AV22" s="176"/>
+      <c r="AW22" s="176"/>
+      <c r="AX22" s="176"/>
+      <c r="AY22" s="176"/>
+      <c r="AZ22" s="184"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="186"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="176"/>
-      <c r="L23" s="176"/>
-      <c r="M23" s="176"/>
-      <c r="N23" s="176"/>
-      <c r="O23" s="176"/>
-      <c r="P23" s="177"/>
-      <c r="Q23" s="197"/>
-      <c r="R23" s="198"/>
-      <c r="S23" s="199"/>
-      <c r="T23" s="192" t="s">
+      <c r="B23" s="189"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="178"/>
+      <c r="K23" s="179"/>
+      <c r="L23" s="179"/>
+      <c r="M23" s="179"/>
+      <c r="N23" s="179"/>
+      <c r="O23" s="179"/>
+      <c r="P23" s="180"/>
+      <c r="Q23" s="200"/>
+      <c r="R23" s="201"/>
+      <c r="S23" s="202"/>
+      <c r="T23" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="193"/>
-      <c r="V23" s="179">
+      <c r="U23" s="196"/>
+      <c r="V23" s="182">
         <v>0</v>
       </c>
-      <c r="W23" s="180"/>
-      <c r="X23" s="200">
+      <c r="W23" s="183"/>
+      <c r="X23" s="203">
         <v>0</v>
       </c>
-      <c r="Y23" s="201"/>
+      <c r="Y23" s="204"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8642,18 +8911,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="175"/>
-      <c r="AP23" s="176"/>
-      <c r="AQ23" s="176"/>
-      <c r="AR23" s="176"/>
-      <c r="AS23" s="176"/>
-      <c r="AT23" s="176"/>
-      <c r="AU23" s="176"/>
-      <c r="AV23" s="176"/>
-      <c r="AW23" s="176"/>
-      <c r="AX23" s="176"/>
-      <c r="AY23" s="176"/>
-      <c r="AZ23" s="182"/>
+      <c r="AO23" s="178"/>
+      <c r="AP23" s="179"/>
+      <c r="AQ23" s="179"/>
+      <c r="AR23" s="179"/>
+      <c r="AS23" s="179"/>
+      <c r="AT23" s="179"/>
+      <c r="AU23" s="179"/>
+      <c r="AV23" s="179"/>
+      <c r="AW23" s="179"/>
+      <c r="AX23" s="179"/>
+      <c r="AY23" s="179"/>
+      <c r="AZ23" s="185"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8848,602 +9117,602 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34">
+      <c r="A1" s="54">
         <v>1</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34">
+      <c r="A3" s="54">
         <v>2</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="74"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="206" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="209" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="207"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="209"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="209"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="210"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34">
+      <c r="A5" s="54">
         <v>3</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="74"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="92"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
-      <c r="B6" s="81" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="82"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="100"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34">
+      <c r="A7" s="54">
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="74"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="92"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35"/>
-      <c r="B8" s="77" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="78"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="70"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="52"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="70"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="52"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="35"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="52"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="70"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="70"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="77" t="s">
+      <c r="A15" s="55"/>
+      <c r="B15" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="78"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="96"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="70"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="70"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="70"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="70"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="65"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="34">
+      <c r="A22" s="54">
         <v>5</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="74"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="92"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="70"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="70"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="52"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="70"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="52"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="70"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="52"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="70"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="35"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="52"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="70"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="52"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="70"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="46"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="65"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="34">
+      <c r="A31" s="54">
         <v>6</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="74"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="92"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="52"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="70"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="52"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="70"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="52"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="70"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="52"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="70"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="35"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="52"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="70"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="52"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="70"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="35"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="52"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="70"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="52"/>
+      <c r="A39" s="55"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="70"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="52"/>
+      <c r="A40" s="55"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="70"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="52"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="70"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="35"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="52"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="70"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="52"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="52"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="70"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="35"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="52"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="70"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="52"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="70"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="79"/>
-      <c r="J47" s="80"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CE61B7-6581-44A5-BB21-0652E35E4B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CAF4B7-1D04-436D-AFC9-8A41C9805203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="177">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -635,32 +635,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>被害状況管理</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害情報登録</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>被害写真登録</t>
     <rPh sb="0" eb="2">
       <t>ヒガイ</t>
@@ -683,19 +657,6 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況分析</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブンセキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2116,6 +2077,23 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況・分析</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3204,6 +3182,21 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3235,12 +3228,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3264,6 +3251,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3736,31 +3738,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4644,1582 +4622,1582 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="54">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62" t="s">
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="71"/>
+    </row>
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="66"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
+    </row>
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="62">
+        <v>2</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="68"/>
+    </row>
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="63"/>
+      <c r="B5" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="80"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="63"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="80"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="63"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="63"/>
+      <c r="B8" s="94" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="63"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="99"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="63"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
+    </row>
+    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="63"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="63"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="63"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="99"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="63"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="63"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="98"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="99"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="63"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="66"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="66"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="66"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="66"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="62">
+        <v>3</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="68"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="63"/>
+      <c r="B22" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="85"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="63"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="85"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="63"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="85"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="63"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="88"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="63"/>
+      <c r="B26" s="89" t="s">
         <v>152</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-    </row>
-    <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-    </row>
-    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="54">
-        <v>2</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
-    </row>
-    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="55"/>
-      <c r="B5" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="72"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="55"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-    </row>
-    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="55"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="74"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="55"/>
-      <c r="B8" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="88"/>
-    </row>
-    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="55"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="91"/>
-    </row>
-    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="91"/>
-    </row>
-    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="55"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="91"/>
-    </row>
-    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="55"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="91"/>
-    </row>
-    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="55"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="91"/>
-    </row>
-    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="55"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="91"/>
-    </row>
-    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="55"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="91"/>
-    </row>
-    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="91"/>
-    </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="58"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="91"/>
-    </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="58"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="91"/>
-    </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="58"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="91"/>
-    </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="58"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="91"/>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="54">
-        <v>3</v>
-      </c>
-      <c r="B21" s="59" t="s">
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="63"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="63"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="63"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="63"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="63"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="90"/>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="63"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="90"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="63"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="90"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="63"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="90"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="63"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="89"/>
+      <c r="J35" s="90"/>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="63"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
+      <c r="E36" s="89"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="90"/>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="63"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="90"/>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="63"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="90"/>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="63"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="90"/>
+    </row>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="63"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="90"/>
+    </row>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="63"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="90"/>
+    </row>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="63"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="89"/>
+      <c r="E42" s="89"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="89"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="90"/>
+    </row>
+    <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="63"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="89"/>
+      <c r="D43" s="89"/>
+      <c r="E43" s="89"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="90"/>
+    </row>
+    <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="63"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="90"/>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="63"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="89"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="89"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="90"/>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="63"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="89"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="90"/>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="63"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="89"/>
+      <c r="E47" s="89"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="90"/>
+    </row>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="63"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="89"/>
+      <c r="J48" s="90"/>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="63"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="90"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="63"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="89"/>
+      <c r="J50" s="90"/>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="63"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="89"/>
+      <c r="D51" s="89"/>
+      <c r="E51" s="89"/>
+      <c r="F51" s="89"/>
+      <c r="G51" s="89"/>
+      <c r="H51" s="89"/>
+      <c r="I51" s="89"/>
+      <c r="J51" s="90"/>
+    </row>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="63"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="89"/>
+      <c r="J52" s="90"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="63"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="89"/>
+      <c r="D53" s="89"/>
+      <c r="E53" s="89"/>
+      <c r="F53" s="89"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="89"/>
+      <c r="J53" s="90"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="63"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
+      <c r="E54" s="89"/>
+      <c r="F54" s="89"/>
+      <c r="G54" s="89"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="89"/>
+      <c r="J54" s="90"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="63"/>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="89"/>
+      <c r="J55" s="90"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="63"/>
+      <c r="B56" s="89"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="89"/>
+      <c r="E56" s="89"/>
+      <c r="F56" s="89"/>
+      <c r="G56" s="89"/>
+      <c r="H56" s="89"/>
+      <c r="I56" s="89"/>
+      <c r="J56" s="90"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="63"/>
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="89"/>
+      <c r="J57" s="90"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="63"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="89"/>
+      <c r="J58" s="90"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="63"/>
+      <c r="B59" s="89"/>
+      <c r="C59" s="89"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
+      <c r="H59" s="89"/>
+      <c r="I59" s="89"/>
+      <c r="J59" s="90"/>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="63"/>
+      <c r="B60" s="89"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+      <c r="J60" s="90"/>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="63"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="89"/>
+      <c r="J61" s="90"/>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="64"/>
+      <c r="B62" s="91"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="91"/>
+      <c r="H62" s="91"/>
+      <c r="I62" s="91"/>
+      <c r="J62" s="92"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="62">
         <v>4</v>
       </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="60"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="55"/>
-      <c r="B22" s="75" t="s">
+      <c r="B63" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="100"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="63"/>
+      <c r="B64" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="65"/>
+      <c r="D64" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="77"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="77"/>
+      <c r="I64" s="77"/>
+      <c r="J64" s="78"/>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="63"/>
+      <c r="B65" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="65"/>
+      <c r="D65" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="E65" s="77"/>
+      <c r="F65" s="77"/>
+      <c r="G65" s="77"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="78"/>
+    </row>
+    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="63"/>
+      <c r="B66" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="65"/>
+      <c r="D66" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="77"/>
+      <c r="F66" s="77"/>
+      <c r="G66" s="77"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="78"/>
+    </row>
+    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="63"/>
+      <c r="B67" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="65"/>
+      <c r="D67" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" s="77"/>
+      <c r="F67" s="77"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="77"/>
+      <c r="I67" s="77"/>
+      <c r="J67" s="78"/>
+    </row>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="63"/>
+      <c r="B68" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="65"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="65"/>
+      <c r="F68" s="65"/>
+      <c r="G68" s="65"/>
+      <c r="H68" s="65"/>
+      <c r="I68" s="65"/>
+      <c r="J68" s="93"/>
+    </row>
+    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="63"/>
+      <c r="B69" s="74" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C69" s="74"/>
+      <c r="D69" s="74"/>
+      <c r="E69" s="74"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="74"/>
+      <c r="I69" s="74"/>
+      <c r="J69" s="75"/>
+    </row>
+    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="63"/>
+      <c r="B70" s="74"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="75"/>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="63"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="75"/>
+    </row>
+    <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="63"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="75"/>
+    </row>
+    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="63"/>
+      <c r="B73" s="74"/>
+      <c r="C73" s="74"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="74"/>
+      <c r="I73" s="74"/>
+      <c r="J73" s="75"/>
+    </row>
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="63"/>
+      <c r="B74" s="74"/>
+      <c r="C74" s="74"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="74"/>
+      <c r="H74" s="74"/>
+      <c r="I74" s="74"/>
+      <c r="J74" s="75"/>
+    </row>
+    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="63"/>
+      <c r="B75" s="74"/>
+      <c r="C75" s="74"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="74"/>
+      <c r="J75" s="75"/>
+    </row>
+    <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="63"/>
+      <c r="B76" s="74"/>
+      <c r="C76" s="74"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="74"/>
+      <c r="J76" s="75"/>
+    </row>
+    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="63"/>
+      <c r="B77" s="74"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="74"/>
+      <c r="E77" s="74"/>
+      <c r="F77" s="74"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="74"/>
+      <c r="I77" s="74"/>
+      <c r="J77" s="75"/>
+    </row>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="63"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="74"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="74"/>
+      <c r="F78" s="74"/>
+      <c r="G78" s="74"/>
+      <c r="H78" s="74"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="75"/>
+    </row>
+    <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="63"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="74"/>
+      <c r="F79" s="74"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="74"/>
+      <c r="I79" s="74"/>
+      <c r="J79" s="75"/>
+    </row>
+    <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="63"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
+      <c r="J80" s="75"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="63"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="75"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="63"/>
+      <c r="B82" s="74"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="74"/>
+      <c r="F82" s="74"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="74"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="75"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="63"/>
+      <c r="B83" s="74"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="74"/>
+      <c r="F83" s="74"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="74"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="75"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="63"/>
+      <c r="B84" s="74"/>
+      <c r="C84" s="74"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="74"/>
+      <c r="F84" s="74"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="75"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="63"/>
+      <c r="B85" s="74"/>
+      <c r="C85" s="74"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="74"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="74"/>
+      <c r="H85" s="74"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="75"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="66"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="51"/>
+      <c r="J86" s="76"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="62">
         <v>5</v>
       </c>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="77"/>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="55"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="77"/>
-    </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="55"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="77"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="80"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="55"/>
-      <c r="B26" s="81" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="82"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="55"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="82"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="55"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81"/>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-      <c r="J28" s="82"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="55"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="82"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="55"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="82"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="55"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="82"/>
-    </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="55"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="82"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="55"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="82"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="55"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="82"/>
-    </row>
-    <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="82"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="55"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="82"/>
-    </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="55"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="82"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="55"/>
-      <c r="B38" s="81"/>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="82"/>
-    </row>
-    <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="55"/>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="82"/>
-    </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="55"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="81"/>
-      <c r="I40" s="81"/>
-      <c r="J40" s="82"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="55"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="82"/>
-    </row>
-    <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="55"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="82"/>
-    </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="55"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="82"/>
-    </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="55"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="82"/>
-    </row>
-    <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="55"/>
-      <c r="B45" s="81"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="82"/>
-    </row>
-    <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="55"/>
-      <c r="B46" s="81"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="82"/>
-    </row>
-    <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="55"/>
-      <c r="B47" s="81"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="81"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="82"/>
-    </row>
-    <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="55"/>
-      <c r="B48" s="81"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="82"/>
-    </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="55"/>
-      <c r="B49" s="81"/>
-      <c r="C49" s="81"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="82"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="55"/>
-      <c r="B50" s="81"/>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="82"/>
-    </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="55"/>
-      <c r="B51" s="81"/>
-      <c r="C51" s="81"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="82"/>
-    </row>
-    <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="55"/>
-      <c r="B52" s="81"/>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="82"/>
-    </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="55"/>
-      <c r="B53" s="81"/>
-      <c r="C53" s="81"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="82"/>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="55"/>
-      <c r="B54" s="81"/>
-      <c r="C54" s="81"/>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="81"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="82"/>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="55"/>
-      <c r="B55" s="81"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="81"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="82"/>
-    </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="55"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="81"/>
-      <c r="I56" s="81"/>
-      <c r="J56" s="82"/>
-    </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="55"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="81"/>
-      <c r="D57" s="81"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="81"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="82"/>
-    </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="55"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="82"/>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="55"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="81"/>
-      <c r="D59" s="81"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="81"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="82"/>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="55"/>
-      <c r="B60" s="81"/>
-      <c r="C60" s="81"/>
-      <c r="D60" s="81"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="81"/>
-      <c r="I60" s="81"/>
-      <c r="J60" s="82"/>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="55"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="81"/>
-      <c r="I61" s="81"/>
-      <c r="J61" s="82"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="56"/>
-      <c r="B62" s="83"/>
-      <c r="C62" s="83"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="83"/>
-      <c r="F62" s="83"/>
-      <c r="G62" s="83"/>
-      <c r="H62" s="83"/>
-      <c r="I62" s="83"/>
-      <c r="J62" s="84"/>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="54">
-        <v>4</v>
-      </c>
-      <c r="B63" s="61" t="s">
+      <c r="B87" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="69"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="69"/>
+      <c r="F87" s="69"/>
+      <c r="G87" s="69"/>
+      <c r="H87" s="69"/>
+      <c r="I87" s="69"/>
+      <c r="J87" s="100"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="63"/>
+      <c r="B88" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
+      <c r="J88" s="110"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="62">
         <v>6</v>
       </c>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61"/>
-      <c r="J63" s="92"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="55"/>
-      <c r="B64" s="57" t="s">
+      <c r="B89" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="67"/>
+      <c r="D89" s="67"/>
+      <c r="E89" s="67"/>
+      <c r="F89" s="67"/>
+      <c r="G89" s="67"/>
+      <c r="H89" s="67"/>
+      <c r="I89" s="67"/>
+      <c r="J89" s="68"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="109"/>
+      <c r="B90" s="79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="79"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="79"/>
+      <c r="F90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="79"/>
+      <c r="I90" s="79"/>
+      <c r="J90" s="80"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="109"/>
+      <c r="B91" s="79"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="79"/>
+      <c r="E91" s="79"/>
+      <c r="F91" s="79"/>
+      <c r="G91" s="79"/>
+      <c r="H91" s="79"/>
+      <c r="I91" s="79"/>
+      <c r="J91" s="80"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="109"/>
+      <c r="B92" s="81"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
+      <c r="E92" s="81"/>
+      <c r="F92" s="81"/>
+      <c r="G92" s="81"/>
+      <c r="H92" s="81"/>
+      <c r="I92" s="81"/>
+      <c r="J92" s="82"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="63"/>
+      <c r="B93" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" s="95"/>
+      <c r="D93" s="95"/>
+      <c r="E93" s="95"/>
+      <c r="F93" s="95"/>
+      <c r="G93" s="95"/>
+      <c r="H93" s="95"/>
+      <c r="I93" s="95"/>
+      <c r="J93" s="96"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="63"/>
+      <c r="B94" s="97"/>
+      <c r="C94" s="98"/>
+      <c r="D94" s="98"/>
+      <c r="E94" s="98"/>
+      <c r="F94" s="98"/>
+      <c r="G94" s="98"/>
+      <c r="H94" s="98"/>
+      <c r="I94" s="98"/>
+      <c r="J94" s="99"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="63"/>
+      <c r="B95" s="97"/>
+      <c r="C95" s="98"/>
+      <c r="D95" s="98"/>
+      <c r="E95" s="98"/>
+      <c r="F95" s="98"/>
+      <c r="G95" s="98"/>
+      <c r="H95" s="98"/>
+      <c r="I95" s="98"/>
+      <c r="J95" s="99"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="63"/>
+      <c r="B96" s="97"/>
+      <c r="C96" s="98"/>
+      <c r="D96" s="98"/>
+      <c r="E96" s="98"/>
+      <c r="F96" s="98"/>
+      <c r="G96" s="98"/>
+      <c r="H96" s="98"/>
+      <c r="I96" s="98"/>
+      <c r="J96" s="99"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="63"/>
+      <c r="B97" s="97"/>
+      <c r="C97" s="98"/>
+      <c r="D97" s="98"/>
+      <c r="E97" s="98"/>
+      <c r="F97" s="98"/>
+      <c r="G97" s="98"/>
+      <c r="H97" s="98"/>
+      <c r="I97" s="98"/>
+      <c r="J97" s="99"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="63"/>
+      <c r="B98" s="97"/>
+      <c r="C98" s="98"/>
+      <c r="D98" s="98"/>
+      <c r="E98" s="98"/>
+      <c r="F98" s="98"/>
+      <c r="G98" s="98"/>
+      <c r="H98" s="98"/>
+      <c r="I98" s="98"/>
+      <c r="J98" s="99"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="63"/>
+      <c r="B99" s="97"/>
+      <c r="C99" s="98"/>
+      <c r="D99" s="98"/>
+      <c r="E99" s="98"/>
+      <c r="F99" s="98"/>
+      <c r="G99" s="98"/>
+      <c r="H99" s="98"/>
+      <c r="I99" s="98"/>
+      <c r="J99" s="99"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="63"/>
+      <c r="B100" s="97"/>
+      <c r="C100" s="98"/>
+      <c r="D100" s="98"/>
+      <c r="E100" s="98"/>
+      <c r="F100" s="98"/>
+      <c r="G100" s="98"/>
+      <c r="H100" s="98"/>
+      <c r="I100" s="98"/>
+      <c r="J100" s="99"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="63"/>
+      <c r="B101" s="97"/>
+      <c r="C101" s="98"/>
+      <c r="D101" s="98"/>
+      <c r="E101" s="98"/>
+      <c r="F101" s="98"/>
+      <c r="G101" s="98"/>
+      <c r="H101" s="98"/>
+      <c r="I101" s="98"/>
+      <c r="J101" s="99"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="63"/>
+      <c r="B102" s="97"/>
+      <c r="C102" s="98"/>
+      <c r="D102" s="98"/>
+      <c r="E102" s="98"/>
+      <c r="F102" s="98"/>
+      <c r="G102" s="98"/>
+      <c r="H102" s="98"/>
+      <c r="I102" s="98"/>
+      <c r="J102" s="99"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="63"/>
+      <c r="B103" s="97"/>
+      <c r="C103" s="98"/>
+      <c r="D103" s="98"/>
+      <c r="E103" s="98"/>
+      <c r="F103" s="98"/>
+      <c r="G103" s="98"/>
+      <c r="H103" s="98"/>
+      <c r="I103" s="98"/>
+      <c r="J103" s="99"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="63"/>
+      <c r="B104" s="97"/>
+      <c r="C104" s="98"/>
+      <c r="D104" s="98"/>
+      <c r="E104" s="98"/>
+      <c r="F104" s="98"/>
+      <c r="G104" s="98"/>
+      <c r="H104" s="98"/>
+      <c r="I104" s="98"/>
+      <c r="J104" s="99"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="63"/>
+      <c r="B105" s="97"/>
+      <c r="C105" s="98"/>
+      <c r="D105" s="98"/>
+      <c r="E105" s="98"/>
+      <c r="F105" s="98"/>
+      <c r="G105" s="98"/>
+      <c r="H105" s="98"/>
+      <c r="I105" s="98"/>
+      <c r="J105" s="99"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="63"/>
+      <c r="B106" s="97"/>
+      <c r="C106" s="98"/>
+      <c r="D106" s="98"/>
+      <c r="E106" s="98"/>
+      <c r="F106" s="98"/>
+      <c r="G106" s="98"/>
+      <c r="H106" s="98"/>
+      <c r="I106" s="98"/>
+      <c r="J106" s="99"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="64"/>
+      <c r="B107" s="111"/>
+      <c r="C107" s="112"/>
+      <c r="D107" s="112"/>
+      <c r="E107" s="112"/>
+      <c r="F107" s="112"/>
+      <c r="G107" s="112"/>
+      <c r="H107" s="112"/>
+      <c r="I107" s="112"/>
+      <c r="J107" s="113"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="62">
         <v>7</v>
       </c>
-      <c r="C64" s="57"/>
-      <c r="D64" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="70"/>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="55"/>
-      <c r="B65" s="57" t="s">
+      <c r="B108" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="69"/>
+      <c r="D108" s="69"/>
+      <c r="E108" s="69"/>
+      <c r="F108" s="69"/>
+      <c r="G108" s="69"/>
+      <c r="H108" s="69"/>
+      <c r="I108" s="69"/>
+      <c r="J108" s="100"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="66"/>
+      <c r="B109" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" s="107"/>
+      <c r="D109" s="107"/>
+      <c r="E109" s="107"/>
+      <c r="F109" s="107"/>
+      <c r="G109" s="107"/>
+      <c r="H109" s="107"/>
+      <c r="I109" s="107"/>
+      <c r="J109" s="108"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="62">
         <v>8</v>
       </c>
-      <c r="C65" s="57"/>
-      <c r="D65" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="E65" s="69"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="69"/>
-      <c r="J65" s="70"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="55"/>
-      <c r="B66" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="57"/>
-      <c r="D66" s="69" t="s">
-        <v>150</v>
-      </c>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="69"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="70"/>
-    </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="55"/>
-      <c r="B67" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="57"/>
-      <c r="D67" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="69"/>
-      <c r="I67" s="69"/>
-      <c r="J67" s="70"/>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="55"/>
-      <c r="B68" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="85"/>
-    </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="55"/>
-      <c r="B69" s="66" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C69" s="66"/>
-      <c r="D69" s="66"/>
-      <c r="E69" s="66"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="66"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="67"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="55"/>
-      <c r="B70" s="66"/>
-      <c r="C70" s="66"/>
-      <c r="D70" s="66"/>
-      <c r="E70" s="66"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="66"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="67"/>
-    </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="55"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="66"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="66"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="66"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="67"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="55"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="66"/>
-      <c r="E72" s="66"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="66"/>
-      <c r="I72" s="66"/>
-      <c r="J72" s="67"/>
-    </row>
-    <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="55"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="66"/>
-      <c r="E73" s="66"/>
-      <c r="F73" s="66"/>
-      <c r="G73" s="66"/>
-      <c r="H73" s="66"/>
-      <c r="I73" s="66"/>
-      <c r="J73" s="67"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="55"/>
-      <c r="B74" s="66"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="66"/>
-      <c r="F74" s="66"/>
-      <c r="G74" s="66"/>
-      <c r="H74" s="66"/>
-      <c r="I74" s="66"/>
-      <c r="J74" s="67"/>
-    </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="55"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="66"/>
-      <c r="F75" s="66"/>
-      <c r="G75" s="66"/>
-      <c r="H75" s="66"/>
-      <c r="I75" s="66"/>
-      <c r="J75" s="67"/>
-    </row>
-    <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="55"/>
-      <c r="B76" s="66"/>
-      <c r="C76" s="66"/>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="66"/>
-      <c r="I76" s="66"/>
-      <c r="J76" s="67"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="55"/>
-      <c r="B77" s="66"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="66"/>
-      <c r="H77" s="66"/>
-      <c r="I77" s="66"/>
-      <c r="J77" s="67"/>
-    </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="55"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="66"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="66"/>
-      <c r="F78" s="66"/>
-      <c r="G78" s="66"/>
-      <c r="H78" s="66"/>
-      <c r="I78" s="66"/>
-      <c r="J78" s="67"/>
-    </row>
-    <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="55"/>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="66"/>
-      <c r="F79" s="66"/>
-      <c r="G79" s="66"/>
-      <c r="H79" s="66"/>
-      <c r="I79" s="66"/>
-      <c r="J79" s="67"/>
-    </row>
-    <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="55"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="67"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="55"/>
-      <c r="B81" s="66"/>
-      <c r="C81" s="66"/>
-      <c r="D81" s="66"/>
-      <c r="E81" s="66"/>
-      <c r="F81" s="66"/>
-      <c r="G81" s="66"/>
-      <c r="H81" s="66"/>
-      <c r="I81" s="66"/>
-      <c r="J81" s="67"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="55"/>
-      <c r="B82" s="66"/>
-      <c r="C82" s="66"/>
-      <c r="D82" s="66"/>
-      <c r="E82" s="66"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="66"/>
-      <c r="H82" s="66"/>
-      <c r="I82" s="66"/>
-      <c r="J82" s="67"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="55"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="66"/>
-      <c r="D83" s="66"/>
-      <c r="E83" s="66"/>
-      <c r="F83" s="66"/>
-      <c r="G83" s="66"/>
-      <c r="H83" s="66"/>
-      <c r="I83" s="66"/>
-      <c r="J83" s="67"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="55"/>
-      <c r="B84" s="66"/>
-      <c r="C84" s="66"/>
-      <c r="D84" s="66"/>
-      <c r="E84" s="66"/>
-      <c r="F84" s="66"/>
-      <c r="G84" s="66"/>
-      <c r="H84" s="66"/>
-      <c r="I84" s="66"/>
-      <c r="J84" s="67"/>
-    </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="55"/>
-      <c r="B85" s="66"/>
-      <c r="C85" s="66"/>
-      <c r="D85" s="66"/>
-      <c r="E85" s="66"/>
-      <c r="F85" s="66"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="66"/>
-      <c r="I85" s="66"/>
-      <c r="J85" s="67"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="58"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="68"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="54">
-        <v>5</v>
-      </c>
-      <c r="B87" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="61"/>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61"/>
-      <c r="J87" s="92"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="55"/>
-      <c r="B88" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="102"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="54">
-        <v>6</v>
-      </c>
-      <c r="B89" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" s="59"/>
-      <c r="D89" s="59"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="60"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="101"/>
-      <c r="B90" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="C90" s="71"/>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
-      <c r="F90" s="71"/>
-      <c r="G90" s="71"/>
-      <c r="H90" s="71"/>
-      <c r="I90" s="71"/>
-      <c r="J90" s="72"/>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="101"/>
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
-      <c r="G91" s="71"/>
-      <c r="H91" s="71"/>
-      <c r="I91" s="71"/>
-      <c r="J91" s="72"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="101"/>
-      <c r="B92" s="73"/>
-      <c r="C92" s="73"/>
-      <c r="D92" s="73"/>
-      <c r="E92" s="73"/>
-      <c r="F92" s="73"/>
-      <c r="G92" s="73"/>
-      <c r="H92" s="73"/>
-      <c r="I92" s="73"/>
-      <c r="J92" s="74"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="55"/>
-      <c r="B93" s="86" t="s">
-        <v>146</v>
-      </c>
-      <c r="C93" s="87"/>
-      <c r="D93" s="87"/>
-      <c r="E93" s="87"/>
-      <c r="F93" s="87"/>
-      <c r="G93" s="87"/>
-      <c r="H93" s="87"/>
-      <c r="I93" s="87"/>
-      <c r="J93" s="88"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="55"/>
-      <c r="B94" s="89"/>
-      <c r="C94" s="90"/>
-      <c r="D94" s="90"/>
-      <c r="E94" s="90"/>
-      <c r="F94" s="90"/>
-      <c r="G94" s="90"/>
-      <c r="H94" s="90"/>
-      <c r="I94" s="90"/>
-      <c r="J94" s="91"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="55"/>
-      <c r="B95" s="89"/>
-      <c r="C95" s="90"/>
-      <c r="D95" s="90"/>
-      <c r="E95" s="90"/>
-      <c r="F95" s="90"/>
-      <c r="G95" s="90"/>
-      <c r="H95" s="90"/>
-      <c r="I95" s="90"/>
-      <c r="J95" s="91"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="55"/>
-      <c r="B96" s="89"/>
-      <c r="C96" s="90"/>
-      <c r="D96" s="90"/>
-      <c r="E96" s="90"/>
-      <c r="F96" s="90"/>
-      <c r="G96" s="90"/>
-      <c r="H96" s="90"/>
-      <c r="I96" s="90"/>
-      <c r="J96" s="91"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="55"/>
-      <c r="B97" s="89"/>
-      <c r="C97" s="90"/>
-      <c r="D97" s="90"/>
-      <c r="E97" s="90"/>
-      <c r="F97" s="90"/>
-      <c r="G97" s="90"/>
-      <c r="H97" s="90"/>
-      <c r="I97" s="90"/>
-      <c r="J97" s="91"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="55"/>
-      <c r="B98" s="89"/>
-      <c r="C98" s="90"/>
-      <c r="D98" s="90"/>
-      <c r="E98" s="90"/>
-      <c r="F98" s="90"/>
-      <c r="G98" s="90"/>
-      <c r="H98" s="90"/>
-      <c r="I98" s="90"/>
-      <c r="J98" s="91"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="55"/>
-      <c r="B99" s="89"/>
-      <c r="C99" s="90"/>
-      <c r="D99" s="90"/>
-      <c r="E99" s="90"/>
-      <c r="F99" s="90"/>
-      <c r="G99" s="90"/>
-      <c r="H99" s="90"/>
-      <c r="I99" s="90"/>
-      <c r="J99" s="91"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="55"/>
-      <c r="B100" s="89"/>
-      <c r="C100" s="90"/>
-      <c r="D100" s="90"/>
-      <c r="E100" s="90"/>
-      <c r="F100" s="90"/>
-      <c r="G100" s="90"/>
-      <c r="H100" s="90"/>
-      <c r="I100" s="90"/>
-      <c r="J100" s="91"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="55"/>
-      <c r="B101" s="89"/>
-      <c r="C101" s="90"/>
-      <c r="D101" s="90"/>
-      <c r="E101" s="90"/>
-      <c r="F101" s="90"/>
-      <c r="G101" s="90"/>
-      <c r="H101" s="90"/>
-      <c r="I101" s="90"/>
-      <c r="J101" s="91"/>
-    </row>
-    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="55"/>
-      <c r="B102" s="89"/>
-      <c r="C102" s="90"/>
-      <c r="D102" s="90"/>
-      <c r="E102" s="90"/>
-      <c r="F102" s="90"/>
-      <c r="G102" s="90"/>
-      <c r="H102" s="90"/>
-      <c r="I102" s="90"/>
-      <c r="J102" s="91"/>
-    </row>
-    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="55"/>
-      <c r="B103" s="89"/>
-      <c r="C103" s="90"/>
-      <c r="D103" s="90"/>
-      <c r="E103" s="90"/>
-      <c r="F103" s="90"/>
-      <c r="G103" s="90"/>
-      <c r="H103" s="90"/>
-      <c r="I103" s="90"/>
-      <c r="J103" s="91"/>
-    </row>
-    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="55"/>
-      <c r="B104" s="89"/>
-      <c r="C104" s="90"/>
-      <c r="D104" s="90"/>
-      <c r="E104" s="90"/>
-      <c r="F104" s="90"/>
-      <c r="G104" s="90"/>
-      <c r="H104" s="90"/>
-      <c r="I104" s="90"/>
-      <c r="J104" s="91"/>
-    </row>
-    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="55"/>
-      <c r="B105" s="89"/>
-      <c r="C105" s="90"/>
-      <c r="D105" s="90"/>
-      <c r="E105" s="90"/>
-      <c r="F105" s="90"/>
-      <c r="G105" s="90"/>
-      <c r="H105" s="90"/>
-      <c r="I105" s="90"/>
-      <c r="J105" s="91"/>
-    </row>
-    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="55"/>
-      <c r="B106" s="89"/>
-      <c r="C106" s="90"/>
-      <c r="D106" s="90"/>
-      <c r="E106" s="90"/>
-      <c r="F106" s="90"/>
-      <c r="G106" s="90"/>
-      <c r="H106" s="90"/>
-      <c r="I106" s="90"/>
-      <c r="J106" s="91"/>
-    </row>
-    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="56"/>
-      <c r="B107" s="103"/>
-      <c r="C107" s="104"/>
-      <c r="D107" s="104"/>
-      <c r="E107" s="104"/>
-      <c r="F107" s="104"/>
-      <c r="G107" s="104"/>
-      <c r="H107" s="104"/>
-      <c r="I107" s="104"/>
-      <c r="J107" s="105"/>
-    </row>
-    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="54">
-        <v>7</v>
-      </c>
-      <c r="B108" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="61"/>
-      <c r="D108" s="61"/>
-      <c r="E108" s="61"/>
-      <c r="F108" s="61"/>
-      <c r="G108" s="61"/>
-      <c r="H108" s="61"/>
-      <c r="I108" s="61"/>
-      <c r="J108" s="92"/>
-    </row>
-    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="58"/>
-      <c r="B109" s="99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" s="99"/>
-      <c r="D109" s="99"/>
-      <c r="E109" s="99"/>
-      <c r="F109" s="99"/>
-      <c r="G109" s="99"/>
-      <c r="H109" s="99"/>
-      <c r="I109" s="99"/>
-      <c r="J109" s="100"/>
-    </row>
-    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="54">
-        <v>8</v>
-      </c>
-      <c r="B110" s="61" t="s">
+      <c r="B110" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="61"/>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
-      <c r="F110" s="61"/>
-      <c r="G110" s="61"/>
-      <c r="H110" s="61"/>
-      <c r="I110" s="61"/>
-      <c r="J110" s="92"/>
+      <c r="C110" s="69"/>
+      <c r="D110" s="69"/>
+      <c r="E110" s="69"/>
+      <c r="F110" s="69"/>
+      <c r="G110" s="69"/>
+      <c r="H110" s="69"/>
+      <c r="I110" s="69"/>
+      <c r="J110" s="100"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="55"/>
-      <c r="B111" s="94" t="s">
-        <v>147</v>
-      </c>
-      <c r="C111" s="69"/>
-      <c r="D111" s="69"/>
-      <c r="E111" s="69"/>
-      <c r="F111" s="69"/>
-      <c r="G111" s="69"/>
-      <c r="H111" s="69"/>
-      <c r="I111" s="69"/>
-      <c r="J111" s="70"/>
+      <c r="A111" s="63"/>
+      <c r="B111" s="102" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111" s="77"/>
+      <c r="D111" s="77"/>
+      <c r="E111" s="77"/>
+      <c r="F111" s="77"/>
+      <c r="G111" s="77"/>
+      <c r="H111" s="77"/>
+      <c r="I111" s="77"/>
+      <c r="J111" s="78"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="55"/>
-      <c r="B112" s="69"/>
-      <c r="C112" s="69"/>
-      <c r="D112" s="69"/>
-      <c r="E112" s="69"/>
-      <c r="F112" s="69"/>
-      <c r="G112" s="69"/>
-      <c r="H112" s="69"/>
-      <c r="I112" s="69"/>
-      <c r="J112" s="70"/>
+      <c r="A112" s="63"/>
+      <c r="B112" s="77"/>
+      <c r="C112" s="77"/>
+      <c r="D112" s="77"/>
+      <c r="E112" s="77"/>
+      <c r="F112" s="77"/>
+      <c r="G112" s="77"/>
+      <c r="H112" s="77"/>
+      <c r="I112" s="77"/>
+      <c r="J112" s="78"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="55"/>
-      <c r="B113" s="69"/>
-      <c r="C113" s="69"/>
-      <c r="D113" s="69"/>
-      <c r="E113" s="69"/>
-      <c r="F113" s="69"/>
-      <c r="G113" s="69"/>
-      <c r="H113" s="69"/>
-      <c r="I113" s="69"/>
-      <c r="J113" s="70"/>
+      <c r="A113" s="63"/>
+      <c r="B113" s="77"/>
+      <c r="C113" s="77"/>
+      <c r="D113" s="77"/>
+      <c r="E113" s="77"/>
+      <c r="F113" s="77"/>
+      <c r="G113" s="77"/>
+      <c r="H113" s="77"/>
+      <c r="I113" s="77"/>
+      <c r="J113" s="78"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="55"/>
-      <c r="B114" s="69"/>
-      <c r="C114" s="69"/>
-      <c r="D114" s="69"/>
-      <c r="E114" s="69"/>
-      <c r="F114" s="69"/>
-      <c r="G114" s="69"/>
-      <c r="H114" s="69"/>
-      <c r="I114" s="69"/>
-      <c r="J114" s="70"/>
+      <c r="A114" s="63"/>
+      <c r="B114" s="77"/>
+      <c r="C114" s="77"/>
+      <c r="D114" s="77"/>
+      <c r="E114" s="77"/>
+      <c r="F114" s="77"/>
+      <c r="G114" s="77"/>
+      <c r="H114" s="77"/>
+      <c r="I114" s="77"/>
+      <c r="J114" s="78"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="55"/>
-      <c r="B115" s="69"/>
-      <c r="C115" s="69"/>
-      <c r="D115" s="69"/>
-      <c r="E115" s="69"/>
-      <c r="F115" s="69"/>
-      <c r="G115" s="69"/>
-      <c r="H115" s="69"/>
-      <c r="I115" s="69"/>
-      <c r="J115" s="70"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="77"/>
+      <c r="C115" s="77"/>
+      <c r="D115" s="77"/>
+      <c r="E115" s="77"/>
+      <c r="F115" s="77"/>
+      <c r="G115" s="77"/>
+      <c r="H115" s="77"/>
+      <c r="I115" s="77"/>
+      <c r="J115" s="78"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="55"/>
-      <c r="B116" s="69"/>
-      <c r="C116" s="69"/>
-      <c r="D116" s="69"/>
-      <c r="E116" s="69"/>
-      <c r="F116" s="69"/>
-      <c r="G116" s="69"/>
-      <c r="H116" s="69"/>
-      <c r="I116" s="69"/>
-      <c r="J116" s="70"/>
+      <c r="A116" s="63"/>
+      <c r="B116" s="77"/>
+      <c r="C116" s="77"/>
+      <c r="D116" s="77"/>
+      <c r="E116" s="77"/>
+      <c r="F116" s="77"/>
+      <c r="G116" s="77"/>
+      <c r="H116" s="77"/>
+      <c r="I116" s="77"/>
+      <c r="J116" s="78"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="55"/>
-      <c r="B117" s="95" t="s">
+      <c r="A117" s="63"/>
+      <c r="B117" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="95"/>
-      <c r="D117" s="95"/>
-      <c r="E117" s="95"/>
-      <c r="F117" s="95"/>
-      <c r="G117" s="95"/>
-      <c r="H117" s="95"/>
-      <c r="I117" s="95"/>
-      <c r="J117" s="96"/>
+      <c r="C117" s="103"/>
+      <c r="D117" s="103"/>
+      <c r="E117" s="103"/>
+      <c r="F117" s="103"/>
+      <c r="G117" s="103"/>
+      <c r="H117" s="103"/>
+      <c r="I117" s="103"/>
+      <c r="J117" s="104"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="55"/>
-      <c r="B118" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="C118" s="69"/>
-      <c r="D118" s="69"/>
-      <c r="E118" s="69"/>
-      <c r="F118" s="69"/>
-      <c r="G118" s="69"/>
-      <c r="H118" s="69"/>
-      <c r="I118" s="69"/>
-      <c r="J118" s="70"/>
+      <c r="A118" s="63"/>
+      <c r="B118" s="102" t="s">
+        <v>145</v>
+      </c>
+      <c r="C118" s="77"/>
+      <c r="D118" s="77"/>
+      <c r="E118" s="77"/>
+      <c r="F118" s="77"/>
+      <c r="G118" s="77"/>
+      <c r="H118" s="77"/>
+      <c r="I118" s="77"/>
+      <c r="J118" s="78"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="55"/>
-      <c r="B119" s="69"/>
-      <c r="C119" s="69"/>
-      <c r="D119" s="69"/>
-      <c r="E119" s="69"/>
-      <c r="F119" s="69"/>
-      <c r="G119" s="69"/>
-      <c r="H119" s="69"/>
-      <c r="I119" s="69"/>
-      <c r="J119" s="70"/>
+      <c r="A119" s="63"/>
+      <c r="B119" s="77"/>
+      <c r="C119" s="77"/>
+      <c r="D119" s="77"/>
+      <c r="E119" s="77"/>
+      <c r="F119" s="77"/>
+      <c r="G119" s="77"/>
+      <c r="H119" s="77"/>
+      <c r="I119" s="77"/>
+      <c r="J119" s="78"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="55"/>
-      <c r="B120" s="69"/>
-      <c r="C120" s="69"/>
-      <c r="D120" s="69"/>
-      <c r="E120" s="69"/>
-      <c r="F120" s="69"/>
-      <c r="G120" s="69"/>
-      <c r="H120" s="69"/>
-      <c r="I120" s="69"/>
-      <c r="J120" s="70"/>
+      <c r="A120" s="63"/>
+      <c r="B120" s="77"/>
+      <c r="C120" s="77"/>
+      <c r="D120" s="77"/>
+      <c r="E120" s="77"/>
+      <c r="F120" s="77"/>
+      <c r="G120" s="77"/>
+      <c r="H120" s="77"/>
+      <c r="I120" s="77"/>
+      <c r="J120" s="78"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="55"/>
-      <c r="B121" s="69"/>
-      <c r="C121" s="69"/>
-      <c r="D121" s="69"/>
-      <c r="E121" s="69"/>
-      <c r="F121" s="69"/>
-      <c r="G121" s="69"/>
-      <c r="H121" s="69"/>
-      <c r="I121" s="69"/>
-      <c r="J121" s="70"/>
+      <c r="A121" s="63"/>
+      <c r="B121" s="77"/>
+      <c r="C121" s="77"/>
+      <c r="D121" s="77"/>
+      <c r="E121" s="77"/>
+      <c r="F121" s="77"/>
+      <c r="G121" s="77"/>
+      <c r="H121" s="77"/>
+      <c r="I121" s="77"/>
+      <c r="J121" s="78"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="55"/>
-      <c r="B122" s="69"/>
-      <c r="C122" s="69"/>
-      <c r="D122" s="69"/>
-      <c r="E122" s="69"/>
-      <c r="F122" s="69"/>
-      <c r="G122" s="69"/>
-      <c r="H122" s="69"/>
-      <c r="I122" s="69"/>
-      <c r="J122" s="70"/>
+      <c r="A122" s="63"/>
+      <c r="B122" s="77"/>
+      <c r="C122" s="77"/>
+      <c r="D122" s="77"/>
+      <c r="E122" s="77"/>
+      <c r="F122" s="77"/>
+      <c r="G122" s="77"/>
+      <c r="H122" s="77"/>
+      <c r="I122" s="77"/>
+      <c r="J122" s="78"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="55"/>
-      <c r="B123" s="69"/>
-      <c r="C123" s="69"/>
-      <c r="D123" s="69"/>
-      <c r="E123" s="69"/>
-      <c r="F123" s="69"/>
-      <c r="G123" s="69"/>
-      <c r="H123" s="69"/>
-      <c r="I123" s="69"/>
-      <c r="J123" s="70"/>
+      <c r="A123" s="63"/>
+      <c r="B123" s="77"/>
+      <c r="C123" s="77"/>
+      <c r="D123" s="77"/>
+      <c r="E123" s="77"/>
+      <c r="F123" s="77"/>
+      <c r="G123" s="77"/>
+      <c r="H123" s="77"/>
+      <c r="I123" s="77"/>
+      <c r="J123" s="78"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="55"/>
-      <c r="B124" s="69"/>
-      <c r="C124" s="69"/>
-      <c r="D124" s="69"/>
-      <c r="E124" s="69"/>
-      <c r="F124" s="69"/>
-      <c r="G124" s="69"/>
-      <c r="H124" s="69"/>
-      <c r="I124" s="69"/>
-      <c r="J124" s="70"/>
+      <c r="A124" s="63"/>
+      <c r="B124" s="77"/>
+      <c r="C124" s="77"/>
+      <c r="D124" s="77"/>
+      <c r="E124" s="77"/>
+      <c r="F124" s="77"/>
+      <c r="G124" s="77"/>
+      <c r="H124" s="77"/>
+      <c r="I124" s="77"/>
+      <c r="J124" s="78"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="56"/>
-      <c r="B125" s="97"/>
-      <c r="C125" s="97"/>
-      <c r="D125" s="97"/>
-      <c r="E125" s="97"/>
-      <c r="F125" s="97"/>
-      <c r="G125" s="97"/>
-      <c r="H125" s="97"/>
-      <c r="I125" s="97"/>
-      <c r="J125" s="98"/>
+      <c r="A125" s="64"/>
+      <c r="B125" s="105"/>
+      <c r="C125" s="105"/>
+      <c r="D125" s="105"/>
+      <c r="E125" s="105"/>
+      <c r="F125" s="105"/>
+      <c r="G125" s="105"/>
+      <c r="H125" s="105"/>
+      <c r="I125" s="105"/>
+      <c r="J125" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -6292,71 +6270,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="39"/>
-      <c r="H6" s="42" t="s">
+      <c r="G6" s="44"/>
+      <c r="H6" s="47" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="36"/>
+      <c r="A7" s="41"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6366,554 +6344,555 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="43"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="48"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="211"/>
-      <c r="B8" s="217" t="s">
+      <c r="A8" s="219">
+        <v>1</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="61"/>
+      <c r="H8" s="36"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="219">
+        <v>2</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C8" s="212" t="s">
+      <c r="E9" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="61"/>
+      <c r="H9" s="36"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="219">
+        <v>3</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="213" t="s">
+      <c r="E10" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="G10" s="61"/>
+      <c r="H10" s="36"/>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="219">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="213" t="s">
+      <c r="E11" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="61"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="219">
+        <v>5</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="61"/>
+      <c r="H12" s="36"/>
+    </row>
+    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="219">
+        <v>6</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="38"/>
+      <c r="H13" s="27"/>
+    </row>
+    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="219">
+        <v>7</v>
+      </c>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="27"/>
+    </row>
+    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="219">
+        <v>8</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="27"/>
+    </row>
+    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="219">
+        <v>9</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="27"/>
+    </row>
+    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="219">
+        <v>10</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="27"/>
+    </row>
+    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="219">
+        <v>11</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="27"/>
+    </row>
+    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="219">
+        <v>12</v>
+      </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="G19" s="50"/>
+      <c r="H19" s="27"/>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="219">
+        <v>13</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="27"/>
+    </row>
+    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="219">
+        <v>14</v>
+      </c>
+      <c r="B21" s="53"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="50"/>
+      <c r="H21" s="27"/>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="219">
+        <v>15</v>
+      </c>
+      <c r="B22" s="54"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="50"/>
+      <c r="H22" s="27"/>
+    </row>
+    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="219">
+        <v>16</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="27"/>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="219">
+        <v>17</v>
+      </c>
+      <c r="B24" s="55"/>
+      <c r="C24" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="27"/>
+    </row>
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="219">
+        <v>18</v>
+      </c>
+      <c r="B25" s="52"/>
+      <c r="C25" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="27"/>
+    </row>
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="219">
+        <v>19</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="215" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="216"/>
-      <c r="H8" s="214"/>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="211"/>
-      <c r="B9" s="218"/>
-      <c r="C9" s="217" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="213" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9" s="213" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="215" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="216"/>
-      <c r="H9" s="214"/>
-    </row>
-    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="211"/>
-      <c r="B10" s="218"/>
-      <c r="C10" s="218"/>
-      <c r="D10" s="213" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="213" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="215" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="216"/>
-      <c r="H10" s="214"/>
-    </row>
-    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="211"/>
-      <c r="B11" s="218"/>
-      <c r="C11" s="218"/>
-      <c r="D11" s="213" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="213" t="s">
+      <c r="F26" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="27"/>
+    </row>
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="219">
+        <v>20</v>
+      </c>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="215" t="s">
-        <v>176</v>
-      </c>
-      <c r="G11" s="216"/>
-      <c r="H11" s="214"/>
-    </row>
-    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="211"/>
-      <c r="B12" s="219"/>
-      <c r="C12" s="219"/>
-      <c r="D12" s="213" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="213" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="215" t="s">
-        <v>177</v>
-      </c>
-      <c r="G12" s="216"/>
-      <c r="H12" s="214"/>
-    </row>
-    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>2</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="45"/>
-      <c r="H13" s="27"/>
-    </row>
-    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>3</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="27"/>
-    </row>
-    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>6</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="44" t="s">
+      <c r="F27" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>7</v>
-      </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="45"/>
-      <c r="H16" s="27"/>
-    </row>
-    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
-        <v>8</v>
-      </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="45"/>
-      <c r="H17" s="27"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
-        <v>9</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="27"/>
-    </row>
-    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
-        <v>10</v>
-      </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="G19" s="47"/>
-      <c r="H19" s="27"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
-        <v>11</v>
-      </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="27"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
-        <v>12</v>
-      </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G21" s="47"/>
-      <c r="H21" s="27"/>
-    </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>13</v>
-      </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="G22" s="47"/>
-      <c r="H22" s="27"/>
-    </row>
-    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
-        <v>14</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" s="45"/>
-      <c r="H23" s="27"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>15</v>
-      </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="45"/>
-      <c r="H24" s="27"/>
-    </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>16</v>
-      </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="45"/>
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>17</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="45"/>
-      <c r="H26" s="27"/>
-    </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>18</v>
-      </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="G27" s="45"/>
+      <c r="G27" s="38"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
-        <v>19</v>
+      <c r="A28" s="219">
+        <v>21</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="45"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
-        <v>20</v>
+      <c r="A29" s="219">
+        <v>22</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="45"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
-        <v>21</v>
+      <c r="A30" s="219">
+        <v>23</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="45"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
-        <v>22</v>
+      <c r="A31" s="219">
+        <v>24</v>
       </c>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="45"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="38"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
-        <v>23</v>
+      <c r="A32" s="219">
+        <v>25</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="45"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
-        <v>24</v>
+      <c r="A33" s="219">
+        <v>26</v>
       </c>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="45"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>25</v>
+      <c r="A34" s="219">
+        <v>27</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="45"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
-        <v>26</v>
+      <c r="A35" s="219">
+        <v>28</v>
       </c>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="45"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>27</v>
+      <c r="A36" s="219">
+        <v>29</v>
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="45"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>28</v>
+      <c r="A37" s="219">
+        <v>30</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="45"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="38"/>
       <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
-        <v>29</v>
+      <c r="A38" s="219">
+        <v>31</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="45"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38"/>
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>30</v>
+      <c r="A39" s="219">
+        <v>32</v>
       </c>
       <c r="B39" s="27"/>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="38"/>
       <c r="H39" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
+  <mergeCells count="49">
     <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:B22"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B15:B22"/>
     <mergeCell ref="C19:C22"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="F35:G35"/>
@@ -6949,6 +6928,12 @@
     <mergeCell ref="A2:H4"/>
     <mergeCell ref="F6:G7"/>
     <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6975,458 +6960,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="112"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="36" t="s">
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="41" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="36"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="114" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
+        <v>106</v>
+      </c>
+      <c r="D7" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="109"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="109"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="107"/>
+      <c r="B10" s="115"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="108" t="s">
+      <c r="B11" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="106" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
+      <c r="C11" s="114" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="109"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="69" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="109"/>
+      <c r="B13" s="117"/>
       <c r="C13" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="94" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
+        <v>111</v>
+      </c>
+      <c r="D13" s="102" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="107"/>
+      <c r="B14" s="115"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="116" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
+        <v>113</v>
+      </c>
+      <c r="D15" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="109"/>
+      <c r="B16" s="117"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="109"/>
+      <c r="B17" s="117"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="107"/>
+      <c r="B18" s="115"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="116" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
+        <v>115</v>
+      </c>
+      <c r="D19" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="109"/>
+      <c r="B20" s="117"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="109"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="107"/>
+      <c r="B22" s="115"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="116" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="69" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
+        <v>117</v>
+      </c>
+      <c r="D23" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="113"/>
+      <c r="B24" s="121"/>
       <c r="C24" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="69" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
+        <v>119</v>
+      </c>
+      <c r="D24" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="113"/>
+      <c r="B25" s="121"/>
       <c r="C25" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
+        <v>120</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="113"/>
+      <c r="B26" s="121"/>
       <c r="C26" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="94"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
+        <v>121</v>
+      </c>
+      <c r="D26" s="102" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="114"/>
+      <c r="B27" s="122"/>
       <c r="C27" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="115" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="117"/>
+        <v>123</v>
+      </c>
+      <c r="D27" s="123" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="125"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="108" t="s">
+      <c r="B28" s="116" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
+        <v>124</v>
+      </c>
+      <c r="D28" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="109"/>
+      <c r="B29" s="117"/>
       <c r="C29" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
+        <v>126</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="109"/>
+      <c r="B30" s="117"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="107"/>
+      <c r="B31" s="115"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7435,11 +7420,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7448,11 +7433,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7461,11 +7446,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7474,11 +7459,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7487,11 +7472,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7500,11 +7485,11 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
@@ -7578,23 +7563,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="205" t="s">
+      <c r="B1" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="206"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
+      <c r="N1" s="214"/>
+      <c r="O1" s="214"/>
+      <c r="P1" s="214"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7611,141 +7596,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="158" t="s">
-        <v>152</v>
-      </c>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="158"/>
-      <c r="S2" s="158"/>
-      <c r="T2" s="158"/>
-      <c r="U2" s="158"/>
-      <c r="V2" s="158"/>
-      <c r="W2" s="158"/>
-      <c r="X2" s="158"/>
-      <c r="Y2" s="158"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="158"/>
-      <c r="AB2" s="158"/>
-      <c r="AC2" s="158"/>
-      <c r="AD2" s="158"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="166" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="166"/>
+      <c r="P2" s="166"/>
+      <c r="Q2" s="166"/>
+      <c r="R2" s="166"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="166"/>
+      <c r="U2" s="166"/>
+      <c r="V2" s="166"/>
+      <c r="W2" s="166"/>
+      <c r="X2" s="166"/>
+      <c r="Y2" s="166"/>
+      <c r="Z2" s="166"/>
+      <c r="AA2" s="166"/>
+      <c r="AB2" s="166"/>
+      <c r="AC2" s="166"/>
+      <c r="AD2" s="166"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="165" t="s">
+      <c r="B4" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152" t="s">
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="152"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="152"/>
-      <c r="Q4" s="159" t="s">
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="160"/>
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="160"/>
+      <c r="Q4" s="167" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="163"/>
-      <c r="S4" s="160"/>
-      <c r="T4" s="159" t="s">
+      <c r="R4" s="171"/>
+      <c r="S4" s="168"/>
+      <c r="T4" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="163"/>
-      <c r="V4" s="163"/>
-      <c r="W4" s="160"/>
-      <c r="X4" s="159" t="s">
+      <c r="U4" s="171"/>
+      <c r="V4" s="171"/>
+      <c r="W4" s="168"/>
+      <c r="X4" s="167" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="160"/>
-      <c r="Z4" s="152" t="s">
+      <c r="Y4" s="168"/>
+      <c r="Z4" s="160" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA4" s="160"/>
+      <c r="AB4" s="160"/>
+      <c r="AC4" s="160" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD4" s="160"/>
+      <c r="AE4" s="160"/>
+      <c r="AF4" s="160" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG4" s="160"/>
+      <c r="AH4" s="160"/>
+      <c r="AI4" s="160" t="s">
         <v>137</v>
       </c>
-      <c r="AA4" s="152"/>
-      <c r="AB4" s="152"/>
-      <c r="AC4" s="152" t="s">
+      <c r="AJ4" s="160"/>
+      <c r="AK4" s="160"/>
+      <c r="AL4" s="160" t="s">
         <v>138</v>
       </c>
-      <c r="AD4" s="152"/>
-      <c r="AE4" s="152"/>
-      <c r="AF4" s="152" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG4" s="152"/>
-      <c r="AH4" s="152"/>
-      <c r="AI4" s="152" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ4" s="152"/>
-      <c r="AK4" s="152"/>
-      <c r="AL4" s="152" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM4" s="152"/>
-      <c r="AN4" s="152"/>
-      <c r="AO4" s="152" t="s">
+      <c r="AM4" s="160"/>
+      <c r="AN4" s="160"/>
+      <c r="AO4" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="152"/>
-      <c r="AQ4" s="152"/>
-      <c r="AR4" s="152"/>
-      <c r="AS4" s="152"/>
-      <c r="AT4" s="152"/>
-      <c r="AU4" s="152"/>
-      <c r="AV4" s="152"/>
-      <c r="AW4" s="152"/>
-      <c r="AX4" s="152"/>
-      <c r="AY4" s="152"/>
-      <c r="AZ4" s="153"/>
+      <c r="AP4" s="160"/>
+      <c r="AQ4" s="160"/>
+      <c r="AR4" s="160"/>
+      <c r="AS4" s="160"/>
+      <c r="AT4" s="160"/>
+      <c r="AU4" s="160"/>
+      <c r="AV4" s="160"/>
+      <c r="AW4" s="160"/>
+      <c r="AX4" s="160"/>
+      <c r="AY4" s="160"/>
+      <c r="AZ4" s="161"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="166"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
-      <c r="L5" s="154"/>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
-      <c r="O5" s="154"/>
-      <c r="P5" s="154"/>
-      <c r="Q5" s="161"/>
-      <c r="R5" s="164"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="161"/>
-      <c r="U5" s="164"/>
-      <c r="V5" s="164"/>
-      <c r="W5" s="162"/>
-      <c r="X5" s="161"/>
-      <c r="Y5" s="162"/>
+      <c r="B5" s="174"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="162"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="162"/>
+      <c r="J5" s="162"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="162"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="169"/>
+      <c r="R5" s="172"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="169"/>
+      <c r="U5" s="172"/>
+      <c r="V5" s="172"/>
+      <c r="W5" s="170"/>
+      <c r="X5" s="169"/>
+      <c r="Y5" s="170"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7791,58 +7776,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="154"/>
-      <c r="AP5" s="154"/>
-      <c r="AQ5" s="154"/>
-      <c r="AR5" s="154"/>
-      <c r="AS5" s="154"/>
-      <c r="AT5" s="154"/>
-      <c r="AU5" s="154"/>
-      <c r="AV5" s="154"/>
-      <c r="AW5" s="154"/>
-      <c r="AX5" s="154"/>
-      <c r="AY5" s="154"/>
-      <c r="AZ5" s="155"/>
+      <c r="AO5" s="162"/>
+      <c r="AP5" s="162"/>
+      <c r="AQ5" s="162"/>
+      <c r="AR5" s="162"/>
+      <c r="AS5" s="162"/>
+      <c r="AT5" s="162"/>
+      <c r="AU5" s="162"/>
+      <c r="AV5" s="162"/>
+      <c r="AW5" s="162"/>
+      <c r="AX5" s="162"/>
+      <c r="AY5" s="162"/>
+      <c r="AZ5" s="163"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="181">
+      <c r="B6" s="189">
         <v>1</v>
       </c>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="175" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="167" t="s">
-        <v>132</v>
-      </c>
-      <c r="K6" s="167"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="167"/>
-      <c r="N6" s="167"/>
-      <c r="O6" s="167"/>
-      <c r="P6" s="167"/>
-      <c r="Q6" s="158" t="s">
-        <v>133</v>
-      </c>
-      <c r="R6" s="158"/>
-      <c r="S6" s="158"/>
-      <c r="T6" s="172" t="s">
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="175"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="175"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="175" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="175"/>
+      <c r="L6" s="175"/>
+      <c r="M6" s="175"/>
+      <c r="N6" s="175"/>
+      <c r="O6" s="175"/>
+      <c r="P6" s="175"/>
+      <c r="Q6" s="166" t="s">
+        <v>130</v>
+      </c>
+      <c r="R6" s="166"/>
+      <c r="S6" s="166"/>
+      <c r="T6" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="172"/>
-      <c r="V6" s="170">
+      <c r="U6" s="180"/>
+      <c r="V6" s="178">
         <v>0</v>
       </c>
-      <c r="W6" s="170"/>
-      <c r="X6" s="156">
+      <c r="W6" s="178"/>
+      <c r="X6" s="164">
         <v>0</v>
       </c>
-      <c r="Y6" s="156"/>
+      <c r="Y6" s="164"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7858,50 +7843,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="167"/>
-      <c r="AP6" s="167"/>
-      <c r="AQ6" s="167"/>
-      <c r="AR6" s="167"/>
-      <c r="AS6" s="167"/>
-      <c r="AT6" s="167"/>
-      <c r="AU6" s="167"/>
-      <c r="AV6" s="167"/>
-      <c r="AW6" s="167"/>
-      <c r="AX6" s="167"/>
-      <c r="AY6" s="167"/>
-      <c r="AZ6" s="168"/>
+      <c r="AO6" s="175"/>
+      <c r="AP6" s="175"/>
+      <c r="AQ6" s="175"/>
+      <c r="AR6" s="175"/>
+      <c r="AS6" s="175"/>
+      <c r="AT6" s="175"/>
+      <c r="AU6" s="175"/>
+      <c r="AV6" s="175"/>
+      <c r="AW6" s="175"/>
+      <c r="AX6" s="175"/>
+      <c r="AY6" s="175"/>
+      <c r="AZ6" s="176"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="181"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="167"/>
-      <c r="H7" s="167"/>
-      <c r="I7" s="167"/>
-      <c r="J7" s="167"/>
-      <c r="K7" s="167"/>
-      <c r="L7" s="167"/>
-      <c r="M7" s="167"/>
-      <c r="N7" s="167"/>
-      <c r="O7" s="167"/>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="158"/>
-      <c r="R7" s="158"/>
-      <c r="S7" s="158"/>
-      <c r="T7" s="169" t="s">
+      <c r="B7" s="189"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="175"/>
+      <c r="E7" s="175"/>
+      <c r="F7" s="175"/>
+      <c r="G7" s="175"/>
+      <c r="H7" s="175"/>
+      <c r="I7" s="175"/>
+      <c r="J7" s="175"/>
+      <c r="K7" s="175"/>
+      <c r="L7" s="175"/>
+      <c r="M7" s="175"/>
+      <c r="N7" s="175"/>
+      <c r="O7" s="175"/>
+      <c r="P7" s="175"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="166"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="169"/>
-      <c r="V7" s="171">
+      <c r="U7" s="177"/>
+      <c r="V7" s="179">
         <v>0</v>
       </c>
-      <c r="W7" s="171"/>
-      <c r="X7" s="157">
+      <c r="W7" s="179"/>
+      <c r="X7" s="165">
         <v>1</v>
       </c>
-      <c r="Y7" s="157"/>
+      <c r="Y7" s="165"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7917,58 +7902,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="167"/>
-      <c r="AP7" s="167"/>
-      <c r="AQ7" s="167"/>
-      <c r="AR7" s="167"/>
-      <c r="AS7" s="167"/>
-      <c r="AT7" s="167"/>
-      <c r="AU7" s="167"/>
-      <c r="AV7" s="167"/>
-      <c r="AW7" s="167"/>
-      <c r="AX7" s="167"/>
-      <c r="AY7" s="167"/>
-      <c r="AZ7" s="168"/>
+      <c r="AO7" s="175"/>
+      <c r="AP7" s="175"/>
+      <c r="AQ7" s="175"/>
+      <c r="AR7" s="175"/>
+      <c r="AS7" s="175"/>
+      <c r="AT7" s="175"/>
+      <c r="AU7" s="175"/>
+      <c r="AV7" s="175"/>
+      <c r="AW7" s="175"/>
+      <c r="AX7" s="175"/>
+      <c r="AY7" s="175"/>
+      <c r="AZ7" s="176"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="181">
+      <c r="B8" s="189">
         <v>2</v>
       </c>
-      <c r="C8" s="167" t="s">
+      <c r="C8" s="175" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="167"/>
-      <c r="J8" s="143" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="126"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="126"/>
-      <c r="N8" s="126"/>
-      <c r="O8" s="126"/>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="208" t="s">
-        <v>135</v>
-      </c>
-      <c r="R8" s="208"/>
-      <c r="S8" s="208"/>
-      <c r="T8" s="172" t="s">
+      <c r="D8" s="175"/>
+      <c r="E8" s="175"/>
+      <c r="F8" s="175"/>
+      <c r="G8" s="175"/>
+      <c r="H8" s="175"/>
+      <c r="I8" s="175"/>
+      <c r="J8" s="151" t="s">
+        <v>131</v>
+      </c>
+      <c r="K8" s="134"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
+      <c r="N8" s="134"/>
+      <c r="O8" s="134"/>
+      <c r="P8" s="135"/>
+      <c r="Q8" s="216" t="s">
+        <v>132</v>
+      </c>
+      <c r="R8" s="216"/>
+      <c r="S8" s="216"/>
+      <c r="T8" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="172"/>
-      <c r="V8" s="170">
+      <c r="U8" s="180"/>
+      <c r="V8" s="178">
         <v>0</v>
       </c>
-      <c r="W8" s="170"/>
-      <c r="X8" s="156">
+      <c r="W8" s="178"/>
+      <c r="X8" s="164">
         <v>0</v>
       </c>
-      <c r="Y8" s="156"/>
+      <c r="Y8" s="164"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7984,50 +7969,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="167"/>
-      <c r="AP8" s="167"/>
-      <c r="AQ8" s="167"/>
-      <c r="AR8" s="167"/>
-      <c r="AS8" s="167"/>
-      <c r="AT8" s="167"/>
-      <c r="AU8" s="167"/>
-      <c r="AV8" s="167"/>
-      <c r="AW8" s="167"/>
-      <c r="AX8" s="167"/>
-      <c r="AY8" s="167"/>
-      <c r="AZ8" s="168"/>
+      <c r="AO8" s="175"/>
+      <c r="AP8" s="175"/>
+      <c r="AQ8" s="175"/>
+      <c r="AR8" s="175"/>
+      <c r="AS8" s="175"/>
+      <c r="AT8" s="175"/>
+      <c r="AU8" s="175"/>
+      <c r="AV8" s="175"/>
+      <c r="AW8" s="175"/>
+      <c r="AX8" s="175"/>
+      <c r="AY8" s="175"/>
+      <c r="AZ8" s="176"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="181"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="129"/>
-      <c r="N9" s="129"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="208"/>
-      <c r="S9" s="208"/>
-      <c r="T9" s="169" t="s">
+      <c r="B9" s="189"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="175"/>
+      <c r="G9" s="175"/>
+      <c r="H9" s="175"/>
+      <c r="I9" s="175"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="137"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="137"/>
+      <c r="P9" s="138"/>
+      <c r="Q9" s="216"/>
+      <c r="R9" s="216"/>
+      <c r="S9" s="216"/>
+      <c r="T9" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="169"/>
-      <c r="V9" s="171">
+      <c r="U9" s="177"/>
+      <c r="V9" s="179">
         <v>0</v>
       </c>
-      <c r="W9" s="171"/>
-      <c r="X9" s="157">
+      <c r="W9" s="179"/>
+      <c r="X9" s="165">
         <v>1</v>
       </c>
-      <c r="Y9" s="157"/>
+      <c r="Y9" s="165"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -8043,58 +8028,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="167"/>
-      <c r="AP9" s="167"/>
-      <c r="AQ9" s="167"/>
-      <c r="AR9" s="167"/>
-      <c r="AS9" s="167"/>
-      <c r="AT9" s="167"/>
-      <c r="AU9" s="167"/>
-      <c r="AV9" s="167"/>
-      <c r="AW9" s="167"/>
-      <c r="AX9" s="167"/>
-      <c r="AY9" s="167"/>
-      <c r="AZ9" s="168"/>
+      <c r="AO9" s="175"/>
+      <c r="AP9" s="175"/>
+      <c r="AQ9" s="175"/>
+      <c r="AR9" s="175"/>
+      <c r="AS9" s="175"/>
+      <c r="AT9" s="175"/>
+      <c r="AU9" s="175"/>
+      <c r="AV9" s="175"/>
+      <c r="AW9" s="175"/>
+      <c r="AX9" s="175"/>
+      <c r="AY9" s="175"/>
+      <c r="AZ9" s="176"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="181">
+      <c r="B10" s="189">
         <v>3</v>
       </c>
-      <c r="C10" s="167" t="s">
+      <c r="C10" s="175" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
-      <c r="J10" s="207" t="s">
-        <v>142</v>
-      </c>
-      <c r="K10" s="167"/>
-      <c r="L10" s="167"/>
-      <c r="M10" s="167"/>
-      <c r="N10" s="167"/>
-      <c r="O10" s="167"/>
-      <c r="P10" s="167"/>
-      <c r="Q10" s="158" t="s">
-        <v>133</v>
-      </c>
-      <c r="R10" s="158"/>
-      <c r="S10" s="158"/>
-      <c r="T10" s="172" t="s">
+      <c r="D10" s="175"/>
+      <c r="E10" s="175"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="175"/>
+      <c r="I10" s="175"/>
+      <c r="J10" s="215" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="175"/>
+      <c r="L10" s="175"/>
+      <c r="M10" s="175"/>
+      <c r="N10" s="175"/>
+      <c r="O10" s="175"/>
+      <c r="P10" s="175"/>
+      <c r="Q10" s="166" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" s="166"/>
+      <c r="S10" s="166"/>
+      <c r="T10" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="172"/>
-      <c r="V10" s="170">
+      <c r="U10" s="180"/>
+      <c r="V10" s="178">
         <v>0</v>
       </c>
-      <c r="W10" s="170"/>
-      <c r="X10" s="156">
+      <c r="W10" s="178"/>
+      <c r="X10" s="164">
         <v>0</v>
       </c>
-      <c r="Y10" s="156"/>
+      <c r="Y10" s="164"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -8110,50 +8095,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="167"/>
-      <c r="AP10" s="167"/>
-      <c r="AQ10" s="167"/>
-      <c r="AR10" s="167"/>
-      <c r="AS10" s="167"/>
-      <c r="AT10" s="167"/>
-      <c r="AU10" s="167"/>
-      <c r="AV10" s="167"/>
-      <c r="AW10" s="167"/>
-      <c r="AX10" s="167"/>
-      <c r="AY10" s="167"/>
-      <c r="AZ10" s="168"/>
+      <c r="AO10" s="175"/>
+      <c r="AP10" s="175"/>
+      <c r="AQ10" s="175"/>
+      <c r="AR10" s="175"/>
+      <c r="AS10" s="175"/>
+      <c r="AT10" s="175"/>
+      <c r="AU10" s="175"/>
+      <c r="AV10" s="175"/>
+      <c r="AW10" s="175"/>
+      <c r="AX10" s="175"/>
+      <c r="AY10" s="175"/>
+      <c r="AZ10" s="176"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="181"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="167"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
-      <c r="J11" s="167"/>
-      <c r="K11" s="167"/>
-      <c r="L11" s="167"/>
-      <c r="M11" s="167"/>
-      <c r="N11" s="167"/>
-      <c r="O11" s="167"/>
-      <c r="P11" s="167"/>
-      <c r="Q11" s="158"/>
-      <c r="R11" s="158"/>
-      <c r="S11" s="158"/>
-      <c r="T11" s="169" t="s">
+      <c r="B11" s="189"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="175"/>
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="175"/>
+      <c r="N11" s="175"/>
+      <c r="O11" s="175"/>
+      <c r="P11" s="175"/>
+      <c r="Q11" s="166"/>
+      <c r="R11" s="166"/>
+      <c r="S11" s="166"/>
+      <c r="T11" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="169"/>
-      <c r="V11" s="171">
+      <c r="U11" s="177"/>
+      <c r="V11" s="179">
         <v>0</v>
       </c>
-      <c r="W11" s="171"/>
-      <c r="X11" s="157">
+      <c r="W11" s="179"/>
+      <c r="X11" s="165">
         <v>0</v>
       </c>
-      <c r="Y11" s="157"/>
+      <c r="Y11" s="165"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -8169,58 +8154,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="167"/>
-      <c r="AP11" s="167"/>
-      <c r="AQ11" s="167"/>
-      <c r="AR11" s="167"/>
-      <c r="AS11" s="167"/>
-      <c r="AT11" s="167"/>
-      <c r="AU11" s="167"/>
-      <c r="AV11" s="167"/>
-      <c r="AW11" s="167"/>
-      <c r="AX11" s="167"/>
-      <c r="AY11" s="167"/>
-      <c r="AZ11" s="168"/>
+      <c r="AO11" s="175"/>
+      <c r="AP11" s="175"/>
+      <c r="AQ11" s="175"/>
+      <c r="AR11" s="175"/>
+      <c r="AS11" s="175"/>
+      <c r="AT11" s="175"/>
+      <c r="AU11" s="175"/>
+      <c r="AV11" s="175"/>
+      <c r="AW11" s="175"/>
+      <c r="AX11" s="175"/>
+      <c r="AY11" s="175"/>
+      <c r="AZ11" s="176"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="181">
+      <c r="B12" s="189">
         <v>4</v>
       </c>
-      <c r="C12" s="167" t="s">
+      <c r="C12" s="175" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="167" t="s">
-        <v>136</v>
-      </c>
-      <c r="K12" s="167"/>
-      <c r="L12" s="167"/>
-      <c r="M12" s="167"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="167"/>
-      <c r="P12" s="167"/>
-      <c r="Q12" s="131" t="s">
+      <c r="D12" s="175"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="175"/>
+      <c r="H12" s="175"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175" t="s">
         <v>133</v>
       </c>
-      <c r="R12" s="132"/>
-      <c r="S12" s="133"/>
-      <c r="T12" s="172" t="s">
+      <c r="K12" s="175"/>
+      <c r="L12" s="175"/>
+      <c r="M12" s="175"/>
+      <c r="N12" s="175"/>
+      <c r="O12" s="175"/>
+      <c r="P12" s="175"/>
+      <c r="Q12" s="139" t="s">
+        <v>130</v>
+      </c>
+      <c r="R12" s="140"/>
+      <c r="S12" s="141"/>
+      <c r="T12" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="172"/>
-      <c r="V12" s="170">
+      <c r="U12" s="180"/>
+      <c r="V12" s="178">
         <v>0</v>
       </c>
-      <c r="W12" s="170"/>
-      <c r="X12" s="156">
+      <c r="W12" s="178"/>
+      <c r="X12" s="164">
         <v>0</v>
       </c>
-      <c r="Y12" s="156"/>
+      <c r="Y12" s="164"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -8236,50 +8221,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="167"/>
-      <c r="AP12" s="167"/>
-      <c r="AQ12" s="167"/>
-      <c r="AR12" s="167"/>
-      <c r="AS12" s="167"/>
-      <c r="AT12" s="167"/>
-      <c r="AU12" s="167"/>
-      <c r="AV12" s="167"/>
-      <c r="AW12" s="167"/>
-      <c r="AX12" s="167"/>
-      <c r="AY12" s="167"/>
-      <c r="AZ12" s="168"/>
+      <c r="AO12" s="175"/>
+      <c r="AP12" s="175"/>
+      <c r="AQ12" s="175"/>
+      <c r="AR12" s="175"/>
+      <c r="AS12" s="175"/>
+      <c r="AT12" s="175"/>
+      <c r="AU12" s="175"/>
+      <c r="AV12" s="175"/>
+      <c r="AW12" s="175"/>
+      <c r="AX12" s="175"/>
+      <c r="AY12" s="175"/>
+      <c r="AZ12" s="176"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="181"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="167"/>
-      <c r="G13" s="167"/>
-      <c r="H13" s="167"/>
-      <c r="I13" s="167"/>
-      <c r="J13" s="167"/>
-      <c r="K13" s="167"/>
-      <c r="L13" s="167"/>
-      <c r="M13" s="167"/>
-      <c r="N13" s="167"/>
-      <c r="O13" s="167"/>
-      <c r="P13" s="167"/>
-      <c r="Q13" s="134"/>
-      <c r="R13" s="135"/>
-      <c r="S13" s="136"/>
-      <c r="T13" s="169" t="s">
+      <c r="B13" s="189"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
+      <c r="L13" s="175"/>
+      <c r="M13" s="175"/>
+      <c r="N13" s="175"/>
+      <c r="O13" s="175"/>
+      <c r="P13" s="175"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="143"/>
+      <c r="S13" s="144"/>
+      <c r="T13" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="169"/>
-      <c r="V13" s="171">
+      <c r="U13" s="177"/>
+      <c r="V13" s="179">
         <v>0</v>
       </c>
-      <c r="W13" s="171"/>
-      <c r="X13" s="157">
+      <c r="W13" s="179"/>
+      <c r="X13" s="165">
         <v>0</v>
       </c>
-      <c r="Y13" s="157"/>
+      <c r="Y13" s="165"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8295,54 +8280,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="167"/>
-      <c r="AP13" s="167"/>
-      <c r="AQ13" s="167"/>
-      <c r="AR13" s="167"/>
-      <c r="AS13" s="167"/>
-      <c r="AT13" s="167"/>
-      <c r="AU13" s="167"/>
-      <c r="AV13" s="167"/>
-      <c r="AW13" s="167"/>
-      <c r="AX13" s="167"/>
-      <c r="AY13" s="167"/>
-      <c r="AZ13" s="168"/>
+      <c r="AO13" s="175"/>
+      <c r="AP13" s="175"/>
+      <c r="AQ13" s="175"/>
+      <c r="AR13" s="175"/>
+      <c r="AS13" s="175"/>
+      <c r="AT13" s="175"/>
+      <c r="AU13" s="175"/>
+      <c r="AV13" s="175"/>
+      <c r="AW13" s="175"/>
+      <c r="AX13" s="175"/>
+      <c r="AY13" s="175"/>
+      <c r="AZ13" s="176"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="181">
+      <c r="B14" s="189">
         <v>5</v>
       </c>
-      <c r="C14" s="143" t="s">
+      <c r="C14" s="151" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="127"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="167"/>
-      <c r="L14" s="167"/>
-      <c r="M14" s="167"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="132"/>
-      <c r="S14" s="133"/>
-      <c r="T14" s="172" t="s">
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="215"/>
+      <c r="K14" s="175"/>
+      <c r="L14" s="175"/>
+      <c r="M14" s="175"/>
+      <c r="N14" s="175"/>
+      <c r="O14" s="175"/>
+      <c r="P14" s="175"/>
+      <c r="Q14" s="139"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="141"/>
+      <c r="T14" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="172"/>
-      <c r="V14" s="170">
+      <c r="U14" s="180"/>
+      <c r="V14" s="178">
         <v>0</v>
       </c>
-      <c r="W14" s="170"/>
-      <c r="X14" s="156">
+      <c r="W14" s="178"/>
+      <c r="X14" s="164">
         <v>0</v>
       </c>
-      <c r="Y14" s="156"/>
+      <c r="Y14" s="164"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8358,50 +8343,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="167"/>
-      <c r="AP14" s="167"/>
-      <c r="AQ14" s="167"/>
-      <c r="AR14" s="167"/>
-      <c r="AS14" s="167"/>
-      <c r="AT14" s="167"/>
-      <c r="AU14" s="167"/>
-      <c r="AV14" s="167"/>
-      <c r="AW14" s="167"/>
-      <c r="AX14" s="167"/>
-      <c r="AY14" s="167"/>
-      <c r="AZ14" s="168"/>
+      <c r="AO14" s="175"/>
+      <c r="AP14" s="175"/>
+      <c r="AQ14" s="175"/>
+      <c r="AR14" s="175"/>
+      <c r="AS14" s="175"/>
+      <c r="AT14" s="175"/>
+      <c r="AU14" s="175"/>
+      <c r="AV14" s="175"/>
+      <c r="AW14" s="175"/>
+      <c r="AX14" s="175"/>
+      <c r="AY14" s="175"/>
+      <c r="AZ14" s="176"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="181"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="167"/>
-      <c r="K15" s="167"/>
-      <c r="L15" s="167"/>
-      <c r="M15" s="167"/>
-      <c r="N15" s="167"/>
-      <c r="O15" s="167"/>
-      <c r="P15" s="167"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="135"/>
-      <c r="S15" s="136"/>
-      <c r="T15" s="169" t="s">
+      <c r="B15" s="189"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="175"/>
+      <c r="M15" s="175"/>
+      <c r="N15" s="175"/>
+      <c r="O15" s="175"/>
+      <c r="P15" s="175"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="169"/>
-      <c r="V15" s="171">
+      <c r="U15" s="177"/>
+      <c r="V15" s="179">
         <v>0</v>
       </c>
-      <c r="W15" s="171"/>
-      <c r="X15" s="157">
+      <c r="W15" s="179"/>
+      <c r="X15" s="165">
         <v>0</v>
       </c>
-      <c r="Y15" s="157"/>
+      <c r="Y15" s="165"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8417,56 +8402,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="167"/>
-      <c r="AP15" s="167"/>
-      <c r="AQ15" s="167"/>
-      <c r="AR15" s="167"/>
-      <c r="AS15" s="167"/>
-      <c r="AT15" s="167"/>
-      <c r="AU15" s="167"/>
-      <c r="AV15" s="167"/>
-      <c r="AW15" s="167"/>
-      <c r="AX15" s="167"/>
-      <c r="AY15" s="167"/>
-      <c r="AZ15" s="168"/>
+      <c r="AO15" s="175"/>
+      <c r="AP15" s="175"/>
+      <c r="AQ15" s="175"/>
+      <c r="AR15" s="175"/>
+      <c r="AS15" s="175"/>
+      <c r="AT15" s="175"/>
+      <c r="AU15" s="175"/>
+      <c r="AV15" s="175"/>
+      <c r="AW15" s="175"/>
+      <c r="AX15" s="175"/>
+      <c r="AY15" s="175"/>
+      <c r="AZ15" s="176"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="181">
+      <c r="B16" s="189">
         <v>6</v>
       </c>
-      <c r="C16" s="143" t="s">
+      <c r="C16" s="151" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="207" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="167"/>
-      <c r="L16" s="167"/>
-      <c r="M16" s="167"/>
-      <c r="N16" s="167"/>
-      <c r="O16" s="167"/>
-      <c r="P16" s="167"/>
-      <c r="Q16" s="158"/>
-      <c r="R16" s="158"/>
-      <c r="S16" s="158"/>
-      <c r="T16" s="172" t="s">
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="215" t="s">
+        <v>140</v>
+      </c>
+      <c r="K16" s="175"/>
+      <c r="L16" s="175"/>
+      <c r="M16" s="175"/>
+      <c r="N16" s="175"/>
+      <c r="O16" s="175"/>
+      <c r="P16" s="175"/>
+      <c r="Q16" s="166"/>
+      <c r="R16" s="166"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="172"/>
-      <c r="V16" s="170">
+      <c r="U16" s="180"/>
+      <c r="V16" s="178">
         <v>0</v>
       </c>
-      <c r="W16" s="170"/>
-      <c r="X16" s="156">
+      <c r="W16" s="178"/>
+      <c r="X16" s="164">
         <v>0</v>
       </c>
-      <c r="Y16" s="156"/>
+      <c r="Y16" s="164"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8482,50 +8467,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="167"/>
-      <c r="AP16" s="167"/>
-      <c r="AQ16" s="167"/>
-      <c r="AR16" s="167"/>
-      <c r="AS16" s="167"/>
-      <c r="AT16" s="167"/>
-      <c r="AU16" s="167"/>
-      <c r="AV16" s="167"/>
-      <c r="AW16" s="167"/>
-      <c r="AX16" s="167"/>
-      <c r="AY16" s="167"/>
-      <c r="AZ16" s="168"/>
+      <c r="AO16" s="175"/>
+      <c r="AP16" s="175"/>
+      <c r="AQ16" s="175"/>
+      <c r="AR16" s="175"/>
+      <c r="AS16" s="175"/>
+      <c r="AT16" s="175"/>
+      <c r="AU16" s="175"/>
+      <c r="AV16" s="175"/>
+      <c r="AW16" s="175"/>
+      <c r="AX16" s="175"/>
+      <c r="AY16" s="175"/>
+      <c r="AZ16" s="176"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="181"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="167"/>
-      <c r="K17" s="167"/>
-      <c r="L17" s="167"/>
-      <c r="M17" s="167"/>
-      <c r="N17" s="167"/>
-      <c r="O17" s="167"/>
-      <c r="P17" s="167"/>
-      <c r="Q17" s="158"/>
-      <c r="R17" s="158"/>
-      <c r="S17" s="158"/>
-      <c r="T17" s="169" t="s">
+      <c r="B17" s="189"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="175"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="175"/>
+      <c r="N17" s="175"/>
+      <c r="O17" s="175"/>
+      <c r="P17" s="175"/>
+      <c r="Q17" s="166"/>
+      <c r="R17" s="166"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="169"/>
-      <c r="V17" s="171">
+      <c r="U17" s="177"/>
+      <c r="V17" s="179">
         <v>0</v>
       </c>
-      <c r="W17" s="171"/>
-      <c r="X17" s="157">
+      <c r="W17" s="179"/>
+      <c r="X17" s="165">
         <v>0</v>
       </c>
-      <c r="Y17" s="157"/>
+      <c r="Y17" s="165"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8541,56 +8526,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="167"/>
-      <c r="AP17" s="167"/>
-      <c r="AQ17" s="167"/>
-      <c r="AR17" s="167"/>
-      <c r="AS17" s="167"/>
-      <c r="AT17" s="167"/>
-      <c r="AU17" s="167"/>
-      <c r="AV17" s="167"/>
-      <c r="AW17" s="167"/>
-      <c r="AX17" s="167"/>
-      <c r="AY17" s="167"/>
-      <c r="AZ17" s="168"/>
+      <c r="AO17" s="175"/>
+      <c r="AP17" s="175"/>
+      <c r="AQ17" s="175"/>
+      <c r="AR17" s="175"/>
+      <c r="AS17" s="175"/>
+      <c r="AT17" s="175"/>
+      <c r="AU17" s="175"/>
+      <c r="AV17" s="175"/>
+      <c r="AW17" s="175"/>
+      <c r="AX17" s="175"/>
+      <c r="AY17" s="175"/>
+      <c r="AZ17" s="176"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="118">
+      <c r="B18" s="126">
         <v>7</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="143" t="s">
-        <v>144</v>
-      </c>
-      <c r="K18" s="126"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="126"/>
-      <c r="N18" s="126"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="132"/>
-      <c r="S18" s="133"/>
-      <c r="T18" s="137" t="s">
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="151" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="134"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="140"/>
+      <c r="S18" s="141"/>
+      <c r="T18" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="138"/>
-      <c r="V18" s="139">
+      <c r="U18" s="146"/>
+      <c r="V18" s="147">
         <v>0</v>
       </c>
-      <c r="W18" s="140"/>
-      <c r="X18" s="141">
+      <c r="W18" s="148"/>
+      <c r="X18" s="149">
         <v>0</v>
       </c>
-      <c r="Y18" s="142"/>
+      <c r="Y18" s="150"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8606,50 +8591,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="143"/>
-      <c r="AP18" s="126"/>
-      <c r="AQ18" s="126"/>
-      <c r="AR18" s="126"/>
-      <c r="AS18" s="126"/>
-      <c r="AT18" s="126"/>
-      <c r="AU18" s="126"/>
-      <c r="AV18" s="126"/>
-      <c r="AW18" s="126"/>
-      <c r="AX18" s="126"/>
-      <c r="AY18" s="126"/>
-      <c r="AZ18" s="144"/>
+      <c r="AO18" s="151"/>
+      <c r="AP18" s="134"/>
+      <c r="AQ18" s="134"/>
+      <c r="AR18" s="134"/>
+      <c r="AS18" s="134"/>
+      <c r="AT18" s="134"/>
+      <c r="AU18" s="134"/>
+      <c r="AV18" s="134"/>
+      <c r="AW18" s="134"/>
+      <c r="AX18" s="134"/>
+      <c r="AY18" s="134"/>
+      <c r="AZ18" s="152"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="119"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="129"/>
-      <c r="O19" s="129"/>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="135"/>
-      <c r="S19" s="136"/>
-      <c r="T19" s="146" t="s">
+      <c r="B19" s="127"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="138"/>
+      <c r="Q19" s="142"/>
+      <c r="R19" s="143"/>
+      <c r="S19" s="144"/>
+      <c r="T19" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="147"/>
-      <c r="V19" s="148">
+      <c r="U19" s="155"/>
+      <c r="V19" s="156">
         <v>0</v>
       </c>
-      <c r="W19" s="149"/>
-      <c r="X19" s="150">
+      <c r="W19" s="157"/>
+      <c r="X19" s="158">
         <v>0</v>
       </c>
-      <c r="Y19" s="151"/>
+      <c r="Y19" s="159"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8665,56 +8650,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="128"/>
-      <c r="AP19" s="129"/>
-      <c r="AQ19" s="129"/>
-      <c r="AR19" s="129"/>
-      <c r="AS19" s="129"/>
-      <c r="AT19" s="129"/>
-      <c r="AU19" s="129"/>
-      <c r="AV19" s="129"/>
-      <c r="AW19" s="129"/>
-      <c r="AX19" s="129"/>
-      <c r="AY19" s="129"/>
-      <c r="AZ19" s="145"/>
+      <c r="AO19" s="136"/>
+      <c r="AP19" s="137"/>
+      <c r="AQ19" s="137"/>
+      <c r="AR19" s="137"/>
+      <c r="AS19" s="137"/>
+      <c r="AT19" s="137"/>
+      <c r="AU19" s="137"/>
+      <c r="AV19" s="137"/>
+      <c r="AW19" s="137"/>
+      <c r="AX19" s="137"/>
+      <c r="AY19" s="137"/>
+      <c r="AZ19" s="153"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="118">
+      <c r="B20" s="126">
         <v>8</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="128" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="120" t="s">
-        <v>145</v>
-      </c>
-      <c r="K20" s="126"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="126"/>
-      <c r="N20" s="126"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="131"/>
-      <c r="R20" s="132"/>
-      <c r="S20" s="133"/>
-      <c r="T20" s="137" t="s">
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="128" t="s">
+        <v>142</v>
+      </c>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="134"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="135"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="140"/>
+      <c r="S20" s="141"/>
+      <c r="T20" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="138"/>
-      <c r="V20" s="139">
+      <c r="U20" s="146"/>
+      <c r="V20" s="147">
         <v>0</v>
       </c>
-      <c r="W20" s="140"/>
-      <c r="X20" s="141">
+      <c r="W20" s="148"/>
+      <c r="X20" s="149">
         <v>0</v>
       </c>
-      <c r="Y20" s="142"/>
+      <c r="Y20" s="150"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8730,50 +8715,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="143"/>
-      <c r="AP20" s="126"/>
-      <c r="AQ20" s="126"/>
-      <c r="AR20" s="126"/>
-      <c r="AS20" s="126"/>
-      <c r="AT20" s="126"/>
-      <c r="AU20" s="126"/>
-      <c r="AV20" s="126"/>
-      <c r="AW20" s="126"/>
-      <c r="AX20" s="126"/>
-      <c r="AY20" s="126"/>
-      <c r="AZ20" s="144"/>
+      <c r="AO20" s="151"/>
+      <c r="AP20" s="134"/>
+      <c r="AQ20" s="134"/>
+      <c r="AR20" s="134"/>
+      <c r="AS20" s="134"/>
+      <c r="AT20" s="134"/>
+      <c r="AU20" s="134"/>
+      <c r="AV20" s="134"/>
+      <c r="AW20" s="134"/>
+      <c r="AX20" s="134"/>
+      <c r="AY20" s="134"/>
+      <c r="AZ20" s="152"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="119"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="124"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="124"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="129"/>
-      <c r="L21" s="129"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="129"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="130"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="135"/>
-      <c r="S21" s="136"/>
-      <c r="T21" s="146" t="s">
+      <c r="B21" s="127"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="133"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="137"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="137"/>
+      <c r="P21" s="138"/>
+      <c r="Q21" s="142"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="144"/>
+      <c r="T21" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="147"/>
-      <c r="V21" s="148">
+      <c r="U21" s="155"/>
+      <c r="V21" s="156">
         <v>0</v>
       </c>
-      <c r="W21" s="149"/>
-      <c r="X21" s="150">
+      <c r="W21" s="157"/>
+      <c r="X21" s="158">
         <v>0</v>
       </c>
-      <c r="Y21" s="151"/>
+      <c r="Y21" s="159"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8789,54 +8774,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="128"/>
-      <c r="AP21" s="129"/>
-      <c r="AQ21" s="129"/>
-      <c r="AR21" s="129"/>
-      <c r="AS21" s="129"/>
-      <c r="AT21" s="129"/>
-      <c r="AU21" s="129"/>
-      <c r="AV21" s="129"/>
-      <c r="AW21" s="129"/>
-      <c r="AX21" s="129"/>
-      <c r="AY21" s="129"/>
-      <c r="AZ21" s="145"/>
+      <c r="AO21" s="136"/>
+      <c r="AP21" s="137"/>
+      <c r="AQ21" s="137"/>
+      <c r="AR21" s="137"/>
+      <c r="AS21" s="137"/>
+      <c r="AT21" s="137"/>
+      <c r="AU21" s="137"/>
+      <c r="AV21" s="137"/>
+      <c r="AW21" s="137"/>
+      <c r="AX21" s="137"/>
+      <c r="AY21" s="137"/>
+      <c r="AZ21" s="153"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="188">
+      <c r="B22" s="196">
         <v>9</v>
       </c>
-      <c r="C22" s="190" t="s">
+      <c r="C22" s="198" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="191"/>
-      <c r="E22" s="191"/>
-      <c r="F22" s="191"/>
-      <c r="G22" s="191"/>
-      <c r="H22" s="191"/>
-      <c r="I22" s="192"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="176"/>
-      <c r="L22" s="176"/>
-      <c r="M22" s="176"/>
-      <c r="N22" s="176"/>
-      <c r="O22" s="176"/>
-      <c r="P22" s="177"/>
-      <c r="Q22" s="197"/>
-      <c r="R22" s="198"/>
-      <c r="S22" s="199"/>
-      <c r="T22" s="193" t="s">
+      <c r="D22" s="199"/>
+      <c r="E22" s="199"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="183"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+      <c r="N22" s="184"/>
+      <c r="O22" s="184"/>
+      <c r="P22" s="185"/>
+      <c r="Q22" s="205"/>
+      <c r="R22" s="206"/>
+      <c r="S22" s="207"/>
+      <c r="T22" s="201" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="194"/>
-      <c r="V22" s="173">
+      <c r="U22" s="202"/>
+      <c r="V22" s="181">
         <v>0</v>
       </c>
-      <c r="W22" s="174"/>
-      <c r="X22" s="186">
+      <c r="W22" s="182"/>
+      <c r="X22" s="194">
         <v>0</v>
       </c>
-      <c r="Y22" s="187"/>
+      <c r="Y22" s="195"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8852,50 +8837,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="175"/>
-      <c r="AP22" s="176"/>
-      <c r="AQ22" s="176"/>
-      <c r="AR22" s="176"/>
-      <c r="AS22" s="176"/>
-      <c r="AT22" s="176"/>
-      <c r="AU22" s="176"/>
-      <c r="AV22" s="176"/>
-      <c r="AW22" s="176"/>
-      <c r="AX22" s="176"/>
-      <c r="AY22" s="176"/>
-      <c r="AZ22" s="184"/>
+      <c r="AO22" s="183"/>
+      <c r="AP22" s="184"/>
+      <c r="AQ22" s="184"/>
+      <c r="AR22" s="184"/>
+      <c r="AS22" s="184"/>
+      <c r="AT22" s="184"/>
+      <c r="AU22" s="184"/>
+      <c r="AV22" s="184"/>
+      <c r="AW22" s="184"/>
+      <c r="AX22" s="184"/>
+      <c r="AY22" s="184"/>
+      <c r="AZ22" s="192"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="189"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="178"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="179"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="179"/>
-      <c r="O23" s="179"/>
-      <c r="P23" s="180"/>
-      <c r="Q23" s="200"/>
-      <c r="R23" s="201"/>
-      <c r="S23" s="202"/>
-      <c r="T23" s="195" t="s">
+      <c r="B23" s="197"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="133"/>
+      <c r="J23" s="186"/>
+      <c r="K23" s="187"/>
+      <c r="L23" s="187"/>
+      <c r="M23" s="187"/>
+      <c r="N23" s="187"/>
+      <c r="O23" s="187"/>
+      <c r="P23" s="188"/>
+      <c r="Q23" s="208"/>
+      <c r="R23" s="209"/>
+      <c r="S23" s="210"/>
+      <c r="T23" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="196"/>
-      <c r="V23" s="182">
+      <c r="U23" s="204"/>
+      <c r="V23" s="190">
         <v>0</v>
       </c>
-      <c r="W23" s="183"/>
-      <c r="X23" s="203">
+      <c r="W23" s="191"/>
+      <c r="X23" s="211">
         <v>0</v>
       </c>
-      <c r="Y23" s="204"/>
+      <c r="Y23" s="212"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8911,18 +8896,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="178"/>
-      <c r="AP23" s="179"/>
-      <c r="AQ23" s="179"/>
-      <c r="AR23" s="179"/>
-      <c r="AS23" s="179"/>
-      <c r="AT23" s="179"/>
-      <c r="AU23" s="179"/>
-      <c r="AV23" s="179"/>
-      <c r="AW23" s="179"/>
-      <c r="AX23" s="179"/>
-      <c r="AY23" s="179"/>
-      <c r="AZ23" s="185"/>
+      <c r="AO23" s="186"/>
+      <c r="AP23" s="187"/>
+      <c r="AQ23" s="187"/>
+      <c r="AR23" s="187"/>
+      <c r="AS23" s="187"/>
+      <c r="AT23" s="187"/>
+      <c r="AU23" s="187"/>
+      <c r="AV23" s="187"/>
+      <c r="AW23" s="187"/>
+      <c r="AX23" s="187"/>
+      <c r="AY23" s="187"/>
+      <c r="AZ23" s="193"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -9117,602 +9102,602 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54">
+      <c r="A1" s="62">
         <v>1</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="63"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="71"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="65"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="54">
+      <c r="A3" s="62">
         <v>2</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="92"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="100"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="209" t="s">
+      <c r="A4" s="63"/>
+      <c r="B4" s="217" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="210"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="217"/>
+      <c r="J4" s="218"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="54">
+      <c r="A5" s="62">
         <v>3</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="92"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="100"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
-      <c r="B6" s="99" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="100"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="108"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="92"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="100"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="55"/>
-      <c r="B8" s="95" t="s">
+      <c r="A8" s="63"/>
+      <c r="B8" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="55"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="70"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="70"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="55"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="70"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="78"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="55"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="70"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="78"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="55"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="70"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="55"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="70"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="78"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="55"/>
-      <c r="B15" s="95" t="s">
+      <c r="A15" s="63"/>
+      <c r="B15" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="96"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="70"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="55"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="70"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="78"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="55"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="70"/>
+      <c r="A18" s="63"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="78"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="55"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="70"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="78"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="55"/>
-      <c r="B20" s="69"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="70"/>
+      <c r="A20" s="63"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="65"/>
+      <c r="A21" s="66"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="73"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="54">
+      <c r="A22" s="62">
         <v>5</v>
       </c>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="92"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="100"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="55"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="70"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="78"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="55"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="70"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="78"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="70"/>
+      <c r="A25" s="63"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="78"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="55"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="70"/>
+      <c r="A26" s="63"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="78"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="55"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="70"/>
+      <c r="A27" s="63"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="78"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="55"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="70"/>
+      <c r="A28" s="63"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="78"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="55"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="70"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="58"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="65"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="73"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="54">
+      <c r="A31" s="62">
         <v>6</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="92"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="100"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="55"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="70"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="78"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="55"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="70"/>
+      <c r="A33" s="63"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="78"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="55"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="70"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="78"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="70"/>
+      <c r="A35" s="63"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="78"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="55"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="70"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="78"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="55"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="70"/>
+      <c r="A37" s="63"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="78"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="55"/>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="70"/>
+      <c r="A38" s="63"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="78"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="55"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="70"/>
+      <c r="A39" s="63"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="78"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="55"/>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="70"/>
+      <c r="A40" s="63"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="78"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="55"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="70"/>
+      <c r="A41" s="63"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="78"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="55"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="70"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="78"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="55"/>
-      <c r="B43" s="69"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="70"/>
+      <c r="A43" s="63"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="78"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="55"/>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="69"/>
-      <c r="J44" s="70"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="78"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="55"/>
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="70"/>
+      <c r="A45" s="63"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="78"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="55"/>
-      <c r="B46" s="69"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="70"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="77"/>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="77"/>
+      <c r="J46" s="78"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-      <c r="B47" s="97"/>
-      <c r="C47" s="97"/>
-      <c r="D47" s="97"/>
-      <c r="E47" s="97"/>
-      <c r="F47" s="97"/>
-      <c r="G47" s="97"/>
-      <c r="H47" s="97"/>
-      <c r="I47" s="97"/>
-      <c r="J47" s="98"/>
+      <c r="A47" s="64"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CAF4B7-1D04-436D-AFC9-8A41C9805203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB539D59-6295-45B9-AAD0-157ED120C027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="176">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -648,19 +648,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>質問回答登録</t>
-    <rPh sb="0" eb="2">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AI分析</t>
     <rPh sb="2" eb="4">
       <t>ブンセキ</t>
@@ -935,25 +922,6 @@
       <t>シャシン</t>
     </rPh>
     <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況質問への回答を登録できる</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
       <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2093,6 +2061,19 @@
       <t>ジョウキョウ</t>
     </rPh>
     <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -3191,12 +3172,45 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3227,30 +3241,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3260,34 +3250,148 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3302,129 +3406,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3432,7 +3419,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3443,20 +3442,74 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3464,6 +3517,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3473,29 +3619,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3515,50 +3667,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3572,15 +3691,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3605,140 +3715,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4622,1585 +4603,1608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62">
+      <c r="A2" s="64">
         <v>1</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="70" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="71"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="111" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>2</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="68"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="63"/>
-      <c r="B5" s="79" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="80"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="63"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="80"/>
+      <c r="A6" s="66"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="83"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="63"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="82"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="63"/>
-      <c r="B8" s="94" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="63"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="63"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="99"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="63"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="92"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="63"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="99"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="99"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="63"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="63"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="99"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="66"/>
-      <c r="B17" s="97"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="66"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="99"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="66"/>
-      <c r="B19" s="97"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="99"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="66"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="62">
+      <c r="A21" s="64">
         <v>3</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="68"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63"/>
-      <c r="B22" s="83" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="85"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="101"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="85"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="101"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="85"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="101"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="63"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="88"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63"/>
-      <c r="B26" s="89" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="105" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="106"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="63"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="63"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="106"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="106"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="63"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="106"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="90"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="106"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="63"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="90"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="106"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="90"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="106"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="63"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="90"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="106"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="63"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="90"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="106"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="90"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="105"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="106"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="63"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="89"/>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="90"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="106"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="63"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="90"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="105"/>
+      <c r="J38" s="106"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="90"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="106"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="90"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="63"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="90"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63"/>
-      <c r="B42" s="89"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="90"/>
+      <c r="A42" s="66"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="106"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="63"/>
-      <c r="B43" s="89"/>
-      <c r="C43" s="89"/>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="90"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="63"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="89"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89"/>
-      <c r="H44" s="89"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="90"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="106"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="63"/>
-      <c r="B45" s="89"/>
-      <c r="C45" s="89"/>
-      <c r="D45" s="89"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="89"/>
-      <c r="G45" s="89"/>
-      <c r="H45" s="89"/>
-      <c r="I45" s="89"/>
-      <c r="J45" s="90"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="106"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="63"/>
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="89"/>
-      <c r="I46" s="89"/>
-      <c r="J46" s="90"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="106"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="63"/>
-      <c r="B47" s="89"/>
-      <c r="C47" s="89"/>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
-      <c r="J47" s="90"/>
+      <c r="A47" s="66"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="63"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="89"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="89"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="89"/>
-      <c r="I48" s="89"/>
-      <c r="J48" s="90"/>
+      <c r="A48" s="66"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="105"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="106"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="63"/>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="90"/>
+      <c r="A49" s="66"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="106"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="63"/>
-      <c r="B50" s="89"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="89"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="89"/>
-      <c r="J50" s="90"/>
+      <c r="A50" s="66"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="106"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="63"/>
-      <c r="B51" s="89"/>
-      <c r="C51" s="89"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="89"/>
-      <c r="J51" s="90"/>
+      <c r="A51" s="66"/>
+      <c r="B51" s="105"/>
+      <c r="C51" s="105"/>
+      <c r="D51" s="105"/>
+      <c r="E51" s="105"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="105"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="106"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="63"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="89"/>
-      <c r="G52" s="89"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="89"/>
-      <c r="J52" s="90"/>
+      <c r="A52" s="66"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="105"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="106"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="63"/>
-      <c r="B53" s="89"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="89"/>
-      <c r="J53" s="90"/>
+      <c r="A53" s="66"/>
+      <c r="B53" s="105"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="106"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="63"/>
-      <c r="B54" s="89"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="89"/>
-      <c r="J54" s="90"/>
+      <c r="A54" s="66"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="105"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="106"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63"/>
-      <c r="B55" s="89"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
-      <c r="J55" s="90"/>
+      <c r="A55" s="66"/>
+      <c r="B55" s="105"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="106"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="63"/>
-      <c r="B56" s="89"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="89"/>
-      <c r="J56" s="90"/>
+      <c r="A56" s="66"/>
+      <c r="B56" s="105"/>
+      <c r="C56" s="105"/>
+      <c r="D56" s="105"/>
+      <c r="E56" s="105"/>
+      <c r="F56" s="105"/>
+      <c r="G56" s="105"/>
+      <c r="H56" s="105"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="106"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="63"/>
-      <c r="B57" s="89"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
-      <c r="G57" s="89"/>
-      <c r="H57" s="89"/>
-      <c r="I57" s="89"/>
-      <c r="J57" s="90"/>
+      <c r="A57" s="66"/>
+      <c r="B57" s="105"/>
+      <c r="C57" s="105"/>
+      <c r="D57" s="105"/>
+      <c r="E57" s="105"/>
+      <c r="F57" s="105"/>
+      <c r="G57" s="105"/>
+      <c r="H57" s="105"/>
+      <c r="I57" s="105"/>
+      <c r="J57" s="106"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="63"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="89"/>
-      <c r="G58" s="89"/>
-      <c r="H58" s="89"/>
-      <c r="I58" s="89"/>
-      <c r="J58" s="90"/>
+      <c r="A58" s="66"/>
+      <c r="B58" s="105"/>
+      <c r="C58" s="105"/>
+      <c r="D58" s="105"/>
+      <c r="E58" s="105"/>
+      <c r="F58" s="105"/>
+      <c r="G58" s="105"/>
+      <c r="H58" s="105"/>
+      <c r="I58" s="105"/>
+      <c r="J58" s="106"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="63"/>
-      <c r="B59" s="89"/>
-      <c r="C59" s="89"/>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="89"/>
-      <c r="H59" s="89"/>
-      <c r="I59" s="89"/>
-      <c r="J59" s="90"/>
+      <c r="A59" s="66"/>
+      <c r="B59" s="105"/>
+      <c r="C59" s="105"/>
+      <c r="D59" s="105"/>
+      <c r="E59" s="105"/>
+      <c r="F59" s="105"/>
+      <c r="G59" s="105"/>
+      <c r="H59" s="105"/>
+      <c r="I59" s="105"/>
+      <c r="J59" s="106"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="63"/>
-      <c r="B60" s="89"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="89"/>
-      <c r="I60" s="89"/>
-      <c r="J60" s="90"/>
+      <c r="A60" s="66"/>
+      <c r="B60" s="105"/>
+      <c r="C60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="106"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="63"/>
-      <c r="B61" s="89"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="89"/>
-      <c r="H61" s="89"/>
-      <c r="I61" s="89"/>
-      <c r="J61" s="90"/>
+      <c r="A61" s="66"/>
+      <c r="B61" s="105"/>
+      <c r="C61" s="105"/>
+      <c r="D61" s="105"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="105"/>
+      <c r="G61" s="105"/>
+      <c r="H61" s="105"/>
+      <c r="I61" s="105"/>
+      <c r="J61" s="106"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="64"/>
-      <c r="B62" s="91"/>
-      <c r="C62" s="91"/>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="91"/>
-      <c r="G62" s="91"/>
-      <c r="H62" s="91"/>
-      <c r="I62" s="91"/>
-      <c r="J62" s="92"/>
+      <c r="A62" s="67"/>
+      <c r="B62" s="107"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="108"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="62">
+      <c r="A63" s="64">
         <v>4</v>
       </c>
-      <c r="B63" s="69" t="s">
+      <c r="B63" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="69"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="100"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="68"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="68"/>
+      <c r="J63" s="69"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="63"/>
-      <c r="B64" s="65" t="s">
+      <c r="A64" s="66"/>
+      <c r="B64" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="65"/>
-      <c r="D64" s="77" t="s">
+      <c r="C64" s="109"/>
+      <c r="D64" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="77"/>
-      <c r="F64" s="77"/>
-      <c r="G64" s="77"/>
-      <c r="H64" s="77"/>
-      <c r="I64" s="77"/>
-      <c r="J64" s="78"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="72"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="63"/>
-      <c r="B65" s="65" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="65"/>
-      <c r="D65" s="77" t="s">
-        <v>148</v>
-      </c>
-      <c r="E65" s="77"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="77"/>
-      <c r="I65" s="77"/>
-      <c r="J65" s="78"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="72"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="63"/>
-      <c r="B66" s="65" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="65"/>
-      <c r="D66" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="E66" s="77"/>
-      <c r="F66" s="77"/>
-      <c r="G66" s="77"/>
-      <c r="H66" s="77"/>
-      <c r="I66" s="77"/>
-      <c r="J66" s="78"/>
+      <c r="C66" s="109"/>
+      <c r="D66" s="71" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="71"/>
+      <c r="F66" s="71"/>
+      <c r="G66" s="71"/>
+      <c r="H66" s="71"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="72"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="63"/>
-      <c r="B67" s="65" t="s">
+      <c r="A67" s="66"/>
+      <c r="B67" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="65"/>
-      <c r="D67" s="77" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" s="77"/>
-      <c r="F67" s="77"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="77"/>
-      <c r="I67" s="77"/>
-      <c r="J67" s="78"/>
+      <c r="C67" s="109"/>
+      <c r="D67" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="72"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="63"/>
-      <c r="B68" s="65" t="s">
+      <c r="A68" s="66"/>
+      <c r="B68" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="65"/>
-      <c r="D68" s="65"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="65"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
-      <c r="J68" s="93"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="109"/>
+      <c r="E68" s="109"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109"/>
+      <c r="I68" s="109"/>
+      <c r="J68" s="110"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="63"/>
-      <c r="B69" s="74" t="e" vm="1">
+      <c r="A69" s="66"/>
+      <c r="B69" s="96" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="74"/>
-      <c r="D69" s="74"/>
-      <c r="E69" s="74"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="74"/>
-      <c r="H69" s="74"/>
-      <c r="I69" s="74"/>
-      <c r="J69" s="75"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="96"/>
+      <c r="E69" s="96"/>
+      <c r="F69" s="96"/>
+      <c r="G69" s="96"/>
+      <c r="H69" s="96"/>
+      <c r="I69" s="96"/>
+      <c r="J69" s="97"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="63"/>
-      <c r="B70" s="74"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="74"/>
-      <c r="H70" s="74"/>
-      <c r="I70" s="74"/>
-      <c r="J70" s="75"/>
+      <c r="A70" s="66"/>
+      <c r="B70" s="96"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="96"/>
+      <c r="E70" s="96"/>
+      <c r="F70" s="96"/>
+      <c r="G70" s="96"/>
+      <c r="H70" s="96"/>
+      <c r="I70" s="96"/>
+      <c r="J70" s="97"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="63"/>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="74"/>
-      <c r="I71" s="74"/>
-      <c r="J71" s="75"/>
+      <c r="A71" s="66"/>
+      <c r="B71" s="96"/>
+      <c r="C71" s="96"/>
+      <c r="D71" s="96"/>
+      <c r="E71" s="96"/>
+      <c r="F71" s="96"/>
+      <c r="G71" s="96"/>
+      <c r="H71" s="96"/>
+      <c r="I71" s="96"/>
+      <c r="J71" s="97"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="63"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="74"/>
-      <c r="H72" s="74"/>
-      <c r="I72" s="74"/>
-      <c r="J72" s="75"/>
+      <c r="A72" s="66"/>
+      <c r="B72" s="96"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="96"/>
+      <c r="E72" s="96"/>
+      <c r="F72" s="96"/>
+      <c r="G72" s="96"/>
+      <c r="H72" s="96"/>
+      <c r="I72" s="96"/>
+      <c r="J72" s="97"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="63"/>
-      <c r="B73" s="74"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="74"/>
-      <c r="I73" s="74"/>
-      <c r="J73" s="75"/>
+      <c r="A73" s="66"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="96"/>
+      <c r="E73" s="96"/>
+      <c r="F73" s="96"/>
+      <c r="G73" s="96"/>
+      <c r="H73" s="96"/>
+      <c r="I73" s="96"/>
+      <c r="J73" s="97"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="63"/>
-      <c r="B74" s="74"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="74"/>
-      <c r="J74" s="75"/>
+      <c r="A74" s="66"/>
+      <c r="B74" s="96"/>
+      <c r="C74" s="96"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="96"/>
+      <c r="F74" s="96"/>
+      <c r="G74" s="96"/>
+      <c r="H74" s="96"/>
+      <c r="I74" s="96"/>
+      <c r="J74" s="97"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="63"/>
-      <c r="B75" s="74"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="75"/>
+      <c r="A75" s="66"/>
+      <c r="B75" s="96"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
+      <c r="F75" s="96"/>
+      <c r="G75" s="96"/>
+      <c r="H75" s="96"/>
+      <c r="I75" s="96"/>
+      <c r="J75" s="97"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="63"/>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="75"/>
+      <c r="A76" s="66"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="96"/>
+      <c r="D76" s="96"/>
+      <c r="E76" s="96"/>
+      <c r="F76" s="96"/>
+      <c r="G76" s="96"/>
+      <c r="H76" s="96"/>
+      <c r="I76" s="96"/>
+      <c r="J76" s="97"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="63"/>
-      <c r="B77" s="74"/>
-      <c r="C77" s="74"/>
-      <c r="D77" s="74"/>
-      <c r="E77" s="74"/>
-      <c r="F77" s="74"/>
-      <c r="G77" s="74"/>
-      <c r="H77" s="74"/>
-      <c r="I77" s="74"/>
-      <c r="J77" s="75"/>
+      <c r="A77" s="66"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="96"/>
+      <c r="D77" s="96"/>
+      <c r="E77" s="96"/>
+      <c r="F77" s="96"/>
+      <c r="G77" s="96"/>
+      <c r="H77" s="96"/>
+      <c r="I77" s="96"/>
+      <c r="J77" s="97"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="63"/>
-      <c r="B78" s="74"/>
-      <c r="C78" s="74"/>
-      <c r="D78" s="74"/>
-      <c r="E78" s="74"/>
-      <c r="F78" s="74"/>
-      <c r="G78" s="74"/>
-      <c r="H78" s="74"/>
-      <c r="I78" s="74"/>
-      <c r="J78" s="75"/>
+      <c r="A78" s="66"/>
+      <c r="B78" s="96"/>
+      <c r="C78" s="96"/>
+      <c r="D78" s="96"/>
+      <c r="E78" s="96"/>
+      <c r="F78" s="96"/>
+      <c r="G78" s="96"/>
+      <c r="H78" s="96"/>
+      <c r="I78" s="96"/>
+      <c r="J78" s="97"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="63"/>
-      <c r="B79" s="74"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="74"/>
-      <c r="F79" s="74"/>
-      <c r="G79" s="74"/>
-      <c r="H79" s="74"/>
-      <c r="I79" s="74"/>
-      <c r="J79" s="75"/>
+      <c r="A79" s="66"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="96"/>
+      <c r="E79" s="96"/>
+      <c r="F79" s="96"/>
+      <c r="G79" s="96"/>
+      <c r="H79" s="96"/>
+      <c r="I79" s="96"/>
+      <c r="J79" s="97"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="63"/>
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="74"/>
-      <c r="F80" s="74"/>
-      <c r="G80" s="74"/>
-      <c r="H80" s="74"/>
-      <c r="I80" s="74"/>
-      <c r="J80" s="75"/>
+      <c r="A80" s="66"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="96"/>
+      <c r="E80" s="96"/>
+      <c r="F80" s="96"/>
+      <c r="G80" s="96"/>
+      <c r="H80" s="96"/>
+      <c r="I80" s="96"/>
+      <c r="J80" s="97"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="63"/>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="74"/>
-      <c r="I81" s="74"/>
-      <c r="J81" s="75"/>
+      <c r="A81" s="66"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="96"/>
+      <c r="F81" s="96"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="96"/>
+      <c r="I81" s="96"/>
+      <c r="J81" s="97"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="63"/>
-      <c r="B82" s="74"/>
-      <c r="C82" s="74"/>
-      <c r="D82" s="74"/>
-      <c r="E82" s="74"/>
-      <c r="F82" s="74"/>
-      <c r="G82" s="74"/>
-      <c r="H82" s="74"/>
-      <c r="I82" s="74"/>
-      <c r="J82" s="75"/>
+      <c r="A82" s="66"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="96"/>
+      <c r="D82" s="96"/>
+      <c r="E82" s="96"/>
+      <c r="F82" s="96"/>
+      <c r="G82" s="96"/>
+      <c r="H82" s="96"/>
+      <c r="I82" s="96"/>
+      <c r="J82" s="97"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="63"/>
-      <c r="B83" s="74"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="74"/>
-      <c r="E83" s="74"/>
-      <c r="F83" s="74"/>
-      <c r="G83" s="74"/>
-      <c r="H83" s="74"/>
-      <c r="I83" s="74"/>
-      <c r="J83" s="75"/>
+      <c r="A83" s="66"/>
+      <c r="B83" s="96"/>
+      <c r="C83" s="96"/>
+      <c r="D83" s="96"/>
+      <c r="E83" s="96"/>
+      <c r="F83" s="96"/>
+      <c r="G83" s="96"/>
+      <c r="H83" s="96"/>
+      <c r="I83" s="96"/>
+      <c r="J83" s="97"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="63"/>
-      <c r="B84" s="74"/>
-      <c r="C84" s="74"/>
-      <c r="D84" s="74"/>
-      <c r="E84" s="74"/>
-      <c r="F84" s="74"/>
-      <c r="G84" s="74"/>
-      <c r="H84" s="74"/>
-      <c r="I84" s="74"/>
-      <c r="J84" s="75"/>
+      <c r="A84" s="66"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="96"/>
+      <c r="D84" s="96"/>
+      <c r="E84" s="96"/>
+      <c r="F84" s="96"/>
+      <c r="G84" s="96"/>
+      <c r="H84" s="96"/>
+      <c r="I84" s="96"/>
+      <c r="J84" s="97"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="63"/>
-      <c r="B85" s="74"/>
-      <c r="C85" s="74"/>
-      <c r="D85" s="74"/>
-      <c r="E85" s="74"/>
-      <c r="F85" s="74"/>
-      <c r="G85" s="74"/>
-      <c r="H85" s="74"/>
-      <c r="I85" s="74"/>
-      <c r="J85" s="75"/>
+      <c r="A85" s="66"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
+      <c r="F85" s="96"/>
+      <c r="G85" s="96"/>
+      <c r="H85" s="96"/>
+      <c r="I85" s="96"/>
+      <c r="J85" s="97"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
-      <c r="J86" s="76"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="40"/>
+      <c r="J86" s="98"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>5</v>
       </c>
-      <c r="B87" s="69" t="s">
+      <c r="B87" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="69"/>
-      <c r="D87" s="69"/>
-      <c r="E87" s="69"/>
-      <c r="F87" s="69"/>
-      <c r="G87" s="69"/>
-      <c r="H87" s="69"/>
-      <c r="I87" s="69"/>
-      <c r="J87" s="100"/>
+      <c r="C87" s="68"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="68"/>
+      <c r="I87" s="68"/>
+      <c r="J87" s="69"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="63"/>
-      <c r="B88" s="40" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="40"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="40"/>
-      <c r="I88" s="40"/>
-      <c r="J88" s="110"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="86"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="62">
+      <c r="A89" s="64">
         <v>6</v>
       </c>
-      <c r="B89" s="67" t="s">
+      <c r="B89" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="67"/>
-      <c r="D89" s="67"/>
-      <c r="E89" s="67"/>
-      <c r="F89" s="67"/>
-      <c r="G89" s="67"/>
-      <c r="H89" s="67"/>
-      <c r="I89" s="67"/>
-      <c r="J89" s="68"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
+      <c r="H89" s="79"/>
+      <c r="I89" s="79"/>
+      <c r="J89" s="80"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="109"/>
-      <c r="B90" s="79" t="s">
+      <c r="A90" s="81"/>
+      <c r="B90" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="79"/>
-      <c r="D90" s="79"/>
-      <c r="E90" s="79"/>
-      <c r="F90" s="79"/>
-      <c r="G90" s="79"/>
-      <c r="H90" s="79"/>
-      <c r="I90" s="79"/>
-      <c r="J90" s="80"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="82"/>
+      <c r="J90" s="83"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="109"/>
-      <c r="B91" s="79"/>
-      <c r="C91" s="79"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
-      <c r="F91" s="79"/>
-      <c r="G91" s="79"/>
-      <c r="H91" s="79"/>
-      <c r="I91" s="79"/>
-      <c r="J91" s="80"/>
+      <c r="A91" s="81"/>
+      <c r="B91" s="82"/>
+      <c r="C91" s="82"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
+      <c r="I91" s="82"/>
+      <c r="J91" s="83"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="109"/>
-      <c r="B92" s="81"/>
-      <c r="C92" s="81"/>
-      <c r="D92" s="81"/>
-      <c r="E92" s="81"/>
-      <c r="F92" s="81"/>
-      <c r="G92" s="81"/>
-      <c r="H92" s="81"/>
-      <c r="I92" s="81"/>
-      <c r="J92" s="82"/>
+      <c r="A92" s="81"/>
+      <c r="B92" s="84"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="84"/>
+      <c r="E92" s="84"/>
+      <c r="F92" s="84"/>
+      <c r="G92" s="84"/>
+      <c r="H92" s="84"/>
+      <c r="I92" s="84"/>
+      <c r="J92" s="85"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="63"/>
-      <c r="B93" s="94" t="s">
+      <c r="A93" s="66"/>
+      <c r="B93" s="87" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="88"/>
+      <c r="D93" s="88"/>
+      <c r="E93" s="88"/>
+      <c r="F93" s="88"/>
+      <c r="G93" s="88"/>
+      <c r="H93" s="88"/>
+      <c r="I93" s="88"/>
+      <c r="J93" s="89"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="66"/>
+      <c r="B94" s="90"/>
+      <c r="C94" s="91"/>
+      <c r="D94" s="91"/>
+      <c r="E94" s="91"/>
+      <c r="F94" s="91"/>
+      <c r="G94" s="91"/>
+      <c r="H94" s="91"/>
+      <c r="I94" s="91"/>
+      <c r="J94" s="92"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="66"/>
+      <c r="B95" s="90"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="91"/>
+      <c r="E95" s="91"/>
+      <c r="F95" s="91"/>
+      <c r="G95" s="91"/>
+      <c r="H95" s="91"/>
+      <c r="I95" s="91"/>
+      <c r="J95" s="92"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="66"/>
+      <c r="B96" s="90"/>
+      <c r="C96" s="91"/>
+      <c r="D96" s="91"/>
+      <c r="E96" s="91"/>
+      <c r="F96" s="91"/>
+      <c r="G96" s="91"/>
+      <c r="H96" s="91"/>
+      <c r="I96" s="91"/>
+      <c r="J96" s="92"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="66"/>
+      <c r="B97" s="90"/>
+      <c r="C97" s="91"/>
+      <c r="D97" s="91"/>
+      <c r="E97" s="91"/>
+      <c r="F97" s="91"/>
+      <c r="G97" s="91"/>
+      <c r="H97" s="91"/>
+      <c r="I97" s="91"/>
+      <c r="J97" s="92"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="66"/>
+      <c r="B98" s="90"/>
+      <c r="C98" s="91"/>
+      <c r="D98" s="91"/>
+      <c r="E98" s="91"/>
+      <c r="F98" s="91"/>
+      <c r="G98" s="91"/>
+      <c r="H98" s="91"/>
+      <c r="I98" s="91"/>
+      <c r="J98" s="92"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="66"/>
+      <c r="B99" s="90"/>
+      <c r="C99" s="91"/>
+      <c r="D99" s="91"/>
+      <c r="E99" s="91"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="91"/>
+      <c r="H99" s="91"/>
+      <c r="I99" s="91"/>
+      <c r="J99" s="92"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="66"/>
+      <c r="B100" s="90"/>
+      <c r="C100" s="91"/>
+      <c r="D100" s="91"/>
+      <c r="E100" s="91"/>
+      <c r="F100" s="91"/>
+      <c r="G100" s="91"/>
+      <c r="H100" s="91"/>
+      <c r="I100" s="91"/>
+      <c r="J100" s="92"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="66"/>
+      <c r="B101" s="90"/>
+      <c r="C101" s="91"/>
+      <c r="D101" s="91"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
+      <c r="G101" s="91"/>
+      <c r="H101" s="91"/>
+      <c r="I101" s="91"/>
+      <c r="J101" s="92"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="66"/>
+      <c r="B102" s="90"/>
+      <c r="C102" s="91"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
+      <c r="H102" s="91"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="92"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="66"/>
+      <c r="B103" s="90"/>
+      <c r="C103" s="91"/>
+      <c r="D103" s="91"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="91"/>
+      <c r="G103" s="91"/>
+      <c r="H103" s="91"/>
+      <c r="I103" s="91"/>
+      <c r="J103" s="92"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="66"/>
+      <c r="B104" s="90"/>
+      <c r="C104" s="91"/>
+      <c r="D104" s="91"/>
+      <c r="E104" s="91"/>
+      <c r="F104" s="91"/>
+      <c r="G104" s="91"/>
+      <c r="H104" s="91"/>
+      <c r="I104" s="91"/>
+      <c r="J104" s="92"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="66"/>
+      <c r="B105" s="90"/>
+      <c r="C105" s="91"/>
+      <c r="D105" s="91"/>
+      <c r="E105" s="91"/>
+      <c r="F105" s="91"/>
+      <c r="G105" s="91"/>
+      <c r="H105" s="91"/>
+      <c r="I105" s="91"/>
+      <c r="J105" s="92"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="66"/>
+      <c r="B106" s="90"/>
+      <c r="C106" s="91"/>
+      <c r="D106" s="91"/>
+      <c r="E106" s="91"/>
+      <c r="F106" s="91"/>
+      <c r="G106" s="91"/>
+      <c r="H106" s="91"/>
+      <c r="I106" s="91"/>
+      <c r="J106" s="92"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="67"/>
+      <c r="B107" s="93"/>
+      <c r="C107" s="94"/>
+      <c r="D107" s="94"/>
+      <c r="E107" s="94"/>
+      <c r="F107" s="94"/>
+      <c r="G107" s="94"/>
+      <c r="H107" s="94"/>
+      <c r="I107" s="94"/>
+      <c r="J107" s="95"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="64">
+        <v>7</v>
+      </c>
+      <c r="B108" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="68"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
+      <c r="H108" s="68"/>
+      <c r="I108" s="68"/>
+      <c r="J108" s="69"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="65"/>
+      <c r="B109" s="77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" s="77"/>
+      <c r="D109" s="77"/>
+      <c r="E109" s="77"/>
+      <c r="F109" s="77"/>
+      <c r="G109" s="77"/>
+      <c r="H109" s="77"/>
+      <c r="I109" s="77"/>
+      <c r="J109" s="78"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="64">
+        <v>8</v>
+      </c>
+      <c r="B110" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="68"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="68"/>
+      <c r="F110" s="68"/>
+      <c r="G110" s="68"/>
+      <c r="H110" s="68"/>
+      <c r="I110" s="68"/>
+      <c r="J110" s="69"/>
+    </row>
+    <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="66"/>
+      <c r="B111" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="C111" s="71"/>
+      <c r="D111" s="71"/>
+      <c r="E111" s="71"/>
+      <c r="F111" s="71"/>
+      <c r="G111" s="71"/>
+      <c r="H111" s="71"/>
+      <c r="I111" s="71"/>
+      <c r="J111" s="72"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="66"/>
+      <c r="B112" s="71"/>
+      <c r="C112" s="71"/>
+      <c r="D112" s="71"/>
+      <c r="E112" s="71"/>
+      <c r="F112" s="71"/>
+      <c r="G112" s="71"/>
+      <c r="H112" s="71"/>
+      <c r="I112" s="71"/>
+      <c r="J112" s="72"/>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="66"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
+      <c r="G113" s="71"/>
+      <c r="H113" s="71"/>
+      <c r="I113" s="71"/>
+      <c r="J113" s="72"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="66"/>
+      <c r="B114" s="71"/>
+      <c r="C114" s="71"/>
+      <c r="D114" s="71"/>
+      <c r="E114" s="71"/>
+      <c r="F114" s="71"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="71"/>
+      <c r="I114" s="71"/>
+      <c r="J114" s="72"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="66"/>
+      <c r="B115" s="71"/>
+      <c r="C115" s="71"/>
+      <c r="D115" s="71"/>
+      <c r="E115" s="71"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="71"/>
+      <c r="H115" s="71"/>
+      <c r="I115" s="71"/>
+      <c r="J115" s="72"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="66"/>
+      <c r="B116" s="71"/>
+      <c r="C116" s="71"/>
+      <c r="D116" s="71"/>
+      <c r="E116" s="71"/>
+      <c r="F116" s="71"/>
+      <c r="G116" s="71"/>
+      <c r="H116" s="71"/>
+      <c r="I116" s="71"/>
+      <c r="J116" s="72"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="66"/>
+      <c r="B117" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117" s="73"/>
+      <c r="D117" s="73"/>
+      <c r="E117" s="73"/>
+      <c r="F117" s="73"/>
+      <c r="G117" s="73"/>
+      <c r="H117" s="73"/>
+      <c r="I117" s="73"/>
+      <c r="J117" s="74"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="66"/>
+      <c r="B118" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="C93" s="95"/>
-      <c r="D93" s="95"/>
-      <c r="E93" s="95"/>
-      <c r="F93" s="95"/>
-      <c r="G93" s="95"/>
-      <c r="H93" s="95"/>
-      <c r="I93" s="95"/>
-      <c r="J93" s="96"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="63"/>
-      <c r="B94" s="97"/>
-      <c r="C94" s="98"/>
-      <c r="D94" s="98"/>
-      <c r="E94" s="98"/>
-      <c r="F94" s="98"/>
-      <c r="G94" s="98"/>
-      <c r="H94" s="98"/>
-      <c r="I94" s="98"/>
-      <c r="J94" s="99"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="63"/>
-      <c r="B95" s="97"/>
-      <c r="C95" s="98"/>
-      <c r="D95" s="98"/>
-      <c r="E95" s="98"/>
-      <c r="F95" s="98"/>
-      <c r="G95" s="98"/>
-      <c r="H95" s="98"/>
-      <c r="I95" s="98"/>
-      <c r="J95" s="99"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="63"/>
-      <c r="B96" s="97"/>
-      <c r="C96" s="98"/>
-      <c r="D96" s="98"/>
-      <c r="E96" s="98"/>
-      <c r="F96" s="98"/>
-      <c r="G96" s="98"/>
-      <c r="H96" s="98"/>
-      <c r="I96" s="98"/>
-      <c r="J96" s="99"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="63"/>
-      <c r="B97" s="97"/>
-      <c r="C97" s="98"/>
-      <c r="D97" s="98"/>
-      <c r="E97" s="98"/>
-      <c r="F97" s="98"/>
-      <c r="G97" s="98"/>
-      <c r="H97" s="98"/>
-      <c r="I97" s="98"/>
-      <c r="J97" s="99"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="63"/>
-      <c r="B98" s="97"/>
-      <c r="C98" s="98"/>
-      <c r="D98" s="98"/>
-      <c r="E98" s="98"/>
-      <c r="F98" s="98"/>
-      <c r="G98" s="98"/>
-      <c r="H98" s="98"/>
-      <c r="I98" s="98"/>
-      <c r="J98" s="99"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="63"/>
-      <c r="B99" s="97"/>
-      <c r="C99" s="98"/>
-      <c r="D99" s="98"/>
-      <c r="E99" s="98"/>
-      <c r="F99" s="98"/>
-      <c r="G99" s="98"/>
-      <c r="H99" s="98"/>
-      <c r="I99" s="98"/>
-      <c r="J99" s="99"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="63"/>
-      <c r="B100" s="97"/>
-      <c r="C100" s="98"/>
-      <c r="D100" s="98"/>
-      <c r="E100" s="98"/>
-      <c r="F100" s="98"/>
-      <c r="G100" s="98"/>
-      <c r="H100" s="98"/>
-      <c r="I100" s="98"/>
-      <c r="J100" s="99"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="63"/>
-      <c r="B101" s="97"/>
-      <c r="C101" s="98"/>
-      <c r="D101" s="98"/>
-      <c r="E101" s="98"/>
-      <c r="F101" s="98"/>
-      <c r="G101" s="98"/>
-      <c r="H101" s="98"/>
-      <c r="I101" s="98"/>
-      <c r="J101" s="99"/>
-    </row>
-    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="63"/>
-      <c r="B102" s="97"/>
-      <c r="C102" s="98"/>
-      <c r="D102" s="98"/>
-      <c r="E102" s="98"/>
-      <c r="F102" s="98"/>
-      <c r="G102" s="98"/>
-      <c r="H102" s="98"/>
-      <c r="I102" s="98"/>
-      <c r="J102" s="99"/>
-    </row>
-    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="63"/>
-      <c r="B103" s="97"/>
-      <c r="C103" s="98"/>
-      <c r="D103" s="98"/>
-      <c r="E103" s="98"/>
-      <c r="F103" s="98"/>
-      <c r="G103" s="98"/>
-      <c r="H103" s="98"/>
-      <c r="I103" s="98"/>
-      <c r="J103" s="99"/>
-    </row>
-    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="63"/>
-      <c r="B104" s="97"/>
-      <c r="C104" s="98"/>
-      <c r="D104" s="98"/>
-      <c r="E104" s="98"/>
-      <c r="F104" s="98"/>
-      <c r="G104" s="98"/>
-      <c r="H104" s="98"/>
-      <c r="I104" s="98"/>
-      <c r="J104" s="99"/>
-    </row>
-    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="63"/>
-      <c r="B105" s="97"/>
-      <c r="C105" s="98"/>
-      <c r="D105" s="98"/>
-      <c r="E105" s="98"/>
-      <c r="F105" s="98"/>
-      <c r="G105" s="98"/>
-      <c r="H105" s="98"/>
-      <c r="I105" s="98"/>
-      <c r="J105" s="99"/>
-    </row>
-    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="63"/>
-      <c r="B106" s="97"/>
-      <c r="C106" s="98"/>
-      <c r="D106" s="98"/>
-      <c r="E106" s="98"/>
-      <c r="F106" s="98"/>
-      <c r="G106" s="98"/>
-      <c r="H106" s="98"/>
-      <c r="I106" s="98"/>
-      <c r="J106" s="99"/>
-    </row>
-    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="64"/>
-      <c r="B107" s="111"/>
-      <c r="C107" s="112"/>
-      <c r="D107" s="112"/>
-      <c r="E107" s="112"/>
-      <c r="F107" s="112"/>
-      <c r="G107" s="112"/>
-      <c r="H107" s="112"/>
-      <c r="I107" s="112"/>
-      <c r="J107" s="113"/>
-    </row>
-    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="62">
-        <v>7</v>
-      </c>
-      <c r="B108" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="69"/>
-      <c r="D108" s="69"/>
-      <c r="E108" s="69"/>
-      <c r="F108" s="69"/>
-      <c r="G108" s="69"/>
-      <c r="H108" s="69"/>
-      <c r="I108" s="69"/>
-      <c r="J108" s="100"/>
-    </row>
-    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="66"/>
-      <c r="B109" s="107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" s="107"/>
-      <c r="D109" s="107"/>
-      <c r="E109" s="107"/>
-      <c r="F109" s="107"/>
-      <c r="G109" s="107"/>
-      <c r="H109" s="107"/>
-      <c r="I109" s="107"/>
-      <c r="J109" s="108"/>
-    </row>
-    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="62">
-        <v>8</v>
-      </c>
-      <c r="B110" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C110" s="69"/>
-      <c r="D110" s="69"/>
-      <c r="E110" s="69"/>
-      <c r="F110" s="69"/>
-      <c r="G110" s="69"/>
-      <c r="H110" s="69"/>
-      <c r="I110" s="69"/>
-      <c r="J110" s="100"/>
-    </row>
-    <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="63"/>
-      <c r="B111" s="102" t="s">
-        <v>144</v>
-      </c>
-      <c r="C111" s="77"/>
-      <c r="D111" s="77"/>
-      <c r="E111" s="77"/>
-      <c r="F111" s="77"/>
-      <c r="G111" s="77"/>
-      <c r="H111" s="77"/>
-      <c r="I111" s="77"/>
-      <c r="J111" s="78"/>
-    </row>
-    <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="63"/>
-      <c r="B112" s="77"/>
-      <c r="C112" s="77"/>
-      <c r="D112" s="77"/>
-      <c r="E112" s="77"/>
-      <c r="F112" s="77"/>
-      <c r="G112" s="77"/>
-      <c r="H112" s="77"/>
-      <c r="I112" s="77"/>
-      <c r="J112" s="78"/>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="63"/>
-      <c r="B113" s="77"/>
-      <c r="C113" s="77"/>
-      <c r="D113" s="77"/>
-      <c r="E113" s="77"/>
-      <c r="F113" s="77"/>
-      <c r="G113" s="77"/>
-      <c r="H113" s="77"/>
-      <c r="I113" s="77"/>
-      <c r="J113" s="78"/>
-    </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="63"/>
-      <c r="B114" s="77"/>
-      <c r="C114" s="77"/>
-      <c r="D114" s="77"/>
-      <c r="E114" s="77"/>
-      <c r="F114" s="77"/>
-      <c r="G114" s="77"/>
-      <c r="H114" s="77"/>
-      <c r="I114" s="77"/>
-      <c r="J114" s="78"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="63"/>
-      <c r="B115" s="77"/>
-      <c r="C115" s="77"/>
-      <c r="D115" s="77"/>
-      <c r="E115" s="77"/>
-      <c r="F115" s="77"/>
-      <c r="G115" s="77"/>
-      <c r="H115" s="77"/>
-      <c r="I115" s="77"/>
-      <c r="J115" s="78"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="63"/>
-      <c r="B116" s="77"/>
-      <c r="C116" s="77"/>
-      <c r="D116" s="77"/>
-      <c r="E116" s="77"/>
-      <c r="F116" s="77"/>
-      <c r="G116" s="77"/>
-      <c r="H116" s="77"/>
-      <c r="I116" s="77"/>
-      <c r="J116" s="78"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="63"/>
-      <c r="B117" s="103" t="s">
-        <v>18</v>
-      </c>
-      <c r="C117" s="103"/>
-      <c r="D117" s="103"/>
-      <c r="E117" s="103"/>
-      <c r="F117" s="103"/>
-      <c r="G117" s="103"/>
-      <c r="H117" s="103"/>
-      <c r="I117" s="103"/>
-      <c r="J117" s="104"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="63"/>
-      <c r="B118" s="102" t="s">
-        <v>145</v>
-      </c>
-      <c r="C118" s="77"/>
-      <c r="D118" s="77"/>
-      <c r="E118" s="77"/>
-      <c r="F118" s="77"/>
-      <c r="G118" s="77"/>
-      <c r="H118" s="77"/>
-      <c r="I118" s="77"/>
-      <c r="J118" s="78"/>
+      <c r="C118" s="71"/>
+      <c r="D118" s="71"/>
+      <c r="E118" s="71"/>
+      <c r="F118" s="71"/>
+      <c r="G118" s="71"/>
+      <c r="H118" s="71"/>
+      <c r="I118" s="71"/>
+      <c r="J118" s="72"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="63"/>
-      <c r="B119" s="77"/>
-      <c r="C119" s="77"/>
-      <c r="D119" s="77"/>
-      <c r="E119" s="77"/>
-      <c r="F119" s="77"/>
-      <c r="G119" s="77"/>
-      <c r="H119" s="77"/>
-      <c r="I119" s="77"/>
-      <c r="J119" s="78"/>
+      <c r="A119" s="66"/>
+      <c r="B119" s="71"/>
+      <c r="C119" s="71"/>
+      <c r="D119" s="71"/>
+      <c r="E119" s="71"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="71"/>
+      <c r="H119" s="71"/>
+      <c r="I119" s="71"/>
+      <c r="J119" s="72"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="63"/>
-      <c r="B120" s="77"/>
-      <c r="C120" s="77"/>
-      <c r="D120" s="77"/>
-      <c r="E120" s="77"/>
-      <c r="F120" s="77"/>
-      <c r="G120" s="77"/>
-      <c r="H120" s="77"/>
-      <c r="I120" s="77"/>
-      <c r="J120" s="78"/>
+      <c r="A120" s="66"/>
+      <c r="B120" s="71"/>
+      <c r="C120" s="71"/>
+      <c r="D120" s="71"/>
+      <c r="E120" s="71"/>
+      <c r="F120" s="71"/>
+      <c r="G120" s="71"/>
+      <c r="H120" s="71"/>
+      <c r="I120" s="71"/>
+      <c r="J120" s="72"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="63"/>
-      <c r="B121" s="77"/>
-      <c r="C121" s="77"/>
-      <c r="D121" s="77"/>
-      <c r="E121" s="77"/>
-      <c r="F121" s="77"/>
-      <c r="G121" s="77"/>
-      <c r="H121" s="77"/>
-      <c r="I121" s="77"/>
-      <c r="J121" s="78"/>
+      <c r="A121" s="66"/>
+      <c r="B121" s="71"/>
+      <c r="C121" s="71"/>
+      <c r="D121" s="71"/>
+      <c r="E121" s="71"/>
+      <c r="F121" s="71"/>
+      <c r="G121" s="71"/>
+      <c r="H121" s="71"/>
+      <c r="I121" s="71"/>
+      <c r="J121" s="72"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="63"/>
-      <c r="B122" s="77"/>
-      <c r="C122" s="77"/>
-      <c r="D122" s="77"/>
-      <c r="E122" s="77"/>
-      <c r="F122" s="77"/>
-      <c r="G122" s="77"/>
-      <c r="H122" s="77"/>
-      <c r="I122" s="77"/>
-      <c r="J122" s="78"/>
+      <c r="A122" s="66"/>
+      <c r="B122" s="71"/>
+      <c r="C122" s="71"/>
+      <c r="D122" s="71"/>
+      <c r="E122" s="71"/>
+      <c r="F122" s="71"/>
+      <c r="G122" s="71"/>
+      <c r="H122" s="71"/>
+      <c r="I122" s="71"/>
+      <c r="J122" s="72"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="63"/>
-      <c r="B123" s="77"/>
-      <c r="C123" s="77"/>
-      <c r="D123" s="77"/>
-      <c r="E123" s="77"/>
-      <c r="F123" s="77"/>
-      <c r="G123" s="77"/>
-      <c r="H123" s="77"/>
-      <c r="I123" s="77"/>
-      <c r="J123" s="78"/>
+      <c r="A123" s="66"/>
+      <c r="B123" s="71"/>
+      <c r="C123" s="71"/>
+      <c r="D123" s="71"/>
+      <c r="E123" s="71"/>
+      <c r="F123" s="71"/>
+      <c r="G123" s="71"/>
+      <c r="H123" s="71"/>
+      <c r="I123" s="71"/>
+      <c r="J123" s="72"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="63"/>
-      <c r="B124" s="77"/>
-      <c r="C124" s="77"/>
-      <c r="D124" s="77"/>
-      <c r="E124" s="77"/>
-      <c r="F124" s="77"/>
-      <c r="G124" s="77"/>
-      <c r="H124" s="77"/>
-      <c r="I124" s="77"/>
-      <c r="J124" s="78"/>
+      <c r="A124" s="66"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
+      <c r="G124" s="71"/>
+      <c r="H124" s="71"/>
+      <c r="I124" s="71"/>
+      <c r="J124" s="72"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="64"/>
-      <c r="B125" s="105"/>
-      <c r="C125" s="105"/>
-      <c r="D125" s="105"/>
-      <c r="E125" s="105"/>
-      <c r="F125" s="105"/>
-      <c r="G125" s="105"/>
-      <c r="H125" s="105"/>
-      <c r="I125" s="105"/>
-      <c r="J125" s="106"/>
+      <c r="A125" s="67"/>
+      <c r="B125" s="75"/>
+      <c r="C125" s="75"/>
+      <c r="D125" s="75"/>
+      <c r="E125" s="75"/>
+      <c r="F125" s="75"/>
+      <c r="G125" s="75"/>
+      <c r="H125" s="75"/>
+      <c r="I125" s="75"/>
+      <c r="J125" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="B69:J86"/>
+    <mergeCell ref="A63:A86"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="B5:J7"/>
+    <mergeCell ref="B22:J25"/>
+    <mergeCell ref="B26:J62"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B8:J20"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="A110:A125"/>
@@ -6217,29 +6221,6 @@
     <mergeCell ref="B87:J87"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B93:J107"/>
-    <mergeCell ref="B69:J86"/>
-    <mergeCell ref="A63:A86"/>
-    <mergeCell ref="D64:J64"/>
-    <mergeCell ref="B5:J7"/>
-    <mergeCell ref="B22:J25"/>
-    <mergeCell ref="B26:J62"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B8:J20"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D66:J66"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D65:J65"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6270,71 +6251,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="44"/>
-      <c r="H6" s="47" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="58" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6344,547 +6325,580 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="48"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="59"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="219">
+      <c r="A8" s="37">
         <v>1</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="E8" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="39"/>
+      <c r="H8" s="36"/>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="37">
+        <v>2</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="E9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="39"/>
+      <c r="H9" s="36"/>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="37">
+        <v>3</v>
+      </c>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="61"/>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="219">
-        <v>2</v>
-      </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="35" t="s">
+      <c r="E10" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="39"/>
+      <c r="H10" s="36"/>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37">
+        <v>4</v>
+      </c>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="60" t="s">
+      <c r="E11" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="219">
-        <v>3</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="35" t="s">
+      <c r="G11" s="39"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="37">
+        <v>5</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E10" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="60" t="s">
+      <c r="E12" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="219">
-        <v>4</v>
-      </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="60" t="s">
+      <c r="G12" s="39"/>
+      <c r="H12" s="36"/>
+    </row>
+    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="37">
+        <v>6</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="219">
-        <v>5</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="60" t="s">
+      <c r="C13" s="41" t="s">
         <v>174</v>
-      </c>
-      <c r="G12" s="61"/>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="219">
-        <v>6</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="53" t="s">
-        <v>176</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="44"/>
+      <c r="H13" s="27"/>
+    </row>
+    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="37">
+        <v>7</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="44"/>
+      <c r="H14" s="27"/>
+    </row>
+    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="37">
+        <v>8</v>
+      </c>
+      <c r="B15" s="41"/>
+      <c r="C15" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F15" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="44"/>
+      <c r="H15" s="27"/>
+    </row>
+    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="37">
+        <v>9</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="27"/>
-    </row>
-    <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="219">
-        <v>7</v>
-      </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="27" t="s">
+      <c r="G16" s="44"/>
+      <c r="H16" s="27"/>
+    </row>
+    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37">
+        <v>10</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="44"/>
+      <c r="H17" s="27"/>
+    </row>
+    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="37">
+        <v>11</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="44"/>
+      <c r="H18" s="27"/>
+    </row>
+    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="37">
+        <v>12</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="49"/>
+      <c r="H19" s="27"/>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="37">
+        <v>13</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="44"/>
+      <c r="H20" s="27"/>
+    </row>
+    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="37">
+        <v>14</v>
+      </c>
+      <c r="B21" s="41"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="G21" s="49"/>
+      <c r="H21" s="27"/>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="37">
+        <v>15</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="27"/>
-    </row>
-    <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="219">
-        <v>8</v>
-      </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="27" t="s">
+      <c r="F22" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="G22" s="49"/>
+      <c r="H22" s="27"/>
+    </row>
+    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="37">
+        <v>16</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F23" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="44"/>
+      <c r="H23" s="27"/>
+    </row>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="37">
+        <v>17</v>
+      </c>
+      <c r="B24" s="46"/>
+      <c r="C24" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="44"/>
+      <c r="H24" s="27"/>
+    </row>
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="37">
+        <v>18</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="219">
-        <v>9</v>
-      </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="27" t="s">
+      <c r="G25" s="44"/>
+      <c r="H25" s="27"/>
+    </row>
+    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="37">
+        <v>19</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="27"/>
-    </row>
-    <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="219">
-        <v>10</v>
-      </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="27" t="s">
+      <c r="F26" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="44"/>
+      <c r="H26" s="27"/>
+    </row>
+    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="37">
+        <v>20</v>
+      </c>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="27"/>
-    </row>
-    <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="219">
-        <v>11</v>
-      </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="27"/>
-    </row>
-    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="219">
-        <v>12</v>
-      </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="56" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="27"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="219">
-        <v>13</v>
-      </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="27"/>
-    </row>
-    <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="219">
-        <v>14</v>
-      </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="50"/>
-      <c r="H21" s="27"/>
-    </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="219">
-        <v>15</v>
-      </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="27"/>
-    </row>
-    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="219">
-        <v>16</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="37" t="s">
+      <c r="F27" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="27"/>
-    </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="219">
-        <v>17</v>
-      </c>
-      <c r="B24" s="55"/>
-      <c r="C24" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="27"/>
-    </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="219">
-        <v>18</v>
-      </c>
-      <c r="B25" s="52"/>
-      <c r="C25" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="27"/>
-    </row>
-    <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="219">
-        <v>19</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="27"/>
-    </row>
-    <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="219">
-        <v>20</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G27" s="38"/>
+      <c r="G27" s="44"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="219">
+      <c r="A28" s="37">
         <v>21</v>
       </c>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="44"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="219">
+      <c r="A29" s="37">
         <v>22</v>
       </c>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="219">
+      <c r="A30" s="37">
         <v>23</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="44"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="219">
+      <c r="A31" s="37">
         <v>24</v>
       </c>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="219">
+      <c r="A32" s="37">
         <v>25</v>
       </c>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="44"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="219">
+      <c r="A33" s="37">
         <v>26</v>
       </c>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="44"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="219">
+      <c r="A34" s="37">
         <v>27</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="44"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="219">
+      <c r="A35" s="37">
         <v>28</v>
       </c>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="38"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="44"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="219">
+      <c r="A36" s="37">
         <v>29</v>
       </c>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="44"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="219">
+      <c r="A37" s="37">
         <v>30</v>
       </c>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="38"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="44"/>
       <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="219">
+      <c r="A38" s="37">
         <v>31</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="219">
+      <c r="A39" s="37">
         <v>32</v>
       </c>
       <c r="B39" s="27"/>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="38"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="44"/>
       <c r="H39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="B13:B22"/>
     <mergeCell ref="F39:G39"/>
@@ -6901,39 +6915,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6960,458 +6941,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="120"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="41" t="s">
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="41"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="41"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="52"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="115" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="77" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
+        <v>104</v>
+      </c>
+      <c r="D7" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="117"/>
+      <c r="B8" s="116"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="117"/>
+      <c r="B9" s="116"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="114" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="77" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
+      <c r="C11" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="77" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="117"/>
+      <c r="B13" s="116"/>
       <c r="C13" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="102" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
+        <v>109</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="115"/>
+      <c r="B14" s="117"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="116" t="s">
+      <c r="B15" s="118" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="77" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
+        <v>111</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="117"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="117"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="115"/>
+      <c r="B18" s="117"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="116" t="s">
+      <c r="B19" s="118" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
+        <v>113</v>
+      </c>
+      <c r="D19" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="117"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="117"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="115"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="116" t="s">
+      <c r="B23" s="118" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="77" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
+        <v>115</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="121"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="77" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
+        <v>117</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="121"/>
+      <c r="B25" s="119"/>
       <c r="C25" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="77" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
+        <v>118</v>
+      </c>
+      <c r="D25" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="121"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="102" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
+        <v>119</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="122"/>
+      <c r="B27" s="120"/>
       <c r="C27" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="123" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="125"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="123"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="118" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="77" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
+        <v>122</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="117"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="77" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+        <v>124</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="117"/>
+      <c r="B30" s="116"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="115"/>
+      <c r="B31" s="117"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7420,11 +7401,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7433,11 +7414,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7446,11 +7427,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7459,11 +7440,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7472,11 +7453,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7485,15 +7466,45 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B28:B31"/>
@@ -7510,36 +7521,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:H6"/>
     <mergeCell ref="D9:H9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -7563,23 +7544,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="213" t="s">
+      <c r="B1" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="214"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="214"/>
-      <c r="P1" s="214"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7596,141 +7577,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="166" t="s">
-        <v>149</v>
-      </c>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="166"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="166"/>
-      <c r="S2" s="166"/>
-      <c r="T2" s="166"/>
-      <c r="U2" s="166"/>
-      <c r="V2" s="166"/>
-      <c r="W2" s="166"/>
-      <c r="X2" s="166"/>
-      <c r="Y2" s="166"/>
-      <c r="Z2" s="166"/>
-      <c r="AA2" s="166"/>
-      <c r="AB2" s="166"/>
-      <c r="AC2" s="166"/>
-      <c r="AD2" s="166"/>
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="137" t="s">
+        <v>147</v>
+      </c>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="137"/>
+      <c r="W2" s="137"/>
+      <c r="X2" s="137"/>
+      <c r="Y2" s="137"/>
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="137"/>
+      <c r="AD2" s="137"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="160"/>
-      <c r="D4" s="160"/>
-      <c r="E4" s="160"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="160"/>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="160"/>
-      <c r="L4" s="160"/>
-      <c r="M4" s="160"/>
-      <c r="N4" s="160"/>
-      <c r="O4" s="160"/>
-      <c r="P4" s="160"/>
-      <c r="Q4" s="167" t="s">
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="206"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="171"/>
-      <c r="S4" s="168"/>
-      <c r="T4" s="167" t="s">
+      <c r="R4" s="214"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="210" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="171"/>
-      <c r="V4" s="171"/>
-      <c r="W4" s="168"/>
-      <c r="X4" s="167" t="s">
+      <c r="U4" s="214"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="168"/>
-      <c r="Z4" s="160" t="s">
+      <c r="Y4" s="211"/>
+      <c r="Z4" s="206" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA4" s="206"/>
+      <c r="AB4" s="206"/>
+      <c r="AC4" s="206" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD4" s="206"/>
+      <c r="AE4" s="206"/>
+      <c r="AF4" s="206" t="s">
         <v>134</v>
       </c>
-      <c r="AA4" s="160"/>
-      <c r="AB4" s="160"/>
-      <c r="AC4" s="160" t="s">
+      <c r="AG4" s="206"/>
+      <c r="AH4" s="206"/>
+      <c r="AI4" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="AD4" s="160"/>
-      <c r="AE4" s="160"/>
-      <c r="AF4" s="160" t="s">
+      <c r="AJ4" s="206"/>
+      <c r="AK4" s="206"/>
+      <c r="AL4" s="206" t="s">
         <v>136</v>
       </c>
-      <c r="AG4" s="160"/>
-      <c r="AH4" s="160"/>
-      <c r="AI4" s="160" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ4" s="160"/>
-      <c r="AK4" s="160"/>
-      <c r="AL4" s="160" t="s">
-        <v>138</v>
-      </c>
-      <c r="AM4" s="160"/>
-      <c r="AN4" s="160"/>
-      <c r="AO4" s="160" t="s">
+      <c r="AM4" s="206"/>
+      <c r="AN4" s="206"/>
+      <c r="AO4" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="160"/>
-      <c r="AQ4" s="160"/>
-      <c r="AR4" s="160"/>
-      <c r="AS4" s="160"/>
-      <c r="AT4" s="160"/>
-      <c r="AU4" s="160"/>
-      <c r="AV4" s="160"/>
-      <c r="AW4" s="160"/>
-      <c r="AX4" s="160"/>
-      <c r="AY4" s="160"/>
-      <c r="AZ4" s="161"/>
+      <c r="AP4" s="206"/>
+      <c r="AQ4" s="206"/>
+      <c r="AR4" s="206"/>
+      <c r="AS4" s="206"/>
+      <c r="AT4" s="206"/>
+      <c r="AU4" s="206"/>
+      <c r="AV4" s="206"/>
+      <c r="AW4" s="206"/>
+      <c r="AX4" s="206"/>
+      <c r="AY4" s="206"/>
+      <c r="AZ4" s="207"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="174"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="169"/>
-      <c r="R5" s="172"/>
-      <c r="S5" s="170"/>
-      <c r="T5" s="169"/>
-      <c r="U5" s="172"/>
-      <c r="V5" s="172"/>
-      <c r="W5" s="170"/>
-      <c r="X5" s="169"/>
-      <c r="Y5" s="170"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="M5" s="208"/>
+      <c r="N5" s="208"/>
+      <c r="O5" s="208"/>
+      <c r="P5" s="208"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="213"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="213"/>
+      <c r="X5" s="212"/>
+      <c r="Y5" s="213"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7776,58 +7757,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="162"/>
-      <c r="AP5" s="162"/>
-      <c r="AQ5" s="162"/>
-      <c r="AR5" s="162"/>
-      <c r="AS5" s="162"/>
-      <c r="AT5" s="162"/>
-      <c r="AU5" s="162"/>
-      <c r="AV5" s="162"/>
-      <c r="AW5" s="162"/>
-      <c r="AX5" s="162"/>
-      <c r="AY5" s="162"/>
-      <c r="AZ5" s="163"/>
+      <c r="AO5" s="208"/>
+      <c r="AP5" s="208"/>
+      <c r="AQ5" s="208"/>
+      <c r="AR5" s="208"/>
+      <c r="AS5" s="208"/>
+      <c r="AT5" s="208"/>
+      <c r="AU5" s="208"/>
+      <c r="AV5" s="208"/>
+      <c r="AW5" s="208"/>
+      <c r="AX5" s="208"/>
+      <c r="AY5" s="208"/>
+      <c r="AZ5" s="209"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="189">
+      <c r="B6" s="133">
         <v>1</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
-      <c r="J6" s="175" t="s">
-        <v>129</v>
-      </c>
-      <c r="K6" s="175"/>
-      <c r="L6" s="175"/>
-      <c r="M6" s="175"/>
-      <c r="N6" s="175"/>
-      <c r="O6" s="175"/>
-      <c r="P6" s="175"/>
-      <c r="Q6" s="166" t="s">
-        <v>130</v>
-      </c>
-      <c r="R6" s="166"/>
-      <c r="S6" s="166"/>
-      <c r="T6" s="180" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130" t="s">
+        <v>127</v>
+      </c>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="R6" s="137"/>
+      <c r="S6" s="137"/>
+      <c r="T6" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="180"/>
-      <c r="V6" s="178">
+      <c r="U6" s="134"/>
+      <c r="V6" s="131">
         <v>0</v>
       </c>
-      <c r="W6" s="178"/>
-      <c r="X6" s="164">
+      <c r="W6" s="131"/>
+      <c r="X6" s="153">
         <v>0</v>
       </c>
-      <c r="Y6" s="164"/>
+      <c r="Y6" s="153"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7843,50 +7824,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="175"/>
-      <c r="AP6" s="175"/>
-      <c r="AQ6" s="175"/>
-      <c r="AR6" s="175"/>
-      <c r="AS6" s="175"/>
-      <c r="AT6" s="175"/>
-      <c r="AU6" s="175"/>
-      <c r="AV6" s="175"/>
-      <c r="AW6" s="175"/>
-      <c r="AX6" s="175"/>
-      <c r="AY6" s="175"/>
-      <c r="AZ6" s="176"/>
+      <c r="AO6" s="130"/>
+      <c r="AP6" s="130"/>
+      <c r="AQ6" s="130"/>
+      <c r="AR6" s="130"/>
+      <c r="AS6" s="130"/>
+      <c r="AT6" s="130"/>
+      <c r="AU6" s="130"/>
+      <c r="AV6" s="130"/>
+      <c r="AW6" s="130"/>
+      <c r="AX6" s="130"/>
+      <c r="AY6" s="130"/>
+      <c r="AZ6" s="152"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="189"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
-      <c r="J7" s="175"/>
-      <c r="K7" s="175"/>
-      <c r="L7" s="175"/>
-      <c r="M7" s="175"/>
-      <c r="N7" s="175"/>
-      <c r="O7" s="175"/>
-      <c r="P7" s="175"/>
-      <c r="Q7" s="166"/>
-      <c r="R7" s="166"/>
-      <c r="S7" s="166"/>
-      <c r="T7" s="177" t="s">
+      <c r="B7" s="133"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="177"/>
-      <c r="V7" s="179">
+      <c r="U7" s="135"/>
+      <c r="V7" s="132">
         <v>0</v>
       </c>
-      <c r="W7" s="179"/>
-      <c r="X7" s="165">
+      <c r="W7" s="132"/>
+      <c r="X7" s="154">
         <v>1</v>
       </c>
-      <c r="Y7" s="165"/>
+      <c r="Y7" s="154"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7902,58 +7883,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="175"/>
-      <c r="AP7" s="175"/>
-      <c r="AQ7" s="175"/>
-      <c r="AR7" s="175"/>
-      <c r="AS7" s="175"/>
-      <c r="AT7" s="175"/>
-      <c r="AU7" s="175"/>
-      <c r="AV7" s="175"/>
-      <c r="AW7" s="175"/>
-      <c r="AX7" s="175"/>
-      <c r="AY7" s="175"/>
-      <c r="AZ7" s="176"/>
+      <c r="AO7" s="130"/>
+      <c r="AP7" s="130"/>
+      <c r="AQ7" s="130"/>
+      <c r="AR7" s="130"/>
+      <c r="AS7" s="130"/>
+      <c r="AT7" s="130"/>
+      <c r="AU7" s="130"/>
+      <c r="AV7" s="130"/>
+      <c r="AW7" s="130"/>
+      <c r="AX7" s="130"/>
+      <c r="AY7" s="130"/>
+      <c r="AZ7" s="152"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="189">
+      <c r="B8" s="133">
         <v>2</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="151" t="s">
-        <v>131</v>
-      </c>
-      <c r="K8" s="134"/>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
-      <c r="N8" s="134"/>
-      <c r="O8" s="134"/>
-      <c r="P8" s="135"/>
-      <c r="Q8" s="216" t="s">
-        <v>132</v>
-      </c>
-      <c r="R8" s="216"/>
-      <c r="S8" s="216"/>
-      <c r="T8" s="180" t="s">
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="138" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="180"/>
-      <c r="V8" s="178">
+      <c r="U8" s="134"/>
+      <c r="V8" s="131">
         <v>0</v>
       </c>
-      <c r="W8" s="178"/>
-      <c r="X8" s="164">
+      <c r="W8" s="131"/>
+      <c r="X8" s="153">
         <v>0</v>
       </c>
-      <c r="Y8" s="164"/>
+      <c r="Y8" s="153"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7969,50 +7950,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="175"/>
-      <c r="AP8" s="175"/>
-      <c r="AQ8" s="175"/>
-      <c r="AR8" s="175"/>
-      <c r="AS8" s="175"/>
-      <c r="AT8" s="175"/>
-      <c r="AU8" s="175"/>
-      <c r="AV8" s="175"/>
-      <c r="AW8" s="175"/>
-      <c r="AX8" s="175"/>
-      <c r="AY8" s="175"/>
-      <c r="AZ8" s="176"/>
+      <c r="AO8" s="130"/>
+      <c r="AP8" s="130"/>
+      <c r="AQ8" s="130"/>
+      <c r="AR8" s="130"/>
+      <c r="AS8" s="130"/>
+      <c r="AT8" s="130"/>
+      <c r="AU8" s="130"/>
+      <c r="AV8" s="130"/>
+      <c r="AW8" s="130"/>
+      <c r="AX8" s="130"/>
+      <c r="AY8" s="130"/>
+      <c r="AZ8" s="152"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="189"/>
-      <c r="C9" s="175"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="137"/>
-      <c r="P9" s="138"/>
-      <c r="Q9" s="216"/>
-      <c r="R9" s="216"/>
-      <c r="S9" s="216"/>
-      <c r="T9" s="177" t="s">
+      <c r="B9" s="133"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="142"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="142"/>
+      <c r="N9" s="142"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="143"/>
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="136"/>
+      <c r="T9" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="177"/>
-      <c r="V9" s="179">
+      <c r="U9" s="135"/>
+      <c r="V9" s="132">
         <v>0</v>
       </c>
-      <c r="W9" s="179"/>
-      <c r="X9" s="165">
+      <c r="W9" s="132"/>
+      <c r="X9" s="154">
         <v>1</v>
       </c>
-      <c r="Y9" s="165"/>
+      <c r="Y9" s="154"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -8028,58 +8009,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="175"/>
-      <c r="AP9" s="175"/>
-      <c r="AQ9" s="175"/>
-      <c r="AR9" s="175"/>
-      <c r="AS9" s="175"/>
-      <c r="AT9" s="175"/>
-      <c r="AU9" s="175"/>
-      <c r="AV9" s="175"/>
-      <c r="AW9" s="175"/>
-      <c r="AX9" s="175"/>
-      <c r="AY9" s="175"/>
-      <c r="AZ9" s="176"/>
+      <c r="AO9" s="130"/>
+      <c r="AP9" s="130"/>
+      <c r="AQ9" s="130"/>
+      <c r="AR9" s="130"/>
+      <c r="AS9" s="130"/>
+      <c r="AT9" s="130"/>
+      <c r="AU9" s="130"/>
+      <c r="AV9" s="130"/>
+      <c r="AW9" s="130"/>
+      <c r="AX9" s="130"/>
+      <c r="AY9" s="130"/>
+      <c r="AZ9" s="152"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="189">
+      <c r="B10" s="133">
         <v>3</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="215" t="s">
-        <v>139</v>
-      </c>
-      <c r="K10" s="175"/>
-      <c r="L10" s="175"/>
-      <c r="M10" s="175"/>
-      <c r="N10" s="175"/>
-      <c r="O10" s="175"/>
-      <c r="P10" s="175"/>
-      <c r="Q10" s="166" t="s">
-        <v>130</v>
-      </c>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="180" t="s">
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="129" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="130"/>
+      <c r="O10" s="130"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="R10" s="137"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="180"/>
-      <c r="V10" s="178">
+      <c r="U10" s="134"/>
+      <c r="V10" s="131">
         <v>0</v>
       </c>
-      <c r="W10" s="178"/>
-      <c r="X10" s="164">
+      <c r="W10" s="131"/>
+      <c r="X10" s="153">
         <v>0</v>
       </c>
-      <c r="Y10" s="164"/>
+      <c r="Y10" s="153"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -8095,50 +8076,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="175"/>
-      <c r="AP10" s="175"/>
-      <c r="AQ10" s="175"/>
-      <c r="AR10" s="175"/>
-      <c r="AS10" s="175"/>
-      <c r="AT10" s="175"/>
-      <c r="AU10" s="175"/>
-      <c r="AV10" s="175"/>
-      <c r="AW10" s="175"/>
-      <c r="AX10" s="175"/>
-      <c r="AY10" s="175"/>
-      <c r="AZ10" s="176"/>
+      <c r="AO10" s="130"/>
+      <c r="AP10" s="130"/>
+      <c r="AQ10" s="130"/>
+      <c r="AR10" s="130"/>
+      <c r="AS10" s="130"/>
+      <c r="AT10" s="130"/>
+      <c r="AU10" s="130"/>
+      <c r="AV10" s="130"/>
+      <c r="AW10" s="130"/>
+      <c r="AX10" s="130"/>
+      <c r="AY10" s="130"/>
+      <c r="AZ10" s="152"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="189"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="175"/>
-      <c r="L11" s="175"/>
-      <c r="M11" s="175"/>
-      <c r="N11" s="175"/>
-      <c r="O11" s="175"/>
-      <c r="P11" s="175"/>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="177" t="s">
+      <c r="B11" s="133"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+      <c r="N11" s="130"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="177"/>
-      <c r="V11" s="179">
+      <c r="U11" s="135"/>
+      <c r="V11" s="132">
         <v>0</v>
       </c>
-      <c r="W11" s="179"/>
-      <c r="X11" s="165">
+      <c r="W11" s="132"/>
+      <c r="X11" s="154">
         <v>0</v>
       </c>
-      <c r="Y11" s="165"/>
+      <c r="Y11" s="154"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -8154,58 +8135,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="175"/>
-      <c r="AP11" s="175"/>
-      <c r="AQ11" s="175"/>
-      <c r="AR11" s="175"/>
-      <c r="AS11" s="175"/>
-      <c r="AT11" s="175"/>
-      <c r="AU11" s="175"/>
-      <c r="AV11" s="175"/>
-      <c r="AW11" s="175"/>
-      <c r="AX11" s="175"/>
-      <c r="AY11" s="175"/>
-      <c r="AZ11" s="176"/>
+      <c r="AO11" s="130"/>
+      <c r="AP11" s="130"/>
+      <c r="AQ11" s="130"/>
+      <c r="AR11" s="130"/>
+      <c r="AS11" s="130"/>
+      <c r="AT11" s="130"/>
+      <c r="AU11" s="130"/>
+      <c r="AV11" s="130"/>
+      <c r="AW11" s="130"/>
+      <c r="AX11" s="130"/>
+      <c r="AY11" s="130"/>
+      <c r="AZ11" s="152"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="189">
+      <c r="B12" s="133">
         <v>4</v>
       </c>
-      <c r="C12" s="175" t="s">
+      <c r="C12" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="175"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="175"/>
-      <c r="I12" s="175"/>
-      <c r="J12" s="175" t="s">
-        <v>133</v>
-      </c>
-      <c r="K12" s="175"/>
-      <c r="L12" s="175"/>
-      <c r="M12" s="175"/>
-      <c r="N12" s="175"/>
-      <c r="O12" s="175"/>
-      <c r="P12" s="175"/>
-      <c r="Q12" s="139" t="s">
-        <v>130</v>
-      </c>
-      <c r="R12" s="140"/>
-      <c r="S12" s="141"/>
-      <c r="T12" s="180" t="s">
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="130"/>
+      <c r="N12" s="130"/>
+      <c r="O12" s="130"/>
+      <c r="P12" s="130"/>
+      <c r="Q12" s="196" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" s="197"/>
+      <c r="S12" s="198"/>
+      <c r="T12" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="180"/>
-      <c r="V12" s="178">
+      <c r="U12" s="134"/>
+      <c r="V12" s="131">
         <v>0</v>
       </c>
-      <c r="W12" s="178"/>
-      <c r="X12" s="164">
+      <c r="W12" s="131"/>
+      <c r="X12" s="153">
         <v>0</v>
       </c>
-      <c r="Y12" s="164"/>
+      <c r="Y12" s="153"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -8221,50 +8202,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="175"/>
-      <c r="AP12" s="175"/>
-      <c r="AQ12" s="175"/>
-      <c r="AR12" s="175"/>
-      <c r="AS12" s="175"/>
-      <c r="AT12" s="175"/>
-      <c r="AU12" s="175"/>
-      <c r="AV12" s="175"/>
-      <c r="AW12" s="175"/>
-      <c r="AX12" s="175"/>
-      <c r="AY12" s="175"/>
-      <c r="AZ12" s="176"/>
+      <c r="AO12" s="130"/>
+      <c r="AP12" s="130"/>
+      <c r="AQ12" s="130"/>
+      <c r="AR12" s="130"/>
+      <c r="AS12" s="130"/>
+      <c r="AT12" s="130"/>
+      <c r="AU12" s="130"/>
+      <c r="AV12" s="130"/>
+      <c r="AW12" s="130"/>
+      <c r="AX12" s="130"/>
+      <c r="AY12" s="130"/>
+      <c r="AZ12" s="152"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="189"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
-      <c r="L13" s="175"/>
-      <c r="M13" s="175"/>
-      <c r="N13" s="175"/>
-      <c r="O13" s="175"/>
-      <c r="P13" s="175"/>
-      <c r="Q13" s="142"/>
-      <c r="R13" s="143"/>
-      <c r="S13" s="144"/>
-      <c r="T13" s="177" t="s">
+      <c r="B13" s="133"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="199"/>
+      <c r="R13" s="200"/>
+      <c r="S13" s="201"/>
+      <c r="T13" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="177"/>
-      <c r="V13" s="179">
+      <c r="U13" s="135"/>
+      <c r="V13" s="132">
         <v>0</v>
       </c>
-      <c r="W13" s="179"/>
-      <c r="X13" s="165">
+      <c r="W13" s="132"/>
+      <c r="X13" s="154">
         <v>0</v>
       </c>
-      <c r="Y13" s="165"/>
+      <c r="Y13" s="154"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8280,54 +8261,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="175"/>
-      <c r="AP13" s="175"/>
-      <c r="AQ13" s="175"/>
-      <c r="AR13" s="175"/>
-      <c r="AS13" s="175"/>
-      <c r="AT13" s="175"/>
-      <c r="AU13" s="175"/>
-      <c r="AV13" s="175"/>
-      <c r="AW13" s="175"/>
-      <c r="AX13" s="175"/>
-      <c r="AY13" s="175"/>
-      <c r="AZ13" s="176"/>
+      <c r="AO13" s="130"/>
+      <c r="AP13" s="130"/>
+      <c r="AQ13" s="130"/>
+      <c r="AR13" s="130"/>
+      <c r="AS13" s="130"/>
+      <c r="AT13" s="130"/>
+      <c r="AU13" s="130"/>
+      <c r="AV13" s="130"/>
+      <c r="AW13" s="130"/>
+      <c r="AX13" s="130"/>
+      <c r="AY13" s="130"/>
+      <c r="AZ13" s="152"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="189">
+      <c r="B14" s="133">
         <v>5</v>
       </c>
-      <c r="C14" s="151" t="s">
+      <c r="C14" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="215"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="175"/>
-      <c r="M14" s="175"/>
-      <c r="N14" s="175"/>
-      <c r="O14" s="175"/>
-      <c r="P14" s="175"/>
-      <c r="Q14" s="139"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="141"/>
-      <c r="T14" s="180" t="s">
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="196"/>
+      <c r="R14" s="197"/>
+      <c r="S14" s="198"/>
+      <c r="T14" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="180"/>
-      <c r="V14" s="178">
+      <c r="U14" s="134"/>
+      <c r="V14" s="131">
         <v>0</v>
       </c>
-      <c r="W14" s="178"/>
-      <c r="X14" s="164">
+      <c r="W14" s="131"/>
+      <c r="X14" s="153">
         <v>0</v>
       </c>
-      <c r="Y14" s="164"/>
+      <c r="Y14" s="153"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8343,50 +8324,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="175"/>
-      <c r="AP14" s="175"/>
-      <c r="AQ14" s="175"/>
-      <c r="AR14" s="175"/>
-      <c r="AS14" s="175"/>
-      <c r="AT14" s="175"/>
-      <c r="AU14" s="175"/>
-      <c r="AV14" s="175"/>
-      <c r="AW14" s="175"/>
-      <c r="AX14" s="175"/>
-      <c r="AY14" s="175"/>
-      <c r="AZ14" s="176"/>
+      <c r="AO14" s="130"/>
+      <c r="AP14" s="130"/>
+      <c r="AQ14" s="130"/>
+      <c r="AR14" s="130"/>
+      <c r="AS14" s="130"/>
+      <c r="AT14" s="130"/>
+      <c r="AU14" s="130"/>
+      <c r="AV14" s="130"/>
+      <c r="AW14" s="130"/>
+      <c r="AX14" s="130"/>
+      <c r="AY14" s="130"/>
+      <c r="AZ14" s="152"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="189"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="138"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="175"/>
-      <c r="L15" s="175"/>
-      <c r="M15" s="175"/>
-      <c r="N15" s="175"/>
-      <c r="O15" s="175"/>
-      <c r="P15" s="175"/>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="143"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="177" t="s">
+      <c r="B15" s="133"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="199"/>
+      <c r="R15" s="200"/>
+      <c r="S15" s="201"/>
+      <c r="T15" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="177"/>
-      <c r="V15" s="179">
+      <c r="U15" s="135"/>
+      <c r="V15" s="132">
         <v>0</v>
       </c>
-      <c r="W15" s="179"/>
-      <c r="X15" s="165">
+      <c r="W15" s="132"/>
+      <c r="X15" s="154">
         <v>0</v>
       </c>
-      <c r="Y15" s="165"/>
+      <c r="Y15" s="154"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8402,56 +8383,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="175"/>
-      <c r="AP15" s="175"/>
-      <c r="AQ15" s="175"/>
-      <c r="AR15" s="175"/>
-      <c r="AS15" s="175"/>
-      <c r="AT15" s="175"/>
-      <c r="AU15" s="175"/>
-      <c r="AV15" s="175"/>
-      <c r="AW15" s="175"/>
-      <c r="AX15" s="175"/>
-      <c r="AY15" s="175"/>
-      <c r="AZ15" s="176"/>
+      <c r="AO15" s="130"/>
+      <c r="AP15" s="130"/>
+      <c r="AQ15" s="130"/>
+      <c r="AR15" s="130"/>
+      <c r="AS15" s="130"/>
+      <c r="AT15" s="130"/>
+      <c r="AU15" s="130"/>
+      <c r="AV15" s="130"/>
+      <c r="AW15" s="130"/>
+      <c r="AX15" s="130"/>
+      <c r="AY15" s="130"/>
+      <c r="AZ15" s="152"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="189">
+      <c r="B16" s="133">
         <v>6</v>
       </c>
-      <c r="C16" s="151" t="s">
+      <c r="C16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="215" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="175"/>
-      <c r="L16" s="175"/>
-      <c r="M16" s="175"/>
-      <c r="N16" s="175"/>
-      <c r="O16" s="175"/>
-      <c r="P16" s="175"/>
-      <c r="Q16" s="166"/>
-      <c r="R16" s="166"/>
-      <c r="S16" s="166"/>
-      <c r="T16" s="180" t="s">
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="129" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
+      <c r="P16" s="130"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="180"/>
-      <c r="V16" s="178">
+      <c r="U16" s="134"/>
+      <c r="V16" s="131">
         <v>0</v>
       </c>
-      <c r="W16" s="178"/>
-      <c r="X16" s="164">
+      <c r="W16" s="131"/>
+      <c r="X16" s="153">
         <v>0</v>
       </c>
-      <c r="Y16" s="164"/>
+      <c r="Y16" s="153"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8467,50 +8448,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="175"/>
-      <c r="AP16" s="175"/>
-      <c r="AQ16" s="175"/>
-      <c r="AR16" s="175"/>
-      <c r="AS16" s="175"/>
-      <c r="AT16" s="175"/>
-      <c r="AU16" s="175"/>
-      <c r="AV16" s="175"/>
-      <c r="AW16" s="175"/>
-      <c r="AX16" s="175"/>
-      <c r="AY16" s="175"/>
-      <c r="AZ16" s="176"/>
+      <c r="AO16" s="130"/>
+      <c r="AP16" s="130"/>
+      <c r="AQ16" s="130"/>
+      <c r="AR16" s="130"/>
+      <c r="AS16" s="130"/>
+      <c r="AT16" s="130"/>
+      <c r="AU16" s="130"/>
+      <c r="AV16" s="130"/>
+      <c r="AW16" s="130"/>
+      <c r="AX16" s="130"/>
+      <c r="AY16" s="130"/>
+      <c r="AZ16" s="152"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="189"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="138"/>
-      <c r="J17" s="175"/>
-      <c r="K17" s="175"/>
-      <c r="L17" s="175"/>
-      <c r="M17" s="175"/>
-      <c r="N17" s="175"/>
-      <c r="O17" s="175"/>
-      <c r="P17" s="175"/>
-      <c r="Q17" s="166"/>
-      <c r="R17" s="166"/>
-      <c r="S17" s="166"/>
-      <c r="T17" s="177" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="177"/>
-      <c r="V17" s="179">
+      <c r="U17" s="135"/>
+      <c r="V17" s="132">
         <v>0</v>
       </c>
-      <c r="W17" s="179"/>
-      <c r="X17" s="165">
+      <c r="W17" s="132"/>
+      <c r="X17" s="154">
         <v>0</v>
       </c>
-      <c r="Y17" s="165"/>
+      <c r="Y17" s="154"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8526,56 +8507,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="175"/>
-      <c r="AP17" s="175"/>
-      <c r="AQ17" s="175"/>
-      <c r="AR17" s="175"/>
-      <c r="AS17" s="175"/>
-      <c r="AT17" s="175"/>
-      <c r="AU17" s="175"/>
-      <c r="AV17" s="175"/>
-      <c r="AW17" s="175"/>
-      <c r="AX17" s="175"/>
-      <c r="AY17" s="175"/>
-      <c r="AZ17" s="176"/>
+      <c r="AO17" s="130"/>
+      <c r="AP17" s="130"/>
+      <c r="AQ17" s="130"/>
+      <c r="AR17" s="130"/>
+      <c r="AS17" s="130"/>
+      <c r="AT17" s="130"/>
+      <c r="AU17" s="130"/>
+      <c r="AV17" s="130"/>
+      <c r="AW17" s="130"/>
+      <c r="AX17" s="130"/>
+      <c r="AY17" s="130"/>
+      <c r="AZ17" s="152"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="126">
+      <c r="B18" s="150">
         <v>7</v>
       </c>
-      <c r="C18" s="128" t="s">
+      <c r="C18" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="151" t="s">
-        <v>141</v>
-      </c>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="134"/>
-      <c r="N18" s="134"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="135"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="140"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="145" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="184"/>
+      <c r="F18" s="184"/>
+      <c r="G18" s="184"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="138" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="196"/>
+      <c r="R18" s="197"/>
+      <c r="S18" s="198"/>
+      <c r="T18" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="146"/>
-      <c r="V18" s="147">
+      <c r="U18" s="187"/>
+      <c r="V18" s="146">
         <v>0</v>
       </c>
-      <c r="W18" s="148"/>
-      <c r="X18" s="149">
+      <c r="W18" s="147"/>
+      <c r="X18" s="192">
         <v>0</v>
       </c>
-      <c r="Y18" s="150"/>
+      <c r="Y18" s="193"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8591,50 +8572,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="151"/>
-      <c r="AP18" s="134"/>
-      <c r="AQ18" s="134"/>
-      <c r="AR18" s="134"/>
-      <c r="AS18" s="134"/>
-      <c r="AT18" s="134"/>
-      <c r="AU18" s="134"/>
-      <c r="AV18" s="134"/>
-      <c r="AW18" s="134"/>
-      <c r="AX18" s="134"/>
-      <c r="AY18" s="134"/>
-      <c r="AZ18" s="152"/>
+      <c r="AO18" s="138"/>
+      <c r="AP18" s="139"/>
+      <c r="AQ18" s="139"/>
+      <c r="AR18" s="139"/>
+      <c r="AS18" s="139"/>
+      <c r="AT18" s="139"/>
+      <c r="AU18" s="139"/>
+      <c r="AV18" s="139"/>
+      <c r="AW18" s="139"/>
+      <c r="AX18" s="139"/>
+      <c r="AY18" s="139"/>
+      <c r="AZ18" s="188"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="127"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="133"/>
-      <c r="J19" s="136"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="138"/>
-      <c r="Q19" s="142"/>
-      <c r="R19" s="143"/>
-      <c r="S19" s="144"/>
-      <c r="T19" s="154" t="s">
+      <c r="B19" s="151"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="169"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="142"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="142"/>
+      <c r="N19" s="142"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="143"/>
+      <c r="Q19" s="199"/>
+      <c r="R19" s="200"/>
+      <c r="S19" s="201"/>
+      <c r="T19" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="155"/>
-      <c r="V19" s="156">
+      <c r="U19" s="191"/>
+      <c r="V19" s="148">
         <v>0</v>
       </c>
-      <c r="W19" s="157"/>
-      <c r="X19" s="158">
+      <c r="W19" s="149"/>
+      <c r="X19" s="194">
         <v>0</v>
       </c>
-      <c r="Y19" s="159"/>
+      <c r="Y19" s="195"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8650,56 +8631,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="136"/>
-      <c r="AP19" s="137"/>
-      <c r="AQ19" s="137"/>
-      <c r="AR19" s="137"/>
-      <c r="AS19" s="137"/>
-      <c r="AT19" s="137"/>
-      <c r="AU19" s="137"/>
-      <c r="AV19" s="137"/>
-      <c r="AW19" s="137"/>
-      <c r="AX19" s="137"/>
-      <c r="AY19" s="137"/>
-      <c r="AZ19" s="153"/>
+      <c r="AO19" s="141"/>
+      <c r="AP19" s="142"/>
+      <c r="AQ19" s="142"/>
+      <c r="AR19" s="142"/>
+      <c r="AS19" s="142"/>
+      <c r="AT19" s="142"/>
+      <c r="AU19" s="142"/>
+      <c r="AV19" s="142"/>
+      <c r="AW19" s="142"/>
+      <c r="AX19" s="142"/>
+      <c r="AY19" s="142"/>
+      <c r="AZ19" s="189"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="126">
+      <c r="B20" s="150">
         <v>8</v>
       </c>
-      <c r="C20" s="128" t="s">
+      <c r="C20" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="128" t="s">
-        <v>142</v>
-      </c>
-      <c r="K20" s="134"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
-      <c r="N20" s="134"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="135"/>
-      <c r="Q20" s="139"/>
-      <c r="R20" s="140"/>
-      <c r="S20" s="141"/>
-      <c r="T20" s="145" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="183" t="s">
+        <v>140</v>
+      </c>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="196"/>
+      <c r="R20" s="197"/>
+      <c r="S20" s="198"/>
+      <c r="T20" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="146"/>
-      <c r="V20" s="147">
+      <c r="U20" s="187"/>
+      <c r="V20" s="146">
         <v>0</v>
       </c>
-      <c r="W20" s="148"/>
-      <c r="X20" s="149">
+      <c r="W20" s="147"/>
+      <c r="X20" s="192">
         <v>0</v>
       </c>
-      <c r="Y20" s="150"/>
+      <c r="Y20" s="193"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8715,50 +8696,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="151"/>
-      <c r="AP20" s="134"/>
-      <c r="AQ20" s="134"/>
-      <c r="AR20" s="134"/>
-      <c r="AS20" s="134"/>
-      <c r="AT20" s="134"/>
-      <c r="AU20" s="134"/>
-      <c r="AV20" s="134"/>
-      <c r="AW20" s="134"/>
-      <c r="AX20" s="134"/>
-      <c r="AY20" s="134"/>
-      <c r="AZ20" s="152"/>
+      <c r="AO20" s="138"/>
+      <c r="AP20" s="139"/>
+      <c r="AQ20" s="139"/>
+      <c r="AR20" s="139"/>
+      <c r="AS20" s="139"/>
+      <c r="AT20" s="139"/>
+      <c r="AU20" s="139"/>
+      <c r="AV20" s="139"/>
+      <c r="AW20" s="139"/>
+      <c r="AX20" s="139"/>
+      <c r="AY20" s="139"/>
+      <c r="AZ20" s="188"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="127"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="136"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="137"/>
-      <c r="P21" s="138"/>
-      <c r="Q21" s="142"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="144"/>
-      <c r="T21" s="154" t="s">
+      <c r="B21" s="151"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="142"/>
+      <c r="L21" s="142"/>
+      <c r="M21" s="142"/>
+      <c r="N21" s="142"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="199"/>
+      <c r="R21" s="200"/>
+      <c r="S21" s="201"/>
+      <c r="T21" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="155"/>
-      <c r="V21" s="156">
+      <c r="U21" s="191"/>
+      <c r="V21" s="148">
         <v>0</v>
       </c>
-      <c r="W21" s="157"/>
-      <c r="X21" s="158">
+      <c r="W21" s="149"/>
+      <c r="X21" s="194">
         <v>0</v>
       </c>
-      <c r="Y21" s="159"/>
+      <c r="Y21" s="195"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8774,54 +8755,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="136"/>
-      <c r="AP21" s="137"/>
-      <c r="AQ21" s="137"/>
-      <c r="AR21" s="137"/>
-      <c r="AS21" s="137"/>
-      <c r="AT21" s="137"/>
-      <c r="AU21" s="137"/>
-      <c r="AV21" s="137"/>
-      <c r="AW21" s="137"/>
-      <c r="AX21" s="137"/>
-      <c r="AY21" s="137"/>
-      <c r="AZ21" s="153"/>
+      <c r="AO21" s="141"/>
+      <c r="AP21" s="142"/>
+      <c r="AQ21" s="142"/>
+      <c r="AR21" s="142"/>
+      <c r="AS21" s="142"/>
+      <c r="AT21" s="142"/>
+      <c r="AU21" s="142"/>
+      <c r="AV21" s="142"/>
+      <c r="AW21" s="142"/>
+      <c r="AX21" s="142"/>
+      <c r="AY21" s="142"/>
+      <c r="AZ21" s="189"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="196">
+      <c r="B22" s="163">
         <v>9</v>
       </c>
-      <c r="C22" s="198" t="s">
+      <c r="C22" s="165" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="199"/>
-      <c r="E22" s="199"/>
-      <c r="F22" s="199"/>
-      <c r="G22" s="199"/>
-      <c r="H22" s="199"/>
-      <c r="I22" s="200"/>
-      <c r="J22" s="183"/>
-      <c r="K22" s="184"/>
-      <c r="L22" s="184"/>
-      <c r="M22" s="184"/>
-      <c r="N22" s="184"/>
-      <c r="O22" s="184"/>
-      <c r="P22" s="185"/>
-      <c r="Q22" s="205"/>
-      <c r="R22" s="206"/>
-      <c r="S22" s="207"/>
-      <c r="T22" s="201" t="s">
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="156"/>
+      <c r="L22" s="156"/>
+      <c r="M22" s="156"/>
+      <c r="N22" s="156"/>
+      <c r="O22" s="156"/>
+      <c r="P22" s="204"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="176"/>
+      <c r="S22" s="177"/>
+      <c r="T22" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="202"/>
-      <c r="V22" s="181">
+      <c r="U22" s="172"/>
+      <c r="V22" s="202">
         <v>0</v>
       </c>
-      <c r="W22" s="182"/>
-      <c r="X22" s="194">
+      <c r="W22" s="203"/>
+      <c r="X22" s="161">
         <v>0</v>
       </c>
-      <c r="Y22" s="195"/>
+      <c r="Y22" s="162"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8837,50 +8818,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="183"/>
-      <c r="AP22" s="184"/>
-      <c r="AQ22" s="184"/>
-      <c r="AR22" s="184"/>
-      <c r="AS22" s="184"/>
-      <c r="AT22" s="184"/>
-      <c r="AU22" s="184"/>
-      <c r="AV22" s="184"/>
-      <c r="AW22" s="184"/>
-      <c r="AX22" s="184"/>
-      <c r="AY22" s="184"/>
-      <c r="AZ22" s="192"/>
+      <c r="AO22" s="155"/>
+      <c r="AP22" s="156"/>
+      <c r="AQ22" s="156"/>
+      <c r="AR22" s="156"/>
+      <c r="AS22" s="156"/>
+      <c r="AT22" s="156"/>
+      <c r="AU22" s="156"/>
+      <c r="AV22" s="156"/>
+      <c r="AW22" s="156"/>
+      <c r="AX22" s="156"/>
+      <c r="AY22" s="156"/>
+      <c r="AZ22" s="157"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="197"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="133"/>
-      <c r="J23" s="186"/>
-      <c r="K23" s="187"/>
-      <c r="L23" s="187"/>
-      <c r="M23" s="187"/>
-      <c r="N23" s="187"/>
-      <c r="O23" s="187"/>
-      <c r="P23" s="188"/>
-      <c r="Q23" s="208"/>
-      <c r="R23" s="209"/>
-      <c r="S23" s="210"/>
-      <c r="T23" s="203" t="s">
+      <c r="B23" s="164"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="159"/>
+      <c r="L23" s="159"/>
+      <c r="M23" s="159"/>
+      <c r="N23" s="159"/>
+      <c r="O23" s="159"/>
+      <c r="P23" s="205"/>
+      <c r="Q23" s="178"/>
+      <c r="R23" s="179"/>
+      <c r="S23" s="180"/>
+      <c r="T23" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="204"/>
-      <c r="V23" s="190">
+      <c r="U23" s="174"/>
+      <c r="V23" s="144">
         <v>0</v>
       </c>
-      <c r="W23" s="191"/>
-      <c r="X23" s="211">
+      <c r="W23" s="145"/>
+      <c r="X23" s="181">
         <v>0</v>
       </c>
-      <c r="Y23" s="212"/>
+      <c r="Y23" s="182"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8896,18 +8877,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="186"/>
-      <c r="AP23" s="187"/>
-      <c r="AQ23" s="187"/>
-      <c r="AR23" s="187"/>
-      <c r="AS23" s="187"/>
-      <c r="AT23" s="187"/>
-      <c r="AU23" s="187"/>
-      <c r="AV23" s="187"/>
-      <c r="AW23" s="187"/>
-      <c r="AX23" s="187"/>
-      <c r="AY23" s="187"/>
-      <c r="AZ23" s="193"/>
+      <c r="AO23" s="158"/>
+      <c r="AP23" s="159"/>
+      <c r="AQ23" s="159"/>
+      <c r="AR23" s="159"/>
+      <c r="AS23" s="159"/>
+      <c r="AT23" s="159"/>
+      <c r="AU23" s="159"/>
+      <c r="AV23" s="159"/>
+      <c r="AW23" s="159"/>
+      <c r="AX23" s="159"/>
+      <c r="AY23" s="159"/>
+      <c r="AZ23" s="160"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8966,27 +8947,74 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO18:AZ19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q18:S19"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="J22:P23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:I13"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="AO12:AZ13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="AO14:AZ15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Q12:S13"/>
+    <mergeCell ref="Q14:S15"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="V19:W19"/>
@@ -9011,74 +9039,27 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="C18:I19"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AO18:AZ19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q18:S19"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="J22:P23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:I13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="AO12:AZ13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="AO14:AZ15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Q12:S13"/>
-    <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9102,612 +9083,611 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="62">
+      <c r="A1" s="64">
         <v>1</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70" t="s">
-        <v>149</v>
-      </c>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="71"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="111" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="112"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="62">
+      <c r="A3" s="64">
         <v>2</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="100"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
-      <c r="B4" s="217" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="218" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="218"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="219"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="62">
+      <c r="A5" s="64">
         <v>3</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="100"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="107" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="108"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="100"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="63"/>
-      <c r="B8" s="103" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="74"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="63"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="78"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="63"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="78"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="63"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="78"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="63"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="63"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="78"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="63"/>
-      <c r="B15" s="103" t="s">
+      <c r="A15" s="66"/>
+      <c r="B15" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="74"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="78"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="78"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="78"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="78"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="78"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="66"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="73"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>5</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="100"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="78"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="78"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="63"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="78"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="78"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="63"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="78"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="63"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="78"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="78"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="66"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="73"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="114"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62">
+      <c r="A31" s="64">
         <v>6</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="100"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="63"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="78"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="78"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="63"/>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="78"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="63"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="78"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="78"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="63"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="78"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="72"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="63"/>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="78"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="63"/>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="78"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="72"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63"/>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="78"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="72"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="63"/>
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="78"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="72"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63"/>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="78"/>
+      <c r="A42" s="66"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="63"/>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="78"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="72"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="63"/>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-      <c r="J44" s="78"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="63"/>
-      <c r="B45" s="77"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="78"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="63"/>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="77"/>
-      <c r="J46" s="78"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="64"/>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="106"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -9716,12 +9696,13 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9734,6 +9715,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -9940,17 +9932,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9961,6 +9942,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9979,25 +9979,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
   <ds:schemaRefs>

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB539D59-6295-45B9-AAD0-157ED120C027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AA371A-6B4E-4ACE-ABBE-DB31E69E4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1730,6 +1730,284 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>チャットボット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不足情報追加質問</t>
+    <rPh sb="0" eb="2">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シツモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI・分析系</t>
+  </si>
+  <si>
+    <t>追加回答登録</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加質問に対する回答を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果に関する質問受付</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ウケツケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質問に対する回答表示</t>
+    <rPh sb="0" eb="2">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果に関する質問を入力できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIが質問内容と分析結果を基に回答を生成し表示できる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析に必要な情報が不足している場合、不足情報について追加質問できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フソク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シツモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報管理</t>
+  </si>
+  <si>
+    <t>建物情報管理</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報一覧表示</t>
+  </si>
+  <si>
+    <t>建物情報詳細表示</t>
+  </si>
+  <si>
+    <t>建物情報編集</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報削除</t>
+  </si>
+  <si>
+    <t>登録した建物の一覧を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の詳細を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の情報を編集できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した建物の情報を削除できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況・分析</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>①：概要
 本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録すると、AIが被害状況を分析し、その目安を提示することで、被害状況の把握や専門家への相談を支援するWebシステムである。
 また、分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報を提示する。登録した写真や分析結果は履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
@@ -1749,7 +2027,7 @@
 ・災害発生直後にはアクセスが集中すると想定される
 ④：システムとの関係
 提案先：建物調査を実施している企業、修理業者
-利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
+利用者：災害によって建物や室内に被害を受けた個人</t>
     <rPh sb="2" eb="4">
       <t>ガイヨウ</t>
     </rPh>
@@ -1797,284 +2075,6 @@
     </rPh>
     <rPh sb="392" eb="394">
       <t>カンケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チャットボット</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>不足情報追加質問</t>
-    <rPh sb="0" eb="2">
-      <t>フソク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シツモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>AI・分析系</t>
-  </si>
-  <si>
-    <t>追加回答登録</t>
-    <rPh sb="0" eb="2">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>追加質問に対する回答を登録できる</t>
-    <rPh sb="0" eb="2">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分析結果に関する質問受付</t>
-    <rPh sb="0" eb="2">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ウケツケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>質問に対する回答表示</t>
-    <rPh sb="0" eb="2">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分析結果に関する質問を入力できる</t>
-    <rPh sb="0" eb="2">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>AIが質問内容と分析結果を基に回答を生成し表示できる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分析に必要な情報が不足している場合、不足情報について追加質問できる</t>
-    <rPh sb="0" eb="2">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>フソク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>フソク</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シツモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報管理</t>
-  </si>
-  <si>
-    <t>建物情報管理</t>
-    <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報登録</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報登録</t>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報一覧表示</t>
-  </si>
-  <si>
-    <t>建物情報詳細表示</t>
-  </si>
-  <si>
-    <t>建物情報編集</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報削除</t>
-  </si>
-  <si>
-    <t>登録した建物の一覧を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の詳細を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の情報を編集できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の情報を削除できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況・分析</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況登録</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況を登録できる</t>
-    <rPh sb="0" eb="2">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3175,12 +3175,63 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3190,12 +3241,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3205,81 +3250,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3298,48 +3391,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3349,74 +3406,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3433,14 +3442,266 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3452,268 +3713,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -4603,1592 +4603,1601 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64">
+      <c r="A2" s="63">
         <v>1</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="111" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="64">
+      <c r="A4" s="63">
         <v>2</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="80"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="66"/>
-      <c r="B5" s="82" t="s">
+      <c r="A5" s="64"/>
+      <c r="B5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="83"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="83"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="81"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="66"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="85"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="83"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="66"/>
-      <c r="B8" s="87" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="89"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="66"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="92"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="66"/>
-      <c r="B11" s="90"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="92"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="66"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="92"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="92"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="66"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="92"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="100"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="66"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="92"/>
+      <c r="A15" s="64"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="100"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="66"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="92"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="100"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="65"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="92"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="100"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="92"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="100"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="65"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="100"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="100"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="64">
+      <c r="A21" s="63">
         <v>3</v>
       </c>
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="80"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="69"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="66"/>
-      <c r="B22" s="99" t="s">
+      <c r="A22" s="64"/>
+      <c r="B22" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="101"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="86"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="101"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66"/>
-      <c r="B24" s="99"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="101"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="86"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="89"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="66"/>
-      <c r="B26" s="105" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="106"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="90" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="91"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="66"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="106"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="90"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="91"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="66"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="106"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="91"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="66"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="91"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="66"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="106"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="91"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="66"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="106"/>
+      <c r="A31" s="64"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="91"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="66"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="106"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="90"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="91"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="66"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="106"/>
+      <c r="A33" s="64"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="91"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="66"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="106"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="90"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="91"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="66"/>
-      <c r="B35" s="105"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="106"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="91"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="66"/>
-      <c r="B36" s="105"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="106"/>
+      <c r="A36" s="64"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="91"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="66"/>
-      <c r="B37" s="105"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="106"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="91"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66"/>
-      <c r="B38" s="105"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="106"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="90"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="90"/>
+      <c r="I38" s="90"/>
+      <c r="J38" s="91"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66"/>
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="105"/>
-      <c r="G39" s="105"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="106"/>
+      <c r="A39" s="64"/>
+      <c r="B39" s="90"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="90"/>
+      <c r="I39" s="90"/>
+      <c r="J39" s="91"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66"/>
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="106"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="91"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="66"/>
-      <c r="B41" s="105"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="106"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="91"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="66"/>
-      <c r="B42" s="105"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
-      <c r="H42" s="105"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="106"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="91"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="66"/>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="90"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="90"/>
+      <c r="F43" s="90"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="90"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="91"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="66"/>
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="105"/>
-      <c r="I44" s="105"/>
-      <c r="J44" s="106"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="90"/>
+      <c r="F44" s="90"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="90"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="66"/>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="105"/>
-      <c r="J45" s="106"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="90"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="90"/>
+      <c r="F45" s="90"/>
+      <c r="G45" s="90"/>
+      <c r="H45" s="90"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="91"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="66"/>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="106"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="90"/>
+      <c r="F46" s="90"/>
+      <c r="G46" s="90"/>
+      <c r="H46" s="90"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="66"/>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="106"/>
+      <c r="A47" s="64"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="66"/>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="105"/>
-      <c r="F48" s="105"/>
-      <c r="G48" s="105"/>
-      <c r="H48" s="105"/>
-      <c r="I48" s="105"/>
-      <c r="J48" s="106"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="90"/>
+      <c r="F48" s="90"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="90"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="66"/>
-      <c r="B49" s="105"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="105"/>
-      <c r="E49" s="105"/>
-      <c r="F49" s="105"/>
-      <c r="G49" s="105"/>
-      <c r="H49" s="105"/>
-      <c r="I49" s="105"/>
-      <c r="J49" s="106"/>
+      <c r="A49" s="64"/>
+      <c r="B49" s="90"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="90"/>
+      <c r="F49" s="90"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="91"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="66"/>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="106"/>
+      <c r="A50" s="64"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="90"/>
+      <c r="F50" s="90"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="91"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="66"/>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="105"/>
-      <c r="E51" s="105"/>
-      <c r="F51" s="105"/>
-      <c r="G51" s="105"/>
-      <c r="H51" s="105"/>
-      <c r="I51" s="105"/>
-      <c r="J51" s="106"/>
+      <c r="A51" s="64"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="90"/>
+      <c r="F51" s="90"/>
+      <c r="G51" s="90"/>
+      <c r="H51" s="90"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="91"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="66"/>
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="106"/>
+      <c r="A52" s="64"/>
+      <c r="B52" s="90"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="90"/>
+      <c r="F52" s="90"/>
+      <c r="G52" s="90"/>
+      <c r="H52" s="90"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="91"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="66"/>
-      <c r="B53" s="105"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="105"/>
-      <c r="E53" s="105"/>
-      <c r="F53" s="105"/>
-      <c r="G53" s="105"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="106"/>
+      <c r="A53" s="64"/>
+      <c r="B53" s="90"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="90"/>
+      <c r="F53" s="90"/>
+      <c r="G53" s="90"/>
+      <c r="H53" s="90"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="91"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="66"/>
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="105"/>
-      <c r="H54" s="105"/>
-      <c r="I54" s="105"/>
-      <c r="J54" s="106"/>
+      <c r="A54" s="64"/>
+      <c r="B54" s="90"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="90"/>
+      <c r="F54" s="90"/>
+      <c r="G54" s="90"/>
+      <c r="H54" s="90"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="91"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="66"/>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="105"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="105"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
+      <c r="H55" s="90"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="91"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="66"/>
-      <c r="B56" s="105"/>
-      <c r="C56" s="105"/>
-      <c r="D56" s="105"/>
-      <c r="E56" s="105"/>
-      <c r="F56" s="105"/>
-      <c r="G56" s="105"/>
-      <c r="H56" s="105"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="106"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="90"/>
+      <c r="G56" s="90"/>
+      <c r="H56" s="90"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="91"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="66"/>
-      <c r="B57" s="105"/>
-      <c r="C57" s="105"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="105"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="105"/>
-      <c r="H57" s="105"/>
-      <c r="I57" s="105"/>
-      <c r="J57" s="106"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="90"/>
+      <c r="G57" s="90"/>
+      <c r="H57" s="90"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="91"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="66"/>
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="105"/>
-      <c r="H58" s="105"/>
-      <c r="I58" s="105"/>
-      <c r="J58" s="106"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="90"/>
+      <c r="G58" s="90"/>
+      <c r="H58" s="90"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="91"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="66"/>
-      <c r="B59" s="105"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="105"/>
-      <c r="G59" s="105"/>
-      <c r="H59" s="105"/>
-      <c r="I59" s="105"/>
-      <c r="J59" s="106"/>
+      <c r="A59" s="64"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
+      <c r="H59" s="90"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="91"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="66"/>
-      <c r="B60" s="105"/>
-      <c r="C60" s="105"/>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="106"/>
+      <c r="A60" s="64"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
+      <c r="H60" s="90"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="91"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="66"/>
-      <c r="B61" s="105"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="105"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="105"/>
-      <c r="I61" s="105"/>
-      <c r="J61" s="106"/>
+      <c r="A61" s="64"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="90"/>
+      <c r="G61" s="90"/>
+      <c r="H61" s="90"/>
+      <c r="I61" s="90"/>
+      <c r="J61" s="91"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="67"/>
-      <c r="B62" s="107"/>
-      <c r="C62" s="107"/>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="108"/>
+      <c r="A62" s="65"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
+      <c r="J62" s="93"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="64">
+      <c r="A63" s="63">
         <v>4</v>
       </c>
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="68"/>
-      <c r="I63" s="68"/>
-      <c r="J63" s="69"/>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="101"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="66"/>
-      <c r="B64" s="109" t="s">
+      <c r="A64" s="64"/>
+      <c r="B64" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="109"/>
-      <c r="D64" s="71" t="s">
+      <c r="C64" s="66"/>
+      <c r="D64" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="71"/>
-      <c r="F64" s="71"/>
-      <c r="G64" s="71"/>
-      <c r="H64" s="71"/>
-      <c r="I64" s="71"/>
-      <c r="J64" s="72"/>
+      <c r="E64" s="78"/>
+      <c r="F64" s="78"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="78"/>
+      <c r="I64" s="78"/>
+      <c r="J64" s="79"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="66"/>
-      <c r="B65" s="109" t="s">
+      <c r="A65" s="64"/>
+      <c r="B65" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="109"/>
-      <c r="D65" s="71" t="s">
+      <c r="C65" s="66"/>
+      <c r="D65" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="71"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="71"/>
-      <c r="H65" s="71"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="72"/>
+      <c r="E65" s="78"/>
+      <c r="F65" s="78"/>
+      <c r="G65" s="78"/>
+      <c r="H65" s="78"/>
+      <c r="I65" s="78"/>
+      <c r="J65" s="79"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="66"/>
-      <c r="B66" s="109" t="s">
+      <c r="A66" s="64"/>
+      <c r="B66" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="109"/>
-      <c r="D66" s="71" t="s">
+      <c r="C66" s="66"/>
+      <c r="D66" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="E66" s="71"/>
-      <c r="F66" s="71"/>
-      <c r="G66" s="71"/>
-      <c r="H66" s="71"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="72"/>
+      <c r="E66" s="78"/>
+      <c r="F66" s="78"/>
+      <c r="G66" s="78"/>
+      <c r="H66" s="78"/>
+      <c r="I66" s="78"/>
+      <c r="J66" s="79"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="66"/>
-      <c r="B67" s="109" t="s">
+      <c r="A67" s="64"/>
+      <c r="B67" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="109"/>
-      <c r="D67" s="71" t="s">
+      <c r="C67" s="66"/>
+      <c r="D67" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="72"/>
+      <c r="E67" s="78"/>
+      <c r="F67" s="78"/>
+      <c r="G67" s="78"/>
+      <c r="H67" s="78"/>
+      <c r="I67" s="78"/>
+      <c r="J67" s="79"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="66"/>
-      <c r="B68" s="109" t="s">
+      <c r="A68" s="64"/>
+      <c r="B68" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="109"/>
-      <c r="D68" s="109"/>
-      <c r="E68" s="109"/>
-      <c r="F68" s="109"/>
-      <c r="G68" s="109"/>
-      <c r="H68" s="109"/>
-      <c r="I68" s="109"/>
-      <c r="J68" s="110"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="66"/>
+      <c r="H68" s="66"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="94"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="66"/>
-      <c r="B69" s="96" t="e" vm="1">
+      <c r="A69" s="64"/>
+      <c r="B69" s="75" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="96"/>
-      <c r="D69" s="96"/>
-      <c r="E69" s="96"/>
-      <c r="F69" s="96"/>
-      <c r="G69" s="96"/>
-      <c r="H69" s="96"/>
-      <c r="I69" s="96"/>
-      <c r="J69" s="97"/>
+      <c r="C69" s="75"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="75"/>
+      <c r="J69" s="76"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="66"/>
-      <c r="B70" s="96"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="96"/>
-      <c r="E70" s="96"/>
-      <c r="F70" s="96"/>
-      <c r="G70" s="96"/>
-      <c r="H70" s="96"/>
-      <c r="I70" s="96"/>
-      <c r="J70" s="97"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="75"/>
+      <c r="C70" s="75"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="75"/>
+      <c r="I70" s="75"/>
+      <c r="J70" s="76"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="66"/>
-      <c r="B71" s="96"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="96"/>
-      <c r="E71" s="96"/>
-      <c r="F71" s="96"/>
-      <c r="G71" s="96"/>
-      <c r="H71" s="96"/>
-      <c r="I71" s="96"/>
-      <c r="J71" s="97"/>
+      <c r="A71" s="64"/>
+      <c r="B71" s="75"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="75"/>
+      <c r="I71" s="75"/>
+      <c r="J71" s="76"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="66"/>
-      <c r="B72" s="96"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="96"/>
-      <c r="E72" s="96"/>
-      <c r="F72" s="96"/>
-      <c r="G72" s="96"/>
-      <c r="H72" s="96"/>
-      <c r="I72" s="96"/>
-      <c r="J72" s="97"/>
+      <c r="A72" s="64"/>
+      <c r="B72" s="75"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="75"/>
+      <c r="J72" s="76"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="66"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="96"/>
-      <c r="D73" s="96"/>
-      <c r="E73" s="96"/>
-      <c r="F73" s="96"/>
-      <c r="G73" s="96"/>
-      <c r="H73" s="96"/>
-      <c r="I73" s="96"/>
-      <c r="J73" s="97"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="75"/>
+      <c r="C73" s="75"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="75"/>
+      <c r="J73" s="76"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="66"/>
-      <c r="B74" s="96"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="96"/>
-      <c r="E74" s="96"/>
-      <c r="F74" s="96"/>
-      <c r="G74" s="96"/>
-      <c r="H74" s="96"/>
-      <c r="I74" s="96"/>
-      <c r="J74" s="97"/>
+      <c r="A74" s="64"/>
+      <c r="B74" s="75"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="75"/>
+      <c r="J74" s="76"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="66"/>
-      <c r="B75" s="96"/>
-      <c r="C75" s="96"/>
-      <c r="D75" s="96"/>
-      <c r="E75" s="96"/>
-      <c r="F75" s="96"/>
-      <c r="G75" s="96"/>
-      <c r="H75" s="96"/>
-      <c r="I75" s="96"/>
-      <c r="J75" s="97"/>
+      <c r="A75" s="64"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="75"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="75"/>
+      <c r="H75" s="75"/>
+      <c r="I75" s="75"/>
+      <c r="J75" s="76"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="66"/>
-      <c r="B76" s="96"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="96"/>
-      <c r="E76" s="96"/>
-      <c r="F76" s="96"/>
-      <c r="G76" s="96"/>
-      <c r="H76" s="96"/>
-      <c r="I76" s="96"/>
-      <c r="J76" s="97"/>
+      <c r="A76" s="64"/>
+      <c r="B76" s="75"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="76"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="66"/>
-      <c r="B77" s="96"/>
-      <c r="C77" s="96"/>
-      <c r="D77" s="96"/>
-      <c r="E77" s="96"/>
-      <c r="F77" s="96"/>
-      <c r="G77" s="96"/>
-      <c r="H77" s="96"/>
-      <c r="I77" s="96"/>
-      <c r="J77" s="97"/>
+      <c r="A77" s="64"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="76"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="66"/>
-      <c r="B78" s="96"/>
-      <c r="C78" s="96"/>
-      <c r="D78" s="96"/>
-      <c r="E78" s="96"/>
-      <c r="F78" s="96"/>
-      <c r="G78" s="96"/>
-      <c r="H78" s="96"/>
-      <c r="I78" s="96"/>
-      <c r="J78" s="97"/>
+      <c r="A78" s="64"/>
+      <c r="B78" s="75"/>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="75"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="75"/>
+      <c r="H78" s="75"/>
+      <c r="I78" s="75"/>
+      <c r="J78" s="76"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="66"/>
-      <c r="B79" s="96"/>
-      <c r="C79" s="96"/>
-      <c r="D79" s="96"/>
-      <c r="E79" s="96"/>
-      <c r="F79" s="96"/>
-      <c r="G79" s="96"/>
-      <c r="H79" s="96"/>
-      <c r="I79" s="96"/>
-      <c r="J79" s="97"/>
+      <c r="A79" s="64"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="75"/>
+      <c r="I79" s="75"/>
+      <c r="J79" s="76"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="66"/>
-      <c r="B80" s="96"/>
-      <c r="C80" s="96"/>
-      <c r="D80" s="96"/>
-      <c r="E80" s="96"/>
-      <c r="F80" s="96"/>
-      <c r="G80" s="96"/>
-      <c r="H80" s="96"/>
-      <c r="I80" s="96"/>
-      <c r="J80" s="97"/>
+      <c r="A80" s="64"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
+      <c r="J80" s="76"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="66"/>
-      <c r="B81" s="96"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="96"/>
-      <c r="E81" s="96"/>
-      <c r="F81" s="96"/>
-      <c r="G81" s="96"/>
-      <c r="H81" s="96"/>
-      <c r="I81" s="96"/>
-      <c r="J81" s="97"/>
+      <c r="A81" s="64"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="75"/>
+      <c r="F81" s="75"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="75"/>
+      <c r="I81" s="75"/>
+      <c r="J81" s="76"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="66"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="96"/>
-      <c r="D82" s="96"/>
-      <c r="E82" s="96"/>
-      <c r="F82" s="96"/>
-      <c r="G82" s="96"/>
-      <c r="H82" s="96"/>
-      <c r="I82" s="96"/>
-      <c r="J82" s="97"/>
+      <c r="A82" s="64"/>
+      <c r="B82" s="75"/>
+      <c r="C82" s="75"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="76"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="66"/>
-      <c r="B83" s="96"/>
-      <c r="C83" s="96"/>
-      <c r="D83" s="96"/>
-      <c r="E83" s="96"/>
-      <c r="F83" s="96"/>
-      <c r="G83" s="96"/>
-      <c r="H83" s="96"/>
-      <c r="I83" s="96"/>
-      <c r="J83" s="97"/>
+      <c r="A83" s="64"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
+      <c r="I83" s="75"/>
+      <c r="J83" s="76"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="66"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="96"/>
-      <c r="E84" s="96"/>
-      <c r="F84" s="96"/>
-      <c r="G84" s="96"/>
-      <c r="H84" s="96"/>
-      <c r="I84" s="96"/>
-      <c r="J84" s="97"/>
+      <c r="A84" s="64"/>
+      <c r="B84" s="75"/>
+      <c r="C84" s="75"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
+      <c r="I84" s="75"/>
+      <c r="J84" s="76"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="66"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
-      <c r="F85" s="96"/>
-      <c r="G85" s="96"/>
-      <c r="H85" s="96"/>
-      <c r="I85" s="96"/>
-      <c r="J85" s="97"/>
+      <c r="A85" s="64"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="75"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="75"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
+      <c r="I85" s="75"/>
+      <c r="J85" s="76"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="65"/>
-      <c r="B86" s="40"/>
-      <c r="C86" s="40"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="40"/>
-      <c r="J86" s="98"/>
+      <c r="A86" s="67"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="77"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="64">
+      <c r="A87" s="63">
         <v>5</v>
       </c>
-      <c r="B87" s="68" t="s">
+      <c r="B87" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="68"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="69"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="70"/>
+      <c r="I87" s="70"/>
+      <c r="J87" s="101"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="51" t="s">
+      <c r="A88" s="64"/>
+      <c r="B88" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
-      <c r="J88" s="86"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="41"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="41"/>
+      <c r="I88" s="41"/>
+      <c r="J88" s="111"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="64">
+      <c r="A89" s="63">
         <v>6</v>
       </c>
-      <c r="B89" s="79" t="s">
+      <c r="B89" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="79"/>
-      <c r="D89" s="79"/>
-      <c r="E89" s="79"/>
-      <c r="F89" s="79"/>
-      <c r="G89" s="79"/>
-      <c r="H89" s="79"/>
-      <c r="I89" s="79"/>
-      <c r="J89" s="80"/>
+      <c r="C89" s="68"/>
+      <c r="D89" s="68"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="68"/>
+      <c r="G89" s="68"/>
+      <c r="H89" s="68"/>
+      <c r="I89" s="68"/>
+      <c r="J89" s="69"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="81"/>
-      <c r="B90" s="82" t="s">
+      <c r="A90" s="110"/>
+      <c r="B90" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="83"/>
+      <c r="C90" s="80"/>
+      <c r="D90" s="80"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="80"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="81"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="81"/>
-      <c r="B91" s="82"/>
-      <c r="C91" s="82"/>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="83"/>
+      <c r="A91" s="110"/>
+      <c r="B91" s="80"/>
+      <c r="C91" s="80"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="80"/>
+      <c r="I91" s="80"/>
+      <c r="J91" s="81"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="81"/>
-      <c r="B92" s="84"/>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
-      <c r="E92" s="84"/>
-      <c r="F92" s="84"/>
-      <c r="G92" s="84"/>
-      <c r="H92" s="84"/>
-      <c r="I92" s="84"/>
-      <c r="J92" s="85"/>
+      <c r="A92" s="110"/>
+      <c r="B92" s="82"/>
+      <c r="C92" s="82"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="82"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="82"/>
+      <c r="I92" s="82"/>
+      <c r="J92" s="83"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="66"/>
-      <c r="B93" s="87" t="s">
+      <c r="A93" s="64"/>
+      <c r="B93" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C93" s="88"/>
-      <c r="D93" s="88"/>
-      <c r="E93" s="88"/>
-      <c r="F93" s="88"/>
-      <c r="G93" s="88"/>
-      <c r="H93" s="88"/>
-      <c r="I93" s="88"/>
-      <c r="J93" s="89"/>
+      <c r="C93" s="96"/>
+      <c r="D93" s="96"/>
+      <c r="E93" s="96"/>
+      <c r="F93" s="96"/>
+      <c r="G93" s="96"/>
+      <c r="H93" s="96"/>
+      <c r="I93" s="96"/>
+      <c r="J93" s="97"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="66"/>
-      <c r="B94" s="90"/>
-      <c r="C94" s="91"/>
-      <c r="D94" s="91"/>
-      <c r="E94" s="91"/>
-      <c r="F94" s="91"/>
-      <c r="G94" s="91"/>
-      <c r="H94" s="91"/>
-      <c r="I94" s="91"/>
-      <c r="J94" s="92"/>
+      <c r="A94" s="64"/>
+      <c r="B94" s="98"/>
+      <c r="C94" s="99"/>
+      <c r="D94" s="99"/>
+      <c r="E94" s="99"/>
+      <c r="F94" s="99"/>
+      <c r="G94" s="99"/>
+      <c r="H94" s="99"/>
+      <c r="I94" s="99"/>
+      <c r="J94" s="100"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="66"/>
-      <c r="B95" s="90"/>
-      <c r="C95" s="91"/>
-      <c r="D95" s="91"/>
-      <c r="E95" s="91"/>
-      <c r="F95" s="91"/>
-      <c r="G95" s="91"/>
-      <c r="H95" s="91"/>
-      <c r="I95" s="91"/>
-      <c r="J95" s="92"/>
+      <c r="A95" s="64"/>
+      <c r="B95" s="98"/>
+      <c r="C95" s="99"/>
+      <c r="D95" s="99"/>
+      <c r="E95" s="99"/>
+      <c r="F95" s="99"/>
+      <c r="G95" s="99"/>
+      <c r="H95" s="99"/>
+      <c r="I95" s="99"/>
+      <c r="J95" s="100"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="66"/>
-      <c r="B96" s="90"/>
-      <c r="C96" s="91"/>
-      <c r="D96" s="91"/>
-      <c r="E96" s="91"/>
-      <c r="F96" s="91"/>
-      <c r="G96" s="91"/>
-      <c r="H96" s="91"/>
-      <c r="I96" s="91"/>
-      <c r="J96" s="92"/>
+      <c r="A96" s="64"/>
+      <c r="B96" s="98"/>
+      <c r="C96" s="99"/>
+      <c r="D96" s="99"/>
+      <c r="E96" s="99"/>
+      <c r="F96" s="99"/>
+      <c r="G96" s="99"/>
+      <c r="H96" s="99"/>
+      <c r="I96" s="99"/>
+      <c r="J96" s="100"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="66"/>
-      <c r="B97" s="90"/>
-      <c r="C97" s="91"/>
-      <c r="D97" s="91"/>
-      <c r="E97" s="91"/>
-      <c r="F97" s="91"/>
-      <c r="G97" s="91"/>
-      <c r="H97" s="91"/>
-      <c r="I97" s="91"/>
-      <c r="J97" s="92"/>
+      <c r="A97" s="64"/>
+      <c r="B97" s="98"/>
+      <c r="C97" s="99"/>
+      <c r="D97" s="99"/>
+      <c r="E97" s="99"/>
+      <c r="F97" s="99"/>
+      <c r="G97" s="99"/>
+      <c r="H97" s="99"/>
+      <c r="I97" s="99"/>
+      <c r="J97" s="100"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="66"/>
-      <c r="B98" s="90"/>
-      <c r="C98" s="91"/>
-      <c r="D98" s="91"/>
-      <c r="E98" s="91"/>
-      <c r="F98" s="91"/>
-      <c r="G98" s="91"/>
-      <c r="H98" s="91"/>
-      <c r="I98" s="91"/>
-      <c r="J98" s="92"/>
+      <c r="A98" s="64"/>
+      <c r="B98" s="98"/>
+      <c r="C98" s="99"/>
+      <c r="D98" s="99"/>
+      <c r="E98" s="99"/>
+      <c r="F98" s="99"/>
+      <c r="G98" s="99"/>
+      <c r="H98" s="99"/>
+      <c r="I98" s="99"/>
+      <c r="J98" s="100"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="66"/>
-      <c r="B99" s="90"/>
-      <c r="C99" s="91"/>
-      <c r="D99" s="91"/>
-      <c r="E99" s="91"/>
-      <c r="F99" s="91"/>
-      <c r="G99" s="91"/>
-      <c r="H99" s="91"/>
-      <c r="I99" s="91"/>
-      <c r="J99" s="92"/>
+      <c r="A99" s="64"/>
+      <c r="B99" s="98"/>
+      <c r="C99" s="99"/>
+      <c r="D99" s="99"/>
+      <c r="E99" s="99"/>
+      <c r="F99" s="99"/>
+      <c r="G99" s="99"/>
+      <c r="H99" s="99"/>
+      <c r="I99" s="99"/>
+      <c r="J99" s="100"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="66"/>
-      <c r="B100" s="90"/>
-      <c r="C100" s="91"/>
-      <c r="D100" s="91"/>
-      <c r="E100" s="91"/>
-      <c r="F100" s="91"/>
-      <c r="G100" s="91"/>
-      <c r="H100" s="91"/>
-      <c r="I100" s="91"/>
-      <c r="J100" s="92"/>
+      <c r="A100" s="64"/>
+      <c r="B100" s="98"/>
+      <c r="C100" s="99"/>
+      <c r="D100" s="99"/>
+      <c r="E100" s="99"/>
+      <c r="F100" s="99"/>
+      <c r="G100" s="99"/>
+      <c r="H100" s="99"/>
+      <c r="I100" s="99"/>
+      <c r="J100" s="100"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="66"/>
-      <c r="B101" s="90"/>
-      <c r="C101" s="91"/>
-      <c r="D101" s="91"/>
-      <c r="E101" s="91"/>
-      <c r="F101" s="91"/>
-      <c r="G101" s="91"/>
-      <c r="H101" s="91"/>
-      <c r="I101" s="91"/>
-      <c r="J101" s="92"/>
+      <c r="A101" s="64"/>
+      <c r="B101" s="98"/>
+      <c r="C101" s="99"/>
+      <c r="D101" s="99"/>
+      <c r="E101" s="99"/>
+      <c r="F101" s="99"/>
+      <c r="G101" s="99"/>
+      <c r="H101" s="99"/>
+      <c r="I101" s="99"/>
+      <c r="J101" s="100"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="66"/>
-      <c r="B102" s="90"/>
-      <c r="C102" s="91"/>
-      <c r="D102" s="91"/>
-      <c r="E102" s="91"/>
-      <c r="F102" s="91"/>
-      <c r="G102" s="91"/>
-      <c r="H102" s="91"/>
-      <c r="I102" s="91"/>
-      <c r="J102" s="92"/>
+      <c r="A102" s="64"/>
+      <c r="B102" s="98"/>
+      <c r="C102" s="99"/>
+      <c r="D102" s="99"/>
+      <c r="E102" s="99"/>
+      <c r="F102" s="99"/>
+      <c r="G102" s="99"/>
+      <c r="H102" s="99"/>
+      <c r="I102" s="99"/>
+      <c r="J102" s="100"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="66"/>
-      <c r="B103" s="90"/>
-      <c r="C103" s="91"/>
-      <c r="D103" s="91"/>
-      <c r="E103" s="91"/>
-      <c r="F103" s="91"/>
-      <c r="G103" s="91"/>
-      <c r="H103" s="91"/>
-      <c r="I103" s="91"/>
-      <c r="J103" s="92"/>
+      <c r="A103" s="64"/>
+      <c r="B103" s="98"/>
+      <c r="C103" s="99"/>
+      <c r="D103" s="99"/>
+      <c r="E103" s="99"/>
+      <c r="F103" s="99"/>
+      <c r="G103" s="99"/>
+      <c r="H103" s="99"/>
+      <c r="I103" s="99"/>
+      <c r="J103" s="100"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="66"/>
-      <c r="B104" s="90"/>
-      <c r="C104" s="91"/>
-      <c r="D104" s="91"/>
-      <c r="E104" s="91"/>
-      <c r="F104" s="91"/>
-      <c r="G104" s="91"/>
-      <c r="H104" s="91"/>
-      <c r="I104" s="91"/>
-      <c r="J104" s="92"/>
+      <c r="A104" s="64"/>
+      <c r="B104" s="98"/>
+      <c r="C104" s="99"/>
+      <c r="D104" s="99"/>
+      <c r="E104" s="99"/>
+      <c r="F104" s="99"/>
+      <c r="G104" s="99"/>
+      <c r="H104" s="99"/>
+      <c r="I104" s="99"/>
+      <c r="J104" s="100"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="66"/>
-      <c r="B105" s="90"/>
-      <c r="C105" s="91"/>
-      <c r="D105" s="91"/>
-      <c r="E105" s="91"/>
-      <c r="F105" s="91"/>
-      <c r="G105" s="91"/>
-      <c r="H105" s="91"/>
-      <c r="I105" s="91"/>
-      <c r="J105" s="92"/>
+      <c r="A105" s="64"/>
+      <c r="B105" s="98"/>
+      <c r="C105" s="99"/>
+      <c r="D105" s="99"/>
+      <c r="E105" s="99"/>
+      <c r="F105" s="99"/>
+      <c r="G105" s="99"/>
+      <c r="H105" s="99"/>
+      <c r="I105" s="99"/>
+      <c r="J105" s="100"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="66"/>
-      <c r="B106" s="90"/>
-      <c r="C106" s="91"/>
-      <c r="D106" s="91"/>
-      <c r="E106" s="91"/>
-      <c r="F106" s="91"/>
-      <c r="G106" s="91"/>
-      <c r="H106" s="91"/>
-      <c r="I106" s="91"/>
-      <c r="J106" s="92"/>
+      <c r="A106" s="64"/>
+      <c r="B106" s="98"/>
+      <c r="C106" s="99"/>
+      <c r="D106" s="99"/>
+      <c r="E106" s="99"/>
+      <c r="F106" s="99"/>
+      <c r="G106" s="99"/>
+      <c r="H106" s="99"/>
+      <c r="I106" s="99"/>
+      <c r="J106" s="100"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="67"/>
-      <c r="B107" s="93"/>
-      <c r="C107" s="94"/>
-      <c r="D107" s="94"/>
-      <c r="E107" s="94"/>
-      <c r="F107" s="94"/>
-      <c r="G107" s="94"/>
-      <c r="H107" s="94"/>
-      <c r="I107" s="94"/>
-      <c r="J107" s="95"/>
+      <c r="A107" s="65"/>
+      <c r="B107" s="112"/>
+      <c r="C107" s="113"/>
+      <c r="D107" s="113"/>
+      <c r="E107" s="113"/>
+      <c r="F107" s="113"/>
+      <c r="G107" s="113"/>
+      <c r="H107" s="113"/>
+      <c r="I107" s="113"/>
+      <c r="J107" s="114"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="64">
+      <c r="A108" s="63">
         <v>7</v>
       </c>
-      <c r="B108" s="68" t="s">
+      <c r="B108" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="68"/>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="68"/>
-      <c r="I108" s="68"/>
-      <c r="J108" s="69"/>
+      <c r="C108" s="70"/>
+      <c r="D108" s="70"/>
+      <c r="E108" s="70"/>
+      <c r="F108" s="70"/>
+      <c r="G108" s="70"/>
+      <c r="H108" s="70"/>
+      <c r="I108" s="70"/>
+      <c r="J108" s="101"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="65"/>
-      <c r="B109" s="77" t="s">
+      <c r="A109" s="67"/>
+      <c r="B109" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="77"/>
-      <c r="D109" s="77"/>
-      <c r="E109" s="77"/>
-      <c r="F109" s="77"/>
-      <c r="G109" s="77"/>
-      <c r="H109" s="77"/>
-      <c r="I109" s="77"/>
-      <c r="J109" s="78"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="108"/>
+      <c r="E109" s="108"/>
+      <c r="F109" s="108"/>
+      <c r="G109" s="108"/>
+      <c r="H109" s="108"/>
+      <c r="I109" s="108"/>
+      <c r="J109" s="109"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="64">
+      <c r="A110" s="63">
         <v>8</v>
       </c>
-      <c r="B110" s="68" t="s">
+      <c r="B110" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="68"/>
-      <c r="D110" s="68"/>
-      <c r="E110" s="68"/>
-      <c r="F110" s="68"/>
-      <c r="G110" s="68"/>
-      <c r="H110" s="68"/>
-      <c r="I110" s="68"/>
-      <c r="J110" s="69"/>
+      <c r="C110" s="70"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="70"/>
+      <c r="F110" s="70"/>
+      <c r="G110" s="70"/>
+      <c r="H110" s="70"/>
+      <c r="I110" s="70"/>
+      <c r="J110" s="101"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="66"/>
-      <c r="B111" s="70" t="s">
+      <c r="A111" s="64"/>
+      <c r="B111" s="103" t="s">
         <v>142</v>
       </c>
-      <c r="C111" s="71"/>
-      <c r="D111" s="71"/>
-      <c r="E111" s="71"/>
-      <c r="F111" s="71"/>
-      <c r="G111" s="71"/>
-      <c r="H111" s="71"/>
-      <c r="I111" s="71"/>
-      <c r="J111" s="72"/>
+      <c r="C111" s="78"/>
+      <c r="D111" s="78"/>
+      <c r="E111" s="78"/>
+      <c r="F111" s="78"/>
+      <c r="G111" s="78"/>
+      <c r="H111" s="78"/>
+      <c r="I111" s="78"/>
+      <c r="J111" s="79"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="66"/>
-      <c r="B112" s="71"/>
-      <c r="C112" s="71"/>
-      <c r="D112" s="71"/>
-      <c r="E112" s="71"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="71"/>
-      <c r="I112" s="71"/>
-      <c r="J112" s="72"/>
+      <c r="A112" s="64"/>
+      <c r="B112" s="78"/>
+      <c r="C112" s="78"/>
+      <c r="D112" s="78"/>
+      <c r="E112" s="78"/>
+      <c r="F112" s="78"/>
+      <c r="G112" s="78"/>
+      <c r="H112" s="78"/>
+      <c r="I112" s="78"/>
+      <c r="J112" s="79"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="66"/>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
-      <c r="G113" s="71"/>
-      <c r="H113" s="71"/>
-      <c r="I113" s="71"/>
-      <c r="J113" s="72"/>
+      <c r="A113" s="64"/>
+      <c r="B113" s="78"/>
+      <c r="C113" s="78"/>
+      <c r="D113" s="78"/>
+      <c r="E113" s="78"/>
+      <c r="F113" s="78"/>
+      <c r="G113" s="78"/>
+      <c r="H113" s="78"/>
+      <c r="I113" s="78"/>
+      <c r="J113" s="79"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="66"/>
-      <c r="B114" s="71"/>
-      <c r="C114" s="71"/>
-      <c r="D114" s="71"/>
-      <c r="E114" s="71"/>
-      <c r="F114" s="71"/>
-      <c r="G114" s="71"/>
-      <c r="H114" s="71"/>
-      <c r="I114" s="71"/>
-      <c r="J114" s="72"/>
+      <c r="A114" s="64"/>
+      <c r="B114" s="78"/>
+      <c r="C114" s="78"/>
+      <c r="D114" s="78"/>
+      <c r="E114" s="78"/>
+      <c r="F114" s="78"/>
+      <c r="G114" s="78"/>
+      <c r="H114" s="78"/>
+      <c r="I114" s="78"/>
+      <c r="J114" s="79"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="66"/>
-      <c r="B115" s="71"/>
-      <c r="C115" s="71"/>
-      <c r="D115" s="71"/>
-      <c r="E115" s="71"/>
-      <c r="F115" s="71"/>
-      <c r="G115" s="71"/>
-      <c r="H115" s="71"/>
-      <c r="I115" s="71"/>
-      <c r="J115" s="72"/>
+      <c r="A115" s="64"/>
+      <c r="B115" s="78"/>
+      <c r="C115" s="78"/>
+      <c r="D115" s="78"/>
+      <c r="E115" s="78"/>
+      <c r="F115" s="78"/>
+      <c r="G115" s="78"/>
+      <c r="H115" s="78"/>
+      <c r="I115" s="78"/>
+      <c r="J115" s="79"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="66"/>
-      <c r="B116" s="71"/>
-      <c r="C116" s="71"/>
-      <c r="D116" s="71"/>
-      <c r="E116" s="71"/>
-      <c r="F116" s="71"/>
-      <c r="G116" s="71"/>
-      <c r="H116" s="71"/>
-      <c r="I116" s="71"/>
-      <c r="J116" s="72"/>
+      <c r="A116" s="64"/>
+      <c r="B116" s="78"/>
+      <c r="C116" s="78"/>
+      <c r="D116" s="78"/>
+      <c r="E116" s="78"/>
+      <c r="F116" s="78"/>
+      <c r="G116" s="78"/>
+      <c r="H116" s="78"/>
+      <c r="I116" s="78"/>
+      <c r="J116" s="79"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="66"/>
-      <c r="B117" s="73" t="s">
+      <c r="A117" s="64"/>
+      <c r="B117" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="73"/>
-      <c r="D117" s="73"/>
-      <c r="E117" s="73"/>
-      <c r="F117" s="73"/>
-      <c r="G117" s="73"/>
-      <c r="H117" s="73"/>
-      <c r="I117" s="73"/>
-      <c r="J117" s="74"/>
+      <c r="C117" s="104"/>
+      <c r="D117" s="104"/>
+      <c r="E117" s="104"/>
+      <c r="F117" s="104"/>
+      <c r="G117" s="104"/>
+      <c r="H117" s="104"/>
+      <c r="I117" s="104"/>
+      <c r="J117" s="105"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="66"/>
-      <c r="B118" s="70" t="s">
+      <c r="A118" s="64"/>
+      <c r="B118" s="103" t="s">
         <v>143</v>
       </c>
-      <c r="C118" s="71"/>
-      <c r="D118" s="71"/>
-      <c r="E118" s="71"/>
-      <c r="F118" s="71"/>
-      <c r="G118" s="71"/>
-      <c r="H118" s="71"/>
-      <c r="I118" s="71"/>
-      <c r="J118" s="72"/>
+      <c r="C118" s="78"/>
+      <c r="D118" s="78"/>
+      <c r="E118" s="78"/>
+      <c r="F118" s="78"/>
+      <c r="G118" s="78"/>
+      <c r="H118" s="78"/>
+      <c r="I118" s="78"/>
+      <c r="J118" s="79"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="66"/>
-      <c r="B119" s="71"/>
-      <c r="C119" s="71"/>
-      <c r="D119" s="71"/>
-      <c r="E119" s="71"/>
-      <c r="F119" s="71"/>
-      <c r="G119" s="71"/>
-      <c r="H119" s="71"/>
-      <c r="I119" s="71"/>
-      <c r="J119" s="72"/>
+      <c r="A119" s="64"/>
+      <c r="B119" s="78"/>
+      <c r="C119" s="78"/>
+      <c r="D119" s="78"/>
+      <c r="E119" s="78"/>
+      <c r="F119" s="78"/>
+      <c r="G119" s="78"/>
+      <c r="H119" s="78"/>
+      <c r="I119" s="78"/>
+      <c r="J119" s="79"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="66"/>
-      <c r="B120" s="71"/>
-      <c r="C120" s="71"/>
-      <c r="D120" s="71"/>
-      <c r="E120" s="71"/>
-      <c r="F120" s="71"/>
-      <c r="G120" s="71"/>
-      <c r="H120" s="71"/>
-      <c r="I120" s="71"/>
-      <c r="J120" s="72"/>
+      <c r="A120" s="64"/>
+      <c r="B120" s="78"/>
+      <c r="C120" s="78"/>
+      <c r="D120" s="78"/>
+      <c r="E120" s="78"/>
+      <c r="F120" s="78"/>
+      <c r="G120" s="78"/>
+      <c r="H120" s="78"/>
+      <c r="I120" s="78"/>
+      <c r="J120" s="79"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="66"/>
-      <c r="B121" s="71"/>
-      <c r="C121" s="71"/>
-      <c r="D121" s="71"/>
-      <c r="E121" s="71"/>
-      <c r="F121" s="71"/>
-      <c r="G121" s="71"/>
-      <c r="H121" s="71"/>
-      <c r="I121" s="71"/>
-      <c r="J121" s="72"/>
+      <c r="A121" s="64"/>
+      <c r="B121" s="78"/>
+      <c r="C121" s="78"/>
+      <c r="D121" s="78"/>
+      <c r="E121" s="78"/>
+      <c r="F121" s="78"/>
+      <c r="G121" s="78"/>
+      <c r="H121" s="78"/>
+      <c r="I121" s="78"/>
+      <c r="J121" s="79"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="66"/>
-      <c r="B122" s="71"/>
-      <c r="C122" s="71"/>
-      <c r="D122" s="71"/>
-      <c r="E122" s="71"/>
-      <c r="F122" s="71"/>
-      <c r="G122" s="71"/>
-      <c r="H122" s="71"/>
-      <c r="I122" s="71"/>
-      <c r="J122" s="72"/>
+      <c r="A122" s="64"/>
+      <c r="B122" s="78"/>
+      <c r="C122" s="78"/>
+      <c r="D122" s="78"/>
+      <c r="E122" s="78"/>
+      <c r="F122" s="78"/>
+      <c r="G122" s="78"/>
+      <c r="H122" s="78"/>
+      <c r="I122" s="78"/>
+      <c r="J122" s="79"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="66"/>
-      <c r="B123" s="71"/>
-      <c r="C123" s="71"/>
-      <c r="D123" s="71"/>
-      <c r="E123" s="71"/>
-      <c r="F123" s="71"/>
-      <c r="G123" s="71"/>
-      <c r="H123" s="71"/>
-      <c r="I123" s="71"/>
-      <c r="J123" s="72"/>
+      <c r="A123" s="64"/>
+      <c r="B123" s="78"/>
+      <c r="C123" s="78"/>
+      <c r="D123" s="78"/>
+      <c r="E123" s="78"/>
+      <c r="F123" s="78"/>
+      <c r="G123" s="78"/>
+      <c r="H123" s="78"/>
+      <c r="I123" s="78"/>
+      <c r="J123" s="79"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="66"/>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
-      <c r="G124" s="71"/>
-      <c r="H124" s="71"/>
-      <c r="I124" s="71"/>
-      <c r="J124" s="72"/>
+      <c r="A124" s="64"/>
+      <c r="B124" s="78"/>
+      <c r="C124" s="78"/>
+      <c r="D124" s="78"/>
+      <c r="E124" s="78"/>
+      <c r="F124" s="78"/>
+      <c r="G124" s="78"/>
+      <c r="H124" s="78"/>
+      <c r="I124" s="78"/>
+      <c r="J124" s="79"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="67"/>
-      <c r="B125" s="75"/>
-      <c r="C125" s="75"/>
-      <c r="D125" s="75"/>
-      <c r="E125" s="75"/>
-      <c r="F125" s="75"/>
-      <c r="G125" s="75"/>
-      <c r="H125" s="75"/>
-      <c r="I125" s="75"/>
-      <c r="J125" s="76"/>
+      <c r="A125" s="65"/>
+      <c r="B125" s="106"/>
+      <c r="C125" s="106"/>
+      <c r="D125" s="106"/>
+      <c r="E125" s="106"/>
+      <c r="F125" s="106"/>
+      <c r="G125" s="106"/>
+      <c r="H125" s="106"/>
+      <c r="I125" s="106"/>
+      <c r="J125" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
     <mergeCell ref="B69:J86"/>
     <mergeCell ref="A63:A86"/>
     <mergeCell ref="D64:J64"/>
@@ -6205,22 +6214,13 @@
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A125"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="B111:J116"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B118:J125"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="A89:A107"/>
-    <mergeCell ref="B90:J92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="B93:J107"/>
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6251,71 +6251,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="45"/>
+      <c r="H6" s="48" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6325,116 +6325,116 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="59"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>1</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="D8" s="35" t="s">
         <v>163</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>164</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="39"/>
+      <c r="G8" s="54"/>
       <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="37">
         <v>2</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="60" t="s">
-        <v>161</v>
+      <c r="B9" s="51"/>
+      <c r="C9" s="50" t="s">
+        <v>160</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="39"/>
+      <c r="F9" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="G9" s="54"/>
       <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E10" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G10" s="39"/>
+      <c r="F10" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="54"/>
       <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>4</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E11" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="39"/>
+      <c r="F11" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="54"/>
       <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>5</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="G12" s="39"/>
+      <c r="F12" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="54"/>
       <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37">
         <v>6</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="58" t="s">
         <v>173</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>174</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>70</v>
@@ -6442,35 +6442,35 @@
       <c r="E13" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="44"/>
+      <c r="G13" s="39"/>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="37">
         <v>7</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" s="44"/>
+      <c r="F14" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="39"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <v>8</v>
       </c>
-      <c r="B15" s="41"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="27" t="s">
         <v>71</v>
       </c>
@@ -6480,17 +6480,17 @@
       <c r="E15" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="44"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <v>9</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="27" t="s">
         <v>73</v>
       </c>
@@ -6500,18 +6500,18 @@
       <c r="E16" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="44"/>
+      <c r="G16" s="39"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <v>10</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="40" t="s">
+      <c r="B17" s="58"/>
+      <c r="C17" s="57" t="s">
         <v>75</v>
       </c>
       <c r="D17" s="27" t="s">
@@ -6520,109 +6520,109 @@
       <c r="E17" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="44"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="60"/>
       <c r="D18" s="27" t="s">
         <v>77</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="44"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <v>12</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="47" t="s">
+      <c r="B19" s="58"/>
+      <c r="C19" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="E19" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19" s="49"/>
+      <c r="F19" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="56"/>
       <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <v>13</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="46"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="44"/>
+      <c r="F20" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="39"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <v>14</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="46"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="G21" s="49"/>
+      <c r="F21" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="56"/>
       <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <v>15</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="G22" s="49"/>
+      <c r="F22" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" s="56"/>
       <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <v>16</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="57" t="s">
         <v>78</v>
       </c>
       <c r="C23" s="27" t="s">
@@ -6634,17 +6634,17 @@
       <c r="E23" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="44"/>
+      <c r="G23" s="39"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <v>17</v>
       </c>
-      <c r="B24" s="46"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="27" t="s">
         <v>81</v>
       </c>
@@ -6654,17 +6654,17 @@
       <c r="E24" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="44"/>
+      <c r="G24" s="39"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <v>18</v>
       </c>
-      <c r="B25" s="45"/>
+      <c r="B25" s="60"/>
       <c r="C25" s="27" t="s">
         <v>83</v>
       </c>
@@ -6674,20 +6674,20 @@
       <c r="E25" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="43" t="s">
+      <c r="F25" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="44"/>
+      <c r="G25" s="39"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <v>19</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="57" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="27" t="s">
@@ -6696,28 +6696,28 @@
       <c r="E26" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="44"/>
+      <c r="G26" s="39"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <v>20</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="27" t="s">
         <v>88</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="G27" s="44"/>
+      <c r="G27" s="39"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6728,8 +6728,8 @@
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="39"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6740,8 +6740,8 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="39"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6752,8 +6752,8 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6764,8 +6764,8 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="39"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6776,8 +6776,8 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="39"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6788,8 +6788,8 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="39"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6800,8 +6800,8 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="39"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6812,8 +6812,8 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="39"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6824,8 +6824,8 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="39"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6836,8 +6836,8 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="39"/>
       <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6848,8 +6848,8 @@
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="39"/>
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6860,12 +6860,45 @@
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="39"/>
       <c r="H39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:B22"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="A1:C1"/>
@@ -6882,39 +6915,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:B22"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6941,72 +6941,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="121"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="52" t="s">
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="42" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="52"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
@@ -7018,381 +7018,381 @@
       <c r="C7" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="116"/>
+      <c r="B8" s="118"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="116"/>
+      <c r="B9" s="118"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="117"/>
+      <c r="B10" s="116"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="117" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="116"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="71" t="s">
+      <c r="B12" s="118"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="116"/>
+      <c r="B13" s="118"/>
       <c r="C13" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="103" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="117"/>
+      <c r="B14" s="116"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="118" t="s">
+      <c r="B15" s="117" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="116"/>
+      <c r="B16" s="118"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="116"/>
+      <c r="B17" s="118"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="117"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="117" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="116"/>
+      <c r="B20" s="118"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="116"/>
+      <c r="B21" s="118"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="117"/>
+      <c r="B22" s="116"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="117" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D23" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="119"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="119"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="119"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="D26" s="103" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="120"/>
+      <c r="B27" s="123"/>
       <c r="C27" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="121" t="s">
+      <c r="D27" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="122"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="123"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="126"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="117" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="71" t="s">
+      <c r="D28" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="78"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="116"/>
+      <c r="B29" s="118"/>
       <c r="C29" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="71" t="s">
+      <c r="D29" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="116"/>
+      <c r="B30" s="118"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="117"/>
+      <c r="B31" s="116"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7401,11 +7401,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7414,11 +7414,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7427,11 +7427,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7453,11 +7453,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7466,29 +7466,31 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D25:H25"/>
@@ -7505,22 +7507,20 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -7544,23 +7544,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7577,141 +7577,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="137" t="s">
+      <c r="C2" s="163"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="167" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="137"/>
-      <c r="W2" s="137"/>
-      <c r="X2" s="137"/>
-      <c r="Y2" s="137"/>
-      <c r="Z2" s="137"/>
-      <c r="AA2" s="137"/>
-      <c r="AB2" s="137"/>
-      <c r="AC2" s="137"/>
-      <c r="AD2" s="137"/>
+      <c r="K2" s="167"/>
+      <c r="L2" s="167"/>
+      <c r="M2" s="167"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="167"/>
+      <c r="P2" s="167"/>
+      <c r="Q2" s="167"/>
+      <c r="R2" s="167"/>
+      <c r="S2" s="167"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="167"/>
+      <c r="AA2" s="167"/>
+      <c r="AB2" s="167"/>
+      <c r="AC2" s="167"/>
+      <c r="AD2" s="167"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="206" t="s">
+      <c r="C4" s="161"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="206"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="210" t="s">
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
+      <c r="O4" s="161"/>
+      <c r="P4" s="161"/>
+      <c r="Q4" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="214"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="210" t="s">
+      <c r="R4" s="172"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="168" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="214"/>
-      <c r="V4" s="214"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="210" t="s">
+      <c r="U4" s="172"/>
+      <c r="V4" s="172"/>
+      <c r="W4" s="169"/>
+      <c r="X4" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="206" t="s">
+      <c r="Y4" s="169"/>
+      <c r="Z4" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="AA4" s="206"/>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="206" t="s">
+      <c r="AA4" s="161"/>
+      <c r="AB4" s="161"/>
+      <c r="AC4" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="AD4" s="206"/>
-      <c r="AE4" s="206"/>
-      <c r="AF4" s="206" t="s">
+      <c r="AD4" s="161"/>
+      <c r="AE4" s="161"/>
+      <c r="AF4" s="161" t="s">
         <v>134</v>
       </c>
-      <c r="AG4" s="206"/>
-      <c r="AH4" s="206"/>
-      <c r="AI4" s="206" t="s">
+      <c r="AG4" s="161"/>
+      <c r="AH4" s="161"/>
+      <c r="AI4" s="161" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="206"/>
-      <c r="AK4" s="206"/>
-      <c r="AL4" s="206" t="s">
+      <c r="AJ4" s="161"/>
+      <c r="AK4" s="161"/>
+      <c r="AL4" s="161" t="s">
         <v>136</v>
       </c>
-      <c r="AM4" s="206"/>
-      <c r="AN4" s="206"/>
-      <c r="AO4" s="206" t="s">
+      <c r="AM4" s="161"/>
+      <c r="AN4" s="161"/>
+      <c r="AO4" s="161" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="206"/>
-      <c r="AQ4" s="206"/>
-      <c r="AR4" s="206"/>
-      <c r="AS4" s="206"/>
-      <c r="AT4" s="206"/>
-      <c r="AU4" s="206"/>
-      <c r="AV4" s="206"/>
-      <c r="AW4" s="206"/>
-      <c r="AX4" s="206"/>
-      <c r="AY4" s="206"/>
-      <c r="AZ4" s="207"/>
+      <c r="AP4" s="161"/>
+      <c r="AQ4" s="161"/>
+      <c r="AR4" s="161"/>
+      <c r="AS4" s="161"/>
+      <c r="AT4" s="161"/>
+      <c r="AU4" s="161"/>
+      <c r="AV4" s="161"/>
+      <c r="AW4" s="161"/>
+      <c r="AX4" s="161"/>
+      <c r="AY4" s="161"/>
+      <c r="AZ4" s="162"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="217"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="M5" s="208"/>
-      <c r="N5" s="208"/>
-      <c r="O5" s="208"/>
-      <c r="P5" s="208"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="215"/>
-      <c r="S5" s="213"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="215"/>
-      <c r="V5" s="215"/>
-      <c r="W5" s="213"/>
-      <c r="X5" s="212"/>
-      <c r="Y5" s="213"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="163"/>
+      <c r="N5" s="163"/>
+      <c r="O5" s="163"/>
+      <c r="P5" s="163"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="173"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="170"/>
+      <c r="U5" s="173"/>
+      <c r="V5" s="173"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="170"/>
+      <c r="Y5" s="171"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7757,58 +7757,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="208"/>
-      <c r="AP5" s="208"/>
-      <c r="AQ5" s="208"/>
-      <c r="AR5" s="208"/>
-      <c r="AS5" s="208"/>
-      <c r="AT5" s="208"/>
-      <c r="AU5" s="208"/>
-      <c r="AV5" s="208"/>
-      <c r="AW5" s="208"/>
-      <c r="AX5" s="208"/>
-      <c r="AY5" s="208"/>
-      <c r="AZ5" s="209"/>
+      <c r="AO5" s="163"/>
+      <c r="AP5" s="163"/>
+      <c r="AQ5" s="163"/>
+      <c r="AR5" s="163"/>
+      <c r="AS5" s="163"/>
+      <c r="AT5" s="163"/>
+      <c r="AU5" s="163"/>
+      <c r="AV5" s="163"/>
+      <c r="AW5" s="163"/>
+      <c r="AX5" s="163"/>
+      <c r="AY5" s="163"/>
+      <c r="AZ5" s="164"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="133">
+      <c r="B6" s="190">
         <v>1</v>
       </c>
-      <c r="C6" s="130" t="s">
+      <c r="C6" s="176" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130" t="s">
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="176"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="176" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="137" t="s">
+      <c r="K6" s="176"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="176"/>
+      <c r="N6" s="176"/>
+      <c r="O6" s="176"/>
+      <c r="P6" s="176"/>
+      <c r="Q6" s="167" t="s">
         <v>128</v>
       </c>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="134" t="s">
+      <c r="R6" s="167"/>
+      <c r="S6" s="167"/>
+      <c r="T6" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="134"/>
-      <c r="V6" s="131">
+      <c r="U6" s="181"/>
+      <c r="V6" s="179">
         <v>0</v>
       </c>
-      <c r="W6" s="131"/>
-      <c r="X6" s="153">
+      <c r="W6" s="179"/>
+      <c r="X6" s="165">
         <v>0</v>
       </c>
-      <c r="Y6" s="153"/>
+      <c r="Y6" s="165"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7824,50 +7824,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="130"/>
-      <c r="AP6" s="130"/>
-      <c r="AQ6" s="130"/>
-      <c r="AR6" s="130"/>
-      <c r="AS6" s="130"/>
-      <c r="AT6" s="130"/>
-      <c r="AU6" s="130"/>
-      <c r="AV6" s="130"/>
-      <c r="AW6" s="130"/>
-      <c r="AX6" s="130"/>
-      <c r="AY6" s="130"/>
-      <c r="AZ6" s="152"/>
+      <c r="AO6" s="176"/>
+      <c r="AP6" s="176"/>
+      <c r="AQ6" s="176"/>
+      <c r="AR6" s="176"/>
+      <c r="AS6" s="176"/>
+      <c r="AT6" s="176"/>
+      <c r="AU6" s="176"/>
+      <c r="AV6" s="176"/>
+      <c r="AW6" s="176"/>
+      <c r="AX6" s="176"/>
+      <c r="AY6" s="176"/>
+      <c r="AZ6" s="177"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="133"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="137"/>
-      <c r="R7" s="137"/>
-      <c r="S7" s="137"/>
-      <c r="T7" s="135" t="s">
+      <c r="B7" s="190"/>
+      <c r="C7" s="176"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="176"/>
+      <c r="G7" s="176"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="176"/>
+      <c r="O7" s="176"/>
+      <c r="P7" s="176"/>
+      <c r="Q7" s="167"/>
+      <c r="R7" s="167"/>
+      <c r="S7" s="167"/>
+      <c r="T7" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="135"/>
-      <c r="V7" s="132">
+      <c r="U7" s="178"/>
+      <c r="V7" s="180">
         <v>0</v>
       </c>
-      <c r="W7" s="132"/>
-      <c r="X7" s="154">
+      <c r="W7" s="180"/>
+      <c r="X7" s="166">
         <v>1</v>
       </c>
-      <c r="Y7" s="154"/>
+      <c r="Y7" s="166"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7883,58 +7883,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="130"/>
-      <c r="AP7" s="130"/>
-      <c r="AQ7" s="130"/>
-      <c r="AR7" s="130"/>
-      <c r="AS7" s="130"/>
-      <c r="AT7" s="130"/>
-      <c r="AU7" s="130"/>
-      <c r="AV7" s="130"/>
-      <c r="AW7" s="130"/>
-      <c r="AX7" s="130"/>
-      <c r="AY7" s="130"/>
-      <c r="AZ7" s="152"/>
+      <c r="AO7" s="176"/>
+      <c r="AP7" s="176"/>
+      <c r="AQ7" s="176"/>
+      <c r="AR7" s="176"/>
+      <c r="AS7" s="176"/>
+      <c r="AT7" s="176"/>
+      <c r="AU7" s="176"/>
+      <c r="AV7" s="176"/>
+      <c r="AW7" s="176"/>
+      <c r="AX7" s="176"/>
+      <c r="AY7" s="176"/>
+      <c r="AZ7" s="177"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="133">
+      <c r="B8" s="190">
         <v>2</v>
       </c>
-      <c r="C8" s="130" t="s">
+      <c r="C8" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="138" t="s">
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="176"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="152" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="136" t="s">
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="217" t="s">
         <v>130</v>
       </c>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="134" t="s">
+      <c r="R8" s="217"/>
+      <c r="S8" s="217"/>
+      <c r="T8" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="134"/>
-      <c r="V8" s="131">
+      <c r="U8" s="181"/>
+      <c r="V8" s="179">
         <v>0</v>
       </c>
-      <c r="W8" s="131"/>
-      <c r="X8" s="153">
+      <c r="W8" s="179"/>
+      <c r="X8" s="165">
         <v>0</v>
       </c>
-      <c r="Y8" s="153"/>
+      <c r="Y8" s="165"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7950,50 +7950,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="130"/>
-      <c r="AP8" s="130"/>
-      <c r="AQ8" s="130"/>
-      <c r="AR8" s="130"/>
-      <c r="AS8" s="130"/>
-      <c r="AT8" s="130"/>
-      <c r="AU8" s="130"/>
-      <c r="AV8" s="130"/>
-      <c r="AW8" s="130"/>
-      <c r="AX8" s="130"/>
-      <c r="AY8" s="130"/>
-      <c r="AZ8" s="152"/>
+      <c r="AO8" s="176"/>
+      <c r="AP8" s="176"/>
+      <c r="AQ8" s="176"/>
+      <c r="AR8" s="176"/>
+      <c r="AS8" s="176"/>
+      <c r="AT8" s="176"/>
+      <c r="AU8" s="176"/>
+      <c r="AV8" s="176"/>
+      <c r="AW8" s="176"/>
+      <c r="AX8" s="176"/>
+      <c r="AY8" s="176"/>
+      <c r="AZ8" s="177"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="133"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="143"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="135" t="s">
+      <c r="B9" s="190"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="176"/>
+      <c r="F9" s="176"/>
+      <c r="G9" s="176"/>
+      <c r="H9" s="176"/>
+      <c r="I9" s="176"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="138"/>
+      <c r="L9" s="138"/>
+      <c r="M9" s="138"/>
+      <c r="N9" s="138"/>
+      <c r="O9" s="138"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="217"/>
+      <c r="R9" s="217"/>
+      <c r="S9" s="217"/>
+      <c r="T9" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="135"/>
-      <c r="V9" s="132">
+      <c r="U9" s="178"/>
+      <c r="V9" s="180">
         <v>0</v>
       </c>
-      <c r="W9" s="132"/>
-      <c r="X9" s="154">
+      <c r="W9" s="180"/>
+      <c r="X9" s="166">
         <v>1</v>
       </c>
-      <c r="Y9" s="154"/>
+      <c r="Y9" s="166"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -8009,58 +8009,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="130"/>
-      <c r="AP9" s="130"/>
-      <c r="AQ9" s="130"/>
-      <c r="AR9" s="130"/>
-      <c r="AS9" s="130"/>
-      <c r="AT9" s="130"/>
-      <c r="AU9" s="130"/>
-      <c r="AV9" s="130"/>
-      <c r="AW9" s="130"/>
-      <c r="AX9" s="130"/>
-      <c r="AY9" s="130"/>
-      <c r="AZ9" s="152"/>
+      <c r="AO9" s="176"/>
+      <c r="AP9" s="176"/>
+      <c r="AQ9" s="176"/>
+      <c r="AR9" s="176"/>
+      <c r="AS9" s="176"/>
+      <c r="AT9" s="176"/>
+      <c r="AU9" s="176"/>
+      <c r="AV9" s="176"/>
+      <c r="AW9" s="176"/>
+      <c r="AX9" s="176"/>
+      <c r="AY9" s="176"/>
+      <c r="AZ9" s="177"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="133">
+      <c r="B10" s="190">
         <v>3</v>
       </c>
-      <c r="C10" s="130" t="s">
+      <c r="C10" s="176" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="129" t="s">
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
+      <c r="F10" s="176"/>
+      <c r="G10" s="176"/>
+      <c r="H10" s="176"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="216" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="137" t="s">
+      <c r="K10" s="176"/>
+      <c r="L10" s="176"/>
+      <c r="M10" s="176"/>
+      <c r="N10" s="176"/>
+      <c r="O10" s="176"/>
+      <c r="P10" s="176"/>
+      <c r="Q10" s="167" t="s">
         <v>128</v>
       </c>
-      <c r="R10" s="137"/>
-      <c r="S10" s="137"/>
-      <c r="T10" s="134" t="s">
+      <c r="R10" s="167"/>
+      <c r="S10" s="167"/>
+      <c r="T10" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="134"/>
-      <c r="V10" s="131">
+      <c r="U10" s="181"/>
+      <c r="V10" s="179">
         <v>0</v>
       </c>
-      <c r="W10" s="131"/>
-      <c r="X10" s="153">
+      <c r="W10" s="179"/>
+      <c r="X10" s="165">
         <v>0</v>
       </c>
-      <c r="Y10" s="153"/>
+      <c r="Y10" s="165"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -8076,50 +8076,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="130"/>
-      <c r="AP10" s="130"/>
-      <c r="AQ10" s="130"/>
-      <c r="AR10" s="130"/>
-      <c r="AS10" s="130"/>
-      <c r="AT10" s="130"/>
-      <c r="AU10" s="130"/>
-      <c r="AV10" s="130"/>
-      <c r="AW10" s="130"/>
-      <c r="AX10" s="130"/>
-      <c r="AY10" s="130"/>
-      <c r="AZ10" s="152"/>
+      <c r="AO10" s="176"/>
+      <c r="AP10" s="176"/>
+      <c r="AQ10" s="176"/>
+      <c r="AR10" s="176"/>
+      <c r="AS10" s="176"/>
+      <c r="AT10" s="176"/>
+      <c r="AU10" s="176"/>
+      <c r="AV10" s="176"/>
+      <c r="AW10" s="176"/>
+      <c r="AX10" s="176"/>
+      <c r="AY10" s="176"/>
+      <c r="AZ10" s="177"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="133"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
-      <c r="S11" s="137"/>
-      <c r="T11" s="135" t="s">
+      <c r="B11" s="190"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
+      <c r="M11" s="176"/>
+      <c r="N11" s="176"/>
+      <c r="O11" s="176"/>
+      <c r="P11" s="176"/>
+      <c r="Q11" s="167"/>
+      <c r="R11" s="167"/>
+      <c r="S11" s="167"/>
+      <c r="T11" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="135"/>
-      <c r="V11" s="132">
+      <c r="U11" s="178"/>
+      <c r="V11" s="180">
         <v>0</v>
       </c>
-      <c r="W11" s="132"/>
-      <c r="X11" s="154">
+      <c r="W11" s="180"/>
+      <c r="X11" s="166">
         <v>0</v>
       </c>
-      <c r="Y11" s="154"/>
+      <c r="Y11" s="166"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -8135,58 +8135,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="130"/>
-      <c r="AP11" s="130"/>
-      <c r="AQ11" s="130"/>
-      <c r="AR11" s="130"/>
-      <c r="AS11" s="130"/>
-      <c r="AT11" s="130"/>
-      <c r="AU11" s="130"/>
-      <c r="AV11" s="130"/>
-      <c r="AW11" s="130"/>
-      <c r="AX11" s="130"/>
-      <c r="AY11" s="130"/>
-      <c r="AZ11" s="152"/>
+      <c r="AO11" s="176"/>
+      <c r="AP11" s="176"/>
+      <c r="AQ11" s="176"/>
+      <c r="AR11" s="176"/>
+      <c r="AS11" s="176"/>
+      <c r="AT11" s="176"/>
+      <c r="AU11" s="176"/>
+      <c r="AV11" s="176"/>
+      <c r="AW11" s="176"/>
+      <c r="AX11" s="176"/>
+      <c r="AY11" s="176"/>
+      <c r="AZ11" s="177"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="133">
+      <c r="B12" s="190">
         <v>4</v>
       </c>
-      <c r="C12" s="130" t="s">
+      <c r="C12" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130" t="s">
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="176" t="s">
         <v>131</v>
       </c>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="130"/>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="196" t="s">
+      <c r="K12" s="176"/>
+      <c r="L12" s="176"/>
+      <c r="M12" s="176"/>
+      <c r="N12" s="176"/>
+      <c r="O12" s="176"/>
+      <c r="P12" s="176"/>
+      <c r="Q12" s="140" t="s">
         <v>128</v>
       </c>
-      <c r="R12" s="197"/>
-      <c r="S12" s="198"/>
-      <c r="T12" s="134" t="s">
+      <c r="R12" s="141"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="134"/>
-      <c r="V12" s="131">
+      <c r="U12" s="181"/>
+      <c r="V12" s="179">
         <v>0</v>
       </c>
-      <c r="W12" s="131"/>
-      <c r="X12" s="153">
+      <c r="W12" s="179"/>
+      <c r="X12" s="165">
         <v>0</v>
       </c>
-      <c r="Y12" s="153"/>
+      <c r="Y12" s="165"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -8202,50 +8202,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="130"/>
-      <c r="AP12" s="130"/>
-      <c r="AQ12" s="130"/>
-      <c r="AR12" s="130"/>
-      <c r="AS12" s="130"/>
-      <c r="AT12" s="130"/>
-      <c r="AU12" s="130"/>
-      <c r="AV12" s="130"/>
-      <c r="AW12" s="130"/>
-      <c r="AX12" s="130"/>
-      <c r="AY12" s="130"/>
-      <c r="AZ12" s="152"/>
+      <c r="AO12" s="176"/>
+      <c r="AP12" s="176"/>
+      <c r="AQ12" s="176"/>
+      <c r="AR12" s="176"/>
+      <c r="AS12" s="176"/>
+      <c r="AT12" s="176"/>
+      <c r="AU12" s="176"/>
+      <c r="AV12" s="176"/>
+      <c r="AW12" s="176"/>
+      <c r="AX12" s="176"/>
+      <c r="AY12" s="176"/>
+      <c r="AZ12" s="177"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="133"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="199"/>
-      <c r="R13" s="200"/>
-      <c r="S13" s="201"/>
-      <c r="T13" s="135" t="s">
+      <c r="B13" s="190"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="176"/>
+      <c r="K13" s="176"/>
+      <c r="L13" s="176"/>
+      <c r="M13" s="176"/>
+      <c r="N13" s="176"/>
+      <c r="O13" s="176"/>
+      <c r="P13" s="176"/>
+      <c r="Q13" s="143"/>
+      <c r="R13" s="144"/>
+      <c r="S13" s="145"/>
+      <c r="T13" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="135"/>
-      <c r="V13" s="132">
+      <c r="U13" s="178"/>
+      <c r="V13" s="180">
         <v>0</v>
       </c>
-      <c r="W13" s="132"/>
-      <c r="X13" s="154">
+      <c r="W13" s="180"/>
+      <c r="X13" s="166">
         <v>0</v>
       </c>
-      <c r="Y13" s="154"/>
+      <c r="Y13" s="166"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8261,54 +8261,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="130"/>
-      <c r="AP13" s="130"/>
-      <c r="AQ13" s="130"/>
-      <c r="AR13" s="130"/>
-      <c r="AS13" s="130"/>
-      <c r="AT13" s="130"/>
-      <c r="AU13" s="130"/>
-      <c r="AV13" s="130"/>
-      <c r="AW13" s="130"/>
-      <c r="AX13" s="130"/>
-      <c r="AY13" s="130"/>
-      <c r="AZ13" s="152"/>
+      <c r="AO13" s="176"/>
+      <c r="AP13" s="176"/>
+      <c r="AQ13" s="176"/>
+      <c r="AR13" s="176"/>
+      <c r="AS13" s="176"/>
+      <c r="AT13" s="176"/>
+      <c r="AU13" s="176"/>
+      <c r="AV13" s="176"/>
+      <c r="AW13" s="176"/>
+      <c r="AX13" s="176"/>
+      <c r="AY13" s="176"/>
+      <c r="AZ13" s="177"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="133">
+      <c r="B14" s="190">
         <v>5</v>
       </c>
-      <c r="C14" s="138" t="s">
+      <c r="C14" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="196"/>
-      <c r="R14" s="197"/>
-      <c r="S14" s="198"/>
-      <c r="T14" s="134" t="s">
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="216"/>
+      <c r="K14" s="176"/>
+      <c r="L14" s="176"/>
+      <c r="M14" s="176"/>
+      <c r="N14" s="176"/>
+      <c r="O14" s="176"/>
+      <c r="P14" s="176"/>
+      <c r="Q14" s="140"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="142"/>
+      <c r="T14" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="134"/>
-      <c r="V14" s="131">
+      <c r="U14" s="181"/>
+      <c r="V14" s="179">
         <v>0</v>
       </c>
-      <c r="W14" s="131"/>
-      <c r="X14" s="153">
+      <c r="W14" s="179"/>
+      <c r="X14" s="165">
         <v>0</v>
       </c>
-      <c r="Y14" s="153"/>
+      <c r="Y14" s="165"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8324,50 +8324,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="130"/>
-      <c r="AP14" s="130"/>
-      <c r="AQ14" s="130"/>
-      <c r="AR14" s="130"/>
-      <c r="AS14" s="130"/>
-      <c r="AT14" s="130"/>
-      <c r="AU14" s="130"/>
-      <c r="AV14" s="130"/>
-      <c r="AW14" s="130"/>
-      <c r="AX14" s="130"/>
-      <c r="AY14" s="130"/>
-      <c r="AZ14" s="152"/>
+      <c r="AO14" s="176"/>
+      <c r="AP14" s="176"/>
+      <c r="AQ14" s="176"/>
+      <c r="AR14" s="176"/>
+      <c r="AS14" s="176"/>
+      <c r="AT14" s="176"/>
+      <c r="AU14" s="176"/>
+      <c r="AV14" s="176"/>
+      <c r="AW14" s="176"/>
+      <c r="AX14" s="176"/>
+      <c r="AY14" s="176"/>
+      <c r="AZ14" s="177"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="133"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="142"/>
-      <c r="I15" s="143"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="199"/>
-      <c r="R15" s="200"/>
-      <c r="S15" s="201"/>
-      <c r="T15" s="135" t="s">
+      <c r="B15" s="190"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="176"/>
+      <c r="K15" s="176"/>
+      <c r="L15" s="176"/>
+      <c r="M15" s="176"/>
+      <c r="N15" s="176"/>
+      <c r="O15" s="176"/>
+      <c r="P15" s="176"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="145"/>
+      <c r="T15" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="135"/>
-      <c r="V15" s="132">
+      <c r="U15" s="178"/>
+      <c r="V15" s="180">
         <v>0</v>
       </c>
-      <c r="W15" s="132"/>
-      <c r="X15" s="154">
+      <c r="W15" s="180"/>
+      <c r="X15" s="166">
         <v>0</v>
       </c>
-      <c r="Y15" s="154"/>
+      <c r="Y15" s="166"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8383,56 +8383,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="130"/>
-      <c r="AP15" s="130"/>
-      <c r="AQ15" s="130"/>
-      <c r="AR15" s="130"/>
-      <c r="AS15" s="130"/>
-      <c r="AT15" s="130"/>
-      <c r="AU15" s="130"/>
-      <c r="AV15" s="130"/>
-      <c r="AW15" s="130"/>
-      <c r="AX15" s="130"/>
-      <c r="AY15" s="130"/>
-      <c r="AZ15" s="152"/>
+      <c r="AO15" s="176"/>
+      <c r="AP15" s="176"/>
+      <c r="AQ15" s="176"/>
+      <c r="AR15" s="176"/>
+      <c r="AS15" s="176"/>
+      <c r="AT15" s="176"/>
+      <c r="AU15" s="176"/>
+      <c r="AV15" s="176"/>
+      <c r="AW15" s="176"/>
+      <c r="AX15" s="176"/>
+      <c r="AY15" s="176"/>
+      <c r="AZ15" s="177"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="133">
+      <c r="B16" s="190">
         <v>6</v>
       </c>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="129" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="216" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="130"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="137"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="134" t="s">
+      <c r="K16" s="176"/>
+      <c r="L16" s="176"/>
+      <c r="M16" s="176"/>
+      <c r="N16" s="176"/>
+      <c r="O16" s="176"/>
+      <c r="P16" s="176"/>
+      <c r="Q16" s="167"/>
+      <c r="R16" s="167"/>
+      <c r="S16" s="167"/>
+      <c r="T16" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="134"/>
-      <c r="V16" s="131">
+      <c r="U16" s="181"/>
+      <c r="V16" s="179">
         <v>0</v>
       </c>
-      <c r="W16" s="131"/>
-      <c r="X16" s="153">
+      <c r="W16" s="179"/>
+      <c r="X16" s="165">
         <v>0</v>
       </c>
-      <c r="Y16" s="153"/>
+      <c r="Y16" s="165"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8448,50 +8448,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="130"/>
-      <c r="AP16" s="130"/>
-      <c r="AQ16" s="130"/>
-      <c r="AR16" s="130"/>
-      <c r="AS16" s="130"/>
-      <c r="AT16" s="130"/>
-      <c r="AU16" s="130"/>
-      <c r="AV16" s="130"/>
-      <c r="AW16" s="130"/>
-      <c r="AX16" s="130"/>
-      <c r="AY16" s="130"/>
-      <c r="AZ16" s="152"/>
+      <c r="AO16" s="176"/>
+      <c r="AP16" s="176"/>
+      <c r="AQ16" s="176"/>
+      <c r="AR16" s="176"/>
+      <c r="AS16" s="176"/>
+      <c r="AT16" s="176"/>
+      <c r="AU16" s="176"/>
+      <c r="AV16" s="176"/>
+      <c r="AW16" s="176"/>
+      <c r="AX16" s="176"/>
+      <c r="AY16" s="176"/>
+      <c r="AZ16" s="177"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="133"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="137"/>
-      <c r="R17" s="137"/>
-      <c r="S17" s="137"/>
-      <c r="T17" s="135" t="s">
+      <c r="B17" s="190"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="176"/>
+      <c r="K17" s="176"/>
+      <c r="L17" s="176"/>
+      <c r="M17" s="176"/>
+      <c r="N17" s="176"/>
+      <c r="O17" s="176"/>
+      <c r="P17" s="176"/>
+      <c r="Q17" s="167"/>
+      <c r="R17" s="167"/>
+      <c r="S17" s="167"/>
+      <c r="T17" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="135"/>
-      <c r="V17" s="132">
+      <c r="U17" s="178"/>
+      <c r="V17" s="180">
         <v>0</v>
       </c>
-      <c r="W17" s="132"/>
-      <c r="X17" s="154">
+      <c r="W17" s="180"/>
+      <c r="X17" s="166">
         <v>0</v>
       </c>
-      <c r="Y17" s="154"/>
+      <c r="Y17" s="166"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8507,56 +8507,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="130"/>
-      <c r="AP17" s="130"/>
-      <c r="AQ17" s="130"/>
-      <c r="AR17" s="130"/>
-      <c r="AS17" s="130"/>
-      <c r="AT17" s="130"/>
-      <c r="AU17" s="130"/>
-      <c r="AV17" s="130"/>
-      <c r="AW17" s="130"/>
-      <c r="AX17" s="130"/>
-      <c r="AY17" s="130"/>
-      <c r="AZ17" s="152"/>
+      <c r="AO17" s="176"/>
+      <c r="AP17" s="176"/>
+      <c r="AQ17" s="176"/>
+      <c r="AR17" s="176"/>
+      <c r="AS17" s="176"/>
+      <c r="AT17" s="176"/>
+      <c r="AU17" s="176"/>
+      <c r="AV17" s="176"/>
+      <c r="AW17" s="176"/>
+      <c r="AX17" s="176"/>
+      <c r="AY17" s="176"/>
+      <c r="AZ17" s="177"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="150">
+      <c r="B18" s="127">
         <v>7</v>
       </c>
-      <c r="C18" s="183" t="s">
+      <c r="C18" s="129" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="184"/>
-      <c r="F18" s="184"/>
-      <c r="G18" s="184"/>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="138" t="s">
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="152" t="s">
         <v>139</v>
       </c>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="196"/>
-      <c r="R18" s="197"/>
-      <c r="S18" s="198"/>
-      <c r="T18" s="186" t="s">
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="140"/>
+      <c r="R18" s="141"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="146" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="187"/>
-      <c r="V18" s="146">
+      <c r="U18" s="147"/>
+      <c r="V18" s="148">
         <v>0</v>
       </c>
-      <c r="W18" s="147"/>
-      <c r="X18" s="192">
+      <c r="W18" s="149"/>
+      <c r="X18" s="150">
         <v>0</v>
       </c>
-      <c r="Y18" s="193"/>
+      <c r="Y18" s="151"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8572,50 +8572,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="138"/>
-      <c r="AP18" s="139"/>
-      <c r="AQ18" s="139"/>
-      <c r="AR18" s="139"/>
-      <c r="AS18" s="139"/>
-      <c r="AT18" s="139"/>
-      <c r="AU18" s="139"/>
-      <c r="AV18" s="139"/>
-      <c r="AW18" s="139"/>
-      <c r="AX18" s="139"/>
-      <c r="AY18" s="139"/>
-      <c r="AZ18" s="188"/>
+      <c r="AO18" s="152"/>
+      <c r="AP18" s="135"/>
+      <c r="AQ18" s="135"/>
+      <c r="AR18" s="135"/>
+      <c r="AS18" s="135"/>
+      <c r="AT18" s="135"/>
+      <c r="AU18" s="135"/>
+      <c r="AV18" s="135"/>
+      <c r="AW18" s="135"/>
+      <c r="AX18" s="135"/>
+      <c r="AY18" s="135"/>
+      <c r="AZ18" s="153"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="151"/>
-      <c r="C19" s="168"/>
-      <c r="D19" s="169"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="170"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-      <c r="M19" s="142"/>
-      <c r="N19" s="142"/>
-      <c r="O19" s="142"/>
-      <c r="P19" s="143"/>
-      <c r="Q19" s="199"/>
-      <c r="R19" s="200"/>
-      <c r="S19" s="201"/>
-      <c r="T19" s="190" t="s">
+      <c r="B19" s="128"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="138"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="138"/>
+      <c r="N19" s="138"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="139"/>
+      <c r="Q19" s="143"/>
+      <c r="R19" s="144"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="191"/>
-      <c r="V19" s="148">
+      <c r="U19" s="156"/>
+      <c r="V19" s="157">
         <v>0</v>
       </c>
-      <c r="W19" s="149"/>
-      <c r="X19" s="194">
+      <c r="W19" s="158"/>
+      <c r="X19" s="159">
         <v>0</v>
       </c>
-      <c r="Y19" s="195"/>
+      <c r="Y19" s="160"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8631,56 +8631,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="141"/>
-      <c r="AP19" s="142"/>
-      <c r="AQ19" s="142"/>
-      <c r="AR19" s="142"/>
-      <c r="AS19" s="142"/>
-      <c r="AT19" s="142"/>
-      <c r="AU19" s="142"/>
-      <c r="AV19" s="142"/>
-      <c r="AW19" s="142"/>
-      <c r="AX19" s="142"/>
-      <c r="AY19" s="142"/>
-      <c r="AZ19" s="189"/>
+      <c r="AO19" s="137"/>
+      <c r="AP19" s="138"/>
+      <c r="AQ19" s="138"/>
+      <c r="AR19" s="138"/>
+      <c r="AS19" s="138"/>
+      <c r="AT19" s="138"/>
+      <c r="AU19" s="138"/>
+      <c r="AV19" s="138"/>
+      <c r="AW19" s="138"/>
+      <c r="AX19" s="138"/>
+      <c r="AY19" s="138"/>
+      <c r="AZ19" s="154"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="150">
+      <c r="B20" s="127">
         <v>8</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="184"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="183" t="s">
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="129" t="s">
         <v>140</v>
       </c>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="196"/>
-      <c r="R20" s="197"/>
-      <c r="S20" s="198"/>
-      <c r="T20" s="186" t="s">
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="140"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="142"/>
+      <c r="T20" s="146" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="187"/>
-      <c r="V20" s="146">
+      <c r="U20" s="147"/>
+      <c r="V20" s="148">
         <v>0</v>
       </c>
-      <c r="W20" s="147"/>
-      <c r="X20" s="192">
+      <c r="W20" s="149"/>
+      <c r="X20" s="150">
         <v>0</v>
       </c>
-      <c r="Y20" s="193"/>
+      <c r="Y20" s="151"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8696,50 +8696,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="138"/>
-      <c r="AP20" s="139"/>
-      <c r="AQ20" s="139"/>
-      <c r="AR20" s="139"/>
-      <c r="AS20" s="139"/>
-      <c r="AT20" s="139"/>
-      <c r="AU20" s="139"/>
-      <c r="AV20" s="139"/>
-      <c r="AW20" s="139"/>
-      <c r="AX20" s="139"/>
-      <c r="AY20" s="139"/>
-      <c r="AZ20" s="188"/>
+      <c r="AO20" s="152"/>
+      <c r="AP20" s="135"/>
+      <c r="AQ20" s="135"/>
+      <c r="AR20" s="135"/>
+      <c r="AS20" s="135"/>
+      <c r="AT20" s="135"/>
+      <c r="AU20" s="135"/>
+      <c r="AV20" s="135"/>
+      <c r="AW20" s="135"/>
+      <c r="AX20" s="135"/>
+      <c r="AY20" s="135"/>
+      <c r="AZ20" s="153"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="151"/>
-      <c r="C21" s="168"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="142"/>
-      <c r="L21" s="142"/>
-      <c r="M21" s="142"/>
-      <c r="N21" s="142"/>
-      <c r="O21" s="142"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="199"/>
-      <c r="R21" s="200"/>
-      <c r="S21" s="201"/>
-      <c r="T21" s="190" t="s">
+      <c r="B21" s="128"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="137"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="138"/>
+      <c r="N21" s="138"/>
+      <c r="O21" s="138"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="143"/>
+      <c r="R21" s="144"/>
+      <c r="S21" s="145"/>
+      <c r="T21" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="191"/>
-      <c r="V21" s="148">
+      <c r="U21" s="156"/>
+      <c r="V21" s="157">
         <v>0</v>
       </c>
-      <c r="W21" s="149"/>
-      <c r="X21" s="194">
+      <c r="W21" s="158"/>
+      <c r="X21" s="159">
         <v>0</v>
       </c>
-      <c r="Y21" s="195"/>
+      <c r="Y21" s="160"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8755,54 +8755,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="141"/>
-      <c r="AP21" s="142"/>
-      <c r="AQ21" s="142"/>
-      <c r="AR21" s="142"/>
-      <c r="AS21" s="142"/>
-      <c r="AT21" s="142"/>
-      <c r="AU21" s="142"/>
-      <c r="AV21" s="142"/>
-      <c r="AW21" s="142"/>
-      <c r="AX21" s="142"/>
-      <c r="AY21" s="142"/>
-      <c r="AZ21" s="189"/>
+      <c r="AO21" s="137"/>
+      <c r="AP21" s="138"/>
+      <c r="AQ21" s="138"/>
+      <c r="AR21" s="138"/>
+      <c r="AS21" s="138"/>
+      <c r="AT21" s="138"/>
+      <c r="AU21" s="138"/>
+      <c r="AV21" s="138"/>
+      <c r="AW21" s="138"/>
+      <c r="AX21" s="138"/>
+      <c r="AY21" s="138"/>
+      <c r="AZ21" s="154"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="163">
+      <c r="B22" s="197">
         <v>9</v>
       </c>
-      <c r="C22" s="165" t="s">
+      <c r="C22" s="199" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="156"/>
-      <c r="L22" s="156"/>
-      <c r="M22" s="156"/>
-      <c r="N22" s="156"/>
-      <c r="O22" s="156"/>
-      <c r="P22" s="204"/>
-      <c r="Q22" s="175"/>
-      <c r="R22" s="176"/>
-      <c r="S22" s="177"/>
-      <c r="T22" s="171" t="s">
+      <c r="D22" s="200"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="185"/>
+      <c r="L22" s="185"/>
+      <c r="M22" s="185"/>
+      <c r="N22" s="185"/>
+      <c r="O22" s="185"/>
+      <c r="P22" s="186"/>
+      <c r="Q22" s="206"/>
+      <c r="R22" s="207"/>
+      <c r="S22" s="208"/>
+      <c r="T22" s="202" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="172"/>
-      <c r="V22" s="202">
+      <c r="U22" s="203"/>
+      <c r="V22" s="182">
         <v>0</v>
       </c>
-      <c r="W22" s="203"/>
-      <c r="X22" s="161">
+      <c r="W22" s="183"/>
+      <c r="X22" s="195">
         <v>0</v>
       </c>
-      <c r="Y22" s="162"/>
+      <c r="Y22" s="196"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8818,50 +8818,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="155"/>
-      <c r="AP22" s="156"/>
-      <c r="AQ22" s="156"/>
-      <c r="AR22" s="156"/>
-      <c r="AS22" s="156"/>
-      <c r="AT22" s="156"/>
-      <c r="AU22" s="156"/>
-      <c r="AV22" s="156"/>
-      <c r="AW22" s="156"/>
-      <c r="AX22" s="156"/>
-      <c r="AY22" s="156"/>
-      <c r="AZ22" s="157"/>
+      <c r="AO22" s="184"/>
+      <c r="AP22" s="185"/>
+      <c r="AQ22" s="185"/>
+      <c r="AR22" s="185"/>
+      <c r="AS22" s="185"/>
+      <c r="AT22" s="185"/>
+      <c r="AU22" s="185"/>
+      <c r="AV22" s="185"/>
+      <c r="AW22" s="185"/>
+      <c r="AX22" s="185"/>
+      <c r="AY22" s="185"/>
+      <c r="AZ22" s="193"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="164"/>
-      <c r="C23" s="168"/>
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="170"/>
-      <c r="J23" s="158"/>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
-      <c r="M23" s="159"/>
-      <c r="N23" s="159"/>
-      <c r="O23" s="159"/>
-      <c r="P23" s="205"/>
-      <c r="Q23" s="178"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="180"/>
-      <c r="T23" s="173" t="s">
+      <c r="B23" s="198"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="188"/>
+      <c r="L23" s="188"/>
+      <c r="M23" s="188"/>
+      <c r="N23" s="188"/>
+      <c r="O23" s="188"/>
+      <c r="P23" s="189"/>
+      <c r="Q23" s="209"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="211"/>
+      <c r="T23" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="174"/>
-      <c r="V23" s="144">
+      <c r="U23" s="205"/>
+      <c r="V23" s="191">
         <v>0</v>
       </c>
-      <c r="W23" s="145"/>
-      <c r="X23" s="181">
+      <c r="W23" s="192"/>
+      <c r="X23" s="212">
         <v>0</v>
       </c>
-      <c r="Y23" s="182"/>
+      <c r="Y23" s="213"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8877,18 +8877,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="158"/>
-      <c r="AP23" s="159"/>
-      <c r="AQ23" s="159"/>
-      <c r="AR23" s="159"/>
-      <c r="AS23" s="159"/>
-      <c r="AT23" s="159"/>
-      <c r="AU23" s="159"/>
-      <c r="AV23" s="159"/>
-      <c r="AW23" s="159"/>
-      <c r="AX23" s="159"/>
-      <c r="AY23" s="159"/>
-      <c r="AZ23" s="160"/>
+      <c r="AO23" s="187"/>
+      <c r="AP23" s="188"/>
+      <c r="AQ23" s="188"/>
+      <c r="AR23" s="188"/>
+      <c r="AS23" s="188"/>
+      <c r="AT23" s="188"/>
+      <c r="AU23" s="188"/>
+      <c r="AV23" s="188"/>
+      <c r="AW23" s="188"/>
+      <c r="AX23" s="188"/>
+      <c r="AY23" s="188"/>
+      <c r="AZ23" s="194"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8947,50 +8947,51 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AO16:AZ17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AO22:AZ23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:I23"/>
+    <mergeCell ref="J18:P19"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q16:S17"/>
+    <mergeCell ref="Q22:S23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C18:I19"/>
+    <mergeCell ref="T18:U18"/>
     <mergeCell ref="AO18:AZ19"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="X18:Y18"/>
@@ -9015,51 +9016,50 @@
     <mergeCell ref="X15:Y15"/>
     <mergeCell ref="Q12:S13"/>
     <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AO16:AZ17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AO22:AZ23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:I23"/>
-    <mergeCell ref="J18:P19"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q16:S17"/>
-    <mergeCell ref="Q22:S23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C18:I19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9083,53 +9083,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64">
+      <c r="A1" s="63">
         <v>1</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="111" t="s">
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="112"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="72"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="114"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64">
+      <c r="A3" s="63">
         <v>2</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="101"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="218" t="s">
         <v>60</v>
       </c>
@@ -9143,551 +9143,552 @@
       <c r="J4" s="219"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64">
+      <c r="A5" s="63">
         <v>3</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="101"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="77" t="s">
+      <c r="A6" s="67"/>
+      <c r="B6" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="78"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64">
+      <c r="A7" s="63">
         <v>4</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="66"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="66"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="66"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="66"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="66"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="72"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="66"/>
-      <c r="B15" s="73" t="s">
+      <c r="A15" s="64"/>
+      <c r="B15" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="74"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="66"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="72"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="66"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="72"/>
+      <c r="A17" s="64"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="66"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="72"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="79"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="66"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="72"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="79"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="66"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="72"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="79"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="114"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="74"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="64">
+      <c r="A22" s="63">
         <v>5</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="69"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="101"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="79"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="79"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="72"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="79"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="66"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="72"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="79"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="66"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="72"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="79"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="66"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="72"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="78"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="79"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="66"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="72"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="79"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65"/>
-      <c r="B30" s="113"/>
-      <c r="C30" s="113"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="113"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="114"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="74"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="64">
+      <c r="A31" s="63">
         <v>6</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="69"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="101"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="66"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="72"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="79"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="66"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="72"/>
+      <c r="A33" s="64"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="79"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="66"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="72"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="79"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="66"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="72"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="79"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="66"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="72"/>
+      <c r="A36" s="64"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="79"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="66"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="72"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
+      <c r="J37" s="79"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="72"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="78"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="78"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
+      <c r="J38" s="79"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="72"/>
+      <c r="A39" s="64"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="72"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="79"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="66"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="72"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="78"/>
+      <c r="I41" s="78"/>
+      <c r="J41" s="79"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="66"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="72"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="79"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="66"/>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="72"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="79"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="66"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="71"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="72"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="79"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="66"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="71"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="72"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="78"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="78"/>
+      <c r="E45" s="78"/>
+      <c r="F45" s="78"/>
+      <c r="G45" s="78"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="79"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="66"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="71"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="72"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="78"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="79"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="A47" s="65"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -9696,13 +9697,12 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9715,14 +9715,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9933,29 +9931,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9980,9 +9969,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AA371A-6B4E-4ACE-ABBE-DB31E69E4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE031C-3307-469E-AFEA-F3660E7F8809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -2021,6 +2021,7 @@
 ・LINEログイン
 ・被害状況分析履歴
 追加機能
+・チャットボットによる追加質問
 ・罹災証明書の申請案内
 ③：システム規模
 ・個人(事業者・建物管理者を含む)での利用を想定している
@@ -2067,13 +2068,19 @@
     <rPh sb="236" eb="238">
       <t>カイトウ</t>
     </rPh>
-    <rPh sb="326" eb="328">
+    <rPh sb="323" eb="325">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="325" eb="327">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="342" eb="344">
       <t>キボ</t>
     </rPh>
-    <rPh sb="343" eb="344">
+    <rPh sb="359" eb="360">
       <t>フク</t>
     </rPh>
-    <rPh sb="392" eb="394">
+    <rPh sb="408" eb="410">
       <t>カンケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -3175,12 +3182,42 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3220,58 +3257,148 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3286,129 +3413,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3416,7 +3426,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3427,20 +3449,74 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3448,6 +3524,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3457,29 +3626,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3499,50 +3674,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3556,15 +3698,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3588,132 +3721,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -4603,1585 +4610,1608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63">
+      <c r="A2" s="64">
         <v>1</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="71" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="111" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="112"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="63">
+      <c r="A4" s="64">
         <v>2</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="69"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64"/>
-      <c r="B5" s="80" t="s">
+      <c r="A5" s="66"/>
+      <c r="B5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="64"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="81"/>
+      <c r="A6" s="66"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="83"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="83"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64"/>
-      <c r="B8" s="95" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="97"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="64"/>
-      <c r="B9" s="98"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="100"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="100"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="92"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="64"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="100"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="92"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="64"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="100"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="92"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="64"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="100"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="92"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="64"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="100"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="64"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="100"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="64"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="100"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="92"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="67"/>
-      <c r="B17" s="98"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="99"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="92"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="67"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="100"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="92"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="67"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="100"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="100"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="63">
+      <c r="A21" s="64">
         <v>3</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="64"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="86"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="101"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="64"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="86"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="101"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="64"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="85"/>
-      <c r="D24" s="85"/>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="86"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="101"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="64"/>
-      <c r="B25" s="87"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="89"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="104"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="64"/>
-      <c r="B26" s="90" t="s">
+      <c r="A26" s="66"/>
+      <c r="B26" s="105" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="91"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="106"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="64"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="91"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="64"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="91"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="106"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="64"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="91"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="106"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="64"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="91"/>
+      <c r="A30" s="66"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="106"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="64"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="91"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="106"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="64"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="90"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="91"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="106"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="64"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="90"/>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="90"/>
-      <c r="I33" s="90"/>
-      <c r="J33" s="91"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="106"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="64"/>
-      <c r="B34" s="90"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="90"/>
-      <c r="J34" s="91"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="106"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="64"/>
-      <c r="B35" s="90"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="90"/>
-      <c r="J35" s="91"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="106"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="64"/>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="91"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="105"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="106"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64"/>
-      <c r="B37" s="90"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="91"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="106"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="64"/>
-      <c r="B38" s="90"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="90"/>
-      <c r="H38" s="90"/>
-      <c r="I38" s="90"/>
-      <c r="J38" s="91"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="105"/>
+      <c r="J38" s="106"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="64"/>
-      <c r="B39" s="90"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="90"/>
-      <c r="J39" s="91"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="106"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64"/>
-      <c r="B40" s="90"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="90"/>
-      <c r="F40" s="90"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="91"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="64"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="91"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="64"/>
-      <c r="B42" s="90"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="90"/>
-      <c r="F42" s="90"/>
-      <c r="G42" s="90"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="91"/>
+      <c r="A42" s="66"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="106"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="64"/>
-      <c r="B43" s="90"/>
-      <c r="C43" s="90"/>
-      <c r="D43" s="90"/>
-      <c r="E43" s="90"/>
-      <c r="F43" s="90"/>
-      <c r="G43" s="90"/>
-      <c r="H43" s="90"/>
-      <c r="I43" s="90"/>
-      <c r="J43" s="91"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="64"/>
-      <c r="B44" s="90"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="90"/>
-      <c r="F44" s="90"/>
-      <c r="G44" s="90"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="91"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="106"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="64"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="90"/>
-      <c r="E45" s="90"/>
-      <c r="F45" s="90"/>
-      <c r="G45" s="90"/>
-      <c r="H45" s="90"/>
-      <c r="I45" s="90"/>
-      <c r="J45" s="91"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="106"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="64"/>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="90"/>
-      <c r="F46" s="90"/>
-      <c r="G46" s="90"/>
-      <c r="H46" s="90"/>
-      <c r="I46" s="90"/>
-      <c r="J46" s="91"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="106"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="64"/>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="90"/>
-      <c r="E47" s="90"/>
-      <c r="F47" s="90"/>
-      <c r="G47" s="90"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="91"/>
+      <c r="A47" s="66"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="64"/>
-      <c r="B48" s="90"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="90"/>
-      <c r="F48" s="90"/>
-      <c r="G48" s="90"/>
-      <c r="H48" s="90"/>
-      <c r="I48" s="90"/>
-      <c r="J48" s="91"/>
+      <c r="A48" s="66"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="105"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="106"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="64"/>
-      <c r="B49" s="90"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90"/>
-      <c r="F49" s="90"/>
-      <c r="G49" s="90"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="91"/>
+      <c r="A49" s="66"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="106"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="64"/>
-      <c r="B50" s="90"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="90"/>
-      <c r="F50" s="90"/>
-      <c r="G50" s="90"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="91"/>
+      <c r="A50" s="66"/>
+      <c r="B50" s="105"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="105"/>
+      <c r="J50" s="106"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="64"/>
-      <c r="B51" s="90"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="90"/>
-      <c r="E51" s="90"/>
-      <c r="F51" s="90"/>
-      <c r="G51" s="90"/>
-      <c r="H51" s="90"/>
-      <c r="I51" s="90"/>
-      <c r="J51" s="91"/>
+      <c r="A51" s="66"/>
+      <c r="B51" s="105"/>
+      <c r="C51" s="105"/>
+      <c r="D51" s="105"/>
+      <c r="E51" s="105"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="105"/>
+      <c r="H51" s="105"/>
+      <c r="I51" s="105"/>
+      <c r="J51" s="106"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="64"/>
-      <c r="B52" s="90"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="90"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="90"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="91"/>
+      <c r="A52" s="66"/>
+      <c r="B52" s="105"/>
+      <c r="C52" s="105"/>
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="105"/>
+      <c r="I52" s="105"/>
+      <c r="J52" s="106"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="64"/>
-      <c r="B53" s="90"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="90"/>
-      <c r="E53" s="90"/>
-      <c r="F53" s="90"/>
-      <c r="G53" s="90"/>
-      <c r="H53" s="90"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="91"/>
+      <c r="A53" s="66"/>
+      <c r="B53" s="105"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="105"/>
+      <c r="I53" s="105"/>
+      <c r="J53" s="106"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="64"/>
-      <c r="B54" s="90"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="90"/>
-      <c r="E54" s="90"/>
-      <c r="F54" s="90"/>
-      <c r="G54" s="90"/>
-      <c r="H54" s="90"/>
-      <c r="I54" s="90"/>
-      <c r="J54" s="91"/>
+      <c r="A54" s="66"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="105"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="106"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="64"/>
-      <c r="B55" s="90"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
-      <c r="H55" s="90"/>
-      <c r="I55" s="90"/>
-      <c r="J55" s="91"/>
+      <c r="A55" s="66"/>
+      <c r="B55" s="105"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="106"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="64"/>
-      <c r="B56" s="90"/>
-      <c r="C56" s="90"/>
-      <c r="D56" s="90"/>
-      <c r="E56" s="90"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="90"/>
-      <c r="H56" s="90"/>
-      <c r="I56" s="90"/>
-      <c r="J56" s="91"/>
+      <c r="A56" s="66"/>
+      <c r="B56" s="105"/>
+      <c r="C56" s="105"/>
+      <c r="D56" s="105"/>
+      <c r="E56" s="105"/>
+      <c r="F56" s="105"/>
+      <c r="G56" s="105"/>
+      <c r="H56" s="105"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="106"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="64"/>
-      <c r="B57" s="90"/>
-      <c r="C57" s="90"/>
-      <c r="D57" s="90"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
-      <c r="H57" s="90"/>
-      <c r="I57" s="90"/>
-      <c r="J57" s="91"/>
+      <c r="A57" s="66"/>
+      <c r="B57" s="105"/>
+      <c r="C57" s="105"/>
+      <c r="D57" s="105"/>
+      <c r="E57" s="105"/>
+      <c r="F57" s="105"/>
+      <c r="G57" s="105"/>
+      <c r="H57" s="105"/>
+      <c r="I57" s="105"/>
+      <c r="J57" s="106"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="64"/>
-      <c r="B58" s="90"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="90"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="90"/>
-      <c r="H58" s="90"/>
-      <c r="I58" s="90"/>
-      <c r="J58" s="91"/>
+      <c r="A58" s="66"/>
+      <c r="B58" s="105"/>
+      <c r="C58" s="105"/>
+      <c r="D58" s="105"/>
+      <c r="E58" s="105"/>
+      <c r="F58" s="105"/>
+      <c r="G58" s="105"/>
+      <c r="H58" s="105"/>
+      <c r="I58" s="105"/>
+      <c r="J58" s="106"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="64"/>
-      <c r="B59" s="90"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
-      <c r="H59" s="90"/>
-      <c r="I59" s="90"/>
-      <c r="J59" s="91"/>
+      <c r="A59" s="66"/>
+      <c r="B59" s="105"/>
+      <c r="C59" s="105"/>
+      <c r="D59" s="105"/>
+      <c r="E59" s="105"/>
+      <c r="F59" s="105"/>
+      <c r="G59" s="105"/>
+      <c r="H59" s="105"/>
+      <c r="I59" s="105"/>
+      <c r="J59" s="106"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="64"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="90"/>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
-      <c r="H60" s="90"/>
-      <c r="I60" s="90"/>
-      <c r="J60" s="91"/>
+      <c r="A60" s="66"/>
+      <c r="B60" s="105"/>
+      <c r="C60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="106"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="64"/>
-      <c r="B61" s="90"/>
-      <c r="C61" s="90"/>
-      <c r="D61" s="90"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="90"/>
-      <c r="H61" s="90"/>
-      <c r="I61" s="90"/>
-      <c r="J61" s="91"/>
+      <c r="A61" s="66"/>
+      <c r="B61" s="105"/>
+      <c r="C61" s="105"/>
+      <c r="D61" s="105"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="105"/>
+      <c r="G61" s="105"/>
+      <c r="H61" s="105"/>
+      <c r="I61" s="105"/>
+      <c r="J61" s="106"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="65"/>
-      <c r="B62" s="92"/>
-      <c r="C62" s="92"/>
-      <c r="D62" s="92"/>
-      <c r="E62" s="92"/>
-      <c r="F62" s="92"/>
-      <c r="G62" s="92"/>
-      <c r="H62" s="92"/>
-      <c r="I62" s="92"/>
-      <c r="J62" s="93"/>
+      <c r="A62" s="67"/>
+      <c r="B62" s="107"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107"/>
+      <c r="J62" s="108"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="63">
+      <c r="A63" s="64">
         <v>4</v>
       </c>
-      <c r="B63" s="70" t="s">
+      <c r="B63" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="70"/>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
-      <c r="H63" s="70"/>
-      <c r="I63" s="70"/>
-      <c r="J63" s="101"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="68"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="68"/>
+      <c r="J63" s="69"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="64"/>
-      <c r="B64" s="66" t="s">
+      <c r="A64" s="66"/>
+      <c r="B64" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="66"/>
-      <c r="D64" s="78" t="s">
+      <c r="C64" s="109"/>
+      <c r="D64" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="78"/>
-      <c r="F64" s="78"/>
-      <c r="G64" s="78"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="79"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="71"/>
+      <c r="J64" s="72"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="64"/>
-      <c r="B65" s="66" t="s">
+      <c r="A65" s="66"/>
+      <c r="B65" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="66"/>
-      <c r="D65" s="78" t="s">
+      <c r="C65" s="109"/>
+      <c r="D65" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="78"/>
-      <c r="F65" s="78"/>
-      <c r="G65" s="78"/>
-      <c r="H65" s="78"/>
-      <c r="I65" s="78"/>
-      <c r="J65" s="79"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="72"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="64"/>
-      <c r="B66" s="66" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="66"/>
-      <c r="D66" s="78" t="s">
+      <c r="C66" s="109"/>
+      <c r="D66" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="E66" s="78"/>
-      <c r="F66" s="78"/>
-      <c r="G66" s="78"/>
-      <c r="H66" s="78"/>
-      <c r="I66" s="78"/>
-      <c r="J66" s="79"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="71"/>
+      <c r="G66" s="71"/>
+      <c r="H66" s="71"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="72"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="64"/>
-      <c r="B67" s="66" t="s">
+      <c r="A67" s="66"/>
+      <c r="B67" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="66"/>
-      <c r="D67" s="78" t="s">
+      <c r="C67" s="109"/>
+      <c r="D67" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="E67" s="78"/>
-      <c r="F67" s="78"/>
-      <c r="G67" s="78"/>
-      <c r="H67" s="78"/>
-      <c r="I67" s="78"/>
-      <c r="J67" s="79"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="72"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="64"/>
-      <c r="B68" s="66" t="s">
+      <c r="A68" s="66"/>
+      <c r="B68" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="66"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="66"/>
-      <c r="F68" s="66"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="66"/>
-      <c r="I68" s="66"/>
-      <c r="J68" s="94"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="109"/>
+      <c r="E68" s="109"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109"/>
+      <c r="I68" s="109"/>
+      <c r="J68" s="110"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="64"/>
-      <c r="B69" s="75" t="e" vm="1">
+      <c r="A69" s="66"/>
+      <c r="B69" s="96" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="75"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="75"/>
-      <c r="F69" s="75"/>
-      <c r="G69" s="75"/>
-      <c r="H69" s="75"/>
-      <c r="I69" s="75"/>
-      <c r="J69" s="76"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="96"/>
+      <c r="E69" s="96"/>
+      <c r="F69" s="96"/>
+      <c r="G69" s="96"/>
+      <c r="H69" s="96"/>
+      <c r="I69" s="96"/>
+      <c r="J69" s="97"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="64"/>
-      <c r="B70" s="75"/>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="76"/>
+      <c r="A70" s="66"/>
+      <c r="B70" s="96"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="96"/>
+      <c r="E70" s="96"/>
+      <c r="F70" s="96"/>
+      <c r="G70" s="96"/>
+      <c r="H70" s="96"/>
+      <c r="I70" s="96"/>
+      <c r="J70" s="97"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="64"/>
-      <c r="B71" s="75"/>
-      <c r="C71" s="75"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75"/>
-      <c r="F71" s="75"/>
-      <c r="G71" s="75"/>
-      <c r="H71" s="75"/>
-      <c r="I71" s="75"/>
-      <c r="J71" s="76"/>
+      <c r="A71" s="66"/>
+      <c r="B71" s="96"/>
+      <c r="C71" s="96"/>
+      <c r="D71" s="96"/>
+      <c r="E71" s="96"/>
+      <c r="F71" s="96"/>
+      <c r="G71" s="96"/>
+      <c r="H71" s="96"/>
+      <c r="I71" s="96"/>
+      <c r="J71" s="97"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="64"/>
-      <c r="B72" s="75"/>
-      <c r="C72" s="75"/>
-      <c r="D72" s="75"/>
-      <c r="E72" s="75"/>
-      <c r="F72" s="75"/>
-      <c r="G72" s="75"/>
-      <c r="H72" s="75"/>
-      <c r="I72" s="75"/>
-      <c r="J72" s="76"/>
+      <c r="A72" s="66"/>
+      <c r="B72" s="96"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="96"/>
+      <c r="E72" s="96"/>
+      <c r="F72" s="96"/>
+      <c r="G72" s="96"/>
+      <c r="H72" s="96"/>
+      <c r="I72" s="96"/>
+      <c r="J72" s="97"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="64"/>
-      <c r="B73" s="75"/>
-      <c r="C73" s="75"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="75"/>
-      <c r="J73" s="76"/>
+      <c r="A73" s="66"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="96"/>
+      <c r="E73" s="96"/>
+      <c r="F73" s="96"/>
+      <c r="G73" s="96"/>
+      <c r="H73" s="96"/>
+      <c r="I73" s="96"/>
+      <c r="J73" s="97"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="64"/>
-      <c r="B74" s="75"/>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="75"/>
-      <c r="F74" s="75"/>
-      <c r="G74" s="75"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="75"/>
-      <c r="J74" s="76"/>
+      <c r="A74" s="66"/>
+      <c r="B74" s="96"/>
+      <c r="C74" s="96"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="96"/>
+      <c r="F74" s="96"/>
+      <c r="G74" s="96"/>
+      <c r="H74" s="96"/>
+      <c r="I74" s="96"/>
+      <c r="J74" s="97"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="64"/>
-      <c r="B75" s="75"/>
-      <c r="C75" s="75"/>
-      <c r="D75" s="75"/>
-      <c r="E75" s="75"/>
-      <c r="F75" s="75"/>
-      <c r="G75" s="75"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="75"/>
-      <c r="J75" s="76"/>
+      <c r="A75" s="66"/>
+      <c r="B75" s="96"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
+      <c r="F75" s="96"/>
+      <c r="G75" s="96"/>
+      <c r="H75" s="96"/>
+      <c r="I75" s="96"/>
+      <c r="J75" s="97"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="64"/>
-      <c r="B76" s="75"/>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="75"/>
-      <c r="F76" s="75"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="75"/>
-      <c r="J76" s="76"/>
+      <c r="A76" s="66"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="96"/>
+      <c r="D76" s="96"/>
+      <c r="E76" s="96"/>
+      <c r="F76" s="96"/>
+      <c r="G76" s="96"/>
+      <c r="H76" s="96"/>
+      <c r="I76" s="96"/>
+      <c r="J76" s="97"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="64"/>
-      <c r="B77" s="75"/>
-      <c r="C77" s="75"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="75"/>
-      <c r="F77" s="75"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="75"/>
-      <c r="J77" s="76"/>
+      <c r="A77" s="66"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="96"/>
+      <c r="D77" s="96"/>
+      <c r="E77" s="96"/>
+      <c r="F77" s="96"/>
+      <c r="G77" s="96"/>
+      <c r="H77" s="96"/>
+      <c r="I77" s="96"/>
+      <c r="J77" s="97"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="64"/>
-      <c r="B78" s="75"/>
-      <c r="C78" s="75"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="75"/>
-      <c r="F78" s="75"/>
-      <c r="G78" s="75"/>
-      <c r="H78" s="75"/>
-      <c r="I78" s="75"/>
-      <c r="J78" s="76"/>
+      <c r="A78" s="66"/>
+      <c r="B78" s="96"/>
+      <c r="C78" s="96"/>
+      <c r="D78" s="96"/>
+      <c r="E78" s="96"/>
+      <c r="F78" s="96"/>
+      <c r="G78" s="96"/>
+      <c r="H78" s="96"/>
+      <c r="I78" s="96"/>
+      <c r="J78" s="97"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="64"/>
-      <c r="B79" s="75"/>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
-      <c r="E79" s="75"/>
-      <c r="F79" s="75"/>
-      <c r="G79" s="75"/>
-      <c r="H79" s="75"/>
-      <c r="I79" s="75"/>
-      <c r="J79" s="76"/>
+      <c r="A79" s="66"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="96"/>
+      <c r="E79" s="96"/>
+      <c r="F79" s="96"/>
+      <c r="G79" s="96"/>
+      <c r="H79" s="96"/>
+      <c r="I79" s="96"/>
+      <c r="J79" s="97"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="64"/>
-      <c r="B80" s="75"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="75"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="75"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="75"/>
-      <c r="I80" s="75"/>
-      <c r="J80" s="76"/>
+      <c r="A80" s="66"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="96"/>
+      <c r="E80" s="96"/>
+      <c r="F80" s="96"/>
+      <c r="G80" s="96"/>
+      <c r="H80" s="96"/>
+      <c r="I80" s="96"/>
+      <c r="J80" s="97"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="64"/>
-      <c r="B81" s="75"/>
-      <c r="C81" s="75"/>
-      <c r="D81" s="75"/>
-      <c r="E81" s="75"/>
-      <c r="F81" s="75"/>
-      <c r="G81" s="75"/>
-      <c r="H81" s="75"/>
-      <c r="I81" s="75"/>
-      <c r="J81" s="76"/>
+      <c r="A81" s="66"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="96"/>
+      <c r="F81" s="96"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="96"/>
+      <c r="I81" s="96"/>
+      <c r="J81" s="97"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="64"/>
-      <c r="B82" s="75"/>
-      <c r="C82" s="75"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="75"/>
-      <c r="F82" s="75"/>
-      <c r="G82" s="75"/>
-      <c r="H82" s="75"/>
-      <c r="I82" s="75"/>
-      <c r="J82" s="76"/>
+      <c r="A82" s="66"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="96"/>
+      <c r="D82" s="96"/>
+      <c r="E82" s="96"/>
+      <c r="F82" s="96"/>
+      <c r="G82" s="96"/>
+      <c r="H82" s="96"/>
+      <c r="I82" s="96"/>
+      <c r="J82" s="97"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="64"/>
-      <c r="B83" s="75"/>
-      <c r="C83" s="75"/>
-      <c r="D83" s="75"/>
-      <c r="E83" s="75"/>
-      <c r="F83" s="75"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="75"/>
-      <c r="I83" s="75"/>
-      <c r="J83" s="76"/>
+      <c r="A83" s="66"/>
+      <c r="B83" s="96"/>
+      <c r="C83" s="96"/>
+      <c r="D83" s="96"/>
+      <c r="E83" s="96"/>
+      <c r="F83" s="96"/>
+      <c r="G83" s="96"/>
+      <c r="H83" s="96"/>
+      <c r="I83" s="96"/>
+      <c r="J83" s="97"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="64"/>
-      <c r="B84" s="75"/>
-      <c r="C84" s="75"/>
-      <c r="D84" s="75"/>
-      <c r="E84" s="75"/>
-      <c r="F84" s="75"/>
-      <c r="G84" s="75"/>
-      <c r="H84" s="75"/>
-      <c r="I84" s="75"/>
-      <c r="J84" s="76"/>
+      <c r="A84" s="66"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="96"/>
+      <c r="D84" s="96"/>
+      <c r="E84" s="96"/>
+      <c r="F84" s="96"/>
+      <c r="G84" s="96"/>
+      <c r="H84" s="96"/>
+      <c r="I84" s="96"/>
+      <c r="J84" s="97"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="64"/>
-      <c r="B85" s="75"/>
-      <c r="C85" s="75"/>
-      <c r="D85" s="75"/>
-      <c r="E85" s="75"/>
-      <c r="F85" s="75"/>
-      <c r="G85" s="75"/>
-      <c r="H85" s="75"/>
-      <c r="I85" s="75"/>
-      <c r="J85" s="76"/>
+      <c r="A85" s="66"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
+      <c r="F85" s="96"/>
+      <c r="G85" s="96"/>
+      <c r="H85" s="96"/>
+      <c r="I85" s="96"/>
+      <c r="J85" s="97"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="67"/>
-      <c r="B86" s="57"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="57"/>
-      <c r="J86" s="77"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="40"/>
+      <c r="J86" s="98"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="63">
+      <c r="A87" s="64">
         <v>5</v>
       </c>
-      <c r="B87" s="70" t="s">
+      <c r="B87" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="70"/>
-      <c r="D87" s="70"/>
-      <c r="E87" s="70"/>
-      <c r="F87" s="70"/>
-      <c r="G87" s="70"/>
-      <c r="H87" s="70"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="101"/>
+      <c r="C87" s="68"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="68"/>
+      <c r="I87" s="68"/>
+      <c r="J87" s="69"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="64"/>
-      <c r="B88" s="41" t="s">
+      <c r="A88" s="66"/>
+      <c r="B88" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="41"/>
-      <c r="I88" s="41"/>
-      <c r="J88" s="111"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
+      <c r="J88" s="86"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="63">
+      <c r="A89" s="64">
         <v>6</v>
       </c>
-      <c r="B89" s="68" t="s">
+      <c r="B89" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="68"/>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="68"/>
-      <c r="I89" s="68"/>
-      <c r="J89" s="69"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
+      <c r="H89" s="79"/>
+      <c r="I89" s="79"/>
+      <c r="J89" s="80"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="110"/>
-      <c r="B90" s="80" t="s">
+      <c r="A90" s="81"/>
+      <c r="B90" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="80"/>
-      <c r="I90" s="80"/>
-      <c r="J90" s="81"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="82"/>
+      <c r="J90" s="83"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="110"/>
-      <c r="B91" s="80"/>
-      <c r="C91" s="80"/>
-      <c r="D91" s="80"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="80"/>
-      <c r="I91" s="80"/>
-      <c r="J91" s="81"/>
+      <c r="A91" s="81"/>
+      <c r="B91" s="82"/>
+      <c r="C91" s="82"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
+      <c r="I91" s="82"/>
+      <c r="J91" s="83"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="110"/>
-      <c r="B92" s="82"/>
-      <c r="C92" s="82"/>
-      <c r="D92" s="82"/>
-      <c r="E92" s="82"/>
-      <c r="F92" s="82"/>
-      <c r="G92" s="82"/>
-      <c r="H92" s="82"/>
-      <c r="I92" s="82"/>
-      <c r="J92" s="83"/>
+      <c r="A92" s="81"/>
+      <c r="B92" s="84"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="84"/>
+      <c r="E92" s="84"/>
+      <c r="F92" s="84"/>
+      <c r="G92" s="84"/>
+      <c r="H92" s="84"/>
+      <c r="I92" s="84"/>
+      <c r="J92" s="85"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="64"/>
-      <c r="B93" s="95" t="s">
+      <c r="A93" s="66"/>
+      <c r="B93" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="C93" s="96"/>
-      <c r="D93" s="96"/>
-      <c r="E93" s="96"/>
-      <c r="F93" s="96"/>
-      <c r="G93" s="96"/>
-      <c r="H93" s="96"/>
-      <c r="I93" s="96"/>
-      <c r="J93" s="97"/>
+      <c r="C93" s="88"/>
+      <c r="D93" s="88"/>
+      <c r="E93" s="88"/>
+      <c r="F93" s="88"/>
+      <c r="G93" s="88"/>
+      <c r="H93" s="88"/>
+      <c r="I93" s="88"/>
+      <c r="J93" s="89"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="64"/>
-      <c r="B94" s="98"/>
-      <c r="C94" s="99"/>
-      <c r="D94" s="99"/>
-      <c r="E94" s="99"/>
-      <c r="F94" s="99"/>
-      <c r="G94" s="99"/>
-      <c r="H94" s="99"/>
-      <c r="I94" s="99"/>
-      <c r="J94" s="100"/>
+      <c r="A94" s="66"/>
+      <c r="B94" s="90"/>
+      <c r="C94" s="91"/>
+      <c r="D94" s="91"/>
+      <c r="E94" s="91"/>
+      <c r="F94" s="91"/>
+      <c r="G94" s="91"/>
+      <c r="H94" s="91"/>
+      <c r="I94" s="91"/>
+      <c r="J94" s="92"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="64"/>
-      <c r="B95" s="98"/>
-      <c r="C95" s="99"/>
-      <c r="D95" s="99"/>
-      <c r="E95" s="99"/>
-      <c r="F95" s="99"/>
-      <c r="G95" s="99"/>
-      <c r="H95" s="99"/>
-      <c r="I95" s="99"/>
-      <c r="J95" s="100"/>
+      <c r="A95" s="66"/>
+      <c r="B95" s="90"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="91"/>
+      <c r="E95" s="91"/>
+      <c r="F95" s="91"/>
+      <c r="G95" s="91"/>
+      <c r="H95" s="91"/>
+      <c r="I95" s="91"/>
+      <c r="J95" s="92"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="64"/>
-      <c r="B96" s="98"/>
-      <c r="C96" s="99"/>
-      <c r="D96" s="99"/>
-      <c r="E96" s="99"/>
-      <c r="F96" s="99"/>
-      <c r="G96" s="99"/>
-      <c r="H96" s="99"/>
-      <c r="I96" s="99"/>
-      <c r="J96" s="100"/>
+      <c r="A96" s="66"/>
+      <c r="B96" s="90"/>
+      <c r="C96" s="91"/>
+      <c r="D96" s="91"/>
+      <c r="E96" s="91"/>
+      <c r="F96" s="91"/>
+      <c r="G96" s="91"/>
+      <c r="H96" s="91"/>
+      <c r="I96" s="91"/>
+      <c r="J96" s="92"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="64"/>
-      <c r="B97" s="98"/>
-      <c r="C97" s="99"/>
-      <c r="D97" s="99"/>
-      <c r="E97" s="99"/>
-      <c r="F97" s="99"/>
-      <c r="G97" s="99"/>
-      <c r="H97" s="99"/>
-      <c r="I97" s="99"/>
-      <c r="J97" s="100"/>
+      <c r="A97" s="66"/>
+      <c r="B97" s="90"/>
+      <c r="C97" s="91"/>
+      <c r="D97" s="91"/>
+      <c r="E97" s="91"/>
+      <c r="F97" s="91"/>
+      <c r="G97" s="91"/>
+      <c r="H97" s="91"/>
+      <c r="I97" s="91"/>
+      <c r="J97" s="92"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="64"/>
-      <c r="B98" s="98"/>
-      <c r="C98" s="99"/>
-      <c r="D98" s="99"/>
-      <c r="E98" s="99"/>
-      <c r="F98" s="99"/>
-      <c r="G98" s="99"/>
-      <c r="H98" s="99"/>
-      <c r="I98" s="99"/>
-      <c r="J98" s="100"/>
+      <c r="A98" s="66"/>
+      <c r="B98" s="90"/>
+      <c r="C98" s="91"/>
+      <c r="D98" s="91"/>
+      <c r="E98" s="91"/>
+      <c r="F98" s="91"/>
+      <c r="G98" s="91"/>
+      <c r="H98" s="91"/>
+      <c r="I98" s="91"/>
+      <c r="J98" s="92"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="64"/>
-      <c r="B99" s="98"/>
-      <c r="C99" s="99"/>
-      <c r="D99" s="99"/>
-      <c r="E99" s="99"/>
-      <c r="F99" s="99"/>
-      <c r="G99" s="99"/>
-      <c r="H99" s="99"/>
-      <c r="I99" s="99"/>
-      <c r="J99" s="100"/>
+      <c r="A99" s="66"/>
+      <c r="B99" s="90"/>
+      <c r="C99" s="91"/>
+      <c r="D99" s="91"/>
+      <c r="E99" s="91"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="91"/>
+      <c r="H99" s="91"/>
+      <c r="I99" s="91"/>
+      <c r="J99" s="92"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="64"/>
-      <c r="B100" s="98"/>
-      <c r="C100" s="99"/>
-      <c r="D100" s="99"/>
-      <c r="E100" s="99"/>
-      <c r="F100" s="99"/>
-      <c r="G100" s="99"/>
-      <c r="H100" s="99"/>
-      <c r="I100" s="99"/>
-      <c r="J100" s="100"/>
+      <c r="A100" s="66"/>
+      <c r="B100" s="90"/>
+      <c r="C100" s="91"/>
+      <c r="D100" s="91"/>
+      <c r="E100" s="91"/>
+      <c r="F100" s="91"/>
+      <c r="G100" s="91"/>
+      <c r="H100" s="91"/>
+      <c r="I100" s="91"/>
+      <c r="J100" s="92"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="64"/>
-      <c r="B101" s="98"/>
-      <c r="C101" s="99"/>
-      <c r="D101" s="99"/>
-      <c r="E101" s="99"/>
-      <c r="F101" s="99"/>
-      <c r="G101" s="99"/>
-      <c r="H101" s="99"/>
-      <c r="I101" s="99"/>
-      <c r="J101" s="100"/>
+      <c r="A101" s="66"/>
+      <c r="B101" s="90"/>
+      <c r="C101" s="91"/>
+      <c r="D101" s="91"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
+      <c r="G101" s="91"/>
+      <c r="H101" s="91"/>
+      <c r="I101" s="91"/>
+      <c r="J101" s="92"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="64"/>
-      <c r="B102" s="98"/>
-      <c r="C102" s="99"/>
-      <c r="D102" s="99"/>
-      <c r="E102" s="99"/>
-      <c r="F102" s="99"/>
-      <c r="G102" s="99"/>
-      <c r="H102" s="99"/>
-      <c r="I102" s="99"/>
-      <c r="J102" s="100"/>
+      <c r="A102" s="66"/>
+      <c r="B102" s="90"/>
+      <c r="C102" s="91"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
+      <c r="H102" s="91"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="92"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="64"/>
-      <c r="B103" s="98"/>
-      <c r="C103" s="99"/>
-      <c r="D103" s="99"/>
-      <c r="E103" s="99"/>
-      <c r="F103" s="99"/>
-      <c r="G103" s="99"/>
-      <c r="H103" s="99"/>
-      <c r="I103" s="99"/>
-      <c r="J103" s="100"/>
+      <c r="A103" s="66"/>
+      <c r="B103" s="90"/>
+      <c r="C103" s="91"/>
+      <c r="D103" s="91"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="91"/>
+      <c r="G103" s="91"/>
+      <c r="H103" s="91"/>
+      <c r="I103" s="91"/>
+      <c r="J103" s="92"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="64"/>
-      <c r="B104" s="98"/>
-      <c r="C104" s="99"/>
-      <c r="D104" s="99"/>
-      <c r="E104" s="99"/>
-      <c r="F104" s="99"/>
-      <c r="G104" s="99"/>
-      <c r="H104" s="99"/>
-      <c r="I104" s="99"/>
-      <c r="J104" s="100"/>
+      <c r="A104" s="66"/>
+      <c r="B104" s="90"/>
+      <c r="C104" s="91"/>
+      <c r="D104" s="91"/>
+      <c r="E104" s="91"/>
+      <c r="F104" s="91"/>
+      <c r="G104" s="91"/>
+      <c r="H104" s="91"/>
+      <c r="I104" s="91"/>
+      <c r="J104" s="92"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="64"/>
-      <c r="B105" s="98"/>
-      <c r="C105" s="99"/>
-      <c r="D105" s="99"/>
-      <c r="E105" s="99"/>
-      <c r="F105" s="99"/>
-      <c r="G105" s="99"/>
-      <c r="H105" s="99"/>
-      <c r="I105" s="99"/>
-      <c r="J105" s="100"/>
+      <c r="A105" s="66"/>
+      <c r="B105" s="90"/>
+      <c r="C105" s="91"/>
+      <c r="D105" s="91"/>
+      <c r="E105" s="91"/>
+      <c r="F105" s="91"/>
+      <c r="G105" s="91"/>
+      <c r="H105" s="91"/>
+      <c r="I105" s="91"/>
+      <c r="J105" s="92"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="64"/>
-      <c r="B106" s="98"/>
-      <c r="C106" s="99"/>
-      <c r="D106" s="99"/>
-      <c r="E106" s="99"/>
-      <c r="F106" s="99"/>
-      <c r="G106" s="99"/>
-      <c r="H106" s="99"/>
-      <c r="I106" s="99"/>
-      <c r="J106" s="100"/>
+      <c r="A106" s="66"/>
+      <c r="B106" s="90"/>
+      <c r="C106" s="91"/>
+      <c r="D106" s="91"/>
+      <c r="E106" s="91"/>
+      <c r="F106" s="91"/>
+      <c r="G106" s="91"/>
+      <c r="H106" s="91"/>
+      <c r="I106" s="91"/>
+      <c r="J106" s="92"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="65"/>
-      <c r="B107" s="112"/>
-      <c r="C107" s="113"/>
-      <c r="D107" s="113"/>
-      <c r="E107" s="113"/>
-      <c r="F107" s="113"/>
-      <c r="G107" s="113"/>
-      <c r="H107" s="113"/>
-      <c r="I107" s="113"/>
-      <c r="J107" s="114"/>
+      <c r="A107" s="67"/>
+      <c r="B107" s="93"/>
+      <c r="C107" s="94"/>
+      <c r="D107" s="94"/>
+      <c r="E107" s="94"/>
+      <c r="F107" s="94"/>
+      <c r="G107" s="94"/>
+      <c r="H107" s="94"/>
+      <c r="I107" s="94"/>
+      <c r="J107" s="95"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="63">
+      <c r="A108" s="64">
         <v>7</v>
       </c>
-      <c r="B108" s="70" t="s">
+      <c r="B108" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="70"/>
-      <c r="D108" s="70"/>
-      <c r="E108" s="70"/>
-      <c r="F108" s="70"/>
-      <c r="G108" s="70"/>
-      <c r="H108" s="70"/>
-      <c r="I108" s="70"/>
-      <c r="J108" s="101"/>
+      <c r="C108" s="68"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
+      <c r="H108" s="68"/>
+      <c r="I108" s="68"/>
+      <c r="J108" s="69"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="67"/>
-      <c r="B109" s="108" t="s">
+      <c r="A109" s="65"/>
+      <c r="B109" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="108"/>
-      <c r="D109" s="108"/>
-      <c r="E109" s="108"/>
-      <c r="F109" s="108"/>
-      <c r="G109" s="108"/>
-      <c r="H109" s="108"/>
-      <c r="I109" s="108"/>
-      <c r="J109" s="109"/>
+      <c r="C109" s="77"/>
+      <c r="D109" s="77"/>
+      <c r="E109" s="77"/>
+      <c r="F109" s="77"/>
+      <c r="G109" s="77"/>
+      <c r="H109" s="77"/>
+      <c r="I109" s="77"/>
+      <c r="J109" s="78"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="63">
+      <c r="A110" s="64">
         <v>8</v>
       </c>
-      <c r="B110" s="70" t="s">
+      <c r="B110" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="70"/>
-      <c r="D110" s="70"/>
-      <c r="E110" s="70"/>
-      <c r="F110" s="70"/>
-      <c r="G110" s="70"/>
-      <c r="H110" s="70"/>
-      <c r="I110" s="70"/>
-      <c r="J110" s="101"/>
+      <c r="C110" s="68"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="68"/>
+      <c r="F110" s="68"/>
+      <c r="G110" s="68"/>
+      <c r="H110" s="68"/>
+      <c r="I110" s="68"/>
+      <c r="J110" s="69"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="64"/>
-      <c r="B111" s="103" t="s">
+      <c r="A111" s="66"/>
+      <c r="B111" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="C111" s="78"/>
-      <c r="D111" s="78"/>
-      <c r="E111" s="78"/>
-      <c r="F111" s="78"/>
-      <c r="G111" s="78"/>
-      <c r="H111" s="78"/>
-      <c r="I111" s="78"/>
-      <c r="J111" s="79"/>
+      <c r="C111" s="71"/>
+      <c r="D111" s="71"/>
+      <c r="E111" s="71"/>
+      <c r="F111" s="71"/>
+      <c r="G111" s="71"/>
+      <c r="H111" s="71"/>
+      <c r="I111" s="71"/>
+      <c r="J111" s="72"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="64"/>
-      <c r="B112" s="78"/>
-      <c r="C112" s="78"/>
-      <c r="D112" s="78"/>
-      <c r="E112" s="78"/>
-      <c r="F112" s="78"/>
-      <c r="G112" s="78"/>
-      <c r="H112" s="78"/>
-      <c r="I112" s="78"/>
-      <c r="J112" s="79"/>
+      <c r="A112" s="66"/>
+      <c r="B112" s="71"/>
+      <c r="C112" s="71"/>
+      <c r="D112" s="71"/>
+      <c r="E112" s="71"/>
+      <c r="F112" s="71"/>
+      <c r="G112" s="71"/>
+      <c r="H112" s="71"/>
+      <c r="I112" s="71"/>
+      <c r="J112" s="72"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="64"/>
-      <c r="B113" s="78"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="78"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="78"/>
-      <c r="J113" s="79"/>
+      <c r="A113" s="66"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
+      <c r="G113" s="71"/>
+      <c r="H113" s="71"/>
+      <c r="I113" s="71"/>
+      <c r="J113" s="72"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="64"/>
-      <c r="B114" s="78"/>
-      <c r="C114" s="78"/>
-      <c r="D114" s="78"/>
-      <c r="E114" s="78"/>
-      <c r="F114" s="78"/>
-      <c r="G114" s="78"/>
-      <c r="H114" s="78"/>
-      <c r="I114" s="78"/>
-      <c r="J114" s="79"/>
+      <c r="A114" s="66"/>
+      <c r="B114" s="71"/>
+      <c r="C114" s="71"/>
+      <c r="D114" s="71"/>
+      <c r="E114" s="71"/>
+      <c r="F114" s="71"/>
+      <c r="G114" s="71"/>
+      <c r="H114" s="71"/>
+      <c r="I114" s="71"/>
+      <c r="J114" s="72"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="64"/>
-      <c r="B115" s="78"/>
-      <c r="C115" s="78"/>
-      <c r="D115" s="78"/>
-      <c r="E115" s="78"/>
-      <c r="F115" s="78"/>
-      <c r="G115" s="78"/>
-      <c r="H115" s="78"/>
-      <c r="I115" s="78"/>
-      <c r="J115" s="79"/>
+      <c r="A115" s="66"/>
+      <c r="B115" s="71"/>
+      <c r="C115" s="71"/>
+      <c r="D115" s="71"/>
+      <c r="E115" s="71"/>
+      <c r="F115" s="71"/>
+      <c r="G115" s="71"/>
+      <c r="H115" s="71"/>
+      <c r="I115" s="71"/>
+      <c r="J115" s="72"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="64"/>
-      <c r="B116" s="78"/>
-      <c r="C116" s="78"/>
-      <c r="D116" s="78"/>
-      <c r="E116" s="78"/>
-      <c r="F116" s="78"/>
-      <c r="G116" s="78"/>
-      <c r="H116" s="78"/>
-      <c r="I116" s="78"/>
-      <c r="J116" s="79"/>
+      <c r="A116" s="66"/>
+      <c r="B116" s="71"/>
+      <c r="C116" s="71"/>
+      <c r="D116" s="71"/>
+      <c r="E116" s="71"/>
+      <c r="F116" s="71"/>
+      <c r="G116" s="71"/>
+      <c r="H116" s="71"/>
+      <c r="I116" s="71"/>
+      <c r="J116" s="72"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="64"/>
-      <c r="B117" s="104" t="s">
+      <c r="A117" s="66"/>
+      <c r="B117" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="104"/>
-      <c r="D117" s="104"/>
-      <c r="E117" s="104"/>
-      <c r="F117" s="104"/>
-      <c r="G117" s="104"/>
-      <c r="H117" s="104"/>
-      <c r="I117" s="104"/>
-      <c r="J117" s="105"/>
+      <c r="C117" s="73"/>
+      <c r="D117" s="73"/>
+      <c r="E117" s="73"/>
+      <c r="F117" s="73"/>
+      <c r="G117" s="73"/>
+      <c r="H117" s="73"/>
+      <c r="I117" s="73"/>
+      <c r="J117" s="74"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="64"/>
-      <c r="B118" s="103" t="s">
+      <c r="A118" s="66"/>
+      <c r="B118" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="C118" s="78"/>
-      <c r="D118" s="78"/>
-      <c r="E118" s="78"/>
-      <c r="F118" s="78"/>
-      <c r="G118" s="78"/>
-      <c r="H118" s="78"/>
-      <c r="I118" s="78"/>
-      <c r="J118" s="79"/>
+      <c r="C118" s="71"/>
+      <c r="D118" s="71"/>
+      <c r="E118" s="71"/>
+      <c r="F118" s="71"/>
+      <c r="G118" s="71"/>
+      <c r="H118" s="71"/>
+      <c r="I118" s="71"/>
+      <c r="J118" s="72"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="64"/>
-      <c r="B119" s="78"/>
-      <c r="C119" s="78"/>
-      <c r="D119" s="78"/>
-      <c r="E119" s="78"/>
-      <c r="F119" s="78"/>
-      <c r="G119" s="78"/>
-      <c r="H119" s="78"/>
-      <c r="I119" s="78"/>
-      <c r="J119" s="79"/>
+      <c r="A119" s="66"/>
+      <c r="B119" s="71"/>
+      <c r="C119" s="71"/>
+      <c r="D119" s="71"/>
+      <c r="E119" s="71"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="71"/>
+      <c r="H119" s="71"/>
+      <c r="I119" s="71"/>
+      <c r="J119" s="72"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="64"/>
-      <c r="B120" s="78"/>
-      <c r="C120" s="78"/>
-      <c r="D120" s="78"/>
-      <c r="E120" s="78"/>
-      <c r="F120" s="78"/>
-      <c r="G120" s="78"/>
-      <c r="H120" s="78"/>
-      <c r="I120" s="78"/>
-      <c r="J120" s="79"/>
+      <c r="A120" s="66"/>
+      <c r="B120" s="71"/>
+      <c r="C120" s="71"/>
+      <c r="D120" s="71"/>
+      <c r="E120" s="71"/>
+      <c r="F120" s="71"/>
+      <c r="G120" s="71"/>
+      <c r="H120" s="71"/>
+      <c r="I120" s="71"/>
+      <c r="J120" s="72"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="64"/>
-      <c r="B121" s="78"/>
-      <c r="C121" s="78"/>
-      <c r="D121" s="78"/>
-      <c r="E121" s="78"/>
-      <c r="F121" s="78"/>
-      <c r="G121" s="78"/>
-      <c r="H121" s="78"/>
-      <c r="I121" s="78"/>
-      <c r="J121" s="79"/>
+      <c r="A121" s="66"/>
+      <c r="B121" s="71"/>
+      <c r="C121" s="71"/>
+      <c r="D121" s="71"/>
+      <c r="E121" s="71"/>
+      <c r="F121" s="71"/>
+      <c r="G121" s="71"/>
+      <c r="H121" s="71"/>
+      <c r="I121" s="71"/>
+      <c r="J121" s="72"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="64"/>
-      <c r="B122" s="78"/>
-      <c r="C122" s="78"/>
-      <c r="D122" s="78"/>
-      <c r="E122" s="78"/>
-      <c r="F122" s="78"/>
-      <c r="G122" s="78"/>
-      <c r="H122" s="78"/>
-      <c r="I122" s="78"/>
-      <c r="J122" s="79"/>
+      <c r="A122" s="66"/>
+      <c r="B122" s="71"/>
+      <c r="C122" s="71"/>
+      <c r="D122" s="71"/>
+      <c r="E122" s="71"/>
+      <c r="F122" s="71"/>
+      <c r="G122" s="71"/>
+      <c r="H122" s="71"/>
+      <c r="I122" s="71"/>
+      <c r="J122" s="72"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="64"/>
-      <c r="B123" s="78"/>
-      <c r="C123" s="78"/>
-      <c r="D123" s="78"/>
-      <c r="E123" s="78"/>
-      <c r="F123" s="78"/>
-      <c r="G123" s="78"/>
-      <c r="H123" s="78"/>
-      <c r="I123" s="78"/>
-      <c r="J123" s="79"/>
+      <c r="A123" s="66"/>
+      <c r="B123" s="71"/>
+      <c r="C123" s="71"/>
+      <c r="D123" s="71"/>
+      <c r="E123" s="71"/>
+      <c r="F123" s="71"/>
+      <c r="G123" s="71"/>
+      <c r="H123" s="71"/>
+      <c r="I123" s="71"/>
+      <c r="J123" s="72"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="64"/>
-      <c r="B124" s="78"/>
-      <c r="C124" s="78"/>
-      <c r="D124" s="78"/>
-      <c r="E124" s="78"/>
-      <c r="F124" s="78"/>
-      <c r="G124" s="78"/>
-      <c r="H124" s="78"/>
-      <c r="I124" s="78"/>
-      <c r="J124" s="79"/>
+      <c r="A124" s="66"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
+      <c r="G124" s="71"/>
+      <c r="H124" s="71"/>
+      <c r="I124" s="71"/>
+      <c r="J124" s="72"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="65"/>
-      <c r="B125" s="106"/>
-      <c r="C125" s="106"/>
-      <c r="D125" s="106"/>
-      <c r="E125" s="106"/>
-      <c r="F125" s="106"/>
-      <c r="G125" s="106"/>
-      <c r="H125" s="106"/>
-      <c r="I125" s="106"/>
-      <c r="J125" s="107"/>
+      <c r="A125" s="67"/>
+      <c r="B125" s="75"/>
+      <c r="C125" s="75"/>
+      <c r="D125" s="75"/>
+      <c r="E125" s="75"/>
+      <c r="F125" s="75"/>
+      <c r="G125" s="75"/>
+      <c r="H125" s="75"/>
+      <c r="I125" s="75"/>
+      <c r="J125" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="B69:J86"/>
+    <mergeCell ref="A63:A86"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="B5:J7"/>
+    <mergeCell ref="B22:J25"/>
+    <mergeCell ref="B26:J62"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B8:J20"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="A110:A125"/>
@@ -6198,29 +6228,6 @@
     <mergeCell ref="B87:J87"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B93:J107"/>
-    <mergeCell ref="B69:J86"/>
-    <mergeCell ref="A63:A86"/>
-    <mergeCell ref="D64:J64"/>
-    <mergeCell ref="B5:J7"/>
-    <mergeCell ref="B22:J25"/>
-    <mergeCell ref="B26:J62"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B8:J20"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D66:J66"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D65:J65"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6251,71 +6258,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="45"/>
-      <c r="H6" s="48" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="58" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6325,16 +6332,16 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="49"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="59"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>1</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="60" t="s">
         <v>161</v>
       </c>
       <c r="C8" s="34" t="s">
@@ -6346,18 +6353,18 @@
       <c r="E8" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="54"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="37">
         <v>2</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="50" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="60" t="s">
         <v>160</v>
       </c>
       <c r="D9" s="35" t="s">
@@ -6366,74 +6373,74 @@
       <c r="E9" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="G9" s="54"/>
+      <c r="G9" s="39"/>
       <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
       <c r="D10" s="35" t="s">
         <v>165</v>
       </c>
       <c r="E10" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>4</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
       <c r="D11" s="35" t="s">
         <v>166</v>
       </c>
       <c r="E11" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="G11" s="54"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>5</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
       <c r="D12" s="35" t="s">
         <v>167</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="G12" s="54"/>
+      <c r="G12" s="39"/>
       <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37">
         <v>6</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="41" t="s">
         <v>173</v>
       </c>
       <c r="D13" s="27" t="s">
@@ -6442,35 +6449,35 @@
       <c r="E13" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="39"/>
+      <c r="G13" s="44"/>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="37">
         <v>7</v>
       </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="59"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="27" t="s">
         <v>173</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="39"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <v>8</v>
       </c>
-      <c r="B15" s="58"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="27" t="s">
         <v>71</v>
       </c>
@@ -6480,17 +6487,17 @@
       <c r="E15" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="39"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <v>9</v>
       </c>
-      <c r="B16" s="58"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="27" t="s">
         <v>73</v>
       </c>
@@ -6500,18 +6507,18 @@
       <c r="E16" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="39"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <v>10</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="57" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="40" t="s">
         <v>75</v>
       </c>
       <c r="D17" s="27" t="s">
@@ -6520,36 +6527,36 @@
       <c r="E17" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="39"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <v>11</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="60"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="27" t="s">
         <v>77</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="39"/>
+      <c r="G18" s="44"/>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <v>12</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="62" t="s">
+      <c r="B19" s="41"/>
+      <c r="C19" s="47" t="s">
         <v>150</v>
       </c>
       <c r="D19" s="27" t="s">
@@ -6558,71 +6565,71 @@
       <c r="E19" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="F19" s="55" t="s">
+      <c r="F19" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="56"/>
+      <c r="G19" s="49"/>
       <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <v>13</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="61"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="46"/>
       <c r="D20" s="27" t="s">
         <v>153</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="39"/>
+      <c r="G20" s="44"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <v>14</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="61"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="46"/>
       <c r="D21" s="27" t="s">
         <v>155</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="56"/>
+      <c r="G21" s="49"/>
       <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <v>15</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="60"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="27" t="s">
         <v>156</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="G22" s="56"/>
+      <c r="G22" s="49"/>
       <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <v>16</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="40" t="s">
         <v>78</v>
       </c>
       <c r="C23" s="27" t="s">
@@ -6634,17 +6641,17 @@
       <c r="E23" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="38" t="s">
+      <c r="F23" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="39"/>
+      <c r="G23" s="44"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <v>17</v>
       </c>
-      <c r="B24" s="61"/>
+      <c r="B24" s="46"/>
       <c r="C24" s="27" t="s">
         <v>81</v>
       </c>
@@ -6654,17 +6661,17 @@
       <c r="E24" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="39"/>
+      <c r="G24" s="44"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <v>18</v>
       </c>
-      <c r="B25" s="60"/>
+      <c r="B25" s="45"/>
       <c r="C25" s="27" t="s">
         <v>83</v>
       </c>
@@ -6674,20 +6681,20 @@
       <c r="E25" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="39"/>
+      <c r="G25" s="44"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <v>19</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="40" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="27" t="s">
@@ -6696,28 +6703,28 @@
       <c r="E26" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="39"/>
+      <c r="G26" s="44"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <v>20</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="27" t="s">
         <v>88</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="38" t="s">
+      <c r="F27" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="G27" s="39"/>
+      <c r="G27" s="44"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6728,8 +6735,8 @@
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="44"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6740,8 +6747,8 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="39"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6752,8 +6759,8 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="39"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="44"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6764,8 +6771,8 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="39"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6776,8 +6783,8 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="39"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="44"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6788,8 +6795,8 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="39"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="44"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6800,8 +6807,8 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="39"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="44"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6812,8 +6819,8 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="39"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="44"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6824,8 +6831,8 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="39"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="44"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6836,8 +6843,8 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="44"/>
       <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6848,8 +6855,8 @@
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="44"/>
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6860,12 +6867,45 @@
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="39"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="44"/>
       <c r="H39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="B13:B22"/>
     <mergeCell ref="F39:G39"/>
@@ -6882,39 +6922,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6941,72 +6948,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="42" t="s">
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="42"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="52"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
@@ -7018,381 +7025,381 @@
       <c r="C7" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="118"/>
+      <c r="B8" s="116"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="118"/>
+      <c r="B9" s="116"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="116"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="117" t="s">
+      <c r="B11" s="118" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="71" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="78" t="s">
+      <c r="B12" s="116"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="118"/>
+      <c r="B13" s="116"/>
       <c r="C13" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="103" t="s">
+      <c r="D13" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="116"/>
+      <c r="B14" s="117"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="118" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="78" t="s">
+      <c r="D15" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="118"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="118"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="116"/>
+      <c r="B18" s="117"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="118" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="78" t="s">
+      <c r="D19" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="118"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="118"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="116"/>
+      <c r="B22" s="117"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="118" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="78" t="s">
+      <c r="D23" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="122"/>
+      <c r="B24" s="119"/>
       <c r="C24" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="78" t="s">
+      <c r="D24" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="122"/>
+      <c r="B25" s="119"/>
       <c r="C25" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="122"/>
+      <c r="B26" s="119"/>
       <c r="C26" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="103" t="s">
+      <c r="D26" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="123"/>
+      <c r="B27" s="120"/>
       <c r="C27" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="124" t="s">
+      <c r="D27" s="121" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="125"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="126"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="123"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="117" t="s">
+      <c r="B28" s="118" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="118"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="118"/>
+      <c r="B30" s="116"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="116"/>
+      <c r="B31" s="117"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7401,11 +7408,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7414,11 +7421,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7427,11 +7434,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7440,11 +7447,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7453,11 +7460,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7466,15 +7473,45 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B28:B31"/>
@@ -7491,36 +7528,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:H6"/>
     <mergeCell ref="D9:H9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -7544,23 +7551,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="214" t="s">
+      <c r="B1" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-      <c r="M1" s="215"/>
-      <c r="N1" s="215"/>
-      <c r="O1" s="215"/>
-      <c r="P1" s="215"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7577,141 +7584,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="208" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="163"/>
-      <c r="D2" s="163"/>
-      <c r="E2" s="163"/>
-      <c r="F2" s="163"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="163"/>
-      <c r="I2" s="163"/>
-      <c r="J2" s="167" t="s">
+      <c r="C2" s="208"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="167"/>
-      <c r="L2" s="167"/>
-      <c r="M2" s="167"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="167"/>
-      <c r="Q2" s="167"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="167"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="167"/>
-      <c r="AA2" s="167"/>
-      <c r="AB2" s="167"/>
-      <c r="AC2" s="167"/>
-      <c r="AD2" s="167"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="137"/>
+      <c r="W2" s="137"/>
+      <c r="X2" s="137"/>
+      <c r="Y2" s="137"/>
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="137"/>
+      <c r="AD2" s="137"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="161"/>
-      <c r="P4" s="161"/>
-      <c r="Q4" s="168" t="s">
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="206"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="172"/>
-      <c r="S4" s="169"/>
-      <c r="T4" s="168" t="s">
+      <c r="R4" s="214"/>
+      <c r="S4" s="211"/>
+      <c r="T4" s="210" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="172"/>
-      <c r="V4" s="172"/>
-      <c r="W4" s="169"/>
-      <c r="X4" s="168" t="s">
+      <c r="U4" s="214"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="211"/>
+      <c r="X4" s="210" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="169"/>
-      <c r="Z4" s="161" t="s">
+      <c r="Y4" s="211"/>
+      <c r="Z4" s="206" t="s">
         <v>132</v>
       </c>
-      <c r="AA4" s="161"/>
-      <c r="AB4" s="161"/>
-      <c r="AC4" s="161" t="s">
+      <c r="AA4" s="206"/>
+      <c r="AB4" s="206"/>
+      <c r="AC4" s="206" t="s">
         <v>133</v>
       </c>
-      <c r="AD4" s="161"/>
-      <c r="AE4" s="161"/>
-      <c r="AF4" s="161" t="s">
+      <c r="AD4" s="206"/>
+      <c r="AE4" s="206"/>
+      <c r="AF4" s="206" t="s">
         <v>134</v>
       </c>
-      <c r="AG4" s="161"/>
-      <c r="AH4" s="161"/>
-      <c r="AI4" s="161" t="s">
+      <c r="AG4" s="206"/>
+      <c r="AH4" s="206"/>
+      <c r="AI4" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="161"/>
-      <c r="AK4" s="161"/>
-      <c r="AL4" s="161" t="s">
+      <c r="AJ4" s="206"/>
+      <c r="AK4" s="206"/>
+      <c r="AL4" s="206" t="s">
         <v>136</v>
       </c>
-      <c r="AM4" s="161"/>
-      <c r="AN4" s="161"/>
-      <c r="AO4" s="161" t="s">
+      <c r="AM4" s="206"/>
+      <c r="AN4" s="206"/>
+      <c r="AO4" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="161"/>
-      <c r="AQ4" s="161"/>
-      <c r="AR4" s="161"/>
-      <c r="AS4" s="161"/>
-      <c r="AT4" s="161"/>
-      <c r="AU4" s="161"/>
-      <c r="AV4" s="161"/>
-      <c r="AW4" s="161"/>
-      <c r="AX4" s="161"/>
-      <c r="AY4" s="161"/>
-      <c r="AZ4" s="162"/>
+      <c r="AP4" s="206"/>
+      <c r="AQ4" s="206"/>
+      <c r="AR4" s="206"/>
+      <c r="AS4" s="206"/>
+      <c r="AT4" s="206"/>
+      <c r="AU4" s="206"/>
+      <c r="AV4" s="206"/>
+      <c r="AW4" s="206"/>
+      <c r="AX4" s="206"/>
+      <c r="AY4" s="206"/>
+      <c r="AZ4" s="207"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="175"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="163"/>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
-      <c r="J5" s="163"/>
-      <c r="K5" s="163"/>
-      <c r="L5" s="163"/>
-      <c r="M5" s="163"/>
-      <c r="N5" s="163"/>
-      <c r="O5" s="163"/>
-      <c r="P5" s="163"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="173"/>
-      <c r="S5" s="171"/>
-      <c r="T5" s="170"/>
-      <c r="U5" s="173"/>
-      <c r="V5" s="173"/>
-      <c r="W5" s="171"/>
-      <c r="X5" s="170"/>
-      <c r="Y5" s="171"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="M5" s="208"/>
+      <c r="N5" s="208"/>
+      <c r="O5" s="208"/>
+      <c r="P5" s="208"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="213"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="213"/>
+      <c r="X5" s="212"/>
+      <c r="Y5" s="213"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7757,58 +7764,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="163"/>
-      <c r="AP5" s="163"/>
-      <c r="AQ5" s="163"/>
-      <c r="AR5" s="163"/>
-      <c r="AS5" s="163"/>
-      <c r="AT5" s="163"/>
-      <c r="AU5" s="163"/>
-      <c r="AV5" s="163"/>
-      <c r="AW5" s="163"/>
-      <c r="AX5" s="163"/>
-      <c r="AY5" s="163"/>
-      <c r="AZ5" s="164"/>
+      <c r="AO5" s="208"/>
+      <c r="AP5" s="208"/>
+      <c r="AQ5" s="208"/>
+      <c r="AR5" s="208"/>
+      <c r="AS5" s="208"/>
+      <c r="AT5" s="208"/>
+      <c r="AU5" s="208"/>
+      <c r="AV5" s="208"/>
+      <c r="AW5" s="208"/>
+      <c r="AX5" s="208"/>
+      <c r="AY5" s="208"/>
+      <c r="AZ5" s="209"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="190">
+      <c r="B6" s="133">
         <v>1</v>
       </c>
-      <c r="C6" s="176" t="s">
+      <c r="C6" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="176" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="176"/>
-      <c r="L6" s="176"/>
-      <c r="M6" s="176"/>
-      <c r="N6" s="176"/>
-      <c r="O6" s="176"/>
-      <c r="P6" s="176"/>
-      <c r="Q6" s="167" t="s">
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="R6" s="167"/>
-      <c r="S6" s="167"/>
-      <c r="T6" s="181" t="s">
+      <c r="R6" s="137"/>
+      <c r="S6" s="137"/>
+      <c r="T6" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="181"/>
-      <c r="V6" s="179">
+      <c r="U6" s="134"/>
+      <c r="V6" s="131">
         <v>0</v>
       </c>
-      <c r="W6" s="179"/>
-      <c r="X6" s="165">
+      <c r="W6" s="131"/>
+      <c r="X6" s="153">
         <v>0</v>
       </c>
-      <c r="Y6" s="165"/>
+      <c r="Y6" s="153"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7824,50 +7831,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="176"/>
-      <c r="AP6" s="176"/>
-      <c r="AQ6" s="176"/>
-      <c r="AR6" s="176"/>
-      <c r="AS6" s="176"/>
-      <c r="AT6" s="176"/>
-      <c r="AU6" s="176"/>
-      <c r="AV6" s="176"/>
-      <c r="AW6" s="176"/>
-      <c r="AX6" s="176"/>
-      <c r="AY6" s="176"/>
-      <c r="AZ6" s="177"/>
+      <c r="AO6" s="130"/>
+      <c r="AP6" s="130"/>
+      <c r="AQ6" s="130"/>
+      <c r="AR6" s="130"/>
+      <c r="AS6" s="130"/>
+      <c r="AT6" s="130"/>
+      <c r="AU6" s="130"/>
+      <c r="AV6" s="130"/>
+      <c r="AW6" s="130"/>
+      <c r="AX6" s="130"/>
+      <c r="AY6" s="130"/>
+      <c r="AZ6" s="152"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="190"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
-      <c r="P7" s="176"/>
-      <c r="Q7" s="167"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
-      <c r="T7" s="178" t="s">
+      <c r="B7" s="133"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="137"/>
+      <c r="T7" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="178"/>
-      <c r="V7" s="180">
+      <c r="U7" s="135"/>
+      <c r="V7" s="132">
         <v>0</v>
       </c>
-      <c r="W7" s="180"/>
-      <c r="X7" s="166">
+      <c r="W7" s="132"/>
+      <c r="X7" s="154">
         <v>1</v>
       </c>
-      <c r="Y7" s="166"/>
+      <c r="Y7" s="154"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7883,58 +7890,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="176"/>
-      <c r="AP7" s="176"/>
-      <c r="AQ7" s="176"/>
-      <c r="AR7" s="176"/>
-      <c r="AS7" s="176"/>
-      <c r="AT7" s="176"/>
-      <c r="AU7" s="176"/>
-      <c r="AV7" s="176"/>
-      <c r="AW7" s="176"/>
-      <c r="AX7" s="176"/>
-      <c r="AY7" s="176"/>
-      <c r="AZ7" s="177"/>
+      <c r="AO7" s="130"/>
+      <c r="AP7" s="130"/>
+      <c r="AQ7" s="130"/>
+      <c r="AR7" s="130"/>
+      <c r="AS7" s="130"/>
+      <c r="AT7" s="130"/>
+      <c r="AU7" s="130"/>
+      <c r="AV7" s="130"/>
+      <c r="AW7" s="130"/>
+      <c r="AX7" s="130"/>
+      <c r="AY7" s="130"/>
+      <c r="AZ7" s="152"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="190">
+      <c r="B8" s="133">
         <v>2</v>
       </c>
-      <c r="C8" s="176" t="s">
+      <c r="C8" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="176"/>
-      <c r="E8" s="176"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="152" t="s">
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="135"/>
-      <c r="O8" s="135"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="217" t="s">
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="136" t="s">
         <v>130</v>
       </c>
-      <c r="R8" s="217"/>
-      <c r="S8" s="217"/>
-      <c r="T8" s="181" t="s">
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="181"/>
-      <c r="V8" s="179">
+      <c r="U8" s="134"/>
+      <c r="V8" s="131">
         <v>0</v>
       </c>
-      <c r="W8" s="179"/>
-      <c r="X8" s="165">
+      <c r="W8" s="131"/>
+      <c r="X8" s="153">
         <v>0</v>
       </c>
-      <c r="Y8" s="165"/>
+      <c r="Y8" s="153"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7950,50 +7957,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="176"/>
-      <c r="AP8" s="176"/>
-      <c r="AQ8" s="176"/>
-      <c r="AR8" s="176"/>
-      <c r="AS8" s="176"/>
-      <c r="AT8" s="176"/>
-      <c r="AU8" s="176"/>
-      <c r="AV8" s="176"/>
-      <c r="AW8" s="176"/>
-      <c r="AX8" s="176"/>
-      <c r="AY8" s="176"/>
-      <c r="AZ8" s="177"/>
+      <c r="AO8" s="130"/>
+      <c r="AP8" s="130"/>
+      <c r="AQ8" s="130"/>
+      <c r="AR8" s="130"/>
+      <c r="AS8" s="130"/>
+      <c r="AT8" s="130"/>
+      <c r="AU8" s="130"/>
+      <c r="AV8" s="130"/>
+      <c r="AW8" s="130"/>
+      <c r="AX8" s="130"/>
+      <c r="AY8" s="130"/>
+      <c r="AZ8" s="152"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="190"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="176"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
-      <c r="N9" s="138"/>
-      <c r="O9" s="138"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="217"/>
-      <c r="R9" s="217"/>
-      <c r="S9" s="217"/>
-      <c r="T9" s="178" t="s">
+      <c r="B9" s="133"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="142"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="142"/>
+      <c r="N9" s="142"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="143"/>
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="136"/>
+      <c r="T9" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="178"/>
-      <c r="V9" s="180">
+      <c r="U9" s="135"/>
+      <c r="V9" s="132">
         <v>0</v>
       </c>
-      <c r="W9" s="180"/>
-      <c r="X9" s="166">
+      <c r="W9" s="132"/>
+      <c r="X9" s="154">
         <v>1</v>
       </c>
-      <c r="Y9" s="166"/>
+      <c r="Y9" s="154"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -8009,58 +8016,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="176"/>
-      <c r="AP9" s="176"/>
-      <c r="AQ9" s="176"/>
-      <c r="AR9" s="176"/>
-      <c r="AS9" s="176"/>
-      <c r="AT9" s="176"/>
-      <c r="AU9" s="176"/>
-      <c r="AV9" s="176"/>
-      <c r="AW9" s="176"/>
-      <c r="AX9" s="176"/>
-      <c r="AY9" s="176"/>
-      <c r="AZ9" s="177"/>
+      <c r="AO9" s="130"/>
+      <c r="AP9" s="130"/>
+      <c r="AQ9" s="130"/>
+      <c r="AR9" s="130"/>
+      <c r="AS9" s="130"/>
+      <c r="AT9" s="130"/>
+      <c r="AU9" s="130"/>
+      <c r="AV9" s="130"/>
+      <c r="AW9" s="130"/>
+      <c r="AX9" s="130"/>
+      <c r="AY9" s="130"/>
+      <c r="AZ9" s="152"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="190">
+      <c r="B10" s="133">
         <v>3</v>
       </c>
-      <c r="C10" s="176" t="s">
+      <c r="C10" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="216" t="s">
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="129" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="176"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="176"/>
-      <c r="N10" s="176"/>
-      <c r="O10" s="176"/>
-      <c r="P10" s="176"/>
-      <c r="Q10" s="167" t="s">
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="130"/>
+      <c r="O10" s="130"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="R10" s="167"/>
-      <c r="S10" s="167"/>
-      <c r="T10" s="181" t="s">
+      <c r="R10" s="137"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="181"/>
-      <c r="V10" s="179">
+      <c r="U10" s="134"/>
+      <c r="V10" s="131">
         <v>0</v>
       </c>
-      <c r="W10" s="179"/>
-      <c r="X10" s="165">
+      <c r="W10" s="131"/>
+      <c r="X10" s="153">
         <v>0</v>
       </c>
-      <c r="Y10" s="165"/>
+      <c r="Y10" s="153"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -8076,50 +8083,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="176"/>
-      <c r="AP10" s="176"/>
-      <c r="AQ10" s="176"/>
-      <c r="AR10" s="176"/>
-      <c r="AS10" s="176"/>
-      <c r="AT10" s="176"/>
-      <c r="AU10" s="176"/>
-      <c r="AV10" s="176"/>
-      <c r="AW10" s="176"/>
-      <c r="AX10" s="176"/>
-      <c r="AY10" s="176"/>
-      <c r="AZ10" s="177"/>
+      <c r="AO10" s="130"/>
+      <c r="AP10" s="130"/>
+      <c r="AQ10" s="130"/>
+      <c r="AR10" s="130"/>
+      <c r="AS10" s="130"/>
+      <c r="AT10" s="130"/>
+      <c r="AU10" s="130"/>
+      <c r="AV10" s="130"/>
+      <c r="AW10" s="130"/>
+      <c r="AX10" s="130"/>
+      <c r="AY10" s="130"/>
+      <c r="AZ10" s="152"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="190"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="176"/>
-      <c r="M11" s="176"/>
-      <c r="N11" s="176"/>
-      <c r="O11" s="176"/>
-      <c r="P11" s="176"/>
-      <c r="Q11" s="167"/>
-      <c r="R11" s="167"/>
-      <c r="S11" s="167"/>
-      <c r="T11" s="178" t="s">
+      <c r="B11" s="133"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+      <c r="N11" s="130"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="178"/>
-      <c r="V11" s="180">
+      <c r="U11" s="135"/>
+      <c r="V11" s="132">
         <v>0</v>
       </c>
-      <c r="W11" s="180"/>
-      <c r="X11" s="166">
+      <c r="W11" s="132"/>
+      <c r="X11" s="154">
         <v>0</v>
       </c>
-      <c r="Y11" s="166"/>
+      <c r="Y11" s="154"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -8135,58 +8142,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="176"/>
-      <c r="AP11" s="176"/>
-      <c r="AQ11" s="176"/>
-      <c r="AR11" s="176"/>
-      <c r="AS11" s="176"/>
-      <c r="AT11" s="176"/>
-      <c r="AU11" s="176"/>
-      <c r="AV11" s="176"/>
-      <c r="AW11" s="176"/>
-      <c r="AX11" s="176"/>
-      <c r="AY11" s="176"/>
-      <c r="AZ11" s="177"/>
+      <c r="AO11" s="130"/>
+      <c r="AP11" s="130"/>
+      <c r="AQ11" s="130"/>
+      <c r="AR11" s="130"/>
+      <c r="AS11" s="130"/>
+      <c r="AT11" s="130"/>
+      <c r="AU11" s="130"/>
+      <c r="AV11" s="130"/>
+      <c r="AW11" s="130"/>
+      <c r="AX11" s="130"/>
+      <c r="AY11" s="130"/>
+      <c r="AZ11" s="152"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="190">
+      <c r="B12" s="133">
         <v>4</v>
       </c>
-      <c r="C12" s="176" t="s">
+      <c r="C12" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="176" t="s">
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="K12" s="176"/>
-      <c r="L12" s="176"/>
-      <c r="M12" s="176"/>
-      <c r="N12" s="176"/>
-      <c r="O12" s="176"/>
-      <c r="P12" s="176"/>
-      <c r="Q12" s="140" t="s">
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="130"/>
+      <c r="N12" s="130"/>
+      <c r="O12" s="130"/>
+      <c r="P12" s="130"/>
+      <c r="Q12" s="196" t="s">
         <v>128</v>
       </c>
-      <c r="R12" s="141"/>
-      <c r="S12" s="142"/>
-      <c r="T12" s="181" t="s">
+      <c r="R12" s="197"/>
+      <c r="S12" s="198"/>
+      <c r="T12" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="181"/>
-      <c r="V12" s="179">
+      <c r="U12" s="134"/>
+      <c r="V12" s="131">
         <v>0</v>
       </c>
-      <c r="W12" s="179"/>
-      <c r="X12" s="165">
+      <c r="W12" s="131"/>
+      <c r="X12" s="153">
         <v>0</v>
       </c>
-      <c r="Y12" s="165"/>
+      <c r="Y12" s="153"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -8202,50 +8209,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="176"/>
-      <c r="AP12" s="176"/>
-      <c r="AQ12" s="176"/>
-      <c r="AR12" s="176"/>
-      <c r="AS12" s="176"/>
-      <c r="AT12" s="176"/>
-      <c r="AU12" s="176"/>
-      <c r="AV12" s="176"/>
-      <c r="AW12" s="176"/>
-      <c r="AX12" s="176"/>
-      <c r="AY12" s="176"/>
-      <c r="AZ12" s="177"/>
+      <c r="AO12" s="130"/>
+      <c r="AP12" s="130"/>
+      <c r="AQ12" s="130"/>
+      <c r="AR12" s="130"/>
+      <c r="AS12" s="130"/>
+      <c r="AT12" s="130"/>
+      <c r="AU12" s="130"/>
+      <c r="AV12" s="130"/>
+      <c r="AW12" s="130"/>
+      <c r="AX12" s="130"/>
+      <c r="AY12" s="130"/>
+      <c r="AZ12" s="152"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="190"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="176"/>
-      <c r="K13" s="176"/>
-      <c r="L13" s="176"/>
-      <c r="M13" s="176"/>
-      <c r="N13" s="176"/>
-      <c r="O13" s="176"/>
-      <c r="P13" s="176"/>
-      <c r="Q13" s="143"/>
-      <c r="R13" s="144"/>
-      <c r="S13" s="145"/>
-      <c r="T13" s="178" t="s">
+      <c r="B13" s="133"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="199"/>
+      <c r="R13" s="200"/>
+      <c r="S13" s="201"/>
+      <c r="T13" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="178"/>
-      <c r="V13" s="180">
+      <c r="U13" s="135"/>
+      <c r="V13" s="132">
         <v>0</v>
       </c>
-      <c r="W13" s="180"/>
-      <c r="X13" s="166">
+      <c r="W13" s="132"/>
+      <c r="X13" s="154">
         <v>0</v>
       </c>
-      <c r="Y13" s="166"/>
+      <c r="Y13" s="154"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8261,54 +8268,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="176"/>
-      <c r="AP13" s="176"/>
-      <c r="AQ13" s="176"/>
-      <c r="AR13" s="176"/>
-      <c r="AS13" s="176"/>
-      <c r="AT13" s="176"/>
-      <c r="AU13" s="176"/>
-      <c r="AV13" s="176"/>
-      <c r="AW13" s="176"/>
-      <c r="AX13" s="176"/>
-      <c r="AY13" s="176"/>
-      <c r="AZ13" s="177"/>
+      <c r="AO13" s="130"/>
+      <c r="AP13" s="130"/>
+      <c r="AQ13" s="130"/>
+      <c r="AR13" s="130"/>
+      <c r="AS13" s="130"/>
+      <c r="AT13" s="130"/>
+      <c r="AU13" s="130"/>
+      <c r="AV13" s="130"/>
+      <c r="AW13" s="130"/>
+      <c r="AX13" s="130"/>
+      <c r="AY13" s="130"/>
+      <c r="AZ13" s="152"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="190">
+      <c r="B14" s="133">
         <v>5</v>
       </c>
-      <c r="C14" s="152" t="s">
+      <c r="C14" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="216"/>
-      <c r="K14" s="176"/>
-      <c r="L14" s="176"/>
-      <c r="M14" s="176"/>
-      <c r="N14" s="176"/>
-      <c r="O14" s="176"/>
-      <c r="P14" s="176"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="141"/>
-      <c r="S14" s="142"/>
-      <c r="T14" s="181" t="s">
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="196"/>
+      <c r="R14" s="197"/>
+      <c r="S14" s="198"/>
+      <c r="T14" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="181"/>
-      <c r="V14" s="179">
+      <c r="U14" s="134"/>
+      <c r="V14" s="131">
         <v>0</v>
       </c>
-      <c r="W14" s="179"/>
-      <c r="X14" s="165">
+      <c r="W14" s="131"/>
+      <c r="X14" s="153">
         <v>0</v>
       </c>
-      <c r="Y14" s="165"/>
+      <c r="Y14" s="153"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8324,50 +8331,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="176"/>
-      <c r="AP14" s="176"/>
-      <c r="AQ14" s="176"/>
-      <c r="AR14" s="176"/>
-      <c r="AS14" s="176"/>
-      <c r="AT14" s="176"/>
-      <c r="AU14" s="176"/>
-      <c r="AV14" s="176"/>
-      <c r="AW14" s="176"/>
-      <c r="AX14" s="176"/>
-      <c r="AY14" s="176"/>
-      <c r="AZ14" s="177"/>
+      <c r="AO14" s="130"/>
+      <c r="AP14" s="130"/>
+      <c r="AQ14" s="130"/>
+      <c r="AR14" s="130"/>
+      <c r="AS14" s="130"/>
+      <c r="AT14" s="130"/>
+      <c r="AU14" s="130"/>
+      <c r="AV14" s="130"/>
+      <c r="AW14" s="130"/>
+      <c r="AX14" s="130"/>
+      <c r="AY14" s="130"/>
+      <c r="AZ14" s="152"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="190"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="176"/>
-      <c r="K15" s="176"/>
-      <c r="L15" s="176"/>
-      <c r="M15" s="176"/>
-      <c r="N15" s="176"/>
-      <c r="O15" s="176"/>
-      <c r="P15" s="176"/>
-      <c r="Q15" s="143"/>
-      <c r="R15" s="144"/>
-      <c r="S15" s="145"/>
-      <c r="T15" s="178" t="s">
+      <c r="B15" s="133"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
+      <c r="P15" s="130"/>
+      <c r="Q15" s="199"/>
+      <c r="R15" s="200"/>
+      <c r="S15" s="201"/>
+      <c r="T15" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="178"/>
-      <c r="V15" s="180">
+      <c r="U15" s="135"/>
+      <c r="V15" s="132">
         <v>0</v>
       </c>
-      <c r="W15" s="180"/>
-      <c r="X15" s="166">
+      <c r="W15" s="132"/>
+      <c r="X15" s="154">
         <v>0</v>
       </c>
-      <c r="Y15" s="166"/>
+      <c r="Y15" s="154"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8383,56 +8390,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="176"/>
-      <c r="AP15" s="176"/>
-      <c r="AQ15" s="176"/>
-      <c r="AR15" s="176"/>
-      <c r="AS15" s="176"/>
-      <c r="AT15" s="176"/>
-      <c r="AU15" s="176"/>
-      <c r="AV15" s="176"/>
-      <c r="AW15" s="176"/>
-      <c r="AX15" s="176"/>
-      <c r="AY15" s="176"/>
-      <c r="AZ15" s="177"/>
+      <c r="AO15" s="130"/>
+      <c r="AP15" s="130"/>
+      <c r="AQ15" s="130"/>
+      <c r="AR15" s="130"/>
+      <c r="AS15" s="130"/>
+      <c r="AT15" s="130"/>
+      <c r="AU15" s="130"/>
+      <c r="AV15" s="130"/>
+      <c r="AW15" s="130"/>
+      <c r="AX15" s="130"/>
+      <c r="AY15" s="130"/>
+      <c r="AZ15" s="152"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="190">
+      <c r="B16" s="133">
         <v>6</v>
       </c>
-      <c r="C16" s="152" t="s">
+      <c r="C16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="216" t="s">
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="129" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="176"/>
-      <c r="L16" s="176"/>
-      <c r="M16" s="176"/>
-      <c r="N16" s="176"/>
-      <c r="O16" s="176"/>
-      <c r="P16" s="176"/>
-      <c r="Q16" s="167"/>
-      <c r="R16" s="167"/>
-      <c r="S16" s="167"/>
-      <c r="T16" s="181" t="s">
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
+      <c r="P16" s="130"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="181"/>
-      <c r="V16" s="179">
+      <c r="U16" s="134"/>
+      <c r="V16" s="131">
         <v>0</v>
       </c>
-      <c r="W16" s="179"/>
-      <c r="X16" s="165">
+      <c r="W16" s="131"/>
+      <c r="X16" s="153">
         <v>0</v>
       </c>
-      <c r="Y16" s="165"/>
+      <c r="Y16" s="153"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8448,50 +8455,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="176"/>
-      <c r="AP16" s="176"/>
-      <c r="AQ16" s="176"/>
-      <c r="AR16" s="176"/>
-      <c r="AS16" s="176"/>
-      <c r="AT16" s="176"/>
-      <c r="AU16" s="176"/>
-      <c r="AV16" s="176"/>
-      <c r="AW16" s="176"/>
-      <c r="AX16" s="176"/>
-      <c r="AY16" s="176"/>
-      <c r="AZ16" s="177"/>
+      <c r="AO16" s="130"/>
+      <c r="AP16" s="130"/>
+      <c r="AQ16" s="130"/>
+      <c r="AR16" s="130"/>
+      <c r="AS16" s="130"/>
+      <c r="AT16" s="130"/>
+      <c r="AU16" s="130"/>
+      <c r="AV16" s="130"/>
+      <c r="AW16" s="130"/>
+      <c r="AX16" s="130"/>
+      <c r="AY16" s="130"/>
+      <c r="AZ16" s="152"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="190"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="176"/>
-      <c r="K17" s="176"/>
-      <c r="L17" s="176"/>
-      <c r="M17" s="176"/>
-      <c r="N17" s="176"/>
-      <c r="O17" s="176"/>
-      <c r="P17" s="176"/>
-      <c r="Q17" s="167"/>
-      <c r="R17" s="167"/>
-      <c r="S17" s="167"/>
-      <c r="T17" s="178" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="137"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="178"/>
-      <c r="V17" s="180">
+      <c r="U17" s="135"/>
+      <c r="V17" s="132">
         <v>0</v>
       </c>
-      <c r="W17" s="180"/>
-      <c r="X17" s="166">
+      <c r="W17" s="132"/>
+      <c r="X17" s="154">
         <v>0</v>
       </c>
-      <c r="Y17" s="166"/>
+      <c r="Y17" s="154"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8507,56 +8514,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="176"/>
-      <c r="AP17" s="176"/>
-      <c r="AQ17" s="176"/>
-      <c r="AR17" s="176"/>
-      <c r="AS17" s="176"/>
-      <c r="AT17" s="176"/>
-      <c r="AU17" s="176"/>
-      <c r="AV17" s="176"/>
-      <c r="AW17" s="176"/>
-      <c r="AX17" s="176"/>
-      <c r="AY17" s="176"/>
-      <c r="AZ17" s="177"/>
+      <c r="AO17" s="130"/>
+      <c r="AP17" s="130"/>
+      <c r="AQ17" s="130"/>
+      <c r="AR17" s="130"/>
+      <c r="AS17" s="130"/>
+      <c r="AT17" s="130"/>
+      <c r="AU17" s="130"/>
+      <c r="AV17" s="130"/>
+      <c r="AW17" s="130"/>
+      <c r="AX17" s="130"/>
+      <c r="AY17" s="130"/>
+      <c r="AZ17" s="152"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="127">
+      <c r="B18" s="150">
         <v>7</v>
       </c>
-      <c r="C18" s="129" t="s">
+      <c r="C18" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="152" t="s">
+      <c r="D18" s="184"/>
+      <c r="E18" s="184"/>
+      <c r="F18" s="184"/>
+      <c r="G18" s="184"/>
+      <c r="H18" s="184"/>
+      <c r="I18" s="185"/>
+      <c r="J18" s="138" t="s">
         <v>139</v>
       </c>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="135"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="140"/>
-      <c r="R18" s="141"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="146" t="s">
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="196"/>
+      <c r="R18" s="197"/>
+      <c r="S18" s="198"/>
+      <c r="T18" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="147"/>
-      <c r="V18" s="148">
+      <c r="U18" s="187"/>
+      <c r="V18" s="146">
         <v>0</v>
       </c>
-      <c r="W18" s="149"/>
-      <c r="X18" s="150">
+      <c r="W18" s="147"/>
+      <c r="X18" s="192">
         <v>0</v>
       </c>
-      <c r="Y18" s="151"/>
+      <c r="Y18" s="193"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8572,50 +8579,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="152"/>
-      <c r="AP18" s="135"/>
-      <c r="AQ18" s="135"/>
-      <c r="AR18" s="135"/>
-      <c r="AS18" s="135"/>
-      <c r="AT18" s="135"/>
-      <c r="AU18" s="135"/>
-      <c r="AV18" s="135"/>
-      <c r="AW18" s="135"/>
-      <c r="AX18" s="135"/>
-      <c r="AY18" s="135"/>
-      <c r="AZ18" s="153"/>
+      <c r="AO18" s="138"/>
+      <c r="AP18" s="139"/>
+      <c r="AQ18" s="139"/>
+      <c r="AR18" s="139"/>
+      <c r="AS18" s="139"/>
+      <c r="AT18" s="139"/>
+      <c r="AU18" s="139"/>
+      <c r="AV18" s="139"/>
+      <c r="AW18" s="139"/>
+      <c r="AX18" s="139"/>
+      <c r="AY18" s="139"/>
+      <c r="AZ18" s="188"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="128"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="138"/>
-      <c r="P19" s="139"/>
-      <c r="Q19" s="143"/>
-      <c r="R19" s="144"/>
-      <c r="S19" s="145"/>
-      <c r="T19" s="155" t="s">
+      <c r="B19" s="151"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="169"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="169"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="142"/>
+      <c r="L19" s="142"/>
+      <c r="M19" s="142"/>
+      <c r="N19" s="142"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="143"/>
+      <c r="Q19" s="199"/>
+      <c r="R19" s="200"/>
+      <c r="S19" s="201"/>
+      <c r="T19" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="156"/>
-      <c r="V19" s="157">
+      <c r="U19" s="191"/>
+      <c r="V19" s="148">
         <v>0</v>
       </c>
-      <c r="W19" s="158"/>
-      <c r="X19" s="159">
+      <c r="W19" s="149"/>
+      <c r="X19" s="194">
         <v>0</v>
       </c>
-      <c r="Y19" s="160"/>
+      <c r="Y19" s="195"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8631,56 +8638,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="137"/>
-      <c r="AP19" s="138"/>
-      <c r="AQ19" s="138"/>
-      <c r="AR19" s="138"/>
-      <c r="AS19" s="138"/>
-      <c r="AT19" s="138"/>
-      <c r="AU19" s="138"/>
-      <c r="AV19" s="138"/>
-      <c r="AW19" s="138"/>
-      <c r="AX19" s="138"/>
-      <c r="AY19" s="138"/>
-      <c r="AZ19" s="154"/>
+      <c r="AO19" s="141"/>
+      <c r="AP19" s="142"/>
+      <c r="AQ19" s="142"/>
+      <c r="AR19" s="142"/>
+      <c r="AS19" s="142"/>
+      <c r="AT19" s="142"/>
+      <c r="AU19" s="142"/>
+      <c r="AV19" s="142"/>
+      <c r="AW19" s="142"/>
+      <c r="AX19" s="142"/>
+      <c r="AY19" s="142"/>
+      <c r="AZ19" s="189"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="127">
+      <c r="B20" s="150">
         <v>8</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="C20" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="129" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="185"/>
+      <c r="J20" s="183" t="s">
         <v>140</v>
       </c>
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="135"/>
-      <c r="O20" s="135"/>
-      <c r="P20" s="136"/>
-      <c r="Q20" s="140"/>
-      <c r="R20" s="141"/>
-      <c r="S20" s="142"/>
-      <c r="T20" s="146" t="s">
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
+      <c r="P20" s="140"/>
+      <c r="Q20" s="196"/>
+      <c r="R20" s="197"/>
+      <c r="S20" s="198"/>
+      <c r="T20" s="186" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="147"/>
-      <c r="V20" s="148">
+      <c r="U20" s="187"/>
+      <c r="V20" s="146">
         <v>0</v>
       </c>
-      <c r="W20" s="149"/>
-      <c r="X20" s="150">
+      <c r="W20" s="147"/>
+      <c r="X20" s="192">
         <v>0</v>
       </c>
-      <c r="Y20" s="151"/>
+      <c r="Y20" s="193"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8696,50 +8703,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="152"/>
-      <c r="AP20" s="135"/>
-      <c r="AQ20" s="135"/>
-      <c r="AR20" s="135"/>
-      <c r="AS20" s="135"/>
-      <c r="AT20" s="135"/>
-      <c r="AU20" s="135"/>
-      <c r="AV20" s="135"/>
-      <c r="AW20" s="135"/>
-      <c r="AX20" s="135"/>
-      <c r="AY20" s="135"/>
-      <c r="AZ20" s="153"/>
+      <c r="AO20" s="138"/>
+      <c r="AP20" s="139"/>
+      <c r="AQ20" s="139"/>
+      <c r="AR20" s="139"/>
+      <c r="AS20" s="139"/>
+      <c r="AT20" s="139"/>
+      <c r="AU20" s="139"/>
+      <c r="AV20" s="139"/>
+      <c r="AW20" s="139"/>
+      <c r="AX20" s="139"/>
+      <c r="AY20" s="139"/>
+      <c r="AZ20" s="188"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="128"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="137"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="138"/>
-      <c r="M21" s="138"/>
-      <c r="N21" s="138"/>
-      <c r="O21" s="138"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="144"/>
-      <c r="S21" s="145"/>
-      <c r="T21" s="155" t="s">
+      <c r="B21" s="151"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="142"/>
+      <c r="L21" s="142"/>
+      <c r="M21" s="142"/>
+      <c r="N21" s="142"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="199"/>
+      <c r="R21" s="200"/>
+      <c r="S21" s="201"/>
+      <c r="T21" s="190" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="156"/>
-      <c r="V21" s="157">
+      <c r="U21" s="191"/>
+      <c r="V21" s="148">
         <v>0</v>
       </c>
-      <c r="W21" s="158"/>
-      <c r="X21" s="159">
+      <c r="W21" s="149"/>
+      <c r="X21" s="194">
         <v>0</v>
       </c>
-      <c r="Y21" s="160"/>
+      <c r="Y21" s="195"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8755,54 +8762,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="137"/>
-      <c r="AP21" s="138"/>
-      <c r="AQ21" s="138"/>
-      <c r="AR21" s="138"/>
-      <c r="AS21" s="138"/>
-      <c r="AT21" s="138"/>
-      <c r="AU21" s="138"/>
-      <c r="AV21" s="138"/>
-      <c r="AW21" s="138"/>
-      <c r="AX21" s="138"/>
-      <c r="AY21" s="138"/>
-      <c r="AZ21" s="154"/>
+      <c r="AO21" s="141"/>
+      <c r="AP21" s="142"/>
+      <c r="AQ21" s="142"/>
+      <c r="AR21" s="142"/>
+      <c r="AS21" s="142"/>
+      <c r="AT21" s="142"/>
+      <c r="AU21" s="142"/>
+      <c r="AV21" s="142"/>
+      <c r="AW21" s="142"/>
+      <c r="AX21" s="142"/>
+      <c r="AY21" s="142"/>
+      <c r="AZ21" s="189"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="197">
+      <c r="B22" s="163">
         <v>9</v>
       </c>
-      <c r="C22" s="199" t="s">
+      <c r="C22" s="165" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="200"/>
-      <c r="E22" s="200"/>
-      <c r="F22" s="200"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="200"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="184"/>
-      <c r="K22" s="185"/>
-      <c r="L22" s="185"/>
-      <c r="M22" s="185"/>
-      <c r="N22" s="185"/>
-      <c r="O22" s="185"/>
-      <c r="P22" s="186"/>
-      <c r="Q22" s="206"/>
-      <c r="R22" s="207"/>
-      <c r="S22" s="208"/>
-      <c r="T22" s="202" t="s">
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="167"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="156"/>
+      <c r="L22" s="156"/>
+      <c r="M22" s="156"/>
+      <c r="N22" s="156"/>
+      <c r="O22" s="156"/>
+      <c r="P22" s="204"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="176"/>
+      <c r="S22" s="177"/>
+      <c r="T22" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="203"/>
-      <c r="V22" s="182">
+      <c r="U22" s="172"/>
+      <c r="V22" s="202">
         <v>0</v>
       </c>
-      <c r="W22" s="183"/>
-      <c r="X22" s="195">
+      <c r="W22" s="203"/>
+      <c r="X22" s="161">
         <v>0</v>
       </c>
-      <c r="Y22" s="196"/>
+      <c r="Y22" s="162"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8818,50 +8825,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="184"/>
-      <c r="AP22" s="185"/>
-      <c r="AQ22" s="185"/>
-      <c r="AR22" s="185"/>
-      <c r="AS22" s="185"/>
-      <c r="AT22" s="185"/>
-      <c r="AU22" s="185"/>
-      <c r="AV22" s="185"/>
-      <c r="AW22" s="185"/>
-      <c r="AX22" s="185"/>
-      <c r="AY22" s="185"/>
-      <c r="AZ22" s="193"/>
+      <c r="AO22" s="155"/>
+      <c r="AP22" s="156"/>
+      <c r="AQ22" s="156"/>
+      <c r="AR22" s="156"/>
+      <c r="AS22" s="156"/>
+      <c r="AT22" s="156"/>
+      <c r="AU22" s="156"/>
+      <c r="AV22" s="156"/>
+      <c r="AW22" s="156"/>
+      <c r="AX22" s="156"/>
+      <c r="AY22" s="156"/>
+      <c r="AZ22" s="157"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="198"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="187"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="188"/>
-      <c r="M23" s="188"/>
-      <c r="N23" s="188"/>
-      <c r="O23" s="188"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="209"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="211"/>
-      <c r="T23" s="204" t="s">
+      <c r="B23" s="164"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="158"/>
+      <c r="K23" s="159"/>
+      <c r="L23" s="159"/>
+      <c r="M23" s="159"/>
+      <c r="N23" s="159"/>
+      <c r="O23" s="159"/>
+      <c r="P23" s="205"/>
+      <c r="Q23" s="178"/>
+      <c r="R23" s="179"/>
+      <c r="S23" s="180"/>
+      <c r="T23" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="205"/>
-      <c r="V23" s="191">
+      <c r="U23" s="174"/>
+      <c r="V23" s="144">
         <v>0</v>
       </c>
-      <c r="W23" s="192"/>
-      <c r="X23" s="212">
+      <c r="W23" s="145"/>
+      <c r="X23" s="181">
         <v>0</v>
       </c>
-      <c r="Y23" s="213"/>
+      <c r="Y23" s="182"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8877,18 +8884,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="187"/>
-      <c r="AP23" s="188"/>
-      <c r="AQ23" s="188"/>
-      <c r="AR23" s="188"/>
-      <c r="AS23" s="188"/>
-      <c r="AT23" s="188"/>
-      <c r="AU23" s="188"/>
-      <c r="AV23" s="188"/>
-      <c r="AW23" s="188"/>
-      <c r="AX23" s="188"/>
-      <c r="AY23" s="188"/>
-      <c r="AZ23" s="194"/>
+      <c r="AO23" s="158"/>
+      <c r="AP23" s="159"/>
+      <c r="AQ23" s="159"/>
+      <c r="AR23" s="159"/>
+      <c r="AS23" s="159"/>
+      <c r="AT23" s="159"/>
+      <c r="AU23" s="159"/>
+      <c r="AV23" s="159"/>
+      <c r="AW23" s="159"/>
+      <c r="AX23" s="159"/>
+      <c r="AY23" s="159"/>
+      <c r="AZ23" s="160"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8947,27 +8954,74 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO18:AZ19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q18:S19"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="J22:P23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:I13"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="AO12:AZ13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="AO14:AZ15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Q12:S13"/>
+    <mergeCell ref="Q14:S15"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="V19:W19"/>
@@ -8992,74 +9046,27 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="C18:I19"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AO18:AZ19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q18:S19"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="J22:P23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:I13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="AO12:AZ13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="AO14:AZ15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Q12:S13"/>
-    <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9083,53 +9090,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="63">
+      <c r="A1" s="64">
         <v>1</v>
       </c>
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="71" t="s">
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="111" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="72"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="112"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63">
+      <c r="A3" s="64">
         <v>2</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="101"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="218" t="s">
         <v>60</v>
       </c>
@@ -9143,552 +9150,551 @@
       <c r="J4" s="219"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="63">
+      <c r="A5" s="64">
         <v>3</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="101"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="108" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="78"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="63">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="101"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64"/>
-      <c r="B8" s="104" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="105"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="74"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="64"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="79"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="79"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="64"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="79"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="64"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="79"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="64"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="79"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="64"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="79"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="64"/>
-      <c r="B15" s="104" t="s">
+      <c r="A15" s="66"/>
+      <c r="B15" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="74"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="64"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="79"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="64"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="79"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="64"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="79"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="64"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="79"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="64"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="79"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="74"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63">
+      <c r="A22" s="64">
         <v>5</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="101"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="69"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="64"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="79"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="64"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="79"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="64"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="79"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="64"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="79"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="64"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="79"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="64"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="79"/>
+      <c r="A28" s="66"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="64"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="79"/>
+      <c r="A29" s="66"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="74"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="114"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63">
+      <c r="A31" s="64">
         <v>6</v>
       </c>
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="101"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="64"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="79"/>
+      <c r="A32" s="66"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="64"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="79"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="64"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="79"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="64"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="79"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="64"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="79"/>
+      <c r="A36" s="66"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="79"/>
+      <c r="A37" s="66"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="72"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="64"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="79"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="64"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="79"/>
+      <c r="A39" s="66"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="72"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="79"/>
+      <c r="A40" s="66"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="72"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="64"/>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="79"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="72"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="64"/>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="79"/>
+      <c r="A42" s="66"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="64"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="79"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="72"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="64"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="79"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="64"/>
-      <c r="B45" s="78"/>
-      <c r="C45" s="78"/>
-      <c r="D45" s="78"/>
-      <c r="E45" s="78"/>
-      <c r="F45" s="78"/>
-      <c r="G45" s="78"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="79"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="64"/>
-      <c r="B46" s="78"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="79"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="106"/>
-      <c r="D47" s="106"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="106"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="107"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -9697,12 +9703,13 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9715,15 +9722,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -9930,6 +9928,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9942,14 +9949,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9964,6 +9963,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBE031C-3307-469E-AFEA-F3660E7F8809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC8ADC-C27D-4774-9735-2AB11323BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="実績＆評価" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'別紙１）非機能要件'!$A$1:$I$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'別紙２）開発スケジュール予定＆実績'!$A$1:$AZ$23</definedName>
   </definedNames>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="178">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -888,28 +888,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物の情報(築年数等)を登録できる</t>
-    <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>チク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ネンスウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1890,17 +1868,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>建物情報登録</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報登録</t>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>建物情報一覧表示</t>
   </si>
   <si>
@@ -1912,70 +1879,6 @@
   </si>
   <si>
     <t>建物情報削除</t>
-  </si>
-  <si>
-    <t>登録した建物の一覧を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の詳細を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の情報を編集できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録した建物の情報を削除できる</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>被害状況・分析</t>
@@ -2082,6 +1985,126 @@
     </rPh>
     <rPh sb="408" eb="410">
       <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報保存</t>
+    <rPh sb="4" eb="6">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況登録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物の情報を保存できる</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の一覧を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の詳細を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の情報を編集できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の情報を削除できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析対象の建物の情報を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3067,7 +3090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3182,12 +3205,72 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3197,12 +3280,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3212,81 +3289,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3305,48 +3430,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3356,74 +3445,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3440,14 +3481,266 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3459,274 +3752,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3758,7 +3799,7 @@
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>298825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>74706</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4610,1592 +4651,1601 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64">
+      <c r="A2" s="66">
         <v>1</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="111" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="64">
+      <c r="A4" s="66">
         <v>2</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="80"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="66"/>
-      <c r="B5" s="82" t="s">
+      <c r="A5" s="67"/>
+      <c r="B5" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="83"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="66"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="85"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="66"/>
-      <c r="B8" s="87" t="s">
+      <c r="A8" s="67"/>
+      <c r="B8" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="89"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="66"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+      <c r="J9" s="103"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="92"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="103"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="66"/>
-      <c r="B11" s="90"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="92"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="103"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="66"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="92"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="103"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="92"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="66"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="92"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="103"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="66"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="92"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="103"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="66"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="92"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="103"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="65"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="92"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="103"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="65"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="92"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="103"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="65"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="103"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="64">
+      <c r="A21" s="66">
         <v>3</v>
       </c>
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="80"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="66"/>
-      <c r="B22" s="99" t="s">
+      <c r="A22" s="67"/>
+      <c r="B22" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="101"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="101"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66"/>
-      <c r="B24" s="99"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="101"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="89"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66"/>
-      <c r="B25" s="102"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="91"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="92"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="66"/>
-      <c r="B26" s="105" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="106"/>
+      <c r="A26" s="67"/>
+      <c r="B26" s="93" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="94"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="66"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="106"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="94"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="66"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="105"/>
-      <c r="J28" s="106"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="93"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="93"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="94"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="66"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="106"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="94"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="66"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="105"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="105"/>
-      <c r="I30" s="105"/>
-      <c r="J30" s="106"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="94"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="66"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="106"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="94"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="66"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="106"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="94"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="66"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="105"/>
-      <c r="I33" s="105"/>
-      <c r="J33" s="106"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="94"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="66"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="106"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
+      <c r="J34" s="94"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="66"/>
-      <c r="B35" s="105"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="106"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="94"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="66"/>
-      <c r="B36" s="105"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="106"/>
+      <c r="A36" s="67"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="94"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="66"/>
-      <c r="B37" s="105"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="106"/>
+      <c r="A37" s="67"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
+      <c r="F37" s="93"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="94"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66"/>
-      <c r="B38" s="105"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="106"/>
+      <c r="A38" s="67"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
+      <c r="J38" s="94"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66"/>
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="105"/>
-      <c r="G39" s="105"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="106"/>
+      <c r="A39" s="67"/>
+      <c r="B39" s="93"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="93"/>
+      <c r="E39" s="93"/>
+      <c r="F39" s="93"/>
+      <c r="G39" s="93"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
+      <c r="J39" s="94"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66"/>
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="106"/>
+      <c r="A40" s="67"/>
+      <c r="B40" s="93"/>
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="94"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="66"/>
-      <c r="B41" s="105"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="106"/>
+      <c r="A41" s="67"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="94"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="66"/>
-      <c r="B42" s="105"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="105"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="105"/>
-      <c r="H42" s="105"/>
-      <c r="I42" s="105"/>
-      <c r="J42" s="106"/>
+      <c r="A42" s="67"/>
+      <c r="B42" s="93"/>
+      <c r="C42" s="93"/>
+      <c r="D42" s="93"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="93"/>
+      <c r="G42" s="93"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="94"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="66"/>
-      <c r="B43" s="105"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="105"/>
-      <c r="J43" s="106"/>
+      <c r="A43" s="67"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="93"/>
+      <c r="D43" s="93"/>
+      <c r="E43" s="93"/>
+      <c r="F43" s="93"/>
+      <c r="G43" s="93"/>
+      <c r="H43" s="93"/>
+      <c r="I43" s="93"/>
+      <c r="J43" s="94"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="66"/>
-      <c r="B44" s="105"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="105"/>
-      <c r="I44" s="105"/>
-      <c r="J44" s="106"/>
+      <c r="A44" s="67"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="94"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="66"/>
-      <c r="B45" s="105"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="105"/>
-      <c r="J45" s="106"/>
+      <c r="A45" s="67"/>
+      <c r="B45" s="93"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+      <c r="F45" s="93"/>
+      <c r="G45" s="93"/>
+      <c r="H45" s="93"/>
+      <c r="I45" s="93"/>
+      <c r="J45" s="94"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="66"/>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="106"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="93"/>
+      <c r="J46" s="94"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="66"/>
-      <c r="B47" s="105"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="105"/>
-      <c r="E47" s="105"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="105"/>
-      <c r="H47" s="105"/>
-      <c r="I47" s="105"/>
-      <c r="J47" s="106"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="93"/>
+      <c r="C47" s="93"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="93"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93"/>
+      <c r="J47" s="94"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="66"/>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="105"/>
-      <c r="E48" s="105"/>
-      <c r="F48" s="105"/>
-      <c r="G48" s="105"/>
-      <c r="H48" s="105"/>
-      <c r="I48" s="105"/>
-      <c r="J48" s="106"/>
+      <c r="A48" s="67"/>
+      <c r="B48" s="93"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="93"/>
+      <c r="F48" s="93"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93"/>
+      <c r="J48" s="94"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="66"/>
-      <c r="B49" s="105"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="105"/>
-      <c r="E49" s="105"/>
-      <c r="F49" s="105"/>
-      <c r="G49" s="105"/>
-      <c r="H49" s="105"/>
-      <c r="I49" s="105"/>
-      <c r="J49" s="106"/>
+      <c r="A49" s="67"/>
+      <c r="B49" s="93"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="93"/>
+      <c r="F49" s="93"/>
+      <c r="G49" s="93"/>
+      <c r="H49" s="93"/>
+      <c r="I49" s="93"/>
+      <c r="J49" s="94"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="66"/>
-      <c r="B50" s="105"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="105"/>
-      <c r="J50" s="106"/>
+      <c r="A50" s="67"/>
+      <c r="B50" s="93"/>
+      <c r="C50" s="93"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="93"/>
+      <c r="F50" s="93"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93"/>
+      <c r="J50" s="94"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="66"/>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="105"/>
-      <c r="E51" s="105"/>
-      <c r="F51" s="105"/>
-      <c r="G51" s="105"/>
-      <c r="H51" s="105"/>
-      <c r="I51" s="105"/>
-      <c r="J51" s="106"/>
+      <c r="A51" s="67"/>
+      <c r="B51" s="93"/>
+      <c r="C51" s="93"/>
+      <c r="D51" s="93"/>
+      <c r="E51" s="93"/>
+      <c r="F51" s="93"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93"/>
+      <c r="J51" s="94"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="66"/>
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="105"/>
-      <c r="E52" s="105"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="105"/>
-      <c r="H52" s="105"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="106"/>
+      <c r="A52" s="67"/>
+      <c r="B52" s="93"/>
+      <c r="C52" s="93"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="93"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93"/>
+      <c r="J52" s="94"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="66"/>
-      <c r="B53" s="105"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="105"/>
-      <c r="E53" s="105"/>
-      <c r="F53" s="105"/>
-      <c r="G53" s="105"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="106"/>
+      <c r="A53" s="67"/>
+      <c r="B53" s="93"/>
+      <c r="C53" s="93"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="93"/>
+      <c r="F53" s="93"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93"/>
+      <c r="J53" s="94"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="66"/>
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="105"/>
-      <c r="H54" s="105"/>
-      <c r="I54" s="105"/>
-      <c r="J54" s="106"/>
+      <c r="A54" s="67"/>
+      <c r="B54" s="93"/>
+      <c r="C54" s="93"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="93"/>
+      <c r="F54" s="93"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93"/>
+      <c r="J54" s="94"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="66"/>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="105"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="105"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106"/>
+      <c r="A55" s="67"/>
+      <c r="B55" s="93"/>
+      <c r="C55" s="93"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="93"/>
+      <c r="F55" s="93"/>
+      <c r="G55" s="93"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="93"/>
+      <c r="J55" s="94"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="66"/>
-      <c r="B56" s="105"/>
-      <c r="C56" s="105"/>
-      <c r="D56" s="105"/>
-      <c r="E56" s="105"/>
-      <c r="F56" s="105"/>
-      <c r="G56" s="105"/>
-      <c r="H56" s="105"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="106"/>
+      <c r="A56" s="67"/>
+      <c r="B56" s="93"/>
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="94"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="66"/>
-      <c r="B57" s="105"/>
-      <c r="C57" s="105"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="105"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="105"/>
-      <c r="H57" s="105"/>
-      <c r="I57" s="105"/>
-      <c r="J57" s="106"/>
+      <c r="A57" s="67"/>
+      <c r="B57" s="93"/>
+      <c r="C57" s="93"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="93"/>
+      <c r="F57" s="93"/>
+      <c r="G57" s="93"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93"/>
+      <c r="J57" s="94"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="66"/>
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="105"/>
-      <c r="E58" s="105"/>
-      <c r="F58" s="105"/>
-      <c r="G58" s="105"/>
-      <c r="H58" s="105"/>
-      <c r="I58" s="105"/>
-      <c r="J58" s="106"/>
+      <c r="A58" s="67"/>
+      <c r="B58" s="93"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
+      <c r="E58" s="93"/>
+      <c r="F58" s="93"/>
+      <c r="G58" s="93"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93"/>
+      <c r="J58" s="94"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="66"/>
-      <c r="B59" s="105"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="105"/>
-      <c r="G59" s="105"/>
-      <c r="H59" s="105"/>
-      <c r="I59" s="105"/>
-      <c r="J59" s="106"/>
+      <c r="A59" s="67"/>
+      <c r="B59" s="93"/>
+      <c r="C59" s="93"/>
+      <c r="D59" s="93"/>
+      <c r="E59" s="93"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="93"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="93"/>
+      <c r="J59" s="94"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="66"/>
-      <c r="B60" s="105"/>
-      <c r="C60" s="105"/>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="106"/>
+      <c r="A60" s="67"/>
+      <c r="B60" s="93"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="93"/>
+      <c r="F60" s="93"/>
+      <c r="G60" s="93"/>
+      <c r="H60" s="93"/>
+      <c r="I60" s="93"/>
+      <c r="J60" s="94"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="66"/>
-      <c r="B61" s="105"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="105"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="105"/>
-      <c r="I61" s="105"/>
-      <c r="J61" s="106"/>
+      <c r="A61" s="67"/>
+      <c r="B61" s="93"/>
+      <c r="C61" s="93"/>
+      <c r="D61" s="93"/>
+      <c r="E61" s="93"/>
+      <c r="F61" s="93"/>
+      <c r="G61" s="93"/>
+      <c r="H61" s="93"/>
+      <c r="I61" s="93"/>
+      <c r="J61" s="94"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="67"/>
-      <c r="B62" s="107"/>
-      <c r="C62" s="107"/>
-      <c r="D62" s="107"/>
-      <c r="E62" s="107"/>
-      <c r="F62" s="107"/>
-      <c r="G62" s="107"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="107"/>
-      <c r="J62" s="108"/>
+      <c r="A62" s="68"/>
+      <c r="B62" s="95"/>
+      <c r="C62" s="95"/>
+      <c r="D62" s="95"/>
+      <c r="E62" s="95"/>
+      <c r="F62" s="95"/>
+      <c r="G62" s="95"/>
+      <c r="H62" s="95"/>
+      <c r="I62" s="95"/>
+      <c r="J62" s="96"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="64">
+      <c r="A63" s="66">
         <v>4</v>
       </c>
-      <c r="B63" s="68" t="s">
+      <c r="B63" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="68"/>
-      <c r="I63" s="68"/>
-      <c r="J63" s="69"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="73"/>
+      <c r="F63" s="73"/>
+      <c r="G63" s="73"/>
+      <c r="H63" s="73"/>
+      <c r="I63" s="73"/>
+      <c r="J63" s="104"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="66"/>
-      <c r="B64" s="109" t="s">
+      <c r="A64" s="67"/>
+      <c r="B64" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="109"/>
-      <c r="D64" s="71" t="s">
+      <c r="C64" s="69"/>
+      <c r="D64" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="E64" s="71"/>
-      <c r="F64" s="71"/>
-      <c r="G64" s="71"/>
-      <c r="H64" s="71"/>
-      <c r="I64" s="71"/>
-      <c r="J64" s="72"/>
+      <c r="E64" s="81"/>
+      <c r="F64" s="81"/>
+      <c r="G64" s="81"/>
+      <c r="H64" s="81"/>
+      <c r="I64" s="81"/>
+      <c r="J64" s="82"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="66"/>
-      <c r="B65" s="109" t="s">
+      <c r="A65" s="67"/>
+      <c r="B65" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="109"/>
-      <c r="D65" s="71" t="s">
-        <v>146</v>
-      </c>
-      <c r="E65" s="71"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="71"/>
-      <c r="H65" s="71"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="72"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="81"/>
+      <c r="F65" s="81"/>
+      <c r="G65" s="81"/>
+      <c r="H65" s="81"/>
+      <c r="I65" s="81"/>
+      <c r="J65" s="82"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="66"/>
-      <c r="B66" s="109" t="s">
+      <c r="A66" s="67"/>
+      <c r="B66" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="109"/>
-      <c r="D66" s="71" t="s">
-        <v>145</v>
-      </c>
-      <c r="E66" s="71"/>
-      <c r="F66" s="71"/>
-      <c r="G66" s="71"/>
-      <c r="H66" s="71"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="72"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="81" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
+      <c r="H66" s="81"/>
+      <c r="I66" s="81"/>
+      <c r="J66" s="82"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="66"/>
-      <c r="B67" s="109" t="s">
+      <c r="A67" s="67"/>
+      <c r="B67" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="109"/>
-      <c r="D67" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="72"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="81"/>
+      <c r="F67" s="81"/>
+      <c r="G67" s="81"/>
+      <c r="H67" s="81"/>
+      <c r="I67" s="81"/>
+      <c r="J67" s="82"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="66"/>
-      <c r="B68" s="109" t="s">
+      <c r="A68" s="67"/>
+      <c r="B68" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="109"/>
-      <c r="D68" s="109"/>
-      <c r="E68" s="109"/>
-      <c r="F68" s="109"/>
-      <c r="G68" s="109"/>
-      <c r="H68" s="109"/>
-      <c r="I68" s="109"/>
-      <c r="J68" s="110"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="69"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="97"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="66"/>
-      <c r="B69" s="96" t="e" vm="1">
+      <c r="A69" s="67"/>
+      <c r="B69" s="78" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C69" s="96"/>
-      <c r="D69" s="96"/>
-      <c r="E69" s="96"/>
-      <c r="F69" s="96"/>
-      <c r="G69" s="96"/>
-      <c r="H69" s="96"/>
-      <c r="I69" s="96"/>
-      <c r="J69" s="97"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
+      <c r="J69" s="79"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="66"/>
-      <c r="B70" s="96"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="96"/>
-      <c r="E70" s="96"/>
-      <c r="F70" s="96"/>
-      <c r="G70" s="96"/>
-      <c r="H70" s="96"/>
-      <c r="I70" s="96"/>
-      <c r="J70" s="97"/>
+      <c r="A70" s="67"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="78"/>
+      <c r="J70" s="79"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="66"/>
-      <c r="B71" s="96"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="96"/>
-      <c r="E71" s="96"/>
-      <c r="F71" s="96"/>
-      <c r="G71" s="96"/>
-      <c r="H71" s="96"/>
-      <c r="I71" s="96"/>
-      <c r="J71" s="97"/>
+      <c r="A71" s="67"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="78"/>
+      <c r="I71" s="78"/>
+      <c r="J71" s="79"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="66"/>
-      <c r="B72" s="96"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="96"/>
-      <c r="E72" s="96"/>
-      <c r="F72" s="96"/>
-      <c r="G72" s="96"/>
-      <c r="H72" s="96"/>
-      <c r="I72" s="96"/>
-      <c r="J72" s="97"/>
+      <c r="A72" s="67"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="78"/>
+      <c r="G72" s="78"/>
+      <c r="H72" s="78"/>
+      <c r="I72" s="78"/>
+      <c r="J72" s="79"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="66"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="96"/>
-      <c r="D73" s="96"/>
-      <c r="E73" s="96"/>
-      <c r="F73" s="96"/>
-      <c r="G73" s="96"/>
-      <c r="H73" s="96"/>
-      <c r="I73" s="96"/>
-      <c r="J73" s="97"/>
+      <c r="A73" s="67"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="78"/>
+      <c r="E73" s="78"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="78"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="79"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="66"/>
-      <c r="B74" s="96"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="96"/>
-      <c r="E74" s="96"/>
-      <c r="F74" s="96"/>
-      <c r="G74" s="96"/>
-      <c r="H74" s="96"/>
-      <c r="I74" s="96"/>
-      <c r="J74" s="97"/>
+      <c r="A74" s="67"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="78"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="78"/>
+      <c r="J74" s="79"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="66"/>
-      <c r="B75" s="96"/>
-      <c r="C75" s="96"/>
-      <c r="D75" s="96"/>
-      <c r="E75" s="96"/>
-      <c r="F75" s="96"/>
-      <c r="G75" s="96"/>
-      <c r="H75" s="96"/>
-      <c r="I75" s="96"/>
-      <c r="J75" s="97"/>
+      <c r="A75" s="67"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="78"/>
+      <c r="I75" s="78"/>
+      <c r="J75" s="79"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="66"/>
-      <c r="B76" s="96"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="96"/>
-      <c r="E76" s="96"/>
-      <c r="F76" s="96"/>
-      <c r="G76" s="96"/>
-      <c r="H76" s="96"/>
-      <c r="I76" s="96"/>
-      <c r="J76" s="97"/>
+      <c r="A76" s="67"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="78"/>
+      <c r="D76" s="78"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="78"/>
+      <c r="G76" s="78"/>
+      <c r="H76" s="78"/>
+      <c r="I76" s="78"/>
+      <c r="J76" s="79"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="66"/>
-      <c r="B77" s="96"/>
-      <c r="C77" s="96"/>
-      <c r="D77" s="96"/>
-      <c r="E77" s="96"/>
-      <c r="F77" s="96"/>
-      <c r="G77" s="96"/>
-      <c r="H77" s="96"/>
-      <c r="I77" s="96"/>
-      <c r="J77" s="97"/>
+      <c r="A77" s="67"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="78"/>
+      <c r="I77" s="78"/>
+      <c r="J77" s="79"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="66"/>
-      <c r="B78" s="96"/>
-      <c r="C78" s="96"/>
-      <c r="D78" s="96"/>
-      <c r="E78" s="96"/>
-      <c r="F78" s="96"/>
-      <c r="G78" s="96"/>
-      <c r="H78" s="96"/>
-      <c r="I78" s="96"/>
-      <c r="J78" s="97"/>
+      <c r="A78" s="67"/>
+      <c r="B78" s="78"/>
+      <c r="C78" s="78"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="78"/>
+      <c r="H78" s="78"/>
+      <c r="I78" s="78"/>
+      <c r="J78" s="79"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="66"/>
-      <c r="B79" s="96"/>
-      <c r="C79" s="96"/>
-      <c r="D79" s="96"/>
-      <c r="E79" s="96"/>
-      <c r="F79" s="96"/>
-      <c r="G79" s="96"/>
-      <c r="H79" s="96"/>
-      <c r="I79" s="96"/>
-      <c r="J79" s="97"/>
+      <c r="A79" s="67"/>
+      <c r="B79" s="78"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="78"/>
+      <c r="H79" s="78"/>
+      <c r="I79" s="78"/>
+      <c r="J79" s="79"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="66"/>
-      <c r="B80" s="96"/>
-      <c r="C80" s="96"/>
-      <c r="D80" s="96"/>
-      <c r="E80" s="96"/>
-      <c r="F80" s="96"/>
-      <c r="G80" s="96"/>
-      <c r="H80" s="96"/>
-      <c r="I80" s="96"/>
-      <c r="J80" s="97"/>
+      <c r="A80" s="67"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
+      <c r="J80" s="79"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="66"/>
-      <c r="B81" s="96"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="96"/>
-      <c r="E81" s="96"/>
-      <c r="F81" s="96"/>
-      <c r="G81" s="96"/>
-      <c r="H81" s="96"/>
-      <c r="I81" s="96"/>
-      <c r="J81" s="97"/>
+      <c r="A81" s="67"/>
+      <c r="B81" s="78"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
+      <c r="E81" s="78"/>
+      <c r="F81" s="78"/>
+      <c r="G81" s="78"/>
+      <c r="H81" s="78"/>
+      <c r="I81" s="78"/>
+      <c r="J81" s="79"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="66"/>
-      <c r="B82" s="96"/>
-      <c r="C82" s="96"/>
-      <c r="D82" s="96"/>
-      <c r="E82" s="96"/>
-      <c r="F82" s="96"/>
-      <c r="G82" s="96"/>
-      <c r="H82" s="96"/>
-      <c r="I82" s="96"/>
-      <c r="J82" s="97"/>
+      <c r="A82" s="67"/>
+      <c r="B82" s="78"/>
+      <c r="C82" s="78"/>
+      <c r="D82" s="78"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="78"/>
+      <c r="G82" s="78"/>
+      <c r="H82" s="78"/>
+      <c r="I82" s="78"/>
+      <c r="J82" s="79"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="66"/>
-      <c r="B83" s="96"/>
-      <c r="C83" s="96"/>
-      <c r="D83" s="96"/>
-      <c r="E83" s="96"/>
-      <c r="F83" s="96"/>
-      <c r="G83" s="96"/>
-      <c r="H83" s="96"/>
-      <c r="I83" s="96"/>
-      <c r="J83" s="97"/>
+      <c r="A83" s="67"/>
+      <c r="B83" s="78"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="78"/>
+      <c r="E83" s="78"/>
+      <c r="F83" s="78"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="78"/>
+      <c r="I83" s="78"/>
+      <c r="J83" s="79"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="66"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="96"/>
-      <c r="E84" s="96"/>
-      <c r="F84" s="96"/>
-      <c r="G84" s="96"/>
-      <c r="H84" s="96"/>
-      <c r="I84" s="96"/>
-      <c r="J84" s="97"/>
+      <c r="A84" s="67"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="78"/>
+      <c r="D84" s="78"/>
+      <c r="E84" s="78"/>
+      <c r="F84" s="78"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="78"/>
+      <c r="I84" s="78"/>
+      <c r="J84" s="79"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="66"/>
-      <c r="B85" s="96"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="96"/>
-      <c r="E85" s="96"/>
-      <c r="F85" s="96"/>
-      <c r="G85" s="96"/>
-      <c r="H85" s="96"/>
-      <c r="I85" s="96"/>
-      <c r="J85" s="97"/>
+      <c r="A85" s="67"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
+      <c r="H85" s="78"/>
+      <c r="I85" s="78"/>
+      <c r="J85" s="79"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="65"/>
-      <c r="B86" s="40"/>
-      <c r="C86" s="40"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="40"/>
-      <c r="J86" s="98"/>
+      <c r="A86" s="70"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="60"/>
+      <c r="I86" s="60"/>
+      <c r="J86" s="80"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="64">
+      <c r="A87" s="66">
         <v>5</v>
       </c>
-      <c r="B87" s="68" t="s">
+      <c r="B87" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="68"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="69"/>
+      <c r="C87" s="73"/>
+      <c r="D87" s="73"/>
+      <c r="E87" s="73"/>
+      <c r="F87" s="73"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="73"/>
+      <c r="I87" s="73"/>
+      <c r="J87" s="104"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="66"/>
-      <c r="B88" s="51" t="s">
+      <c r="A88" s="67"/>
+      <c r="B88" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
-      <c r="J88" s="86"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="44"/>
+      <c r="F88" s="44"/>
+      <c r="G88" s="44"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="44"/>
+      <c r="J88" s="114"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="64">
+      <c r="A89" s="66">
         <v>6</v>
       </c>
-      <c r="B89" s="79" t="s">
+      <c r="B89" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="79"/>
-      <c r="D89" s="79"/>
-      <c r="E89" s="79"/>
-      <c r="F89" s="79"/>
-      <c r="G89" s="79"/>
-      <c r="H89" s="79"/>
-      <c r="I89" s="79"/>
-      <c r="J89" s="80"/>
+      <c r="C89" s="71"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="71"/>
+      <c r="F89" s="71"/>
+      <c r="G89" s="71"/>
+      <c r="H89" s="71"/>
+      <c r="I89" s="71"/>
+      <c r="J89" s="72"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="81"/>
-      <c r="B90" s="82" t="s">
+      <c r="A90" s="113"/>
+      <c r="B90" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
-      <c r="J90" s="83"/>
+      <c r="C90" s="83"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="83"/>
+      <c r="G90" s="83"/>
+      <c r="H90" s="83"/>
+      <c r="I90" s="83"/>
+      <c r="J90" s="84"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="81"/>
-      <c r="B91" s="82"/>
-      <c r="C91" s="82"/>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="83"/>
+      <c r="A91" s="113"/>
+      <c r="B91" s="83"/>
+      <c r="C91" s="83"/>
+      <c r="D91" s="83"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="83"/>
+      <c r="G91" s="83"/>
+      <c r="H91" s="83"/>
+      <c r="I91" s="83"/>
+      <c r="J91" s="84"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="81"/>
-      <c r="B92" s="84"/>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
-      <c r="E92" s="84"/>
-      <c r="F92" s="84"/>
-      <c r="G92" s="84"/>
-      <c r="H92" s="84"/>
-      <c r="I92" s="84"/>
-      <c r="J92" s="85"/>
+      <c r="A92" s="113"/>
+      <c r="B92" s="85"/>
+      <c r="C92" s="85"/>
+      <c r="D92" s="85"/>
+      <c r="E92" s="85"/>
+      <c r="F92" s="85"/>
+      <c r="G92" s="85"/>
+      <c r="H92" s="85"/>
+      <c r="I92" s="85"/>
+      <c r="J92" s="86"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="66"/>
-      <c r="B93" s="87" t="s">
+      <c r="A93" s="67"/>
+      <c r="B93" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="C93" s="99"/>
+      <c r="D93" s="99"/>
+      <c r="E93" s="99"/>
+      <c r="F93" s="99"/>
+      <c r="G93" s="99"/>
+      <c r="H93" s="99"/>
+      <c r="I93" s="99"/>
+      <c r="J93" s="100"/>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="67"/>
+      <c r="B94" s="101"/>
+      <c r="C94" s="102"/>
+      <c r="D94" s="102"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="102"/>
+      <c r="I94" s="102"/>
+      <c r="J94" s="103"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="67"/>
+      <c r="B95" s="101"/>
+      <c r="C95" s="102"/>
+      <c r="D95" s="102"/>
+      <c r="E95" s="102"/>
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
+      <c r="H95" s="102"/>
+      <c r="I95" s="102"/>
+      <c r="J95" s="103"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="67"/>
+      <c r="B96" s="101"/>
+      <c r="C96" s="102"/>
+      <c r="D96" s="102"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="102"/>
+      <c r="I96" s="102"/>
+      <c r="J96" s="103"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="67"/>
+      <c r="B97" s="101"/>
+      <c r="C97" s="102"/>
+      <c r="D97" s="102"/>
+      <c r="E97" s="102"/>
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
+      <c r="H97" s="102"/>
+      <c r="I97" s="102"/>
+      <c r="J97" s="103"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="67"/>
+      <c r="B98" s="101"/>
+      <c r="C98" s="102"/>
+      <c r="D98" s="102"/>
+      <c r="E98" s="102"/>
+      <c r="F98" s="102"/>
+      <c r="G98" s="102"/>
+      <c r="H98" s="102"/>
+      <c r="I98" s="102"/>
+      <c r="J98" s="103"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="67"/>
+      <c r="B99" s="101"/>
+      <c r="C99" s="102"/>
+      <c r="D99" s="102"/>
+      <c r="E99" s="102"/>
+      <c r="F99" s="102"/>
+      <c r="G99" s="102"/>
+      <c r="H99" s="102"/>
+      <c r="I99" s="102"/>
+      <c r="J99" s="103"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="67"/>
+      <c r="B100" s="101"/>
+      <c r="C100" s="102"/>
+      <c r="D100" s="102"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="102"/>
+      <c r="I100" s="102"/>
+      <c r="J100" s="103"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="67"/>
+      <c r="B101" s="101"/>
+      <c r="C101" s="102"/>
+      <c r="D101" s="102"/>
+      <c r="E101" s="102"/>
+      <c r="F101" s="102"/>
+      <c r="G101" s="102"/>
+      <c r="H101" s="102"/>
+      <c r="I101" s="102"/>
+      <c r="J101" s="103"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="67"/>
+      <c r="B102" s="101"/>
+      <c r="C102" s="102"/>
+      <c r="D102" s="102"/>
+      <c r="E102" s="102"/>
+      <c r="F102" s="102"/>
+      <c r="G102" s="102"/>
+      <c r="H102" s="102"/>
+      <c r="I102" s="102"/>
+      <c r="J102" s="103"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="67"/>
+      <c r="B103" s="101"/>
+      <c r="C103" s="102"/>
+      <c r="D103" s="102"/>
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
+      <c r="H103" s="102"/>
+      <c r="I103" s="102"/>
+      <c r="J103" s="103"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="67"/>
+      <c r="B104" s="101"/>
+      <c r="C104" s="102"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="102"/>
+      <c r="H104" s="102"/>
+      <c r="I104" s="102"/>
+      <c r="J104" s="103"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="67"/>
+      <c r="B105" s="101"/>
+      <c r="C105" s="102"/>
+      <c r="D105" s="102"/>
+      <c r="E105" s="102"/>
+      <c r="F105" s="102"/>
+      <c r="G105" s="102"/>
+      <c r="H105" s="102"/>
+      <c r="I105" s="102"/>
+      <c r="J105" s="103"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="67"/>
+      <c r="B106" s="101"/>
+      <c r="C106" s="102"/>
+      <c r="D106" s="102"/>
+      <c r="E106" s="102"/>
+      <c r="F106" s="102"/>
+      <c r="G106" s="102"/>
+      <c r="H106" s="102"/>
+      <c r="I106" s="102"/>
+      <c r="J106" s="103"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="68"/>
+      <c r="B107" s="115"/>
+      <c r="C107" s="116"/>
+      <c r="D107" s="116"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="116"/>
+      <c r="H107" s="116"/>
+      <c r="I107" s="116"/>
+      <c r="J107" s="117"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="66">
+        <v>7</v>
+      </c>
+      <c r="B108" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="73"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="73"/>
+      <c r="F108" s="73"/>
+      <c r="G108" s="73"/>
+      <c r="H108" s="73"/>
+      <c r="I108" s="73"/>
+      <c r="J108" s="104"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="70"/>
+      <c r="B109" s="111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" s="111"/>
+      <c r="D109" s="111"/>
+      <c r="E109" s="111"/>
+      <c r="F109" s="111"/>
+      <c r="G109" s="111"/>
+      <c r="H109" s="111"/>
+      <c r="I109" s="111"/>
+      <c r="J109" s="112"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="66">
+        <v>8</v>
+      </c>
+      <c r="B110" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="73"/>
+      <c r="D110" s="73"/>
+      <c r="E110" s="73"/>
+      <c r="F110" s="73"/>
+      <c r="G110" s="73"/>
+      <c r="H110" s="73"/>
+      <c r="I110" s="73"/>
+      <c r="J110" s="104"/>
+    </row>
+    <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="67"/>
+      <c r="B111" s="106" t="s">
         <v>141</v>
       </c>
-      <c r="C93" s="88"/>
-      <c r="D93" s="88"/>
-      <c r="E93" s="88"/>
-      <c r="F93" s="88"/>
-      <c r="G93" s="88"/>
-      <c r="H93" s="88"/>
-      <c r="I93" s="88"/>
-      <c r="J93" s="89"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="66"/>
-      <c r="B94" s="90"/>
-      <c r="C94" s="91"/>
-      <c r="D94" s="91"/>
-      <c r="E94" s="91"/>
-      <c r="F94" s="91"/>
-      <c r="G94" s="91"/>
-      <c r="H94" s="91"/>
-      <c r="I94" s="91"/>
-      <c r="J94" s="92"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="66"/>
-      <c r="B95" s="90"/>
-      <c r="C95" s="91"/>
-      <c r="D95" s="91"/>
-      <c r="E95" s="91"/>
-      <c r="F95" s="91"/>
-      <c r="G95" s="91"/>
-      <c r="H95" s="91"/>
-      <c r="I95" s="91"/>
-      <c r="J95" s="92"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="66"/>
-      <c r="B96" s="90"/>
-      <c r="C96" s="91"/>
-      <c r="D96" s="91"/>
-      <c r="E96" s="91"/>
-      <c r="F96" s="91"/>
-      <c r="G96" s="91"/>
-      <c r="H96" s="91"/>
-      <c r="I96" s="91"/>
-      <c r="J96" s="92"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="66"/>
-      <c r="B97" s="90"/>
-      <c r="C97" s="91"/>
-      <c r="D97" s="91"/>
-      <c r="E97" s="91"/>
-      <c r="F97" s="91"/>
-      <c r="G97" s="91"/>
-      <c r="H97" s="91"/>
-      <c r="I97" s="91"/>
-      <c r="J97" s="92"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="66"/>
-      <c r="B98" s="90"/>
-      <c r="C98" s="91"/>
-      <c r="D98" s="91"/>
-      <c r="E98" s="91"/>
-      <c r="F98" s="91"/>
-      <c r="G98" s="91"/>
-      <c r="H98" s="91"/>
-      <c r="I98" s="91"/>
-      <c r="J98" s="92"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="66"/>
-      <c r="B99" s="90"/>
-      <c r="C99" s="91"/>
-      <c r="D99" s="91"/>
-      <c r="E99" s="91"/>
-      <c r="F99" s="91"/>
-      <c r="G99" s="91"/>
-      <c r="H99" s="91"/>
-      <c r="I99" s="91"/>
-      <c r="J99" s="92"/>
-    </row>
-    <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="66"/>
-      <c r="B100" s="90"/>
-      <c r="C100" s="91"/>
-      <c r="D100" s="91"/>
-      <c r="E100" s="91"/>
-      <c r="F100" s="91"/>
-      <c r="G100" s="91"/>
-      <c r="H100" s="91"/>
-      <c r="I100" s="91"/>
-      <c r="J100" s="92"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="66"/>
-      <c r="B101" s="90"/>
-      <c r="C101" s="91"/>
-      <c r="D101" s="91"/>
-      <c r="E101" s="91"/>
-      <c r="F101" s="91"/>
-      <c r="G101" s="91"/>
-      <c r="H101" s="91"/>
-      <c r="I101" s="91"/>
-      <c r="J101" s="92"/>
-    </row>
-    <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="66"/>
-      <c r="B102" s="90"/>
-      <c r="C102" s="91"/>
-      <c r="D102" s="91"/>
-      <c r="E102" s="91"/>
-      <c r="F102" s="91"/>
-      <c r="G102" s="91"/>
-      <c r="H102" s="91"/>
-      <c r="I102" s="91"/>
-      <c r="J102" s="92"/>
-    </row>
-    <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="66"/>
-      <c r="B103" s="90"/>
-      <c r="C103" s="91"/>
-      <c r="D103" s="91"/>
-      <c r="E103" s="91"/>
-      <c r="F103" s="91"/>
-      <c r="G103" s="91"/>
-      <c r="H103" s="91"/>
-      <c r="I103" s="91"/>
-      <c r="J103" s="92"/>
-    </row>
-    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="66"/>
-      <c r="B104" s="90"/>
-      <c r="C104" s="91"/>
-      <c r="D104" s="91"/>
-      <c r="E104" s="91"/>
-      <c r="F104" s="91"/>
-      <c r="G104" s="91"/>
-      <c r="H104" s="91"/>
-      <c r="I104" s="91"/>
-      <c r="J104" s="92"/>
-    </row>
-    <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="66"/>
-      <c r="B105" s="90"/>
-      <c r="C105" s="91"/>
-      <c r="D105" s="91"/>
-      <c r="E105" s="91"/>
-      <c r="F105" s="91"/>
-      <c r="G105" s="91"/>
-      <c r="H105" s="91"/>
-      <c r="I105" s="91"/>
-      <c r="J105" s="92"/>
-    </row>
-    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="66"/>
-      <c r="B106" s="90"/>
-      <c r="C106" s="91"/>
-      <c r="D106" s="91"/>
-      <c r="E106" s="91"/>
-      <c r="F106" s="91"/>
-      <c r="G106" s="91"/>
-      <c r="H106" s="91"/>
-      <c r="I106" s="91"/>
-      <c r="J106" s="92"/>
-    </row>
-    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="67"/>
-      <c r="B107" s="93"/>
-      <c r="C107" s="94"/>
-      <c r="D107" s="94"/>
-      <c r="E107" s="94"/>
-      <c r="F107" s="94"/>
-      <c r="G107" s="94"/>
-      <c r="H107" s="94"/>
-      <c r="I107" s="94"/>
-      <c r="J107" s="95"/>
-    </row>
-    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="64">
-        <v>7</v>
-      </c>
-      <c r="B108" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="68"/>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="68"/>
-      <c r="I108" s="68"/>
-      <c r="J108" s="69"/>
-    </row>
-    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="65"/>
-      <c r="B109" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" s="77"/>
-      <c r="D109" s="77"/>
-      <c r="E109" s="77"/>
-      <c r="F109" s="77"/>
-      <c r="G109" s="77"/>
-      <c r="H109" s="77"/>
-      <c r="I109" s="77"/>
-      <c r="J109" s="78"/>
-    </row>
-    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="64">
-        <v>8</v>
-      </c>
-      <c r="B110" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C110" s="68"/>
-      <c r="D110" s="68"/>
-      <c r="E110" s="68"/>
-      <c r="F110" s="68"/>
-      <c r="G110" s="68"/>
-      <c r="H110" s="68"/>
-      <c r="I110" s="68"/>
-      <c r="J110" s="69"/>
-    </row>
-    <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="66"/>
-      <c r="B111" s="70" t="s">
+      <c r="C111" s="81"/>
+      <c r="D111" s="81"/>
+      <c r="E111" s="81"/>
+      <c r="F111" s="81"/>
+      <c r="G111" s="81"/>
+      <c r="H111" s="81"/>
+      <c r="I111" s="81"/>
+      <c r="J111" s="82"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="67"/>
+      <c r="B112" s="81"/>
+      <c r="C112" s="81"/>
+      <c r="D112" s="81"/>
+      <c r="E112" s="81"/>
+      <c r="F112" s="81"/>
+      <c r="G112" s="81"/>
+      <c r="H112" s="81"/>
+      <c r="I112" s="81"/>
+      <c r="J112" s="82"/>
+    </row>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="67"/>
+      <c r="B113" s="81"/>
+      <c r="C113" s="81"/>
+      <c r="D113" s="81"/>
+      <c r="E113" s="81"/>
+      <c r="F113" s="81"/>
+      <c r="G113" s="81"/>
+      <c r="H113" s="81"/>
+      <c r="I113" s="81"/>
+      <c r="J113" s="82"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="67"/>
+      <c r="B114" s="81"/>
+      <c r="C114" s="81"/>
+      <c r="D114" s="81"/>
+      <c r="E114" s="81"/>
+      <c r="F114" s="81"/>
+      <c r="G114" s="81"/>
+      <c r="H114" s="81"/>
+      <c r="I114" s="81"/>
+      <c r="J114" s="82"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="67"/>
+      <c r="B115" s="81"/>
+      <c r="C115" s="81"/>
+      <c r="D115" s="81"/>
+      <c r="E115" s="81"/>
+      <c r="F115" s="81"/>
+      <c r="G115" s="81"/>
+      <c r="H115" s="81"/>
+      <c r="I115" s="81"/>
+      <c r="J115" s="82"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="67"/>
+      <c r="B116" s="81"/>
+      <c r="C116" s="81"/>
+      <c r="D116" s="81"/>
+      <c r="E116" s="81"/>
+      <c r="F116" s="81"/>
+      <c r="G116" s="81"/>
+      <c r="H116" s="81"/>
+      <c r="I116" s="81"/>
+      <c r="J116" s="82"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="67"/>
+      <c r="B117" s="107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C117" s="107"/>
+      <c r="D117" s="107"/>
+      <c r="E117" s="107"/>
+      <c r="F117" s="107"/>
+      <c r="G117" s="107"/>
+      <c r="H117" s="107"/>
+      <c r="I117" s="107"/>
+      <c r="J117" s="108"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="67"/>
+      <c r="B118" s="106" t="s">
         <v>142</v>
       </c>
-      <c r="C111" s="71"/>
-      <c r="D111" s="71"/>
-      <c r="E111" s="71"/>
-      <c r="F111" s="71"/>
-      <c r="G111" s="71"/>
-      <c r="H111" s="71"/>
-      <c r="I111" s="71"/>
-      <c r="J111" s="72"/>
-    </row>
-    <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="66"/>
-      <c r="B112" s="71"/>
-      <c r="C112" s="71"/>
-      <c r="D112" s="71"/>
-      <c r="E112" s="71"/>
-      <c r="F112" s="71"/>
-      <c r="G112" s="71"/>
-      <c r="H112" s="71"/>
-      <c r="I112" s="71"/>
-      <c r="J112" s="72"/>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="66"/>
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
-      <c r="G113" s="71"/>
-      <c r="H113" s="71"/>
-      <c r="I113" s="71"/>
-      <c r="J113" s="72"/>
-    </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="66"/>
-      <c r="B114" s="71"/>
-      <c r="C114" s="71"/>
-      <c r="D114" s="71"/>
-      <c r="E114" s="71"/>
-      <c r="F114" s="71"/>
-      <c r="G114" s="71"/>
-      <c r="H114" s="71"/>
-      <c r="I114" s="71"/>
-      <c r="J114" s="72"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="66"/>
-      <c r="B115" s="71"/>
-      <c r="C115" s="71"/>
-      <c r="D115" s="71"/>
-      <c r="E115" s="71"/>
-      <c r="F115" s="71"/>
-      <c r="G115" s="71"/>
-      <c r="H115" s="71"/>
-      <c r="I115" s="71"/>
-      <c r="J115" s="72"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="66"/>
-      <c r="B116" s="71"/>
-      <c r="C116" s="71"/>
-      <c r="D116" s="71"/>
-      <c r="E116" s="71"/>
-      <c r="F116" s="71"/>
-      <c r="G116" s="71"/>
-      <c r="H116" s="71"/>
-      <c r="I116" s="71"/>
-      <c r="J116" s="72"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="66"/>
-      <c r="B117" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="C117" s="73"/>
-      <c r="D117" s="73"/>
-      <c r="E117" s="73"/>
-      <c r="F117" s="73"/>
-      <c r="G117" s="73"/>
-      <c r="H117" s="73"/>
-      <c r="I117" s="73"/>
-      <c r="J117" s="74"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="66"/>
-      <c r="B118" s="70" t="s">
-        <v>143</v>
-      </c>
-      <c r="C118" s="71"/>
-      <c r="D118" s="71"/>
-      <c r="E118" s="71"/>
-      <c r="F118" s="71"/>
-      <c r="G118" s="71"/>
-      <c r="H118" s="71"/>
-      <c r="I118" s="71"/>
-      <c r="J118" s="72"/>
+      <c r="C118" s="81"/>
+      <c r="D118" s="81"/>
+      <c r="E118" s="81"/>
+      <c r="F118" s="81"/>
+      <c r="G118" s="81"/>
+      <c r="H118" s="81"/>
+      <c r="I118" s="81"/>
+      <c r="J118" s="82"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="66"/>
-      <c r="B119" s="71"/>
-      <c r="C119" s="71"/>
-      <c r="D119" s="71"/>
-      <c r="E119" s="71"/>
-      <c r="F119" s="71"/>
-      <c r="G119" s="71"/>
-      <c r="H119" s="71"/>
-      <c r="I119" s="71"/>
-      <c r="J119" s="72"/>
+      <c r="A119" s="67"/>
+      <c r="B119" s="81"/>
+      <c r="C119" s="81"/>
+      <c r="D119" s="81"/>
+      <c r="E119" s="81"/>
+      <c r="F119" s="81"/>
+      <c r="G119" s="81"/>
+      <c r="H119" s="81"/>
+      <c r="I119" s="81"/>
+      <c r="J119" s="82"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="66"/>
-      <c r="B120" s="71"/>
-      <c r="C120" s="71"/>
-      <c r="D120" s="71"/>
-      <c r="E120" s="71"/>
-      <c r="F120" s="71"/>
-      <c r="G120" s="71"/>
-      <c r="H120" s="71"/>
-      <c r="I120" s="71"/>
-      <c r="J120" s="72"/>
+      <c r="A120" s="67"/>
+      <c r="B120" s="81"/>
+      <c r="C120" s="81"/>
+      <c r="D120" s="81"/>
+      <c r="E120" s="81"/>
+      <c r="F120" s="81"/>
+      <c r="G120" s="81"/>
+      <c r="H120" s="81"/>
+      <c r="I120" s="81"/>
+      <c r="J120" s="82"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="66"/>
-      <c r="B121" s="71"/>
-      <c r="C121" s="71"/>
-      <c r="D121" s="71"/>
-      <c r="E121" s="71"/>
-      <c r="F121" s="71"/>
-      <c r="G121" s="71"/>
-      <c r="H121" s="71"/>
-      <c r="I121" s="71"/>
-      <c r="J121" s="72"/>
+      <c r="A121" s="67"/>
+      <c r="B121" s="81"/>
+      <c r="C121" s="81"/>
+      <c r="D121" s="81"/>
+      <c r="E121" s="81"/>
+      <c r="F121" s="81"/>
+      <c r="G121" s="81"/>
+      <c r="H121" s="81"/>
+      <c r="I121" s="81"/>
+      <c r="J121" s="82"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="66"/>
-      <c r="B122" s="71"/>
-      <c r="C122" s="71"/>
-      <c r="D122" s="71"/>
-      <c r="E122" s="71"/>
-      <c r="F122" s="71"/>
-      <c r="G122" s="71"/>
-      <c r="H122" s="71"/>
-      <c r="I122" s="71"/>
-      <c r="J122" s="72"/>
+      <c r="A122" s="67"/>
+      <c r="B122" s="81"/>
+      <c r="C122" s="81"/>
+      <c r="D122" s="81"/>
+      <c r="E122" s="81"/>
+      <c r="F122" s="81"/>
+      <c r="G122" s="81"/>
+      <c r="H122" s="81"/>
+      <c r="I122" s="81"/>
+      <c r="J122" s="82"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="66"/>
-      <c r="B123" s="71"/>
-      <c r="C123" s="71"/>
-      <c r="D123" s="71"/>
-      <c r="E123" s="71"/>
-      <c r="F123" s="71"/>
-      <c r="G123" s="71"/>
-      <c r="H123" s="71"/>
-      <c r="I123" s="71"/>
-      <c r="J123" s="72"/>
+      <c r="A123" s="67"/>
+      <c r="B123" s="81"/>
+      <c r="C123" s="81"/>
+      <c r="D123" s="81"/>
+      <c r="E123" s="81"/>
+      <c r="F123" s="81"/>
+      <c r="G123" s="81"/>
+      <c r="H123" s="81"/>
+      <c r="I123" s="81"/>
+      <c r="J123" s="82"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="66"/>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
-      <c r="G124" s="71"/>
-      <c r="H124" s="71"/>
-      <c r="I124" s="71"/>
-      <c r="J124" s="72"/>
+      <c r="A124" s="67"/>
+      <c r="B124" s="81"/>
+      <c r="C124" s="81"/>
+      <c r="D124" s="81"/>
+      <c r="E124" s="81"/>
+      <c r="F124" s="81"/>
+      <c r="G124" s="81"/>
+      <c r="H124" s="81"/>
+      <c r="I124" s="81"/>
+      <c r="J124" s="82"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="67"/>
-      <c r="B125" s="75"/>
-      <c r="C125" s="75"/>
-      <c r="D125" s="75"/>
-      <c r="E125" s="75"/>
-      <c r="F125" s="75"/>
-      <c r="G125" s="75"/>
-      <c r="H125" s="75"/>
-      <c r="I125" s="75"/>
-      <c r="J125" s="76"/>
+      <c r="A125" s="68"/>
+      <c r="B125" s="109"/>
+      <c r="C125" s="109"/>
+      <c r="D125" s="109"/>
+      <c r="E125" s="109"/>
+      <c r="F125" s="109"/>
+      <c r="G125" s="109"/>
+      <c r="H125" s="109"/>
+      <c r="I125" s="109"/>
+      <c r="J125" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
     <mergeCell ref="B69:J86"/>
     <mergeCell ref="A63:A86"/>
     <mergeCell ref="D64:J64"/>
@@ -6212,22 +6262,13 @@
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A125"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="B111:J116"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B118:J125"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="A89:A107"/>
-    <mergeCell ref="B90:J92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="B93:J107"/>
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6244,7 +6285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
@@ -6258,71 +6299,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="58" t="s">
+      <c r="G6" s="48"/>
+      <c r="H6" s="51" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -6332,411 +6373,417 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="59"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37">
         <v>1</v>
       </c>
-      <c r="B8" s="60" t="s">
-        <v>161</v>
+      <c r="B8" s="53" t="s">
+        <v>160</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="39"/>
+      <c r="F8" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="57"/>
       <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="37">
         <v>2</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="60" t="s">
-        <v>160</v>
+      <c r="B9" s="54"/>
+      <c r="C9" s="53" t="s">
+        <v>159</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E9" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="G9" s="39"/>
+      <c r="F9" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="57"/>
       <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="37">
         <v>3</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="35" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E10" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="39"/>
+      <c r="F10" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="57"/>
       <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="37">
         <v>4</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E11" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" s="39"/>
+      <c r="F11" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="57"/>
       <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="37">
         <v>5</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
       <c r="D12" s="35" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="39"/>
+      <c r="F12" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="57"/>
       <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37">
         <v>6</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="27" t="s">
+      <c r="B13" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="223" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="223" t="s">
         <v>89</v>
       </c>
-      <c r="F13" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="44"/>
-      <c r="H13" s="27"/>
+      <c r="F13" s="224" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" s="225"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="37">
         <v>7</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="27" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="G14" s="44"/>
+      <c r="F14" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="42"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <v>8</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="27" t="s">
-        <v>71</v>
-      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="27" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="44"/>
+        <v>89</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="42"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <v>9</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="44"/>
+        <v>90</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="42"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <v>10</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="40" t="s">
-        <v>75</v>
+      <c r="B17" s="39"/>
+      <c r="C17" s="27" t="s">
+        <v>73</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="G17" s="44"/>
+      <c r="F17" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="42"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="60" t="s">
+        <v>75</v>
+      </c>
       <c r="D18" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="44"/>
+      <c r="F18" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="42"/>
       <c r="H18" s="27"/>
     </row>
-    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <v>12</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="47" t="s">
-        <v>150</v>
-      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="63"/>
       <c r="D19" s="27" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="49"/>
+        <v>91</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="42"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <v>13</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="46"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="65" t="s">
+        <v>149</v>
+      </c>
       <c r="D20" s="27" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="44"/>
+        <v>151</v>
+      </c>
+      <c r="F20" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" s="59"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <v>14</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="46"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="49"/>
+      <c r="F21" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="42"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <v>15</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" s="49"/>
+      <c r="G22" s="59"/>
       <c r="H22" s="27"/>
     </row>
-    <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <v>16</v>
       </c>
-      <c r="B23" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>79</v>
-      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="63"/>
       <c r="D23" s="27" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="44"/>
+        <v>90</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="59"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <v>17</v>
       </c>
-      <c r="B24" s="46"/>
+      <c r="B24" s="60" t="s">
+        <v>78</v>
+      </c>
       <c r="C24" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="44"/>
+      <c r="F24" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="42"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <v>18</v>
       </c>
-      <c r="B25" s="45"/>
+      <c r="B25" s="64"/>
       <c r="C25" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="44"/>
+      <c r="F25" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="42"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <v>19</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>86</v>
+      <c r="B26" s="63"/>
+      <c r="C26" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" s="44"/>
+        <v>91</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="42"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <v>20</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="B27" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>86</v>
+      </c>
       <c r="D27" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="G27" s="44"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="37">
         <v>21</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="42"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6747,8 +6794,8 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6759,8 +6806,8 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6771,8 +6818,8 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6783,8 +6830,8 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="44"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6795,8 +6842,8 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="44"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6807,8 +6854,8 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="44"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6819,8 +6866,8 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="44"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="42"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6831,8 +6878,8 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="44"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="42"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6843,8 +6890,8 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="44"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6855,8 +6902,8 @@
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6867,14 +6914,59 @@
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="42"/>
       <c r="H39" s="27"/>
+    </row>
+    <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="37">
+        <v>33</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="49">
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:A7"/>
@@ -6889,39 +6981,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:B22"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6948,458 +7007,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="52" t="s">
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="45" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="52"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="118" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="71" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="116"/>
+      <c r="B8" s="121"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="116"/>
+      <c r="B9" s="121"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="117"/>
+      <c r="B10" s="119"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="118" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="116"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="116"/>
+      <c r="B13" s="121"/>
       <c r="C13" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="70" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="117"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="118" t="s">
+      <c r="B15" s="120" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="71" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="116"/>
+      <c r="B16" s="121"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="116"/>
+      <c r="B17" s="121"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="117"/>
+      <c r="B18" s="119"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="120" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="71" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="116"/>
+      <c r="B20" s="121"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="116"/>
+      <c r="B21" s="121"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="117"/>
+      <c r="B22" s="119"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="120" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="71" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="119"/>
+      <c r="B24" s="125"/>
       <c r="C24" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>148</v>
-      </c>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
+        <v>116</v>
+      </c>
+      <c r="D24" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="119"/>
+      <c r="B25" s="125"/>
       <c r="C25" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="71" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+        <v>117</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="119"/>
+      <c r="B26" s="125"/>
       <c r="C26" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="120"/>
+      <c r="B27" s="126"/>
       <c r="C27" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="121" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="122"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="123"/>
+        <v>120</v>
+      </c>
+      <c r="D27" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="129"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="120" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+        <v>121</v>
+      </c>
+      <c r="D28" s="81" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="116"/>
+      <c r="B29" s="121"/>
       <c r="C29" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="71" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="116"/>
+      <c r="B30" s="121"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="117"/>
+      <c r="B31" s="119"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7408,11 +7467,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7421,11 +7480,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7434,11 +7493,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7447,11 +7506,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7460,11 +7519,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7473,29 +7532,31 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D25:H25"/>
@@ -7512,22 +7573,20 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -7551,23 +7610,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="217" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
+      <c r="C1" s="218"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="218"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -7584,141 +7643,141 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="137" t="s">
-        <v>147</v>
-      </c>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="137"/>
-      <c r="W2" s="137"/>
-      <c r="X2" s="137"/>
-      <c r="Y2" s="137"/>
-      <c r="Z2" s="137"/>
-      <c r="AA2" s="137"/>
-      <c r="AB2" s="137"/>
-      <c r="AC2" s="137"/>
-      <c r="AD2" s="137"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="170" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="170"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="170"/>
+      <c r="O2" s="170"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="170"/>
+      <c r="T2" s="170"/>
+      <c r="U2" s="170"/>
+      <c r="V2" s="170"/>
+      <c r="W2" s="170"/>
+      <c r="X2" s="170"/>
+      <c r="Y2" s="170"/>
+      <c r="Z2" s="170"/>
+      <c r="AA2" s="170"/>
+      <c r="AB2" s="170"/>
+      <c r="AC2" s="170"/>
+      <c r="AD2" s="170"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="206" t="s">
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="164"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="164" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="206"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="206"/>
-      <c r="N4" s="206"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="210" t="s">
+      <c r="K4" s="164"/>
+      <c r="L4" s="164"/>
+      <c r="M4" s="164"/>
+      <c r="N4" s="164"/>
+      <c r="O4" s="164"/>
+      <c r="P4" s="164"/>
+      <c r="Q4" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="214"/>
-      <c r="S4" s="211"/>
-      <c r="T4" s="210" t="s">
+      <c r="R4" s="175"/>
+      <c r="S4" s="172"/>
+      <c r="T4" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="214"/>
-      <c r="V4" s="214"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="210" t="s">
+      <c r="U4" s="175"/>
+      <c r="V4" s="175"/>
+      <c r="W4" s="172"/>
+      <c r="X4" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="211"/>
-      <c r="Z4" s="206" t="s">
+      <c r="Y4" s="172"/>
+      <c r="Z4" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA4" s="164"/>
+      <c r="AB4" s="164"/>
+      <c r="AC4" s="164" t="s">
         <v>132</v>
       </c>
-      <c r="AA4" s="206"/>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="206" t="s">
+      <c r="AD4" s="164"/>
+      <c r="AE4" s="164"/>
+      <c r="AF4" s="164" t="s">
         <v>133</v>
       </c>
-      <c r="AD4" s="206"/>
-      <c r="AE4" s="206"/>
-      <c r="AF4" s="206" t="s">
+      <c r="AG4" s="164"/>
+      <c r="AH4" s="164"/>
+      <c r="AI4" s="164" t="s">
         <v>134</v>
       </c>
-      <c r="AG4" s="206"/>
-      <c r="AH4" s="206"/>
-      <c r="AI4" s="206" t="s">
+      <c r="AJ4" s="164"/>
+      <c r="AK4" s="164"/>
+      <c r="AL4" s="164" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="206"/>
-      <c r="AK4" s="206"/>
-      <c r="AL4" s="206" t="s">
-        <v>136</v>
-      </c>
-      <c r="AM4" s="206"/>
-      <c r="AN4" s="206"/>
-      <c r="AO4" s="206" t="s">
+      <c r="AM4" s="164"/>
+      <c r="AN4" s="164"/>
+      <c r="AO4" s="164" t="s">
         <v>45</v>
       </c>
-      <c r="AP4" s="206"/>
-      <c r="AQ4" s="206"/>
-      <c r="AR4" s="206"/>
-      <c r="AS4" s="206"/>
-      <c r="AT4" s="206"/>
-      <c r="AU4" s="206"/>
-      <c r="AV4" s="206"/>
-      <c r="AW4" s="206"/>
-      <c r="AX4" s="206"/>
-      <c r="AY4" s="206"/>
-      <c r="AZ4" s="207"/>
+      <c r="AP4" s="164"/>
+      <c r="AQ4" s="164"/>
+      <c r="AR4" s="164"/>
+      <c r="AS4" s="164"/>
+      <c r="AT4" s="164"/>
+      <c r="AU4" s="164"/>
+      <c r="AV4" s="164"/>
+      <c r="AW4" s="164"/>
+      <c r="AX4" s="164"/>
+      <c r="AY4" s="164"/>
+      <c r="AZ4" s="165"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="217"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="208"/>
-      <c r="M5" s="208"/>
-      <c r="N5" s="208"/>
-      <c r="O5" s="208"/>
-      <c r="P5" s="208"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="215"/>
-      <c r="S5" s="213"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="215"/>
-      <c r="V5" s="215"/>
-      <c r="W5" s="213"/>
-      <c r="X5" s="212"/>
-      <c r="Y5" s="213"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="166"/>
+      <c r="I5" s="166"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="166"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="173"/>
+      <c r="R5" s="176"/>
+      <c r="S5" s="174"/>
+      <c r="T5" s="173"/>
+      <c r="U5" s="176"/>
+      <c r="V5" s="176"/>
+      <c r="W5" s="174"/>
+      <c r="X5" s="173"/>
+      <c r="Y5" s="174"/>
       <c r="Z5" s="6" t="s">
         <v>46</v>
       </c>
@@ -7764,58 +7823,58 @@
       <c r="AN5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" s="208"/>
-      <c r="AP5" s="208"/>
-      <c r="AQ5" s="208"/>
-      <c r="AR5" s="208"/>
-      <c r="AS5" s="208"/>
-      <c r="AT5" s="208"/>
-      <c r="AU5" s="208"/>
-      <c r="AV5" s="208"/>
-      <c r="AW5" s="208"/>
-      <c r="AX5" s="208"/>
-      <c r="AY5" s="208"/>
-      <c r="AZ5" s="209"/>
+      <c r="AO5" s="166"/>
+      <c r="AP5" s="166"/>
+      <c r="AQ5" s="166"/>
+      <c r="AR5" s="166"/>
+      <c r="AS5" s="166"/>
+      <c r="AT5" s="166"/>
+      <c r="AU5" s="166"/>
+      <c r="AV5" s="166"/>
+      <c r="AW5" s="166"/>
+      <c r="AX5" s="166"/>
+      <c r="AY5" s="166"/>
+      <c r="AZ5" s="167"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="133">
+      <c r="B6" s="193">
         <v>1</v>
       </c>
-      <c r="C6" s="130" t="s">
+      <c r="C6" s="179" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130" t="s">
+      <c r="D6" s="179"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="179" t="s">
+        <v>126</v>
+      </c>
+      <c r="K6" s="179"/>
+      <c r="L6" s="179"/>
+      <c r="M6" s="179"/>
+      <c r="N6" s="179"/>
+      <c r="O6" s="179"/>
+      <c r="P6" s="179"/>
+      <c r="Q6" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="137" t="s">
-        <v>128</v>
-      </c>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="134" t="s">
+      <c r="R6" s="170"/>
+      <c r="S6" s="170"/>
+      <c r="T6" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="134"/>
-      <c r="V6" s="131">
+      <c r="U6" s="184"/>
+      <c r="V6" s="182">
         <v>0</v>
       </c>
-      <c r="W6" s="131"/>
-      <c r="X6" s="153">
+      <c r="W6" s="182"/>
+      <c r="X6" s="168">
         <v>0</v>
       </c>
-      <c r="Y6" s="153"/>
+      <c r="Y6" s="168"/>
       <c r="Z6" s="29"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7831,50 +7890,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="130"/>
-      <c r="AP6" s="130"/>
-      <c r="AQ6" s="130"/>
-      <c r="AR6" s="130"/>
-      <c r="AS6" s="130"/>
-      <c r="AT6" s="130"/>
-      <c r="AU6" s="130"/>
-      <c r="AV6" s="130"/>
-      <c r="AW6" s="130"/>
-      <c r="AX6" s="130"/>
-      <c r="AY6" s="130"/>
-      <c r="AZ6" s="152"/>
+      <c r="AO6" s="179"/>
+      <c r="AP6" s="179"/>
+      <c r="AQ6" s="179"/>
+      <c r="AR6" s="179"/>
+      <c r="AS6" s="179"/>
+      <c r="AT6" s="179"/>
+      <c r="AU6" s="179"/>
+      <c r="AV6" s="179"/>
+      <c r="AW6" s="179"/>
+      <c r="AX6" s="179"/>
+      <c r="AY6" s="179"/>
+      <c r="AZ6" s="180"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="133"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="137"/>
-      <c r="R7" s="137"/>
-      <c r="S7" s="137"/>
-      <c r="T7" s="135" t="s">
+      <c r="B7" s="193"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="179"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="179"/>
+      <c r="K7" s="179"/>
+      <c r="L7" s="179"/>
+      <c r="M7" s="179"/>
+      <c r="N7" s="179"/>
+      <c r="O7" s="179"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="170"/>
+      <c r="R7" s="170"/>
+      <c r="S7" s="170"/>
+      <c r="T7" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="135"/>
-      <c r="V7" s="132">
+      <c r="U7" s="181"/>
+      <c r="V7" s="183">
         <v>0</v>
       </c>
-      <c r="W7" s="132"/>
-      <c r="X7" s="154">
+      <c r="W7" s="183"/>
+      <c r="X7" s="169">
         <v>1</v>
       </c>
-      <c r="Y7" s="154"/>
+      <c r="Y7" s="169"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7890,58 +7949,58 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="130"/>
-      <c r="AP7" s="130"/>
-      <c r="AQ7" s="130"/>
-      <c r="AR7" s="130"/>
-      <c r="AS7" s="130"/>
-      <c r="AT7" s="130"/>
-      <c r="AU7" s="130"/>
-      <c r="AV7" s="130"/>
-      <c r="AW7" s="130"/>
-      <c r="AX7" s="130"/>
-      <c r="AY7" s="130"/>
-      <c r="AZ7" s="152"/>
+      <c r="AO7" s="179"/>
+      <c r="AP7" s="179"/>
+      <c r="AQ7" s="179"/>
+      <c r="AR7" s="179"/>
+      <c r="AS7" s="179"/>
+      <c r="AT7" s="179"/>
+      <c r="AU7" s="179"/>
+      <c r="AV7" s="179"/>
+      <c r="AW7" s="179"/>
+      <c r="AX7" s="179"/>
+      <c r="AY7" s="179"/>
+      <c r="AZ7" s="180"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="133">
+      <c r="B8" s="193">
         <v>2</v>
       </c>
-      <c r="C8" s="130" t="s">
+      <c r="C8" s="179" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="138" t="s">
+      <c r="D8" s="179"/>
+      <c r="E8" s="179"/>
+      <c r="F8" s="179"/>
+      <c r="G8" s="179"/>
+      <c r="H8" s="179"/>
+      <c r="I8" s="179"/>
+      <c r="J8" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="138"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="136" t="s">
-        <v>130</v>
-      </c>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="134" t="s">
+      <c r="R8" s="220"/>
+      <c r="S8" s="220"/>
+      <c r="T8" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="134"/>
-      <c r="V8" s="131">
+      <c r="U8" s="184"/>
+      <c r="V8" s="182">
         <v>0</v>
       </c>
-      <c r="W8" s="131"/>
-      <c r="X8" s="153">
+      <c r="W8" s="182"/>
+      <c r="X8" s="168">
         <v>0</v>
       </c>
-      <c r="Y8" s="153"/>
+      <c r="Y8" s="168"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7957,50 +8016,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="130"/>
-      <c r="AP8" s="130"/>
-      <c r="AQ8" s="130"/>
-      <c r="AR8" s="130"/>
-      <c r="AS8" s="130"/>
-      <c r="AT8" s="130"/>
-      <c r="AU8" s="130"/>
-      <c r="AV8" s="130"/>
-      <c r="AW8" s="130"/>
-      <c r="AX8" s="130"/>
-      <c r="AY8" s="130"/>
-      <c r="AZ8" s="152"/>
+      <c r="AO8" s="179"/>
+      <c r="AP8" s="179"/>
+      <c r="AQ8" s="179"/>
+      <c r="AR8" s="179"/>
+      <c r="AS8" s="179"/>
+      <c r="AT8" s="179"/>
+      <c r="AU8" s="179"/>
+      <c r="AV8" s="179"/>
+      <c r="AW8" s="179"/>
+      <c r="AX8" s="179"/>
+      <c r="AY8" s="179"/>
+      <c r="AZ8" s="180"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="133"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="143"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="135" t="s">
+      <c r="B9" s="193"/>
+      <c r="C9" s="179"/>
+      <c r="D9" s="179"/>
+      <c r="E9" s="179"/>
+      <c r="F9" s="179"/>
+      <c r="G9" s="179"/>
+      <c r="H9" s="179"/>
+      <c r="I9" s="179"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="141"/>
+      <c r="O9" s="141"/>
+      <c r="P9" s="142"/>
+      <c r="Q9" s="220"/>
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="135"/>
-      <c r="V9" s="132">
+      <c r="U9" s="181"/>
+      <c r="V9" s="183">
         <v>0</v>
       </c>
-      <c r="W9" s="132"/>
-      <c r="X9" s="154">
+      <c r="W9" s="183"/>
+      <c r="X9" s="169">
         <v>1</v>
       </c>
-      <c r="Y9" s="154"/>
+      <c r="Y9" s="169"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -8016,58 +8075,58 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="130"/>
-      <c r="AP9" s="130"/>
-      <c r="AQ9" s="130"/>
-      <c r="AR9" s="130"/>
-      <c r="AS9" s="130"/>
-      <c r="AT9" s="130"/>
-      <c r="AU9" s="130"/>
-      <c r="AV9" s="130"/>
-      <c r="AW9" s="130"/>
-      <c r="AX9" s="130"/>
-      <c r="AY9" s="130"/>
-      <c r="AZ9" s="152"/>
+      <c r="AO9" s="179"/>
+      <c r="AP9" s="179"/>
+      <c r="AQ9" s="179"/>
+      <c r="AR9" s="179"/>
+      <c r="AS9" s="179"/>
+      <c r="AT9" s="179"/>
+      <c r="AU9" s="179"/>
+      <c r="AV9" s="179"/>
+      <c r="AW9" s="179"/>
+      <c r="AX9" s="179"/>
+      <c r="AY9" s="179"/>
+      <c r="AZ9" s="180"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="133">
+      <c r="B10" s="193">
         <v>3</v>
       </c>
-      <c r="C10" s="130" t="s">
+      <c r="C10" s="179" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="129" t="s">
-        <v>137</v>
-      </c>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="137" t="s">
-        <v>128</v>
-      </c>
-      <c r="R10" s="137"/>
-      <c r="S10" s="137"/>
-      <c r="T10" s="134" t="s">
+      <c r="D10" s="179"/>
+      <c r="E10" s="179"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="179"/>
+      <c r="H10" s="179"/>
+      <c r="I10" s="179"/>
+      <c r="J10" s="219" t="s">
+        <v>136</v>
+      </c>
+      <c r="K10" s="179"/>
+      <c r="L10" s="179"/>
+      <c r="M10" s="179"/>
+      <c r="N10" s="179"/>
+      <c r="O10" s="179"/>
+      <c r="P10" s="179"/>
+      <c r="Q10" s="170" t="s">
+        <v>127</v>
+      </c>
+      <c r="R10" s="170"/>
+      <c r="S10" s="170"/>
+      <c r="T10" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="134"/>
-      <c r="V10" s="131">
+      <c r="U10" s="184"/>
+      <c r="V10" s="182">
         <v>0</v>
       </c>
-      <c r="W10" s="131"/>
-      <c r="X10" s="153">
+      <c r="W10" s="182"/>
+      <c r="X10" s="168">
         <v>0</v>
       </c>
-      <c r="Y10" s="153"/>
+      <c r="Y10" s="168"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="11"/>
@@ -8083,50 +8142,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="130"/>
-      <c r="AP10" s="130"/>
-      <c r="AQ10" s="130"/>
-      <c r="AR10" s="130"/>
-      <c r="AS10" s="130"/>
-      <c r="AT10" s="130"/>
-      <c r="AU10" s="130"/>
-      <c r="AV10" s="130"/>
-      <c r="AW10" s="130"/>
-      <c r="AX10" s="130"/>
-      <c r="AY10" s="130"/>
-      <c r="AZ10" s="152"/>
+      <c r="AO10" s="179"/>
+      <c r="AP10" s="179"/>
+      <c r="AQ10" s="179"/>
+      <c r="AR10" s="179"/>
+      <c r="AS10" s="179"/>
+      <c r="AT10" s="179"/>
+      <c r="AU10" s="179"/>
+      <c r="AV10" s="179"/>
+      <c r="AW10" s="179"/>
+      <c r="AX10" s="179"/>
+      <c r="AY10" s="179"/>
+      <c r="AZ10" s="180"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="133"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
-      <c r="S11" s="137"/>
-      <c r="T11" s="135" t="s">
+      <c r="B11" s="193"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="179"/>
+      <c r="H11" s="179"/>
+      <c r="I11" s="179"/>
+      <c r="J11" s="179"/>
+      <c r="K11" s="179"/>
+      <c r="L11" s="179"/>
+      <c r="M11" s="179"/>
+      <c r="N11" s="179"/>
+      <c r="O11" s="179"/>
+      <c r="P11" s="179"/>
+      <c r="Q11" s="170"/>
+      <c r="R11" s="170"/>
+      <c r="S11" s="170"/>
+      <c r="T11" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="135"/>
-      <c r="V11" s="132">
+      <c r="U11" s="181"/>
+      <c r="V11" s="183">
         <v>0</v>
       </c>
-      <c r="W11" s="132"/>
-      <c r="X11" s="154">
+      <c r="W11" s="183"/>
+      <c r="X11" s="169">
         <v>0</v>
       </c>
-      <c r="Y11" s="154"/>
+      <c r="Y11" s="169"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -8142,58 +8201,58 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="130"/>
-      <c r="AP11" s="130"/>
-      <c r="AQ11" s="130"/>
-      <c r="AR11" s="130"/>
-      <c r="AS11" s="130"/>
-      <c r="AT11" s="130"/>
-      <c r="AU11" s="130"/>
-      <c r="AV11" s="130"/>
-      <c r="AW11" s="130"/>
-      <c r="AX11" s="130"/>
-      <c r="AY11" s="130"/>
-      <c r="AZ11" s="152"/>
+      <c r="AO11" s="179"/>
+      <c r="AP11" s="179"/>
+      <c r="AQ11" s="179"/>
+      <c r="AR11" s="179"/>
+      <c r="AS11" s="179"/>
+      <c r="AT11" s="179"/>
+      <c r="AU11" s="179"/>
+      <c r="AV11" s="179"/>
+      <c r="AW11" s="179"/>
+      <c r="AX11" s="179"/>
+      <c r="AY11" s="179"/>
+      <c r="AZ11" s="180"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="133">
+      <c r="B12" s="193">
         <v>4</v>
       </c>
-      <c r="C12" s="130" t="s">
+      <c r="C12" s="179" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130" t="s">
-        <v>131</v>
-      </c>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="130"/>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="196" t="s">
-        <v>128</v>
-      </c>
-      <c r="R12" s="197"/>
-      <c r="S12" s="198"/>
-      <c r="T12" s="134" t="s">
+      <c r="D12" s="179"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="179"/>
+      <c r="H12" s="179"/>
+      <c r="I12" s="179"/>
+      <c r="J12" s="179" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="179"/>
+      <c r="L12" s="179"/>
+      <c r="M12" s="179"/>
+      <c r="N12" s="179"/>
+      <c r="O12" s="179"/>
+      <c r="P12" s="179"/>
+      <c r="Q12" s="143" t="s">
+        <v>127</v>
+      </c>
+      <c r="R12" s="144"/>
+      <c r="S12" s="145"/>
+      <c r="T12" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U12" s="134"/>
-      <c r="V12" s="131">
+      <c r="U12" s="184"/>
+      <c r="V12" s="182">
         <v>0</v>
       </c>
-      <c r="W12" s="131"/>
-      <c r="X12" s="153">
+      <c r="W12" s="182"/>
+      <c r="X12" s="168">
         <v>0</v>
       </c>
-      <c r="Y12" s="153"/>
+      <c r="Y12" s="168"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="31"/>
@@ -8209,50 +8268,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="130"/>
-      <c r="AP12" s="130"/>
-      <c r="AQ12" s="130"/>
-      <c r="AR12" s="130"/>
-      <c r="AS12" s="130"/>
-      <c r="AT12" s="130"/>
-      <c r="AU12" s="130"/>
-      <c r="AV12" s="130"/>
-      <c r="AW12" s="130"/>
-      <c r="AX12" s="130"/>
-      <c r="AY12" s="130"/>
-      <c r="AZ12" s="152"/>
+      <c r="AO12" s="179"/>
+      <c r="AP12" s="179"/>
+      <c r="AQ12" s="179"/>
+      <c r="AR12" s="179"/>
+      <c r="AS12" s="179"/>
+      <c r="AT12" s="179"/>
+      <c r="AU12" s="179"/>
+      <c r="AV12" s="179"/>
+      <c r="AW12" s="179"/>
+      <c r="AX12" s="179"/>
+      <c r="AY12" s="179"/>
+      <c r="AZ12" s="180"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="133"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="199"/>
-      <c r="R13" s="200"/>
-      <c r="S13" s="201"/>
-      <c r="T13" s="135" t="s">
+      <c r="B13" s="193"/>
+      <c r="C13" s="179"/>
+      <c r="D13" s="179"/>
+      <c r="E13" s="179"/>
+      <c r="F13" s="179"/>
+      <c r="G13" s="179"/>
+      <c r="H13" s="179"/>
+      <c r="I13" s="179"/>
+      <c r="J13" s="179"/>
+      <c r="K13" s="179"/>
+      <c r="L13" s="179"/>
+      <c r="M13" s="179"/>
+      <c r="N13" s="179"/>
+      <c r="O13" s="179"/>
+      <c r="P13" s="179"/>
+      <c r="Q13" s="146"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="148"/>
+      <c r="T13" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="135"/>
-      <c r="V13" s="132">
+      <c r="U13" s="181"/>
+      <c r="V13" s="183">
         <v>0</v>
       </c>
-      <c r="W13" s="132"/>
-      <c r="X13" s="154">
+      <c r="W13" s="183"/>
+      <c r="X13" s="169">
         <v>0</v>
       </c>
-      <c r="Y13" s="154"/>
+      <c r="Y13" s="169"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -8268,54 +8327,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="130"/>
-      <c r="AP13" s="130"/>
-      <c r="AQ13" s="130"/>
-      <c r="AR13" s="130"/>
-      <c r="AS13" s="130"/>
-      <c r="AT13" s="130"/>
-      <c r="AU13" s="130"/>
-      <c r="AV13" s="130"/>
-      <c r="AW13" s="130"/>
-      <c r="AX13" s="130"/>
-      <c r="AY13" s="130"/>
-      <c r="AZ13" s="152"/>
+      <c r="AO13" s="179"/>
+      <c r="AP13" s="179"/>
+      <c r="AQ13" s="179"/>
+      <c r="AR13" s="179"/>
+      <c r="AS13" s="179"/>
+      <c r="AT13" s="179"/>
+      <c r="AU13" s="179"/>
+      <c r="AV13" s="179"/>
+      <c r="AW13" s="179"/>
+      <c r="AX13" s="179"/>
+      <c r="AY13" s="179"/>
+      <c r="AZ13" s="180"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="133">
+      <c r="B14" s="193">
         <v>5</v>
       </c>
-      <c r="C14" s="138" t="s">
+      <c r="C14" s="155" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
-      <c r="P14" s="130"/>
-      <c r="Q14" s="196"/>
-      <c r="R14" s="197"/>
-      <c r="S14" s="198"/>
-      <c r="T14" s="134" t="s">
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="219"/>
+      <c r="K14" s="179"/>
+      <c r="L14" s="179"/>
+      <c r="M14" s="179"/>
+      <c r="N14" s="179"/>
+      <c r="O14" s="179"/>
+      <c r="P14" s="179"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="144"/>
+      <c r="S14" s="145"/>
+      <c r="T14" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="134"/>
-      <c r="V14" s="131">
+      <c r="U14" s="184"/>
+      <c r="V14" s="182">
         <v>0</v>
       </c>
-      <c r="W14" s="131"/>
-      <c r="X14" s="153">
+      <c r="W14" s="182"/>
+      <c r="X14" s="168">
         <v>0</v>
       </c>
-      <c r="Y14" s="153"/>
+      <c r="Y14" s="168"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="31"/>
@@ -8331,50 +8390,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="130"/>
-      <c r="AP14" s="130"/>
-      <c r="AQ14" s="130"/>
-      <c r="AR14" s="130"/>
-      <c r="AS14" s="130"/>
-      <c r="AT14" s="130"/>
-      <c r="AU14" s="130"/>
-      <c r="AV14" s="130"/>
-      <c r="AW14" s="130"/>
-      <c r="AX14" s="130"/>
-      <c r="AY14" s="130"/>
-      <c r="AZ14" s="152"/>
+      <c r="AO14" s="179"/>
+      <c r="AP14" s="179"/>
+      <c r="AQ14" s="179"/>
+      <c r="AR14" s="179"/>
+      <c r="AS14" s="179"/>
+      <c r="AT14" s="179"/>
+      <c r="AU14" s="179"/>
+      <c r="AV14" s="179"/>
+      <c r="AW14" s="179"/>
+      <c r="AX14" s="179"/>
+      <c r="AY14" s="179"/>
+      <c r="AZ14" s="180"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="133"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="142"/>
-      <c r="I15" s="143"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
-      <c r="P15" s="130"/>
-      <c r="Q15" s="199"/>
-      <c r="R15" s="200"/>
-      <c r="S15" s="201"/>
-      <c r="T15" s="135" t="s">
+      <c r="B15" s="193"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="179"/>
+      <c r="K15" s="179"/>
+      <c r="L15" s="179"/>
+      <c r="M15" s="179"/>
+      <c r="N15" s="179"/>
+      <c r="O15" s="179"/>
+      <c r="P15" s="179"/>
+      <c r="Q15" s="146"/>
+      <c r="R15" s="147"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="135"/>
-      <c r="V15" s="132">
+      <c r="U15" s="181"/>
+      <c r="V15" s="183">
         <v>0</v>
       </c>
-      <c r="W15" s="132"/>
-      <c r="X15" s="154">
+      <c r="W15" s="183"/>
+      <c r="X15" s="169">
         <v>0</v>
       </c>
-      <c r="Y15" s="154"/>
+      <c r="Y15" s="169"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -8390,56 +8449,56 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="130"/>
-      <c r="AP15" s="130"/>
-      <c r="AQ15" s="130"/>
-      <c r="AR15" s="130"/>
-      <c r="AS15" s="130"/>
-      <c r="AT15" s="130"/>
-      <c r="AU15" s="130"/>
-      <c r="AV15" s="130"/>
-      <c r="AW15" s="130"/>
-      <c r="AX15" s="130"/>
-      <c r="AY15" s="130"/>
-      <c r="AZ15" s="152"/>
+      <c r="AO15" s="179"/>
+      <c r="AP15" s="179"/>
+      <c r="AQ15" s="179"/>
+      <c r="AR15" s="179"/>
+      <c r="AS15" s="179"/>
+      <c r="AT15" s="179"/>
+      <c r="AU15" s="179"/>
+      <c r="AV15" s="179"/>
+      <c r="AW15" s="179"/>
+      <c r="AX15" s="179"/>
+      <c r="AY15" s="179"/>
+      <c r="AZ15" s="180"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="133">
+      <c r="B16" s="193">
         <v>6</v>
       </c>
-      <c r="C16" s="138" t="s">
+      <c r="C16" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="129" t="s">
-        <v>138</v>
-      </c>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
-      <c r="P16" s="130"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="137"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="134" t="s">
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="219" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" s="179"/>
+      <c r="L16" s="179"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="179"/>
+      <c r="O16" s="179"/>
+      <c r="P16" s="179"/>
+      <c r="Q16" s="170"/>
+      <c r="R16" s="170"/>
+      <c r="S16" s="170"/>
+      <c r="T16" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="U16" s="134"/>
-      <c r="V16" s="131">
+      <c r="U16" s="184"/>
+      <c r="V16" s="182">
         <v>0</v>
       </c>
-      <c r="W16" s="131"/>
-      <c r="X16" s="153">
+      <c r="W16" s="182"/>
+      <c r="X16" s="168">
         <v>0</v>
       </c>
-      <c r="Y16" s="153"/>
+      <c r="Y16" s="168"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -8455,50 +8514,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="130"/>
-      <c r="AP16" s="130"/>
-      <c r="AQ16" s="130"/>
-      <c r="AR16" s="130"/>
-      <c r="AS16" s="130"/>
-      <c r="AT16" s="130"/>
-      <c r="AU16" s="130"/>
-      <c r="AV16" s="130"/>
-      <c r="AW16" s="130"/>
-      <c r="AX16" s="130"/>
-      <c r="AY16" s="130"/>
-      <c r="AZ16" s="152"/>
+      <c r="AO16" s="179"/>
+      <c r="AP16" s="179"/>
+      <c r="AQ16" s="179"/>
+      <c r="AR16" s="179"/>
+      <c r="AS16" s="179"/>
+      <c r="AT16" s="179"/>
+      <c r="AU16" s="179"/>
+      <c r="AV16" s="179"/>
+      <c r="AW16" s="179"/>
+      <c r="AX16" s="179"/>
+      <c r="AY16" s="179"/>
+      <c r="AZ16" s="180"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="133"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="137"/>
-      <c r="R17" s="137"/>
-      <c r="S17" s="137"/>
-      <c r="T17" s="135" t="s">
+      <c r="B17" s="193"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="179"/>
+      <c r="K17" s="179"/>
+      <c r="L17" s="179"/>
+      <c r="M17" s="179"/>
+      <c r="N17" s="179"/>
+      <c r="O17" s="179"/>
+      <c r="P17" s="179"/>
+      <c r="Q17" s="170"/>
+      <c r="R17" s="170"/>
+      <c r="S17" s="170"/>
+      <c r="T17" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="135"/>
-      <c r="V17" s="132">
+      <c r="U17" s="181"/>
+      <c r="V17" s="183">
         <v>0</v>
       </c>
-      <c r="W17" s="132"/>
-      <c r="X17" s="154">
+      <c r="W17" s="183"/>
+      <c r="X17" s="169">
         <v>0</v>
       </c>
-      <c r="Y17" s="154"/>
+      <c r="Y17" s="169"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -8514,56 +8573,56 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="130"/>
-      <c r="AP17" s="130"/>
-      <c r="AQ17" s="130"/>
-      <c r="AR17" s="130"/>
-      <c r="AS17" s="130"/>
-      <c r="AT17" s="130"/>
-      <c r="AU17" s="130"/>
-      <c r="AV17" s="130"/>
-      <c r="AW17" s="130"/>
-      <c r="AX17" s="130"/>
-      <c r="AY17" s="130"/>
-      <c r="AZ17" s="152"/>
+      <c r="AO17" s="179"/>
+      <c r="AP17" s="179"/>
+      <c r="AQ17" s="179"/>
+      <c r="AR17" s="179"/>
+      <c r="AS17" s="179"/>
+      <c r="AT17" s="179"/>
+      <c r="AU17" s="179"/>
+      <c r="AV17" s="179"/>
+      <c r="AW17" s="179"/>
+      <c r="AX17" s="179"/>
+      <c r="AY17" s="179"/>
+      <c r="AZ17" s="180"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="150">
+      <c r="B18" s="130">
         <v>7</v>
       </c>
-      <c r="C18" s="183" t="s">
+      <c r="C18" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="184"/>
-      <c r="F18" s="184"/>
-      <c r="G18" s="184"/>
-      <c r="H18" s="184"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="138" t="s">
-        <v>139</v>
-      </c>
-      <c r="K18" s="139"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="139"/>
-      <c r="O18" s="139"/>
-      <c r="P18" s="140"/>
-      <c r="Q18" s="196"/>
-      <c r="R18" s="197"/>
-      <c r="S18" s="198"/>
-      <c r="T18" s="186" t="s">
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="155" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" s="138"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="138"/>
+      <c r="N18" s="138"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="144"/>
+      <c r="S18" s="145"/>
+      <c r="T18" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="U18" s="187"/>
-      <c r="V18" s="146">
+      <c r="U18" s="150"/>
+      <c r="V18" s="151">
         <v>0</v>
       </c>
-      <c r="W18" s="147"/>
-      <c r="X18" s="192">
+      <c r="W18" s="152"/>
+      <c r="X18" s="153">
         <v>0</v>
       </c>
-      <c r="Y18" s="193"/>
+      <c r="Y18" s="154"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -8579,50 +8638,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="138"/>
-      <c r="AP18" s="139"/>
-      <c r="AQ18" s="139"/>
-      <c r="AR18" s="139"/>
-      <c r="AS18" s="139"/>
-      <c r="AT18" s="139"/>
-      <c r="AU18" s="139"/>
-      <c r="AV18" s="139"/>
-      <c r="AW18" s="139"/>
-      <c r="AX18" s="139"/>
-      <c r="AY18" s="139"/>
-      <c r="AZ18" s="188"/>
+      <c r="AO18" s="155"/>
+      <c r="AP18" s="138"/>
+      <c r="AQ18" s="138"/>
+      <c r="AR18" s="138"/>
+      <c r="AS18" s="138"/>
+      <c r="AT18" s="138"/>
+      <c r="AU18" s="138"/>
+      <c r="AV18" s="138"/>
+      <c r="AW18" s="138"/>
+      <c r="AX18" s="138"/>
+      <c r="AY18" s="138"/>
+      <c r="AZ18" s="156"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="151"/>
-      <c r="C19" s="168"/>
-      <c r="D19" s="169"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="170"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-      <c r="M19" s="142"/>
-      <c r="N19" s="142"/>
-      <c r="O19" s="142"/>
-      <c r="P19" s="143"/>
-      <c r="Q19" s="199"/>
-      <c r="R19" s="200"/>
-      <c r="S19" s="201"/>
-      <c r="T19" s="190" t="s">
+      <c r="B19" s="131"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="141"/>
+      <c r="O19" s="141"/>
+      <c r="P19" s="142"/>
+      <c r="Q19" s="146"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="148"/>
+      <c r="T19" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="191"/>
-      <c r="V19" s="148">
+      <c r="U19" s="159"/>
+      <c r="V19" s="160">
         <v>0</v>
       </c>
-      <c r="W19" s="149"/>
-      <c r="X19" s="194">
+      <c r="W19" s="161"/>
+      <c r="X19" s="162">
         <v>0</v>
       </c>
-      <c r="Y19" s="195"/>
+      <c r="Y19" s="163"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -8638,56 +8697,56 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="141"/>
-      <c r="AP19" s="142"/>
-      <c r="AQ19" s="142"/>
-      <c r="AR19" s="142"/>
-      <c r="AS19" s="142"/>
-      <c r="AT19" s="142"/>
-      <c r="AU19" s="142"/>
-      <c r="AV19" s="142"/>
-      <c r="AW19" s="142"/>
-      <c r="AX19" s="142"/>
-      <c r="AY19" s="142"/>
-      <c r="AZ19" s="189"/>
+      <c r="AO19" s="140"/>
+      <c r="AP19" s="141"/>
+      <c r="AQ19" s="141"/>
+      <c r="AR19" s="141"/>
+      <c r="AS19" s="141"/>
+      <c r="AT19" s="141"/>
+      <c r="AU19" s="141"/>
+      <c r="AV19" s="141"/>
+      <c r="AW19" s="141"/>
+      <c r="AX19" s="141"/>
+      <c r="AY19" s="141"/>
+      <c r="AZ19" s="157"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="150">
+      <c r="B20" s="130">
         <v>8</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="184"/>
-      <c r="G20" s="184"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="183" t="s">
-        <v>140</v>
-      </c>
-      <c r="K20" s="139"/>
-      <c r="L20" s="139"/>
-      <c r="M20" s="139"/>
-      <c r="N20" s="139"/>
-      <c r="O20" s="139"/>
-      <c r="P20" s="140"/>
-      <c r="Q20" s="196"/>
-      <c r="R20" s="197"/>
-      <c r="S20" s="198"/>
-      <c r="T20" s="186" t="s">
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="138"/>
+      <c r="N20" s="138"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="139"/>
+      <c r="Q20" s="143"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="145"/>
+      <c r="T20" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="U20" s="187"/>
-      <c r="V20" s="146">
+      <c r="U20" s="150"/>
+      <c r="V20" s="151">
         <v>0</v>
       </c>
-      <c r="W20" s="147"/>
-      <c r="X20" s="192">
+      <c r="W20" s="152"/>
+      <c r="X20" s="153">
         <v>0</v>
       </c>
-      <c r="Y20" s="193"/>
+      <c r="Y20" s="154"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -8703,50 +8762,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="138"/>
-      <c r="AP20" s="139"/>
-      <c r="AQ20" s="139"/>
-      <c r="AR20" s="139"/>
-      <c r="AS20" s="139"/>
-      <c r="AT20" s="139"/>
-      <c r="AU20" s="139"/>
-      <c r="AV20" s="139"/>
-      <c r="AW20" s="139"/>
-      <c r="AX20" s="139"/>
-      <c r="AY20" s="139"/>
-      <c r="AZ20" s="188"/>
+      <c r="AO20" s="155"/>
+      <c r="AP20" s="138"/>
+      <c r="AQ20" s="138"/>
+      <c r="AR20" s="138"/>
+      <c r="AS20" s="138"/>
+      <c r="AT20" s="138"/>
+      <c r="AU20" s="138"/>
+      <c r="AV20" s="138"/>
+      <c r="AW20" s="138"/>
+      <c r="AX20" s="138"/>
+      <c r="AY20" s="138"/>
+      <c r="AZ20" s="156"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="151"/>
-      <c r="C21" s="168"/>
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="142"/>
-      <c r="L21" s="142"/>
-      <c r="M21" s="142"/>
-      <c r="N21" s="142"/>
-      <c r="O21" s="142"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="199"/>
-      <c r="R21" s="200"/>
-      <c r="S21" s="201"/>
-      <c r="T21" s="190" t="s">
+      <c r="B21" s="131"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="141"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="142"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="147"/>
+      <c r="S21" s="148"/>
+      <c r="T21" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="191"/>
-      <c r="V21" s="148">
+      <c r="U21" s="159"/>
+      <c r="V21" s="160">
         <v>0</v>
       </c>
-      <c r="W21" s="149"/>
-      <c r="X21" s="194">
+      <c r="W21" s="161"/>
+      <c r="X21" s="162">
         <v>0</v>
       </c>
-      <c r="Y21" s="195"/>
+      <c r="Y21" s="163"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8762,54 +8821,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="141"/>
-      <c r="AP21" s="142"/>
-      <c r="AQ21" s="142"/>
-      <c r="AR21" s="142"/>
-      <c r="AS21" s="142"/>
-      <c r="AT21" s="142"/>
-      <c r="AU21" s="142"/>
-      <c r="AV21" s="142"/>
-      <c r="AW21" s="142"/>
-      <c r="AX21" s="142"/>
-      <c r="AY21" s="142"/>
-      <c r="AZ21" s="189"/>
+      <c r="AO21" s="140"/>
+      <c r="AP21" s="141"/>
+      <c r="AQ21" s="141"/>
+      <c r="AR21" s="141"/>
+      <c r="AS21" s="141"/>
+      <c r="AT21" s="141"/>
+      <c r="AU21" s="141"/>
+      <c r="AV21" s="141"/>
+      <c r="AW21" s="141"/>
+      <c r="AX21" s="141"/>
+      <c r="AY21" s="141"/>
+      <c r="AZ21" s="157"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="163">
+      <c r="B22" s="200">
         <v>9</v>
       </c>
-      <c r="C22" s="165" t="s">
+      <c r="C22" s="202" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="156"/>
-      <c r="L22" s="156"/>
-      <c r="M22" s="156"/>
-      <c r="N22" s="156"/>
-      <c r="O22" s="156"/>
-      <c r="P22" s="204"/>
-      <c r="Q22" s="175"/>
-      <c r="R22" s="176"/>
-      <c r="S22" s="177"/>
-      <c r="T22" s="171" t="s">
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="203"/>
+      <c r="I22" s="204"/>
+      <c r="J22" s="187"/>
+      <c r="K22" s="188"/>
+      <c r="L22" s="188"/>
+      <c r="M22" s="188"/>
+      <c r="N22" s="188"/>
+      <c r="O22" s="188"/>
+      <c r="P22" s="189"/>
+      <c r="Q22" s="209"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="211"/>
+      <c r="T22" s="205" t="s">
         <v>50</v>
       </c>
-      <c r="U22" s="172"/>
-      <c r="V22" s="202">
+      <c r="U22" s="206"/>
+      <c r="V22" s="185">
         <v>0</v>
       </c>
-      <c r="W22" s="203"/>
-      <c r="X22" s="161">
+      <c r="W22" s="186"/>
+      <c r="X22" s="198">
         <v>0</v>
       </c>
-      <c r="Y22" s="162"/>
+      <c r="Y22" s="199"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8825,50 +8884,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="155"/>
-      <c r="AP22" s="156"/>
-      <c r="AQ22" s="156"/>
-      <c r="AR22" s="156"/>
-      <c r="AS22" s="156"/>
-      <c r="AT22" s="156"/>
-      <c r="AU22" s="156"/>
-      <c r="AV22" s="156"/>
-      <c r="AW22" s="156"/>
-      <c r="AX22" s="156"/>
-      <c r="AY22" s="156"/>
-      <c r="AZ22" s="157"/>
+      <c r="AO22" s="187"/>
+      <c r="AP22" s="188"/>
+      <c r="AQ22" s="188"/>
+      <c r="AR22" s="188"/>
+      <c r="AS22" s="188"/>
+      <c r="AT22" s="188"/>
+      <c r="AU22" s="188"/>
+      <c r="AV22" s="188"/>
+      <c r="AW22" s="188"/>
+      <c r="AX22" s="188"/>
+      <c r="AY22" s="188"/>
+      <c r="AZ22" s="196"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="164"/>
-      <c r="C23" s="168"/>
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="170"/>
-      <c r="J23" s="158"/>
-      <c r="K23" s="159"/>
-      <c r="L23" s="159"/>
-      <c r="M23" s="159"/>
-      <c r="N23" s="159"/>
-      <c r="O23" s="159"/>
-      <c r="P23" s="205"/>
-      <c r="Q23" s="178"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="180"/>
-      <c r="T23" s="173" t="s">
+      <c r="B23" s="201"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="190"/>
+      <c r="K23" s="191"/>
+      <c r="L23" s="191"/>
+      <c r="M23" s="191"/>
+      <c r="N23" s="191"/>
+      <c r="O23" s="191"/>
+      <c r="P23" s="192"/>
+      <c r="Q23" s="212"/>
+      <c r="R23" s="213"/>
+      <c r="S23" s="214"/>
+      <c r="T23" s="207" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="174"/>
-      <c r="V23" s="144">
+      <c r="U23" s="208"/>
+      <c r="V23" s="194">
         <v>0</v>
       </c>
-      <c r="W23" s="145"/>
-      <c r="X23" s="181">
+      <c r="W23" s="195"/>
+      <c r="X23" s="215">
         <v>0</v>
       </c>
-      <c r="Y23" s="182"/>
+      <c r="Y23" s="216"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8884,18 +8943,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="158"/>
-      <c r="AP23" s="159"/>
-      <c r="AQ23" s="159"/>
-      <c r="AR23" s="159"/>
-      <c r="AS23" s="159"/>
-      <c r="AT23" s="159"/>
-      <c r="AU23" s="159"/>
-      <c r="AV23" s="159"/>
-      <c r="AW23" s="159"/>
-      <c r="AX23" s="159"/>
-      <c r="AY23" s="159"/>
-      <c r="AZ23" s="160"/>
+      <c r="AO23" s="190"/>
+      <c r="AP23" s="191"/>
+      <c r="AQ23" s="191"/>
+      <c r="AR23" s="191"/>
+      <c r="AS23" s="191"/>
+      <c r="AT23" s="191"/>
+      <c r="AU23" s="191"/>
+      <c r="AV23" s="191"/>
+      <c r="AW23" s="191"/>
+      <c r="AX23" s="191"/>
+      <c r="AY23" s="191"/>
+      <c r="AZ23" s="197"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8954,50 +9013,51 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AO16:AZ17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AO22:AZ23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:I23"/>
+    <mergeCell ref="J18:P19"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q16:S17"/>
+    <mergeCell ref="Q22:S23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C18:I19"/>
+    <mergeCell ref="T18:U18"/>
     <mergeCell ref="AO18:AZ19"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="X18:Y18"/>
@@ -9022,51 +9082,50 @@
     <mergeCell ref="X15:Y15"/>
     <mergeCell ref="Q12:S13"/>
     <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AO16:AZ17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AO22:AZ23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:I23"/>
-    <mergeCell ref="J18:P19"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q16:S17"/>
-    <mergeCell ref="Q22:S23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C18:I19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9090,611 +9149,612 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64">
+      <c r="A1" s="66">
         <v>1</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="111" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="112"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="114"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64">
+      <c r="A3" s="66">
         <v>2</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="104"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
-      <c r="B4" s="218" t="s">
+      <c r="A4" s="67"/>
+      <c r="B4" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
-      <c r="J4" s="219"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="222"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64">
+      <c r="A5" s="66">
         <v>3</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="104"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="77" t="s">
+      <c r="A6" s="70"/>
+      <c r="B6" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="78"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64">
+      <c r="A7" s="66">
         <v>4</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="66"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="67"/>
+      <c r="B8" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="66"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="66"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="66"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="72"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="66"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="72"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="66"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="72"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="82"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="66"/>
-      <c r="B15" s="73" t="s">
+      <c r="A15" s="67"/>
+      <c r="B15" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="74"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="108"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="66"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="72"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="66"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="72"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="66"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="72"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="66"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="72"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="82"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="66"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="72"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="114"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="77"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="64">
+      <c r="A22" s="66">
         <v>5</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="69"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="104"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="82"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="82"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="72"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="82"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="66"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="72"/>
+      <c r="A26" s="67"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="82"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="66"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="72"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="82"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="66"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="71"/>
-      <c r="J28" s="72"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="82"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="66"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="72"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="82"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65"/>
-      <c r="B30" s="113"/>
-      <c r="C30" s="113"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="113"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="114"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="77"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="64">
+      <c r="A31" s="66">
         <v>6</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="69"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="104"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="66"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="72"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="82"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="66"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="72"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="82"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="66"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="72"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="82"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="66"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="72"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="82"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="66"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="72"/>
+      <c r="A36" s="67"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="82"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="66"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="72"/>
+      <c r="A37" s="67"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="82"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="72"/>
+      <c r="A38" s="67"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="82"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="72"/>
+      <c r="A39" s="67"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="82"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="66"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="72"/>
+      <c r="A40" s="67"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="82"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="66"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="72"/>
+      <c r="A41" s="67"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="82"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="66"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="72"/>
+      <c r="A42" s="67"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="82"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="66"/>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="72"/>
+      <c r="A43" s="67"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="82"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="66"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="71"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="72"/>
+      <c r="A44" s="67"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="82"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="66"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="71"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="72"/>
+      <c r="A45" s="67"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="82"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="66"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="71"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="72"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="82"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="109"/>
+      <c r="C47" s="109"/>
+      <c r="D47" s="109"/>
+      <c r="E47" s="109"/>
+      <c r="F47" s="109"/>
+      <c r="G47" s="109"/>
+      <c r="H47" s="109"/>
+      <c r="I47" s="109"/>
+      <c r="J47" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -9703,13 +9763,12 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9722,6 +9781,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -9928,15 +9996,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9949,6 +10008,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9963,14 +10030,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
+++ b/10_企画書・プロジェクト企画書/11_プロジェクト計画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC8ADC-C27D-4774-9735-2AB11323BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52E4256-5503-4624-B4BD-014CB1C965B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="実績＆評価" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'別紙１）非機能要件'!$A$1:$I$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'別紙２）開発スケジュール予定＆実績'!$A$1:$AZ$23</definedName>
   </definedNames>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="180">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -613,24 +613,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>①：なぜ
-地震災害後、建物の被害状況や修理の必要性が分からず、必要な手続きや対応に困る被災者が多い。そこで、被災直後の情報収集や初期対応を支援することを目的とする。
-②：ソリューション
-建物内部の写真と簡単な質問を入力すると、AIが被害状況の目安を分析し、修理費用や罹災証明書の手続き、修理業者など、状況に応じた情報を提示する。
-③：期待する効果
-被災者が被害状況を把握しやすくなり、「何をすればよいか分からない」という不安を減らす。また、復旧に必要な情報を一つのシステムで確認できることで、被災後の初期対応や復旧作業の効率化が期待できる。</t>
-    <rPh sb="5" eb="7">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>キタイ</t>
-    </rPh>
-    <rPh sb="171" eb="173">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Amazon Linux 2023</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -775,32 +757,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>修理業者情報</t>
-    <rPh sb="0" eb="2">
-      <t>シュウリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ギョウシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>修理業者表示</t>
-    <rPh sb="0" eb="2">
-      <t>シュウリ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ギョウシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>各種申請情報</t>
     <rPh sb="0" eb="2">
       <t>カクシュ</t>
@@ -814,22 +770,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>罹災証明書申請案内</t>
-    <rPh sb="0" eb="2">
-      <t>リサイ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>アンナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ユーザ認証</t>
     <rPh sb="3" eb="5">
       <t>ニンショウ</t>
@@ -988,46 +928,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>罹災証明書申請の案内ができる</t>
-    <rPh sb="0" eb="2">
-      <t>リサイ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>アンナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ログアウトができる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LINEアカウントでログインができる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物周辺の修理業者を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュウヘン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュウリ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ギョウシャ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1911,200 +1812,286 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>建物情報保存</t>
+    <rPh sb="4" eb="6">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況登録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物の情報を保存できる</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の一覧を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の詳細を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の情報を編集できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存した建物の情報を削除できる</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析対象の建物の情報を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>①：概要
 本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録すると、AIが被害状況を分析し、その目安を提示することで、被害状況の把握や専門家への相談を支援するWebシステムである。
-また、分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報を提示する。登録した写真や分析結果は履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
+また、分析結果に応じて、修理費用の目安や罹災証明書の申請方法などの情報を提示する。登録した写真や分析結果は履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
 ②：実現可能な機能
 必須機能
 ・被害情報の登録(建物情報・質問回答)
 ・被害写真の撮影・登録
 ・AIによる被害状況分析
 ・修理費用の目安提示
-・修理業者の情報提示
+・各種申請書・支援制度の案内
 ・LINEログイン
 ・被害状況分析履歴
 追加機能
 ・チャットボットによる追加質問
-・罹災証明書の申請案内
 ③：システム規模
-・個人(事業者・建物管理者を含む)での利用を想定している
+・個人での利用を想定している
 ・災害発生直後にはアクセスが集中すると想定される
 ④：システムとの関係
-提案先：建物調査を実施している企業、修理業者
+提案先：被災後の復旧対応を行う自治体・修理業者
 利用者：災害によって建物や室内に被害を受けた個人</t>
     <rPh sb="2" eb="4">
       <t>ガイヨウ</t>
     </rPh>
+    <rPh sb="202" eb="204">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="204" eb="206">
+      <t>カノウ</t>
+    </rPh>
     <rPh sb="207" eb="209">
-      <t>ジツゲン</t>
-    </rPh>
-    <rPh sb="209" eb="211">
-      <t>カノウ</t>
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>ヒッス</t>
     </rPh>
     <rPh sb="212" eb="214">
       <t>キノウ</t>
     </rPh>
-    <rPh sb="215" eb="217">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="217" eb="219">
-      <t>キノウ</t>
+    <rPh sb="216" eb="218">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>ジョウホウ</t>
     </rPh>
     <rPh sb="221" eb="223">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="223" eb="225">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="224" eb="226">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="226" eb="228">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="226" eb="228">
-      <t>トウロク</t>
-    </rPh>
     <rPh sb="229" eb="231">
-      <t>タテモノ</t>
+      <t>シツモン</t>
     </rPh>
     <rPh sb="231" eb="233">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="234" eb="236">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="272" eb="274">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="274" eb="277">
+      <t>シンセイショ</t>
+    </rPh>
+    <rPh sb="278" eb="280">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="280" eb="282">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="322" eb="324">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="324" eb="326">
       <t>シツモン</t>
     </rPh>
-    <rPh sb="236" eb="238">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="323" eb="325">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="325" eb="327">
-      <t>シツモン</t>
-    </rPh>
-    <rPh sb="342" eb="344">
+    <rPh sb="329" eb="331">
       <t>キボ</t>
     </rPh>
-    <rPh sb="359" eb="360">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="408" eb="410">
+    <rPh sb="381" eb="383">
       <t>カンケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>建物情報保存</t>
+    <t>①：なぜ
+地震災害後、建物の被害状況や修理の必要性が分からず、必要な手続きや対応に困る被災者が多い。そこで、被災直後の情報収集や初期対応を支援することを目的とする。
+②：ソリューション
+建物内部の写真と簡単な質問を入力すると、AIが被害状況の目安を分析し、修理費用の目安や罹災証明書の手続きなど、状況に応じた情報を提示する。
+③：期待する効果
+被災者が被害状況を把握しやすくなり、「何をすればよいか分からない」という不安を減らす。また、復旧に必要な情報を一つのシステムで確認できることで、被災後の初期対応や復旧作業の効率化が期待できる。</t>
+    <rPh sb="5" eb="7">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罹災証明書申請案内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参照系</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罹災証明書申請の案内ができる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINE認証でログインができる</t>
     <rPh sb="4" eb="6">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況登録</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物の情報を保存できる</t>
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応急修理制度案内</t>
+    <rPh sb="6" eb="8">
+      <t>アンナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>応急修理制度の案内ができる</t>
     <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>保存した建物の一覧を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>ホゾン</t>
+      <t>オウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウリ</t>
     </rPh>
     <rPh sb="4" eb="6">
-      <t>タテモノ</t>
+      <t>セイド</t>
     </rPh>
     <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>保存した建物の詳細を表示できる</t>
-    <rPh sb="0" eb="2">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>保存した建物の情報を編集できる</t>
-    <rPh sb="0" eb="2">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>保存した建物の情報を削除できる</t>
-    <rPh sb="0" eb="2">
-      <t>ホゾン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>建物情報登録</t>
-    <rPh sb="0" eb="2">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分析対象の建物の情報を登録できる</t>
-    <rPh sb="0" eb="2">
-      <t>ブンセキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
+      <t>アンナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者生活再建支援制度の案内ができる</t>
+    <rPh sb="12" eb="14">
+      <t>アンナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者生活再建支援制度
+案内</t>
+    <rPh sb="12" eb="14">
+      <t>アンナイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3090,7 +3077,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3214,12 +3201,51 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3259,58 +3285,148 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3325,129 +3441,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3455,7 +3454,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3466,20 +3477,74 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3487,6 +3552,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3496,29 +3654,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3538,50 +3702,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3595,15 +3726,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3628,146 +3750,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4651,1585 +4641,1608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="66">
+      <c r="A2" s="70">
         <v>1</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="75"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="117" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="118"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="120"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="66">
+      <c r="A4" s="70">
         <v>2</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="72"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="67"/>
-      <c r="B5" s="83" t="s">
+      <c r="A5" s="72"/>
+      <c r="B5" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="84"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="89"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="67"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="84"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="67"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="67"/>
-      <c r="B8" s="98" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="93" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="95"/>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="72"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="98"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="72"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="98"/>
+    </row>
+    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="72"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="98"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="72"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="98"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="72"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="98"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="72"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="98"/>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="72"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="98"/>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="72"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="98"/>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="71"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="98"/>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="71"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="98"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="71"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="98"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="71"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="98"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="70">
+        <v>3</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="86"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="72"/>
+      <c r="B22" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="106"/>
+      <c r="D22" s="106"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="107"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="72"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="107"/>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="72"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="107"/>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="72"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="110"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="72"/>
+      <c r="B26" s="111" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"